--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4715,7 +4715,7 @@
         <v>0.595</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:09</t>
+          <t>2026-09-06 05:42:10</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4516,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4637,25 +4637,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4739,29 +4759,41 @@
       <c r="W2" t="n">
         <v>0.767</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>11.848</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.042876</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7958079155</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Discount Stores</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.stock.walmart.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Walmart Inc. engages in the operation of retail and wholesale stores and clubs, ecommerce websites, and mobile applications worldwide. The company operates through three segments: Walmart U.S., Walmart International, and Sam's Club U.S. It operates supercenters, supermarkets, warehouse clubs, cash and carry stores, and discount stores under Walmart and Walmart Neighborhood Market brands; membership-only warehouse clubs; and ecommerce websites, such as walmart.com.mx, walmart.ca, flipkart.com, PhonePe and other sites. It offers grocery items, including dry grocery, snacks, dairy, meat, produce, deli and bakery, frozen foods, alcoholic and nonalcoholic beverages, as well as consumables, such as health and beauty aids, pet supplies, household chemicals, paper goods, and baby products; and fuel and other categories. In addition, it is involved in the provision of health and wellness products covering pharmacy, optical and hearing services, over-the-counter drugs, and protein and nutrition products; and home, hardlines, and seasonal items, including home improvement, outdoor living, gardening, furniture, apparel, jewelry, tools and power equipment, housewares, toys, and mattresses. Further, the company offers consumer electronics and accessories, software, video games, office supplies, appliances, and third-party gift cards. Additionally, it operates digital payment platforms; offers financial services and related products, including money transfers, bill payments, money orders, check cashing, prepaid access, co-branded credit cards, installment lending, and earned wage access; and markets lines of merchandise under private and licensed brands. The company was formerly known as Wal-Mart Stores, Inc. and changed its name to Walmart Inc. in February 2018. Walmart Inc. was founded in 1945 and is based in Bentonville, Arkansas.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:10</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:13</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:13</t>
+          <t>2026-09-06 16:24:49</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:49</t>
+          <t>2026-09-06 16:34:43</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:43</t>
+          <t>2026-09-06 16:49:17</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4737,15 +4737,11 @@
       <c r="Q2" t="n">
         <v>0.92</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0345</v>
       </c>
       <c r="T2" t="n">
         <v>0.22313999</v>
@@ -4793,7 +4789,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:17</t>
+          <t>2026-09-06 16:59:48</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4516,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4657,25 +4657,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4767,29 +4782,38 @@
       <c r="AA2" t="n">
         <v>7958079155</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>735839977472</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>920145559552</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>44073000960</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Discount Stores</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.stock.walmart.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Walmart Inc. engages in the operation of retail and wholesale stores and clubs, ecommerce websites, and mobile applications worldwide. The company operates through three segments: Walmart U.S., Walmart International, and Sam's Club U.S. It operates supercenters, supermarkets, warehouse clubs, cash and carry stores, and discount stores under Walmart and Walmart Neighborhood Market brands; membership-only warehouse clubs; and ecommerce websites, such as walmart.com.mx, walmart.ca, flipkart.com, PhonePe and other sites. It offers grocery items, including dry grocery, snacks, dairy, meat, produce, deli and bakery, frozen foods, alcoholic and nonalcoholic beverages, as well as consumables, such as health and beauty aids, pet supplies, household chemicals, paper goods, and baby products; and fuel and other categories. In addition, it is involved in the provision of health and wellness products covering pharmacy, optical and hearing services, over-the-counter drugs, and protein and nutrition products; and home, hardlines, and seasonal items, including home improvement, outdoor living, gardening, furniture, apparel, jewelry, tools and power equipment, housewares, toys, and mattresses. Further, the company offers consumer electronics and accessories, software, video games, office supplies, appliances, and third-party gift cards. Additionally, it operates digital payment platforms; offers financial services and related products, including money transfers, bill payments, money orders, check cashing, prepaid access, co-branded credit cards, installment lending, and earned wage access; and markets lines of merchandise under private and licensed brands. The company was formerly known as Wal-Mart Stores, Inc. and changed its name to Walmart Inc. in February 2018. Walmart Inc. was founded in 1945 and is based in Bentonville, Arkansas.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:48</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:53</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:53</t>
+          <t>2026-09-06 22:41:48</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:48</t>
+          <t>2026-09-06 22:59:42</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>112.181431315027</v>
+        <v>100.2360551135878</v>
       </c>
       <c r="C2" t="n">
-        <v>112.8897423116165</v>
+        <v>100.6327169088708</v>
       </c>
       <c r="D2" t="n">
-        <v>111.0940382280446</v>
+        <v>98.71883074489759</v>
       </c>
       <c r="E2" t="n">
-        <v>112.0716934204102</v>
+        <v>99.67081451416016</v>
       </c>
       <c r="F2" t="n">
-        <v>21446300</v>
+        <v>13748500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>113.7975687180191</v>
+        <v>100.0079722075202</v>
       </c>
       <c r="C3" t="n">
-        <v>114.2863963302149</v>
+        <v>101.5053668922825</v>
       </c>
       <c r="D3" t="n">
-        <v>110.7748064209645</v>
+        <v>99.5815621012248</v>
       </c>
       <c r="E3" t="n">
-        <v>111.8023452758789</v>
+        <v>101.4260330200195</v>
       </c>
       <c r="F3" t="n">
-        <v>23203100</v>
+        <v>13685700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>110.3458340692701</v>
+        <v>101.1483716213974</v>
       </c>
       <c r="C4" t="n">
-        <v>112.0218220801941</v>
+        <v>101.6342783470665</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2360961700712</v>
+        <v>100.7021318316984</v>
       </c>
       <c r="E4" t="n">
-        <v>111.5828704833984</v>
+        <v>101.4359512329102</v>
       </c>
       <c r="F4" t="n">
-        <v>18819300</v>
+        <v>11819700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>110.8147094920761</v>
+        <v>101.0987907680863</v>
       </c>
       <c r="C5" t="n">
-        <v>112.4308355753539</v>
+        <v>101.5946161422617</v>
       </c>
       <c r="D5" t="n">
-        <v>110.4954740524384</v>
+        <v>99.5518180216814</v>
       </c>
       <c r="E5" t="n">
-        <v>112.3909378051758</v>
+        <v>99.5716552734375</v>
       </c>
       <c r="F5" t="n">
-        <v>19144000</v>
+        <v>17934900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>112.1714606731287</v>
+        <v>100.1468020683853</v>
       </c>
       <c r="C6" t="n">
-        <v>113.069305103701</v>
+        <v>101.9218577291584</v>
       </c>
       <c r="D6" t="n">
-        <v>111.9220577510424</v>
+        <v>99.44273097931239</v>
       </c>
       <c r="E6" t="n">
-        <v>112.989501953125</v>
+        <v>101.7929458618164</v>
       </c>
       <c r="F6" t="n">
-        <v>17005800</v>
+        <v>15900800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>112.1016271407472</v>
+        <v>101.6838580700448</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7728384249456</v>
+        <v>103.111837420202</v>
       </c>
       <c r="D7" t="n">
-        <v>112.011838131802</v>
+        <v>101.5053606512752</v>
       </c>
       <c r="E7" t="n">
-        <v>115.7329330444336</v>
+        <v>102.6259231567383</v>
       </c>
       <c r="F7" t="n">
-        <v>22054700</v>
+        <v>11641900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>115.8925486214695</v>
+        <v>102.7845975900895</v>
       </c>
       <c r="C8" t="n">
-        <v>116.0421918977476</v>
+        <v>103.1118441401098</v>
       </c>
       <c r="D8" t="n">
-        <v>114.5357961092488</v>
+        <v>102.5466035381176</v>
       </c>
       <c r="E8" t="n">
-        <v>115.4436264038086</v>
+        <v>102.8242645263672</v>
       </c>
       <c r="F8" t="n">
-        <v>16822200</v>
+        <v>10756900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>115.3837731369623</v>
+        <v>102.9829210178903</v>
       </c>
       <c r="C9" t="n">
-        <v>116.1718796839166</v>
+        <v>103.3399158659111</v>
       </c>
       <c r="D9" t="n">
-        <v>114.3662049383982</v>
+        <v>102.2689313218488</v>
       </c>
       <c r="E9" t="n">
-        <v>114.9946975708008</v>
+        <v>102.556510925293</v>
       </c>
       <c r="F9" t="n">
-        <v>14520000</v>
+        <v>14481900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>114.0569458007812</v>
+        <v>102.8639369378787</v>
       </c>
       <c r="C10" t="n">
-        <v>114.9049142110052</v>
+        <v>105.2240630293193</v>
       </c>
       <c r="D10" t="n">
-        <v>113.6479213564676</v>
+        <v>102.8639369378787</v>
       </c>
       <c r="E10" t="n">
-        <v>114.0569458007812</v>
+        <v>103.3994216918945</v>
       </c>
       <c r="F10" t="n">
-        <v>18131100</v>
+        <v>25382000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>116.0222446904477</v>
+        <v>102.9135133062164</v>
       </c>
       <c r="C11" t="n">
-        <v>116.0322153274834</v>
+        <v>103.7663335538345</v>
       </c>
       <c r="D11" t="n">
-        <v>114.2065916862473</v>
+        <v>101.2673770004686</v>
       </c>
       <c r="E11" t="n">
-        <v>114.9248657226562</v>
+        <v>102.7350158691406</v>
       </c>
       <c r="F11" t="n">
-        <v>20675000</v>
+        <v>14869400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>114.9148971425914</v>
+        <v>102.9432629724532</v>
       </c>
       <c r="C12" t="n">
-        <v>116.590885146559</v>
+        <v>103.0721824132953</v>
       </c>
       <c r="D12" t="n">
-        <v>113.7177585048011</v>
+        <v>101.2376224547773</v>
       </c>
       <c r="E12" t="n">
-        <v>114.0270233154297</v>
+        <v>101.4756240844727</v>
       </c>
       <c r="F12" t="n">
-        <v>34286600</v>
+        <v>34791600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>106.1259298697332</v>
+        <v>101.5946114796781</v>
       </c>
       <c r="C13" t="n">
-        <v>106.7444518635443</v>
+        <v>102.3383495068081</v>
       </c>
       <c r="D13" t="n">
-        <v>102.6043617877236</v>
+        <v>101.069037817684</v>
       </c>
       <c r="E13" t="n">
-        <v>103.5919952392578</v>
+        <v>101.9615249633789</v>
       </c>
       <c r="F13" t="n">
-        <v>83633100</v>
+        <v>12861900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>103.6900024414062</v>
+        <v>101.5549649811181</v>
       </c>
       <c r="C14" t="n">
-        <v>104.2799987792969</v>
+        <v>101.8227073759147</v>
       </c>
       <c r="D14" t="n">
-        <v>102.1500015258789</v>
+        <v>100.4839802705406</v>
       </c>
       <c r="E14" t="n">
-        <v>103.6999969482422</v>
+        <v>101.6640396118164</v>
       </c>
       <c r="F14" t="n">
-        <v>44454200</v>
+        <v>13158700</v>
       </c>
       <c r="G14" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>104.1399993896484</v>
+        <v>102.1796932441854</v>
       </c>
       <c r="C15" t="n">
-        <v>106.5999984741211</v>
+        <v>102.606103365375</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>101.6243712503365</v>
       </c>
       <c r="E15" t="n">
-        <v>106.4899978637695</v>
+        <v>101.8722839355469</v>
       </c>
       <c r="F15" t="n">
-        <v>35616300</v>
+        <v>11391800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>105.5800018310547</v>
+        <v>102.3581921548903</v>
       </c>
       <c r="C16" t="n">
-        <v>106.0699996948242</v>
+        <v>102.645771781761</v>
       </c>
       <c r="D16" t="n">
-        <v>104.4000015258789</v>
+        <v>101.7235362768635</v>
       </c>
       <c r="E16" t="n">
-        <v>105.379997253418</v>
+        <v>102.1896133422852</v>
       </c>
       <c r="F16" t="n">
-        <v>27032500</v>
+        <v>13366700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>105.5100021362305</v>
+        <v>102.0210298508162</v>
       </c>
       <c r="C17" t="n">
-        <v>106.0899963378906</v>
+        <v>102.625937433817</v>
       </c>
       <c r="D17" t="n">
-        <v>104.0800018310547</v>
+        <v>101.6144569638703</v>
       </c>
       <c r="E17" t="n">
-        <v>104.3399963378906</v>
+        <v>102.298698425293</v>
       </c>
       <c r="F17" t="n">
-        <v>28409400</v>
+        <v>11859300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>103.6100006103516</v>
+        <v>102.1896196669732</v>
       </c>
       <c r="C18" t="n">
-        <v>103.75</v>
+        <v>102.4474434319635</v>
       </c>
       <c r="D18" t="n">
-        <v>102.2699966430664</v>
+        <v>101.2277171644534</v>
       </c>
       <c r="E18" t="n">
-        <v>102.629997253418</v>
+        <v>102.219367980957</v>
       </c>
       <c r="F18" t="n">
-        <v>29816600</v>
+        <v>15477200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>103.0899963378906</v>
+        <v>102.1400273017734</v>
       </c>
       <c r="C19" t="n">
-        <v>103.4000015258789</v>
+        <v>103.0721814282683</v>
       </c>
       <c r="D19" t="n">
-        <v>102.5</v>
+        <v>101.8623663021439</v>
       </c>
       <c r="E19" t="n">
-        <v>103.0899963378906</v>
+        <v>102.1995239257812</v>
       </c>
       <c r="F19" t="n">
-        <v>19420800</v>
+        <v>13873400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>103.0800018310547</v>
+        <v>101.7036925151355</v>
       </c>
       <c r="C20" t="n">
-        <v>104.9899978637695</v>
+        <v>102.0011907489098</v>
       </c>
       <c r="D20" t="n">
-        <v>102.8399963378906</v>
+        <v>99.71048007220848</v>
       </c>
       <c r="E20" t="n">
-        <v>104.870002746582</v>
+        <v>101.1087036132812</v>
       </c>
       <c r="F20" t="n">
-        <v>34188700</v>
+        <v>16142800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>105.1100006103516</v>
+        <v>100.6029707835176</v>
       </c>
       <c r="C21" t="n">
-        <v>106.6399993896484</v>
+        <v>101.2872122575589</v>
       </c>
       <c r="D21" t="n">
-        <v>104.6600036621094</v>
+        <v>99.036168267113</v>
       </c>
       <c r="E21" t="n">
-        <v>105.9199981689453</v>
+        <v>100.8508834838867</v>
       </c>
       <c r="F21" t="n">
-        <v>22074600</v>
+        <v>15605400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>105.9700012207031</v>
+        <v>100.6128811517826</v>
       </c>
       <c r="C22" t="n">
-        <v>106.7799987792969</v>
+        <v>101.9615267363516</v>
       </c>
       <c r="D22" t="n">
-        <v>105.4599990844727</v>
+        <v>100.3550498461664</v>
       </c>
       <c r="E22" t="n">
-        <v>106.0899963378906</v>
+        <v>101.2177886962891</v>
       </c>
       <c r="F22" t="n">
-        <v>25181800</v>
+        <v>11867500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>106.4199981689453</v>
+        <v>101.029368413644</v>
       </c>
       <c r="C23" t="n">
-        <v>109.3499984741211</v>
+        <v>102.2094351422179</v>
       </c>
       <c r="D23" t="n">
-        <v>106.0199966430664</v>
+        <v>100.731877749476</v>
       </c>
       <c r="E23" t="n">
-        <v>108.4199981689453</v>
+        <v>101.8425216674805</v>
       </c>
       <c r="F23" t="n">
-        <v>25541200</v>
+        <v>13303600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101.5252009905733</v>
+      </c>
+      <c r="C24" t="n">
+        <v>102.387939866122</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100.1071401164341</v>
+      </c>
+      <c r="E24" t="n">
+        <v>102.3780212402344</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15538900</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>102.1598562843055</v>
+      </c>
+      <c r="C25" t="n">
+        <v>102.3978579100873</v>
+      </c>
+      <c r="D25" t="n">
+        <v>101.2971249793545</v>
+      </c>
+      <c r="E25" t="n">
+        <v>102.0408630371094</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13584100</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102.2689413702109</v>
+      </c>
+      <c r="C26" t="n">
+        <v>102.5862693145533</v>
+      </c>
+      <c r="D26" t="n">
+        <v>99.53199068739345</v>
+      </c>
+      <c r="E26" t="n">
+        <v>100.920295715332</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19508000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101.1979536153083</v>
+      </c>
+      <c r="C27" t="n">
+        <v>102.7647559195764</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100.6723724065026</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100.9897003173828</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18519400</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100.523634106908</v>
+      </c>
+      <c r="C28" t="n">
+        <v>101.5946111121733</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100.2261358708544</v>
+      </c>
+      <c r="E28" t="n">
+        <v>101.2673721313477</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10871200</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103.1812529973676</v>
+      </c>
+      <c r="C29" t="n">
+        <v>107.01893616482</v>
+      </c>
+      <c r="D29" t="n">
+        <v>102.0309346136339</v>
+      </c>
+      <c r="E29" t="n">
+        <v>106.3148651123047</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30859500</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106.4239604021063</v>
+      </c>
+      <c r="C30" t="n">
+        <v>108.645256009938</v>
+      </c>
+      <c r="D30" t="n">
+        <v>106.4041307155994</v>
+      </c>
+      <c r="E30" t="n">
+        <v>108.1196823120117</v>
+      </c>
+      <c r="F30" t="n">
+        <v>21416300</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108.2882647751407</v>
+      </c>
+      <c r="C31" t="n">
+        <v>108.6650969227217</v>
+      </c>
+      <c r="D31" t="n">
+        <v>104.7778275866427</v>
+      </c>
+      <c r="E31" t="n">
+        <v>105.5810623168945</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16366200</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106.2752063382308</v>
+      </c>
+      <c r="C32" t="n">
+        <v>107.2966053740443</v>
+      </c>
+      <c r="D32" t="n">
+        <v>105.3331411761509</v>
+      </c>
+      <c r="E32" t="n">
+        <v>106.8305358886719</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13735600</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106.9495278840114</v>
+      </c>
+      <c r="C33" t="n">
+        <v>107.3461896823507</v>
+      </c>
+      <c r="D33" t="n">
+        <v>105.7198831182847</v>
+      </c>
+      <c r="E33" t="n">
+        <v>106.1562118530273</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10581200</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106.4338780925878</v>
+      </c>
+      <c r="C34" t="n">
+        <v>106.5826272200147</v>
+      </c>
+      <c r="D34" t="n">
+        <v>105.2934782032414</v>
+      </c>
+      <c r="E34" t="n">
+        <v>105.3331451416016</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10899700</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>105.6603902006062</v>
+      </c>
+      <c r="C35" t="n">
+        <v>106.8701977576955</v>
+      </c>
+      <c r="D35" t="n">
+        <v>104.7778216403512</v>
+      </c>
+      <c r="E35" t="n">
+        <v>106.2454605102539</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12296500</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106.4537107234644</v>
+      </c>
+      <c r="C36" t="n">
+        <v>106.6718751076324</v>
+      </c>
+      <c r="D36" t="n">
+        <v>104.8968192868145</v>
+      </c>
+      <c r="E36" t="n">
+        <v>105.9678039550781</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11408200</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106.1760412293909</v>
+      </c>
+      <c r="C37" t="n">
+        <v>106.2752047872635</v>
+      </c>
+      <c r="D37" t="n">
+        <v>104.6290685426336</v>
+      </c>
+      <c r="E37" t="n">
+        <v>105.2835540771484</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10318000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>105.452129733232</v>
+      </c>
+      <c r="C38" t="n">
+        <v>105.4719669836308</v>
+      </c>
+      <c r="D38" t="n">
+        <v>103.280419887601</v>
+      </c>
+      <c r="E38" t="n">
+        <v>103.5977478027344</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16375900</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>103.1911699012466</v>
+      </c>
+      <c r="C39" t="n">
+        <v>103.2705037733825</v>
+      </c>
+      <c r="D39" t="n">
+        <v>102.1896081368852</v>
+      </c>
+      <c r="E39" t="n">
+        <v>102.3086013793945</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13323000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>102.0507853540776</v>
+      </c>
+      <c r="C40" t="n">
+        <v>102.8044344992282</v>
+      </c>
+      <c r="D40" t="n">
+        <v>101.2574617041669</v>
+      </c>
+      <c r="E40" t="n">
+        <v>101.6045379638672</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11986400</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101.3467013373431</v>
+      </c>
+      <c r="C41" t="n">
+        <v>102.5069384385963</v>
+      </c>
+      <c r="D41" t="n">
+        <v>101.1087072811068</v>
+      </c>
+      <c r="E41" t="n">
+        <v>101.3764572143555</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14065100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100.8508753833576</v>
+      </c>
+      <c r="C42" t="n">
+        <v>101.2475371852267</v>
+      </c>
+      <c r="D42" t="n">
+        <v>99.34356961508874</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100.3352203369141</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20237000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99.97822306298148</v>
+      </c>
+      <c r="C43" t="n">
+        <v>100.9500440758614</v>
+      </c>
+      <c r="D43" t="n">
+        <v>99.56173158561626</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100.7417907714844</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14811700</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101.2772919319017</v>
+      </c>
+      <c r="C44" t="n">
+        <v>101.763206263773</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100.6128877218267</v>
+      </c>
+      <c r="E44" t="n">
+        <v>101.4161224365234</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12636400</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>100.89054510776</v>
+      </c>
+      <c r="C45" t="n">
+        <v>101.8226992330539</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100.0079765462054</v>
+      </c>
+      <c r="E45" t="n">
+        <v>100.622802734375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>13356800</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>100.4938818739751</v>
+      </c>
+      <c r="C46" t="n">
+        <v>101.0789597419063</v>
+      </c>
+      <c r="D46" t="n">
+        <v>99.19482183188099</v>
+      </c>
+      <c r="E46" t="n">
+        <v>100.8310470581055</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14866000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101.2772857883956</v>
+      </c>
+      <c r="C47" t="n">
+        <v>102.1102763312919</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100.8806315510774</v>
+      </c>
+      <c r="E47" t="n">
+        <v>101.7334442138672</v>
+      </c>
+      <c r="F47" t="n">
+        <v>17248700</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101.297130355603</v>
+      </c>
+      <c r="C48" t="n">
+        <v>101.8127854407752</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100.7517193913577</v>
+      </c>
+      <c r="E48" t="n">
+        <v>101.5648727416992</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14507600</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101.6442008637206</v>
+      </c>
+      <c r="C49" t="n">
+        <v>102.8738456630921</v>
+      </c>
+      <c r="D49" t="n">
+        <v>101.4657034278687</v>
+      </c>
+      <c r="E49" t="n">
+        <v>102.5763549804688</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13182100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102.4871024796954</v>
+      </c>
+      <c r="C50" t="n">
+        <v>102.7350151647289</v>
+      </c>
+      <c r="D50" t="n">
+        <v>101.8028686136755</v>
+      </c>
+      <c r="E50" t="n">
+        <v>102.5763549804688</v>
+      </c>
+      <c r="F50" t="n">
+        <v>12084400</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102.7250971521424</v>
+      </c>
+      <c r="C51" t="n">
+        <v>103.0622623399618</v>
+      </c>
+      <c r="D51" t="n">
+        <v>101.1682057834663</v>
+      </c>
+      <c r="E51" t="n">
+        <v>101.6838684082031</v>
+      </c>
+      <c r="F51" t="n">
+        <v>18088500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99.36340427550201</v>
+      </c>
+      <c r="C52" t="n">
+        <v>101.6342854500628</v>
+      </c>
+      <c r="D52" t="n">
+        <v>98.054425559783</v>
+      </c>
+      <c r="E52" t="n">
+        <v>101.6243743896484</v>
+      </c>
+      <c r="F52" t="n">
+        <v>23424200</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101.7235329175373</v>
+      </c>
+      <c r="C53" t="n">
+        <v>102.4573523337042</v>
+      </c>
+      <c r="D53" t="n">
+        <v>101.2475372418891</v>
+      </c>
+      <c r="E53" t="n">
+        <v>102.0904388427734</v>
+      </c>
+      <c r="F53" t="n">
+        <v>15289400</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102.1202009692791</v>
+      </c>
+      <c r="C54" t="n">
+        <v>102.4771882907442</v>
+      </c>
+      <c r="D54" t="n">
+        <v>100.5335536638138</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100.5434722900391</v>
+      </c>
+      <c r="F54" t="n">
+        <v>17604500</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100.7318761079755</v>
+      </c>
+      <c r="C55" t="n">
+        <v>100.8607879704448</v>
+      </c>
+      <c r="D55" t="n">
+        <v>98.84773833617163</v>
+      </c>
+      <c r="E55" t="n">
+        <v>99.76997375488281</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22157000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>103.0721824077765</v>
+      </c>
+      <c r="C56" t="n">
+        <v>107.0090371351957</v>
+      </c>
+      <c r="D56" t="n">
+        <v>101.8227003318746</v>
+      </c>
+      <c r="E56" t="n">
+        <v>106.2157135009766</v>
+      </c>
+      <c r="F56" t="n">
+        <v>50375900</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>107.0784454213155</v>
+      </c>
+      <c r="C57" t="n">
+        <v>107.2470242237718</v>
+      </c>
+      <c r="D57" t="n">
+        <v>103.845662035823</v>
+      </c>
+      <c r="E57" t="n">
+        <v>104.4406509399414</v>
+      </c>
+      <c r="F57" t="n">
+        <v>41420800</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>104.4803186790174</v>
+      </c>
+      <c r="C58" t="n">
+        <v>105.3827168846354</v>
+      </c>
+      <c r="D58" t="n">
+        <v>102.89367906727</v>
+      </c>
+      <c r="E58" t="n">
+        <v>103.1911697387695</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42519200</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>103.7365763126644</v>
+      </c>
+      <c r="C59" t="n">
+        <v>106.5231122506693</v>
+      </c>
+      <c r="D59" t="n">
+        <v>103.3597517849156</v>
+      </c>
+      <c r="E59" t="n">
+        <v>106.1066207885742</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20212900</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106.3049641152269</v>
+      </c>
+      <c r="C60" t="n">
+        <v>108.6750089527716</v>
+      </c>
+      <c r="D60" t="n">
+        <v>106.2752158013515</v>
+      </c>
+      <c r="E60" t="n">
+        <v>108.1891021728516</v>
+      </c>
+      <c r="F60" t="n">
+        <v>17783300</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>108.3874295551272</v>
+      </c>
+      <c r="C61" t="n">
+        <v>109.7757345468567</v>
+      </c>
+      <c r="D61" t="n">
+        <v>108.0899313050738</v>
+      </c>
+      <c r="E61" t="n">
+        <v>109.5873260498047</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9846500</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>109.587335399739</v>
+      </c>
+      <c r="C62" t="n">
+        <v>110.8268989378955</v>
+      </c>
+      <c r="D62" t="n">
+        <v>109.4385862620211</v>
+      </c>
+      <c r="E62" t="n">
+        <v>110.5988159179688</v>
+      </c>
+      <c r="F62" t="n">
+        <v>17236800</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>110.5393043592431</v>
+      </c>
+      <c r="C63" t="n">
+        <v>111.7094524838454</v>
+      </c>
+      <c r="D63" t="n">
+        <v>109.8649815829351</v>
+      </c>
+      <c r="E63" t="n">
+        <v>111.4714584350586</v>
+      </c>
+      <c r="F63" t="n">
+        <v>18711800</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>111.560708766128</v>
+      </c>
+      <c r="C64" t="n">
+        <v>113.9307534404373</v>
+      </c>
+      <c r="D64" t="n">
+        <v>111.2830477681546</v>
+      </c>
+      <c r="E64" t="n">
+        <v>113.4547653198242</v>
+      </c>
+      <c r="F64" t="n">
+        <v>24478300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>112.6713645812471</v>
+      </c>
+      <c r="C65" t="n">
+        <v>113.9307577455568</v>
+      </c>
+      <c r="D65" t="n">
+        <v>112.2152061293831</v>
+      </c>
+      <c r="E65" t="n">
+        <v>113.8811721801758</v>
+      </c>
+      <c r="F65" t="n">
+        <v>25905100</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>113.7720935914494</v>
+      </c>
+      <c r="C66" t="n">
+        <v>115.2992290848131</v>
+      </c>
+      <c r="D66" t="n">
+        <v>113.7225080277957</v>
+      </c>
+      <c r="E66" t="n">
+        <v>114.1489181518555</v>
+      </c>
+      <c r="F66" t="n">
+        <v>23956400</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>113.6134239095882</v>
+      </c>
+      <c r="C67" t="n">
+        <v>114.0299154007005</v>
+      </c>
+      <c r="D67" t="n">
+        <v>111.3623800798857</v>
+      </c>
+      <c r="E67" t="n">
+        <v>112.6118545532227</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22700700</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>112.9985942054707</v>
+      </c>
+      <c r="C68" t="n">
+        <v>114.7538201807431</v>
+      </c>
+      <c r="D68" t="n">
+        <v>112.0763587521143</v>
+      </c>
+      <c r="E68" t="n">
+        <v>114.0993270874023</v>
+      </c>
+      <c r="F68" t="n">
+        <v>24326700</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>114.3869114193454</v>
+      </c>
+      <c r="C69" t="n">
+        <v>115.2595689131506</v>
+      </c>
+      <c r="D69" t="n">
+        <v>112.0466150661863</v>
+      </c>
+      <c r="E69" t="n">
+        <v>112.2350311279297</v>
+      </c>
+      <c r="F69" t="n">
+        <v>22859600</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>112.1953625812108</v>
+      </c>
+      <c r="C70" t="n">
+        <v>114.9025723932263</v>
+      </c>
+      <c r="D70" t="n">
+        <v>111.9077829626674</v>
+      </c>
+      <c r="E70" t="n">
+        <v>114.5554885864258</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21586600</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>114.5306499047423</v>
+      </c>
+      <c r="C71" t="n">
+        <v>116.2099506211051</v>
+      </c>
+      <c r="D71" t="n">
+        <v>114.29216313914</v>
+      </c>
+      <c r="E71" t="n">
+        <v>115.9615325927734</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19092400</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>116.190085480185</v>
+      </c>
+      <c r="C72" t="n">
+        <v>116.7067916655062</v>
+      </c>
+      <c r="D72" t="n">
+        <v>114.9082474894773</v>
+      </c>
+      <c r="E72" t="n">
+        <v>116.0509719848633</v>
+      </c>
+      <c r="F72" t="n">
+        <v>18713700</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>115.8422995482986</v>
+      </c>
+      <c r="C73" t="n">
+        <v>116.1403966407218</v>
+      </c>
+      <c r="D73" t="n">
+        <v>114.2226091131107</v>
+      </c>
+      <c r="E73" t="n">
+        <v>114.6896362304688</v>
+      </c>
+      <c r="F73" t="n">
+        <v>19642300</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>114.4710352169006</v>
+      </c>
+      <c r="C74" t="n">
+        <v>115.6535075692186</v>
+      </c>
+      <c r="D74" t="n">
+        <v>114.3418605591895</v>
+      </c>
+      <c r="E74" t="n">
+        <v>114.9281311035156</v>
+      </c>
+      <c r="F74" t="n">
+        <v>16177800</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>114.2822395916168</v>
+      </c>
+      <c r="C75" t="n">
+        <v>115.7429389097976</v>
+      </c>
+      <c r="D75" t="n">
+        <v>113.8847692032296</v>
+      </c>
+      <c r="E75" t="n">
+        <v>114.1033782958984</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21476700</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>114.411415636222</v>
+      </c>
+      <c r="C76" t="n">
+        <v>114.5505291366805</v>
+      </c>
+      <c r="D76" t="n">
+        <v>112.8116027998319</v>
+      </c>
+      <c r="E76" t="n">
+        <v>113.6363525390625</v>
+      </c>
+      <c r="F76" t="n">
+        <v>50043800</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>113.2885630488155</v>
+      </c>
+      <c r="C77" t="n">
+        <v>113.5965989869235</v>
+      </c>
+      <c r="D77" t="n">
+        <v>111.5098890046396</v>
+      </c>
+      <c r="E77" t="n">
+        <v>111.8874816894531</v>
+      </c>
+      <c r="F77" t="n">
+        <v>21473900</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>111.2813488889387</v>
+      </c>
+      <c r="C78" t="n">
+        <v>111.6390714917152</v>
+      </c>
+      <c r="D78" t="n">
+        <v>109.9995108258424</v>
+      </c>
+      <c r="E78" t="n">
+        <v>110.1982498168945</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20319900</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>110.198241252702</v>
+      </c>
+      <c r="C79" t="n">
+        <v>111.0031132558388</v>
+      </c>
+      <c r="D79" t="n">
+        <v>109.8504575217858</v>
+      </c>
+      <c r="E79" t="n">
+        <v>110.9037475585938</v>
+      </c>
+      <c r="F79" t="n">
+        <v>9009600</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>111.0130583586743</v>
+      </c>
+      <c r="C80" t="n">
+        <v>111.2614764063509</v>
+      </c>
+      <c r="D80" t="n">
+        <v>110.6553357635307</v>
+      </c>
+      <c r="E80" t="n">
+        <v>111.0329284667969</v>
+      </c>
+      <c r="F80" t="n">
+        <v>9003800</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>110.8838778293028</v>
+      </c>
+      <c r="C81" t="n">
+        <v>112.0663501804078</v>
+      </c>
+      <c r="D81" t="n">
+        <v>110.8640077208743</v>
+      </c>
+      <c r="E81" t="n">
+        <v>111.8179321289062</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12979600</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>111.1819754114984</v>
+      </c>
+      <c r="C82" t="n">
+        <v>111.9769161578998</v>
+      </c>
+      <c r="D82" t="n">
+        <v>111.1322887719295</v>
+      </c>
+      <c r="E82" t="n">
+        <v>111.211784362793</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11730600</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>111.022991872357</v>
+      </c>
+      <c r="C83" t="n">
+        <v>111.5396980510222</v>
+      </c>
+      <c r="D83" t="n">
+        <v>110.6155826547936</v>
+      </c>
+      <c r="E83" t="n">
+        <v>110.7050170898438</v>
+      </c>
+      <c r="F83" t="n">
+        <v>11487400</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>110.7248924392647</v>
+      </c>
+      <c r="C84" t="n">
+        <v>112.0762872242068</v>
+      </c>
+      <c r="D84" t="n">
+        <v>110.4168564863102</v>
+      </c>
+      <c r="E84" t="n">
+        <v>112.0464782714844</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14306600</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>112.106092568778</v>
+      </c>
+      <c r="C85" t="n">
+        <v>113.0103378715463</v>
+      </c>
+      <c r="D85" t="n">
+        <v>111.4403340423477</v>
+      </c>
+      <c r="E85" t="n">
+        <v>111.9967880249023</v>
+      </c>
+      <c r="F85" t="n">
+        <v>19557600</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>111.6887515152225</v>
+      </c>
+      <c r="C86" t="n">
+        <v>114.0636273544414</v>
+      </c>
+      <c r="D86" t="n">
+        <v>111.2813422935498</v>
+      </c>
+      <c r="E86" t="n">
+        <v>113.6164703369141</v>
+      </c>
+      <c r="F86" t="n">
+        <v>20120800</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>113.4674284407305</v>
+      </c>
+      <c r="C87" t="n">
+        <v>114.0040123266269</v>
+      </c>
+      <c r="D87" t="n">
+        <v>111.3906496463658</v>
+      </c>
+      <c r="E87" t="n">
+        <v>112.0067291259766</v>
+      </c>
+      <c r="F87" t="n">
+        <v>23306000</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>110.5857797769927</v>
+      </c>
+      <c r="C88" t="n">
+        <v>112.7519854709339</v>
+      </c>
+      <c r="D88" t="n">
+        <v>109.1151415889016</v>
+      </c>
+      <c r="E88" t="n">
+        <v>112.3545150756836</v>
+      </c>
+      <c r="F88" t="n">
+        <v>24058300</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>111.5496424227033</v>
+      </c>
+      <c r="C89" t="n">
+        <v>114.7293904053996</v>
+      </c>
+      <c r="D89" t="n">
+        <v>111.5496424227033</v>
+      </c>
+      <c r="E89" t="n">
+        <v>113.8052749633789</v>
+      </c>
+      <c r="F89" t="n">
+        <v>21902900</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>116.7564835948294</v>
+      </c>
+      <c r="C90" t="n">
+        <v>118.0880007049746</v>
+      </c>
+      <c r="D90" t="n">
+        <v>115.673384534886</v>
+      </c>
+      <c r="E90" t="n">
+        <v>117.2235107421875</v>
+      </c>
+      <c r="F90" t="n">
+        <v>49182100</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>117.1440170823467</v>
+      </c>
+      <c r="C91" t="n">
+        <v>119.7474410206824</v>
+      </c>
+      <c r="D91" t="n">
+        <v>116.9850334697715</v>
+      </c>
+      <c r="E91" t="n">
+        <v>119.598388671875</v>
+      </c>
+      <c r="F91" t="n">
+        <v>31222100</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>119.4294631115365</v>
+      </c>
+      <c r="C92" t="n">
+        <v>120.4728143638468</v>
+      </c>
+      <c r="D92" t="n">
+        <v>118.2767997305645</v>
+      </c>
+      <c r="E92" t="n">
+        <v>119.2804107666016</v>
+      </c>
+      <c r="F92" t="n">
+        <v>32764000</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>119.2207951798175</v>
+      </c>
+      <c r="C93" t="n">
+        <v>120.1051628408833</v>
+      </c>
+      <c r="D93" t="n">
+        <v>117.9787049163972</v>
+      </c>
+      <c r="E93" t="n">
+        <v>118.4457244873047</v>
+      </c>
+      <c r="F93" t="n">
+        <v>34559400</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>117.9190771443211</v>
+      </c>
+      <c r="C94" t="n">
+        <v>119.8368647771362</v>
+      </c>
+      <c r="D94" t="n">
+        <v>116.1602807010803</v>
+      </c>
+      <c r="E94" t="n">
+        <v>118.9425582885742</v>
+      </c>
+      <c r="F94" t="n">
+        <v>415144600</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>120.1250298240042</v>
+      </c>
+      <c r="C95" t="n">
+        <v>120.8504138546603</v>
+      </c>
+      <c r="D95" t="n">
+        <v>116.8657862705671</v>
+      </c>
+      <c r="E95" t="n">
+        <v>117.9588241577148</v>
+      </c>
+      <c r="F95" t="n">
+        <v>45334000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>117.3328142471995</v>
+      </c>
+      <c r="C96" t="n">
+        <v>119.7275602876645</v>
+      </c>
+      <c r="D96" t="n">
+        <v>116.8061691984345</v>
+      </c>
+      <c r="E96" t="n">
+        <v>118.6047134399414</v>
+      </c>
+      <c r="F96" t="n">
+        <v>34811700</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>118.5351568548667</v>
+      </c>
+      <c r="C97" t="n">
+        <v>118.7636972139123</v>
+      </c>
+      <c r="D97" t="n">
+        <v>116.9055350642564</v>
+      </c>
+      <c r="E97" t="n">
+        <v>117.0843963623047</v>
+      </c>
+      <c r="F97" t="n">
+        <v>24547300</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>117.4222340816893</v>
+      </c>
+      <c r="C98" t="n">
+        <v>117.8594522459602</v>
+      </c>
+      <c r="D98" t="n">
+        <v>116.3987529981613</v>
+      </c>
+      <c r="E98" t="n">
+        <v>116.9850234985352</v>
+      </c>
+      <c r="F98" t="n">
+        <v>20806900</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>117.064521823182</v>
+      </c>
+      <c r="C99" t="n">
+        <v>118.0979418418126</v>
+      </c>
+      <c r="D99" t="n">
+        <v>116.6471813102112</v>
+      </c>
+      <c r="E99" t="n">
+        <v>116.8955993652344</v>
+      </c>
+      <c r="F99" t="n">
+        <v>19552200</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>116.7564814621505</v>
+      </c>
+      <c r="C100" t="n">
+        <v>116.8856561166937</v>
+      </c>
+      <c r="D100" t="n">
+        <v>114.7492669888757</v>
+      </c>
+      <c r="E100" t="n">
+        <v>116.2000274658203</v>
+      </c>
+      <c r="F100" t="n">
+        <v>22968600</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>115.9019236934497</v>
+      </c>
+      <c r="C101" t="n">
+        <v>116.7167345864151</v>
+      </c>
+      <c r="D101" t="n">
+        <v>115.1367994424561</v>
+      </c>
+      <c r="E101" t="n">
+        <v>115.8323669433594</v>
+      </c>
+      <c r="F101" t="n">
+        <v>16342000</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>115.7131212672227</v>
+      </c>
+      <c r="C102" t="n">
+        <v>116.9154712653777</v>
+      </c>
+      <c r="D102" t="n">
+        <v>115.3355285714882</v>
+      </c>
+      <c r="E102" t="n">
+        <v>116.6670532226562</v>
+      </c>
+      <c r="F102" t="n">
+        <v>16381100</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>116.1702235798966</v>
+      </c>
+      <c r="C103" t="n">
+        <v>118.6544041448817</v>
+      </c>
+      <c r="D103" t="n">
+        <v>115.8621800346786</v>
+      </c>
+      <c r="E103" t="n">
+        <v>118.3861083984375</v>
+      </c>
+      <c r="F103" t="n">
+        <v>22215400</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>118.7438208421828</v>
+      </c>
+      <c r="C104" t="n">
+        <v>123.4140768721483</v>
+      </c>
+      <c r="D104" t="n">
+        <v>118.2966714112071</v>
+      </c>
+      <c r="E104" t="n">
+        <v>123.2749633789062</v>
+      </c>
+      <c r="F104" t="n">
+        <v>31210100</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>122.8675715680868</v>
+      </c>
+      <c r="C105" t="n">
+        <v>127.3589666685813</v>
+      </c>
+      <c r="D105" t="n">
+        <v>122.8675715680868</v>
+      </c>
+      <c r="E105" t="n">
+        <v>126.9018783569336</v>
+      </c>
+      <c r="F105" t="n">
+        <v>32018700</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>127.3192228252665</v>
+      </c>
+      <c r="C106" t="n">
+        <v>128.5911220181715</v>
+      </c>
+      <c r="D106" t="n">
+        <v>126.2857952546346</v>
+      </c>
+      <c r="E106" t="n">
+        <v>127.1900405883789</v>
+      </c>
+      <c r="F106" t="n">
+        <v>27531800</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>127.7663710403251</v>
+      </c>
+      <c r="C107" t="n">
+        <v>128.779920911861</v>
+      </c>
+      <c r="D107" t="n">
+        <v>125.7591489863279</v>
+      </c>
+      <c r="E107" t="n">
+        <v>126.1367492675781</v>
+      </c>
+      <c r="F107" t="n">
+        <v>30517800</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>126.4845378023196</v>
+      </c>
+      <c r="C108" t="n">
+        <v>130.8666283506429</v>
+      </c>
+      <c r="D108" t="n">
+        <v>126.2460585922159</v>
+      </c>
+      <c r="E108" t="n">
+        <v>130.3499145507812</v>
+      </c>
+      <c r="F108" t="n">
+        <v>26593400</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>130.5884053590928</v>
+      </c>
+      <c r="C109" t="n">
+        <v>130.9560592399128</v>
+      </c>
+      <c r="D109" t="n">
+        <v>127.2794749450073</v>
+      </c>
+      <c r="E109" t="n">
+        <v>128.2035980224609</v>
+      </c>
+      <c r="F109" t="n">
+        <v>27197300</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>128.1240931628847</v>
+      </c>
+      <c r="C110" t="n">
+        <v>128.5215559695187</v>
+      </c>
+      <c r="D110" t="n">
+        <v>125.5902260744493</v>
+      </c>
+      <c r="E110" t="n">
+        <v>125.8982620239258</v>
+      </c>
+      <c r="F110" t="n">
+        <v>24662000</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>125.8982534995816</v>
+      </c>
+      <c r="C111" t="n">
+        <v>128.9190252095116</v>
+      </c>
+      <c r="D111" t="n">
+        <v>125.8286967550185</v>
+      </c>
+      <c r="E111" t="n">
+        <v>127.9551620483398</v>
+      </c>
+      <c r="F111" t="n">
+        <v>19232100</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>128.5613042513025</v>
+      </c>
+      <c r="C112" t="n">
+        <v>133.6389694112844</v>
+      </c>
+      <c r="D112" t="n">
+        <v>128.4917399247525</v>
+      </c>
+      <c r="E112" t="n">
+        <v>132.7943420410156</v>
+      </c>
+      <c r="F112" t="n">
+        <v>33382700</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>131.8602980405916</v>
+      </c>
+      <c r="C113" t="n">
+        <v>133.7979558000997</v>
+      </c>
+      <c r="D113" t="n">
+        <v>130.9163124820861</v>
+      </c>
+      <c r="E113" t="n">
+        <v>133.0427703857422</v>
+      </c>
+      <c r="F113" t="n">
+        <v>24131200</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>132.2677060470971</v>
+      </c>
+      <c r="C114" t="n">
+        <v>133.8377099294918</v>
+      </c>
+      <c r="D114" t="n">
+        <v>127.3490317305018</v>
+      </c>
+      <c r="E114" t="n">
+        <v>128.03466796875</v>
+      </c>
+      <c r="F114" t="n">
+        <v>37995900</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>127.3192261638227</v>
+      </c>
+      <c r="C115" t="n">
+        <v>128.0545339014254</v>
+      </c>
+      <c r="D115" t="n">
+        <v>124.9741515413755</v>
+      </c>
+      <c r="E115" t="n">
+        <v>125.8187789916992</v>
+      </c>
+      <c r="F115" t="n">
+        <v>36485000</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>127.6868765679835</v>
+      </c>
+      <c r="C116" t="n">
+        <v>129.2767581387821</v>
+      </c>
+      <c r="D116" t="n">
+        <v>123.6128221003258</v>
+      </c>
+      <c r="E116" t="n">
+        <v>124.0798492431641</v>
+      </c>
+      <c r="F116" t="n">
+        <v>42993300</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>122.2216774308809</v>
+      </c>
+      <c r="C117" t="n">
+        <v>122.6986434102051</v>
+      </c>
+      <c r="D117" t="n">
+        <v>120.2840197235699</v>
+      </c>
+      <c r="E117" t="n">
+        <v>122.2117385864258</v>
+      </c>
+      <c r="F117" t="n">
+        <v>35151000</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>122.7383904417398</v>
+      </c>
+      <c r="C118" t="n">
+        <v>125.9976417223621</v>
+      </c>
+      <c r="D118" t="n">
+        <v>122.1819364192246</v>
+      </c>
+      <c r="E118" t="n">
+        <v>125.0139007568359</v>
+      </c>
+      <c r="F118" t="n">
+        <v>25662800</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>125.1033248323272</v>
+      </c>
+      <c r="C119" t="n">
+        <v>127.2297750394507</v>
+      </c>
+      <c r="D119" t="n">
+        <v>124.1195915294407</v>
+      </c>
+      <c r="E119" t="n">
+        <v>125.9479446411133</v>
+      </c>
+      <c r="F119" t="n">
+        <v>20161200</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>125.8088357226236</v>
+      </c>
+      <c r="C120" t="n">
+        <v>126.593837657093</v>
+      </c>
+      <c r="D120" t="n">
+        <v>124.626363398647</v>
+      </c>
+      <c r="E120" t="n">
+        <v>124.9542770385742</v>
+      </c>
+      <c r="F120" t="n">
+        <v>17345700</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>125.1828241808018</v>
+      </c>
+      <c r="C121" t="n">
+        <v>126.5242801033853</v>
+      </c>
+      <c r="D121" t="n">
+        <v>123.1557320302039</v>
+      </c>
+      <c r="E121" t="n">
+        <v>123.6326904296875</v>
+      </c>
+      <c r="F121" t="n">
+        <v>18638300</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>124.7257266802137</v>
+      </c>
+      <c r="C122" t="n">
+        <v>127.7862463456887</v>
+      </c>
+      <c r="D122" t="n">
+        <v>124.3580728314762</v>
+      </c>
+      <c r="E122" t="n">
+        <v>127.1403503417969</v>
+      </c>
+      <c r="F122" t="n">
+        <v>29205500</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>126.6534531765271</v>
+      </c>
+      <c r="C123" t="n">
+        <v>127.9352911784569</v>
+      </c>
+      <c r="D123" t="n">
+        <v>126.2460515312658</v>
+      </c>
+      <c r="E123" t="n">
+        <v>126.2957305908203</v>
+      </c>
+      <c r="F123" t="n">
+        <v>17091500</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>125.7193975573372</v>
+      </c>
+      <c r="C124" t="n">
+        <v>127.5576895255598</v>
+      </c>
+      <c r="D124" t="n">
+        <v>124.8747777428692</v>
+      </c>
+      <c r="E124" t="n">
+        <v>127.1006088256836</v>
+      </c>
+      <c r="F124" t="n">
+        <v>16480400</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>126.3056684844515</v>
+      </c>
+      <c r="C125" t="n">
+        <v>127.3589585449282</v>
+      </c>
+      <c r="D125" t="n">
+        <v>125.4411709786478</v>
+      </c>
+      <c r="E125" t="n">
+        <v>127.0012359619141</v>
+      </c>
+      <c r="F125" t="n">
+        <v>16434100</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>124.5866098839056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>124.8847145576342</v>
+      </c>
+      <c r="D126" t="n">
+        <v>120.8802170560586</v>
+      </c>
+      <c r="E126" t="n">
+        <v>122.5297088623047</v>
+      </c>
+      <c r="F126" t="n">
+        <v>28604900</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>121.7248475261227</v>
+      </c>
+      <c r="C127" t="n">
+        <v>123.4041560118284</v>
+      </c>
+      <c r="D127" t="n">
+        <v>120.8504186975863</v>
+      </c>
+      <c r="E127" t="n">
+        <v>123.0166244506836</v>
+      </c>
+      <c r="F127" t="n">
+        <v>21553000</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>122.9073113026852</v>
+      </c>
+      <c r="C128" t="n">
+        <v>123.7221221667048</v>
+      </c>
+      <c r="D128" t="n">
+        <v>121.7248390120394</v>
+      </c>
+      <c r="E128" t="n">
+        <v>123.5531921386719</v>
+      </c>
+      <c r="F128" t="n">
+        <v>19375900</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>123.4240170322698</v>
+      </c>
+      <c r="C129" t="n">
+        <v>125.3020567921792</v>
+      </c>
+      <c r="D129" t="n">
+        <v>122.5694583754614</v>
+      </c>
+      <c r="E129" t="n">
+        <v>124.3282623291016</v>
+      </c>
+      <c r="F129" t="n">
+        <v>18793600</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>124.5170631497059</v>
+      </c>
+      <c r="C130" t="n">
+        <v>124.6959244521016</v>
+      </c>
+      <c r="D130" t="n">
+        <v>122.2713693965471</v>
+      </c>
+      <c r="E130" t="n">
+        <v>122.7085800170898</v>
+      </c>
+      <c r="F130" t="n">
+        <v>18176500</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>121.5261084606577</v>
+      </c>
+      <c r="C131" t="n">
+        <v>124.596551802696</v>
+      </c>
+      <c r="D131" t="n">
+        <v>121.5062307719897</v>
+      </c>
+      <c r="E131" t="n">
+        <v>124.5369338989258</v>
+      </c>
+      <c r="F131" t="n">
+        <v>21751600</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>124.5965441243348</v>
+      </c>
+      <c r="C132" t="n">
+        <v>125.8883208879408</v>
+      </c>
+      <c r="D132" t="n">
+        <v>124.1792036614282</v>
+      </c>
+      <c r="E132" t="n">
+        <v>125.7193908691406</v>
+      </c>
+      <c r="F132" t="n">
+        <v>15194100</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>125.9578808058303</v>
+      </c>
+      <c r="C133" t="n">
+        <v>126.176489886514</v>
+      </c>
+      <c r="D133" t="n">
+        <v>124.0400932995373</v>
+      </c>
+      <c r="E133" t="n">
+        <v>125.1927490234375</v>
+      </c>
+      <c r="F133" t="n">
+        <v>20463200</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>125.8485781413155</v>
+      </c>
+      <c r="C134" t="n">
+        <v>126.3851620070507</v>
+      </c>
+      <c r="D134" t="n">
+        <v>124.0699040996516</v>
+      </c>
+      <c r="E134" t="n">
+        <v>124.2885131835938</v>
+      </c>
+      <c r="F134" t="n">
+        <v>19895000</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>123.5432578745883</v>
+      </c>
+      <c r="C135" t="n">
+        <v>123.8214848583074</v>
+      </c>
+      <c r="D135" t="n">
+        <v>121.0590775469296</v>
+      </c>
+      <c r="E135" t="n">
+        <v>121.2081298828125</v>
+      </c>
+      <c r="F135" t="n">
+        <v>19734900</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>121.6254767010641</v>
+      </c>
+      <c r="C136" t="n">
+        <v>121.9732604488496</v>
+      </c>
+      <c r="D136" t="n">
+        <v>118.5152779167263</v>
+      </c>
+      <c r="E136" t="n">
+        <v>120.3237609863281</v>
+      </c>
+      <c r="F136" t="n">
+        <v>17927700</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>120.1126709520348</v>
+      </c>
+      <c r="C137" t="n">
+        <v>120.7798034051914</v>
+      </c>
+      <c r="D137" t="n">
+        <v>117.513863427923</v>
+      </c>
+      <c r="E137" t="n">
+        <v>118.5095748901367</v>
+      </c>
+      <c r="F137" t="n">
+        <v>57545600</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>119.9633247632631</v>
+      </c>
+      <c r="C138" t="n">
+        <v>120.6105311603868</v>
+      </c>
+      <c r="D138" t="n">
+        <v>118.5394570155744</v>
+      </c>
+      <c r="E138" t="n">
+        <v>120.2022933959961</v>
+      </c>
+      <c r="F138" t="n">
+        <v>22181500</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>120.1126723733929</v>
+      </c>
+      <c r="C139" t="n">
+        <v>123.577751645438</v>
+      </c>
+      <c r="D139" t="n">
+        <v>119.9732733747674</v>
+      </c>
+      <c r="E139" t="n">
+        <v>121.5265884399414</v>
+      </c>
+      <c r="F139" t="n">
+        <v>17269600</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>122.2833215864677</v>
+      </c>
+      <c r="C140" t="n">
+        <v>122.9604056810019</v>
+      </c>
+      <c r="D140" t="n">
+        <v>121.2577400013664</v>
+      </c>
+      <c r="E140" t="n">
+        <v>122.5322494506836</v>
+      </c>
+      <c r="F140" t="n">
+        <v>16597300</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>123.0798964656872</v>
+      </c>
+      <c r="C141" t="n">
+        <v>123.2690840775393</v>
+      </c>
+      <c r="D141" t="n">
+        <v>121.2677018786759</v>
+      </c>
+      <c r="E141" t="n">
+        <v>121.6560287475586</v>
+      </c>
+      <c r="F141" t="n">
+        <v>16442500</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>121.5066712193412</v>
+      </c>
+      <c r="C142" t="n">
+        <v>123.7370628172082</v>
+      </c>
+      <c r="D142" t="n">
+        <v>121.2975727192295</v>
+      </c>
+      <c r="E142" t="n">
+        <v>122.3629837036133</v>
+      </c>
+      <c r="F142" t="n">
+        <v>16543300</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>123.1794659302472</v>
+      </c>
+      <c r="C143" t="n">
+        <v>124.7228217585454</v>
+      </c>
+      <c r="D143" t="n">
+        <v>122.611910692122</v>
+      </c>
+      <c r="E143" t="n">
+        <v>122.9703674316406</v>
+      </c>
+      <c r="F143" t="n">
+        <v>20428900</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>122.9006712768322</v>
+      </c>
+      <c r="C144" t="n">
+        <v>124.4639380346807</v>
+      </c>
+      <c r="D144" t="n">
+        <v>122.313197539037</v>
+      </c>
+      <c r="E144" t="n">
+        <v>123.7470245361328</v>
+      </c>
+      <c r="F144" t="n">
+        <v>21330400</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>123.2690839840767</v>
+      </c>
+      <c r="C145" t="n">
+        <v>124.6929517011257</v>
+      </c>
+      <c r="D145" t="n">
+        <v>122.6019515205109</v>
+      </c>
+      <c r="E145" t="n">
+        <v>124.2050476074219</v>
+      </c>
+      <c r="F145" t="n">
+        <v>17039700</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>124.613294570145</v>
+      </c>
+      <c r="C146" t="n">
+        <v>125.3600781881083</v>
+      </c>
+      <c r="D146" t="n">
+        <v>123.6175830795272</v>
+      </c>
+      <c r="E146" t="n">
+        <v>125.2505493164062</v>
+      </c>
+      <c r="F146" t="n">
+        <v>11898400</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>125.2704609872334</v>
+      </c>
+      <c r="C147" t="n">
+        <v>126.4354492120167</v>
+      </c>
+      <c r="D147" t="n">
+        <v>124.8323530943609</v>
+      </c>
+      <c r="E147" t="n">
+        <v>126.2462615966797</v>
+      </c>
+      <c r="F147" t="n">
+        <v>10850400</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>125.6488358778686</v>
+      </c>
+      <c r="C148" t="n">
+        <v>125.8181050086721</v>
+      </c>
+      <c r="D148" t="n">
+        <v>121.2677037842684</v>
+      </c>
+      <c r="E148" t="n">
+        <v>121.9646987915039</v>
+      </c>
+      <c r="F148" t="n">
+        <v>16076000</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>121.7556020039852</v>
+      </c>
+      <c r="C149" t="n">
+        <v>126.7540780291546</v>
+      </c>
+      <c r="D149" t="n">
+        <v>120.8096791098908</v>
+      </c>
+      <c r="E149" t="n">
+        <v>126.7142486572266</v>
+      </c>
+      <c r="F149" t="n">
+        <v>20194300</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>126.5449729094413</v>
+      </c>
+      <c r="C150" t="n">
+        <v>129.1338289281244</v>
+      </c>
+      <c r="D150" t="n">
+        <v>126.2761341426855</v>
+      </c>
+      <c r="E150" t="n">
+        <v>128.5762329101562</v>
+      </c>
+      <c r="F150" t="n">
+        <v>13853100</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>128.1679831957248</v>
+      </c>
+      <c r="C151" t="n">
+        <v>128.3770740986961</v>
+      </c>
+      <c r="D151" t="n">
+        <v>125.6787044903905</v>
+      </c>
+      <c r="E151" t="n">
+        <v>126.2263412475586</v>
+      </c>
+      <c r="F151" t="n">
+        <v>13894000</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>125.7484068642315</v>
+      </c>
+      <c r="C152" t="n">
+        <v>125.7583661063497</v>
+      </c>
+      <c r="D152" t="n">
+        <v>123.4184379925161</v>
+      </c>
+      <c r="E152" t="n">
+        <v>124.0357818603516</v>
+      </c>
+      <c r="F152" t="n">
+        <v>14510600</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>122.6218644106077</v>
+      </c>
+      <c r="C153" t="n">
+        <v>124.6630682888762</v>
+      </c>
+      <c r="D153" t="n">
+        <v>122.0244390705456</v>
+      </c>
+      <c r="E153" t="n">
+        <v>124.5137176513672</v>
+      </c>
+      <c r="F153" t="n">
+        <v>15320800</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>124.0955129791748</v>
+      </c>
+      <c r="C154" t="n">
+        <v>124.5336284399926</v>
+      </c>
+      <c r="D154" t="n">
+        <v>122.6517344420986</v>
+      </c>
+      <c r="E154" t="n">
+        <v>124.2249603271484</v>
+      </c>
+      <c r="F154" t="n">
+        <v>17001400</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>123.7968020201654</v>
+      </c>
+      <c r="C155" t="n">
+        <v>125.3998980056611</v>
+      </c>
+      <c r="D155" t="n">
+        <v>123.4383453031182</v>
+      </c>
+      <c r="E155" t="n">
+        <v>124.2846984863281</v>
+      </c>
+      <c r="F155" t="n">
+        <v>18324500</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>124.0357815469104</v>
+      </c>
+      <c r="C156" t="n">
+        <v>127.0229160540335</v>
+      </c>
+      <c r="D156" t="n">
+        <v>122.8409307827315</v>
+      </c>
+      <c r="E156" t="n">
+        <v>126.9532165527344</v>
+      </c>
+      <c r="F156" t="n">
+        <v>24763700</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>127.3216255408005</v>
+      </c>
+      <c r="C157" t="n">
+        <v>128.9147623376428</v>
+      </c>
+      <c r="D157" t="n">
+        <v>126.7739812059444</v>
+      </c>
+      <c r="E157" t="n">
+        <v>127.3714065551758</v>
+      </c>
+      <c r="F157" t="n">
+        <v>18933600</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>127.2817912634612</v>
+      </c>
+      <c r="C158" t="n">
+        <v>129.213473828279</v>
+      </c>
+      <c r="D158" t="n">
+        <v>126.9332937895701</v>
+      </c>
+      <c r="E158" t="n">
+        <v>129.0442047119141</v>
+      </c>
+      <c r="F158" t="n">
+        <v>17312400</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>129.4424953884951</v>
+      </c>
+      <c r="C159" t="n">
+        <v>129.8905625261696</v>
+      </c>
+      <c r="D159" t="n">
+        <v>128.2874663986241</v>
+      </c>
+      <c r="E159" t="n">
+        <v>129.4225769042969</v>
+      </c>
+      <c r="F159" t="n">
+        <v>17624500</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>130.010060581267</v>
+      </c>
+      <c r="C160" t="n">
+        <v>131.8919547480997</v>
+      </c>
+      <c r="D160" t="n">
+        <v>129.93040183639</v>
+      </c>
+      <c r="E160" t="n">
+        <v>131.4637908935547</v>
+      </c>
+      <c r="F160" t="n">
+        <v>16376000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>131.3741802679442</v>
+      </c>
+      <c r="C161" t="n">
+        <v>131.5534010485827</v>
+      </c>
+      <c r="D161" t="n">
+        <v>128.7255839805935</v>
+      </c>
+      <c r="E161" t="n">
+        <v>129.3628387451172</v>
+      </c>
+      <c r="F161" t="n">
+        <v>16016300</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>129.0641091249569</v>
+      </c>
+      <c r="C162" t="n">
+        <v>129.253296725292</v>
+      </c>
+      <c r="D162" t="n">
+        <v>126.8536361584495</v>
+      </c>
+      <c r="E162" t="n">
+        <v>127.0428161621094</v>
+      </c>
+      <c r="F162" t="n">
+        <v>17029500</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>128.7853111434159</v>
+      </c>
+      <c r="C163" t="n">
+        <v>129.2134749536506</v>
+      </c>
+      <c r="D163" t="n">
+        <v>126.236292344555</v>
+      </c>
+      <c r="E163" t="n">
+        <v>127.0428161621094</v>
+      </c>
+      <c r="F163" t="n">
+        <v>16341800</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>126.1367309249001</v>
+      </c>
+      <c r="C164" t="n">
+        <v>127.5307285199335</v>
+      </c>
+      <c r="D164" t="n">
+        <v>125.3700364258034</v>
+      </c>
+      <c r="E164" t="n">
+        <v>127.4610214233398</v>
+      </c>
+      <c r="F164" t="n">
+        <v>16538800</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>127.470976777907</v>
+      </c>
+      <c r="C165" t="n">
+        <v>131.8620524738122</v>
+      </c>
+      <c r="D165" t="n">
+        <v>127.4012696875933</v>
+      </c>
+      <c r="E165" t="n">
+        <v>131.3641967773438</v>
+      </c>
+      <c r="F165" t="n">
+        <v>19867700</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>131.3542490271043</v>
+      </c>
+      <c r="C166" t="n">
+        <v>132.7980275509944</v>
+      </c>
+      <c r="D166" t="n">
+        <v>130.4182778590603</v>
+      </c>
+      <c r="E166" t="n">
+        <v>131.0356292724609</v>
+      </c>
+      <c r="F166" t="n">
+        <v>10480900</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>129.8507311252314</v>
+      </c>
+      <c r="C167" t="n">
+        <v>131.184980793923</v>
+      </c>
+      <c r="D167" t="n">
+        <v>129.1238508427206</v>
+      </c>
+      <c r="E167" t="n">
+        <v>129.7710723876953</v>
+      </c>
+      <c r="F167" t="n">
+        <v>10340700</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>129.9502974650302</v>
+      </c>
+      <c r="C168" t="n">
+        <v>131.1650666644096</v>
+      </c>
+      <c r="D168" t="n">
+        <v>129.7412065662402</v>
+      </c>
+      <c r="E168" t="n">
+        <v>130.2290954589844</v>
+      </c>
+      <c r="F168" t="n">
+        <v>10637300</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>130.2988095283542</v>
+      </c>
+      <c r="C169" t="n">
+        <v>130.5875591827794</v>
+      </c>
+      <c r="D169" t="n">
+        <v>128.9745113895137</v>
+      </c>
+      <c r="E169" t="n">
+        <v>129.5221557617188</v>
+      </c>
+      <c r="F169" t="n">
+        <v>16371500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>129.3429155964338</v>
+      </c>
+      <c r="C170" t="n">
+        <v>130.0399257893878</v>
+      </c>
+      <c r="D170" t="n">
+        <v>128.1181947261785</v>
+      </c>
+      <c r="E170" t="n">
+        <v>129.6416320800781</v>
+      </c>
+      <c r="F170" t="n">
+        <v>14935400</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>130.0087618254011</v>
+      </c>
+      <c r="C171" t="n">
+        <v>131.0961549064253</v>
+      </c>
+      <c r="D171" t="n">
+        <v>129.9389217008702</v>
+      </c>
+      <c r="E171" t="n">
+        <v>130.1184844970703</v>
+      </c>
+      <c r="F171" t="n">
+        <v>15183700</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>129.8690812906444</v>
+      </c>
+      <c r="C172" t="n">
+        <v>130.2880915922154</v>
+      </c>
+      <c r="D172" t="n">
+        <v>126.078161470576</v>
+      </c>
+      <c r="E172" t="n">
+        <v>127.285270690918</v>
+      </c>
+      <c r="F172" t="n">
+        <v>18699200</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>127.7741133789013</v>
+      </c>
+      <c r="C173" t="n">
+        <v>130.8068463681294</v>
+      </c>
+      <c r="D173" t="n">
+        <v>127.4149725439082</v>
+      </c>
+      <c r="E173" t="n">
+        <v>130.0386962890625</v>
+      </c>
+      <c r="F173" t="n">
+        <v>17935400</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>128.8814524975413</v>
+      </c>
+      <c r="C174" t="n">
+        <v>132.2134717809921</v>
+      </c>
+      <c r="D174" t="n">
+        <v>128.4624574279768</v>
+      </c>
+      <c r="E174" t="n">
+        <v>131.156005859375</v>
+      </c>
+      <c r="F174" t="n">
+        <v>13786600</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>131.0462673331121</v>
+      </c>
+      <c r="C175" t="n">
+        <v>132.4628740535408</v>
+      </c>
+      <c r="D175" t="n">
+        <v>130.5474615066649</v>
+      </c>
+      <c r="E175" t="n">
+        <v>132.1436462402344</v>
+      </c>
+      <c r="F175" t="n">
+        <v>14200400</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>133.370718441355</v>
+      </c>
+      <c r="C176" t="n">
+        <v>133.6300920185431</v>
+      </c>
+      <c r="D176" t="n">
+        <v>130.4776352080381</v>
+      </c>
+      <c r="E176" t="n">
+        <v>131.1360626220703</v>
+      </c>
+      <c r="F176" t="n">
+        <v>25323000</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>131.2058999637278</v>
+      </c>
+      <c r="C177" t="n">
+        <v>133.1512398071679</v>
+      </c>
+      <c r="D177" t="n">
+        <v>130.8168319950398</v>
+      </c>
+      <c r="E177" t="n">
+        <v>133.0215454101562</v>
+      </c>
+      <c r="F177" t="n">
+        <v>17183200</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>132.6225008315265</v>
+      </c>
+      <c r="C178" t="n">
+        <v>134.8372000065807</v>
+      </c>
+      <c r="D178" t="n">
+        <v>131.7445976710087</v>
+      </c>
+      <c r="E178" t="n">
+        <v>133.8794860839844</v>
+      </c>
+      <c r="F178" t="n">
+        <v>16957100</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>132.5925684137131</v>
+      </c>
+      <c r="C179" t="n">
+        <v>133.3307912944098</v>
+      </c>
+      <c r="D179" t="n">
+        <v>130.0187285230658</v>
+      </c>
+      <c r="E179" t="n">
+        <v>130.5374908447266</v>
+      </c>
+      <c r="F179" t="n">
+        <v>28471600</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>124.112876676945</v>
+      </c>
+      <c r="C180" t="n">
+        <v>125.49955634699</v>
+      </c>
+      <c r="D180" t="n">
+        <v>120.1024733345915</v>
+      </c>
+      <c r="E180" t="n">
+        <v>121.0502014160156</v>
+      </c>
+      <c r="F180" t="n">
+        <v>53006600</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>121.0502017985552</v>
+      </c>
+      <c r="C181" t="n">
+        <v>121.6587455533669</v>
+      </c>
+      <c r="D181" t="n">
+        <v>118.6260126387565</v>
+      </c>
+      <c r="E181" t="n">
+        <v>119.9827575683594</v>
+      </c>
+      <c r="F181" t="n">
+        <v>30330600</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>120.401759010853</v>
+      </c>
+      <c r="C182" t="n">
+        <v>120.7608998332451</v>
+      </c>
+      <c r="D182" t="n">
+        <v>117.638370328068</v>
+      </c>
+      <c r="E182" t="n">
+        <v>118.2868194580078</v>
+      </c>
+      <c r="F182" t="n">
+        <v>28796600</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>118.0473918040102</v>
+      </c>
+      <c r="C183" t="n">
+        <v>119.1447631286873</v>
+      </c>
+      <c r="D183" t="n">
+        <v>117.7580835037564</v>
+      </c>
+      <c r="E183" t="n">
+        <v>118.2568893432617</v>
+      </c>
+      <c r="F183" t="n">
+        <v>22062200</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>118.6758897292679</v>
+      </c>
+      <c r="C184" t="n">
+        <v>118.8853872778886</v>
+      </c>
+      <c r="D184" t="n">
+        <v>117.0497853597791</v>
+      </c>
+      <c r="E184" t="n">
+        <v>118.6160354614258</v>
+      </c>
+      <c r="F184" t="n">
+        <v>21613100</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>117.8279207851919</v>
+      </c>
+      <c r="C185" t="n">
+        <v>118.7956053707809</v>
+      </c>
+      <c r="D185" t="n">
+        <v>114.4360394170558</v>
+      </c>
+      <c r="E185" t="n">
+        <v>115.4735565185547</v>
+      </c>
+      <c r="F185" t="n">
+        <v>42191000</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>114.4559959694409</v>
+      </c>
+      <c r="C186" t="n">
+        <v>115.7030106192767</v>
+      </c>
+      <c r="D186" t="n">
+        <v>113.2887844727029</v>
+      </c>
+      <c r="E186" t="n">
+        <v>114.326301574707</v>
+      </c>
+      <c r="F186" t="n">
+        <v>26176200</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>113.598048691841</v>
+      </c>
+      <c r="C187" t="n">
+        <v>114.2963738476551</v>
+      </c>
+      <c r="D187" t="n">
+        <v>112.4607719459876</v>
+      </c>
+      <c r="E187" t="n">
+        <v>112.7899780273438</v>
+      </c>
+      <c r="F187" t="n">
+        <v>27366400</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>112.829882918774</v>
+      </c>
+      <c r="C188" t="n">
+        <v>117.0098784207316</v>
+      </c>
+      <c r="D188" t="n">
+        <v>112.6902178882183</v>
+      </c>
+      <c r="E188" t="n">
+        <v>116.6108322143555</v>
+      </c>
+      <c r="F188" t="n">
+        <v>32880600</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>119.613646228699</v>
+      </c>
+      <c r="C189" t="n">
+        <v>119.6535516106658</v>
+      </c>
+      <c r="D189" t="n">
+        <v>117.009879041958</v>
+      </c>
+      <c r="E189" t="n">
+        <v>117.4588012695312</v>
+      </c>
+      <c r="F189" t="n">
+        <v>22870400</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>118.0673439785114</v>
+      </c>
+      <c r="C190" t="n">
+        <v>120.601278627145</v>
+      </c>
+      <c r="D190" t="n">
+        <v>117.8179410518094</v>
+      </c>
+      <c r="E190" t="n">
+        <v>118.596076965332</v>
+      </c>
+      <c r="F190" t="n">
+        <v>36638100</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>117.9675872503352</v>
+      </c>
+      <c r="C191" t="n">
+        <v>119.8929781965846</v>
+      </c>
+      <c r="D191" t="n">
+        <v>117.8678275994195</v>
+      </c>
+      <c r="E191" t="n">
+        <v>119.543815612793</v>
+      </c>
+      <c r="F191" t="n">
+        <v>19514100</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>120.0924945255443</v>
+      </c>
+      <c r="C192" t="n">
+        <v>120.2122106703836</v>
+      </c>
+      <c r="D192" t="n">
+        <v>117.7181814033632</v>
+      </c>
+      <c r="E192" t="n">
+        <v>118.596076965332</v>
+      </c>
+      <c r="F192" t="n">
+        <v>23959000</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>119.4240987453198</v>
+      </c>
+      <c r="C193" t="n">
+        <v>120.53144836951</v>
+      </c>
+      <c r="D193" t="n">
+        <v>117.2493048793001</v>
+      </c>
+      <c r="E193" t="n">
+        <v>120.3019943237305</v>
+      </c>
+      <c r="F193" t="n">
+        <v>22414900</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>120.2820441244615</v>
+      </c>
+      <c r="C194" t="n">
+        <v>121.5689641496319</v>
+      </c>
+      <c r="D194" t="n">
+        <v>119.1746945123655</v>
+      </c>
+      <c r="E194" t="n">
+        <v>120.2122116088867</v>
+      </c>
+      <c r="F194" t="n">
+        <v>22438000</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>120.3019933173184</v>
+      </c>
+      <c r="C195" t="n">
+        <v>121.3195615310648</v>
+      </c>
+      <c r="D195" t="n">
+        <v>119.2445273327187</v>
+      </c>
+      <c r="E195" t="n">
+        <v>120.7509231567383</v>
+      </c>
+      <c r="F195" t="n">
+        <v>14753500</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>119.4540258740917</v>
+      </c>
+      <c r="C196" t="n">
+        <v>121.1998463936268</v>
+      </c>
+      <c r="D196" t="n">
+        <v>118.2968002303814</v>
+      </c>
+      <c r="E196" t="n">
+        <v>120.5314483642578</v>
+      </c>
+      <c r="F196" t="n">
+        <v>20722500</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>120.8506818055627</v>
+      </c>
+      <c r="C197" t="n">
+        <v>122.646385926027</v>
+      </c>
+      <c r="D197" t="n">
+        <v>119.5936889212378</v>
+      </c>
+      <c r="E197" t="n">
+        <v>120.7409439086914</v>
+      </c>
+      <c r="F197" t="n">
+        <v>23060700</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>119.2944114353401</v>
+      </c>
+      <c r="C198" t="n">
+        <v>120.7209965009543</v>
+      </c>
+      <c r="D198" t="n">
+        <v>117.1694935982547</v>
+      </c>
+      <c r="E198" t="n">
+        <v>117.8478698730469</v>
+      </c>
+      <c r="F198" t="n">
+        <v>21711100</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>117.9176994360996</v>
+      </c>
+      <c r="C199" t="n">
+        <v>118.1970371043968</v>
+      </c>
+      <c r="D199" t="n">
+        <v>116.5210491504798</v>
+      </c>
+      <c r="E199" t="n">
+        <v>116.9001388549805</v>
+      </c>
+      <c r="F199" t="n">
+        <v>36526800</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>116.6806630640479</v>
+      </c>
+      <c r="C200" t="n">
+        <v>118.1172263420262</v>
+      </c>
+      <c r="D200" t="n">
+        <v>116.6706848159582</v>
+      </c>
+      <c r="E200" t="n">
+        <v>116.9001388549805</v>
+      </c>
+      <c r="F200" t="n">
+        <v>17053900</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>119.4240968222584</v>
+      </c>
+      <c r="C201" t="n">
+        <v>119.9628080586903</v>
+      </c>
+      <c r="D201" t="n">
+        <v>116.0621426214644</v>
+      </c>
+      <c r="E201" t="n">
+        <v>119.1347885131836</v>
+      </c>
+      <c r="F201" t="n">
+        <v>23411400</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>119.2744498995579</v>
+      </c>
+      <c r="C202" t="n">
+        <v>120.112447667685</v>
+      </c>
+      <c r="D202" t="n">
+        <v>118.6459572818424</v>
+      </c>
+      <c r="E202" t="n">
+        <v>118.7157897949219</v>
+      </c>
+      <c r="F202" t="n">
+        <v>20600100</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>117.1894451773868</v>
+      </c>
+      <c r="C203" t="n">
+        <v>118.2967947502302</v>
+      </c>
+      <c r="D203" t="n">
+        <v>115.1044328099781</v>
+      </c>
+      <c r="E203" t="n">
+        <v>115.5034790039062</v>
+      </c>
+      <c r="F203" t="n">
+        <v>20384700</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>117.0098811702962</v>
+      </c>
+      <c r="C204" t="n">
+        <v>117.5984684398727</v>
+      </c>
+      <c r="D204" t="n">
+        <v>114.8151307892405</v>
+      </c>
+      <c r="E204" t="n">
+        <v>115.413703918457</v>
+      </c>
+      <c r="F204" t="n">
+        <v>36636000</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>116.1918382308837</v>
+      </c>
+      <c r="C205" t="n">
+        <v>116.521051925122</v>
+      </c>
+      <c r="D205" t="n">
+        <v>113.9272553645249</v>
+      </c>
+      <c r="E205" t="n">
+        <v>114.326301574707</v>
+      </c>
+      <c r="F205" t="n">
+        <v>20367000</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>113.6978053385094</v>
+      </c>
+      <c r="C206" t="n">
+        <v>114.3362762101566</v>
+      </c>
+      <c r="D206" t="n">
+        <v>112.6602882692895</v>
+      </c>
+      <c r="E206" t="n">
+        <v>112.989501953125</v>
+      </c>
+      <c r="F206" t="n">
+        <v>23034000</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>109.8669732552887</v>
+      </c>
+      <c r="C207" t="n">
+        <v>110.4455898652017</v>
+      </c>
+      <c r="D207" t="n">
+        <v>106.9938543130583</v>
+      </c>
+      <c r="E207" t="n">
+        <v>108.5601043701172</v>
+      </c>
+      <c r="F207" t="n">
+        <v>40391400</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>109.0688912954154</v>
+      </c>
+      <c r="C208" t="n">
+        <v>112.1814349941213</v>
+      </c>
+      <c r="D208" t="n">
+        <v>108.8992991295087</v>
+      </c>
+      <c r="E208" t="n">
+        <v>111.5728912353516</v>
+      </c>
+      <c r="F208" t="n">
+        <v>29512200</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>111.1339433224697</v>
+      </c>
+      <c r="C209" t="n">
+        <v>112.1016278755018</v>
+      </c>
+      <c r="D209" t="n">
+        <v>109.1087928180449</v>
+      </c>
+      <c r="E209" t="n">
+        <v>110.3857345581055</v>
+      </c>
+      <c r="F209" t="n">
+        <v>29523300</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>112.7001980505562</v>
+      </c>
+      <c r="C210" t="n">
+        <v>113.228931048236</v>
+      </c>
+      <c r="D210" t="n">
+        <v>111.0341882926515</v>
+      </c>
+      <c r="E210" t="n">
+        <v>111.2736129760742</v>
+      </c>
+      <c r="F210" t="n">
+        <v>19941400</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>112.879763389333</v>
+      </c>
+      <c r="C211" t="n">
+        <v>113.5880667705184</v>
+      </c>
+      <c r="D211" t="n">
+        <v>111.5429597770651</v>
+      </c>
+      <c r="E211" t="n">
+        <v>112.8298797607422</v>
+      </c>
+      <c r="F211" t="n">
+        <v>19892000</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>110.9743243964893</v>
+      </c>
+      <c r="C212" t="n">
+        <v>112.4906984566786</v>
+      </c>
+      <c r="D212" t="n">
+        <v>110.7748050991254</v>
+      </c>
+      <c r="E212" t="n">
+        <v>111.942008972168</v>
+      </c>
+      <c r="F212" t="n">
+        <v>20464500</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>111.6826280597077</v>
+      </c>
+      <c r="C213" t="n">
+        <v>113.8873566399898</v>
+      </c>
+      <c r="D213" t="n">
+        <v>111.6626791743936</v>
+      </c>
+      <c r="E213" t="n">
+        <v>113.6279754638672</v>
+      </c>
+      <c r="F213" t="n">
+        <v>12461700</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>114.4559909872762</v>
+      </c>
+      <c r="C214" t="n">
+        <v>115.26405400962</v>
+      </c>
+      <c r="D214" t="n">
+        <v>113.7377093624492</v>
+      </c>
+      <c r="E214" t="n">
+        <v>114.5058670043945</v>
+      </c>
+      <c r="F214" t="n">
+        <v>17043400</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>114.8051528853423</v>
+      </c>
+      <c r="C215" t="n">
+        <v>115.6032376551602</v>
+      </c>
+      <c r="D215" t="n">
+        <v>113.2289246190302</v>
+      </c>
+      <c r="E215" t="n">
+        <v>113.4284439086914</v>
+      </c>
+      <c r="F215" t="n">
+        <v>14682000</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>112.9795273843265</v>
+      </c>
+      <c r="C216" t="n">
+        <v>114.4559960800755</v>
+      </c>
+      <c r="D216" t="n">
+        <v>111.8023452492967</v>
+      </c>
+      <c r="E216" t="n">
+        <v>112.2612457275391</v>
+      </c>
+      <c r="F216" t="n">
+        <v>16467900</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>113.4883080789502</v>
+      </c>
+      <c r="C217" t="n">
+        <v>115.3139316886614</v>
+      </c>
+      <c r="D217" t="n">
+        <v>113.288781174082</v>
+      </c>
+      <c r="E217" t="n">
+        <v>114.6754608154297</v>
+      </c>
+      <c r="F217" t="n">
+        <v>20777600</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>116.6806604264181</v>
+      </c>
+      <c r="C218" t="n">
+        <v>117.8079588775203</v>
+      </c>
+      <c r="D218" t="n">
+        <v>113.3286845943574</v>
+      </c>
+      <c r="E218" t="n">
+        <v>113.967155456543</v>
+      </c>
+      <c r="F218" t="n">
+        <v>28289800</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>113.6878284476981</v>
+      </c>
+      <c r="C219" t="n">
+        <v>114.1267800313856</v>
+      </c>
+      <c r="D219" t="n">
+        <v>111.8721754576813</v>
+      </c>
+      <c r="E219" t="n">
+        <v>111.9320297241211</v>
+      </c>
+      <c r="F219" t="n">
+        <v>17738900</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>111.2436859074791</v>
+      </c>
+      <c r="C220" t="n">
+        <v>111.5329942219063</v>
+      </c>
+      <c r="D220" t="n">
+        <v>109.6275521682845</v>
+      </c>
+      <c r="E220" t="n">
+        <v>110.1263580322266</v>
+      </c>
+      <c r="F220" t="n">
+        <v>22717000</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>109.268405092928</v>
+      </c>
+      <c r="C221" t="n">
+        <v>109.737283796026</v>
+      </c>
+      <c r="D221" t="n">
+        <v>108.4603420750963</v>
+      </c>
+      <c r="E221" t="n">
+        <v>109.0688858032227</v>
+      </c>
+      <c r="F221" t="n">
+        <v>23494800</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>107.25323944858</v>
+      </c>
+      <c r="C222" t="n">
+        <v>108.3007272005749</v>
+      </c>
+      <c r="D222" t="n">
+        <v>106.5349577836844</v>
+      </c>
+      <c r="E222" t="n">
+        <v>108.14111328125</v>
+      </c>
+      <c r="F222" t="n">
+        <v>21516800</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>107.8617828177618</v>
+      </c>
+      <c r="C223" t="n">
+        <v>109.3382439135796</v>
+      </c>
+      <c r="D223" t="n">
+        <v>107.7520449187408</v>
+      </c>
+      <c r="E223" t="n">
+        <v>109.2085571289062</v>
+      </c>
+      <c r="F223" t="n">
+        <v>18405900</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>109.6574762821653</v>
+      </c>
+      <c r="C224" t="n">
+        <v>112.2412945440321</v>
+      </c>
+      <c r="D224" t="n">
+        <v>109.6275491489408</v>
+      </c>
+      <c r="E224" t="n">
+        <v>111.4731292724609</v>
+      </c>
+      <c r="F224" t="n">
+        <v>19008700</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>113.6878264165269</v>
+      </c>
+      <c r="C225" t="n">
+        <v>115.7528822947127</v>
+      </c>
+      <c r="D225" t="n">
+        <v>112.5704985921816</v>
+      </c>
+      <c r="E225" t="n">
+        <v>112.8298797607422</v>
+      </c>
+      <c r="F225" t="n">
+        <v>24867900</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>112.9595787445935</v>
+      </c>
+      <c r="C226" t="n">
+        <v>114.4160909468376</v>
+      </c>
+      <c r="D226" t="n">
+        <v>112.1814352072651</v>
+      </c>
+      <c r="E226" t="n">
+        <v>113.9472122192383</v>
+      </c>
+      <c r="F226" t="n">
+        <v>23480000</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>111.3434398479761</v>
+      </c>
+      <c r="C227" t="n">
+        <v>112.7600466022415</v>
+      </c>
+      <c r="D227" t="n">
+        <v>110.1762360128914</v>
+      </c>
+      <c r="E227" t="n">
+        <v>110.8346557617188</v>
+      </c>
+      <c r="F227" t="n">
+        <v>28747000</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>110.2560414658192</v>
+      </c>
+      <c r="C228" t="n">
+        <v>111.642728727712</v>
+      </c>
+      <c r="D228" t="n">
+        <v>109.6275488363764</v>
+      </c>
+      <c r="E228" t="n">
+        <v>110.9344177246094</v>
+      </c>
+      <c r="F228" t="n">
+        <v>22799100</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>112.8298784424625</v>
+      </c>
+      <c r="C229" t="n">
+        <v>113.0194270954852</v>
+      </c>
+      <c r="D229" t="n">
+        <v>109.8969053059805</v>
+      </c>
+      <c r="E229" t="n">
+        <v>110.4455871582031</v>
+      </c>
+      <c r="F229" t="n">
+        <v>23942500</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>108.7496500450106</v>
+      </c>
+      <c r="C230" t="n">
+        <v>111.4132713715266</v>
+      </c>
+      <c r="D230" t="n">
+        <v>108.3007202277679</v>
+      </c>
+      <c r="E230" t="n">
+        <v>111.2835845947266</v>
+      </c>
+      <c r="F230" t="n">
+        <v>29620000</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>112.181431315027</v>
+      </c>
+      <c r="C231" t="n">
+        <v>112.8897423116165</v>
+      </c>
+      <c r="D231" t="n">
+        <v>111.0940382280446</v>
+      </c>
+      <c r="E231" t="n">
+        <v>112.0716934204102</v>
+      </c>
+      <c r="F231" t="n">
+        <v>21446300</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>113.7975687180191</v>
+      </c>
+      <c r="C232" t="n">
+        <v>114.2863963302149</v>
+      </c>
+      <c r="D232" t="n">
+        <v>110.7748064209645</v>
+      </c>
+      <c r="E232" t="n">
+        <v>111.8023452758789</v>
+      </c>
+      <c r="F232" t="n">
+        <v>23203100</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>110.3458340692701</v>
+      </c>
+      <c r="C233" t="n">
+        <v>112.0218220801941</v>
+      </c>
+      <c r="D233" t="n">
+        <v>110.2360961700712</v>
+      </c>
+      <c r="E233" t="n">
+        <v>111.5828704833984</v>
+      </c>
+      <c r="F233" t="n">
+        <v>18819300</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>110.8147094920761</v>
+      </c>
+      <c r="C234" t="n">
+        <v>112.4308355753539</v>
+      </c>
+      <c r="D234" t="n">
+        <v>110.4954740524384</v>
+      </c>
+      <c r="E234" t="n">
+        <v>112.3909378051758</v>
+      </c>
+      <c r="F234" t="n">
+        <v>19144000</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>112.1714606731287</v>
+      </c>
+      <c r="C235" t="n">
+        <v>113.069305103701</v>
+      </c>
+      <c r="D235" t="n">
+        <v>111.9220577510424</v>
+      </c>
+      <c r="E235" t="n">
+        <v>112.989501953125</v>
+      </c>
+      <c r="F235" t="n">
+        <v>17005800</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>112.1016271407472</v>
+      </c>
+      <c r="C236" t="n">
+        <v>115.7728384249456</v>
+      </c>
+      <c r="D236" t="n">
+        <v>112.011838131802</v>
+      </c>
+      <c r="E236" t="n">
+        <v>115.7329330444336</v>
+      </c>
+      <c r="F236" t="n">
+        <v>22054700</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>115.8925486214695</v>
+      </c>
+      <c r="C237" t="n">
+        <v>116.0421918977476</v>
+      </c>
+      <c r="D237" t="n">
+        <v>114.5357961092488</v>
+      </c>
+      <c r="E237" t="n">
+        <v>115.4436264038086</v>
+      </c>
+      <c r="F237" t="n">
+        <v>16822200</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>115.3837731369623</v>
+      </c>
+      <c r="C238" t="n">
+        <v>116.1718796839166</v>
+      </c>
+      <c r="D238" t="n">
+        <v>114.3662049383982</v>
+      </c>
+      <c r="E238" t="n">
+        <v>114.9946975708008</v>
+      </c>
+      <c r="F238" t="n">
+        <v>14520000</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>114.0569458007812</v>
+      </c>
+      <c r="C239" t="n">
+        <v>114.9049142110052</v>
+      </c>
+      <c r="D239" t="n">
+        <v>113.6479213564676</v>
+      </c>
+      <c r="E239" t="n">
+        <v>114.0569458007812</v>
+      </c>
+      <c r="F239" t="n">
+        <v>18131100</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>116.0222446904477</v>
+      </c>
+      <c r="C240" t="n">
+        <v>116.0322153274834</v>
+      </c>
+      <c r="D240" t="n">
+        <v>114.2065916862473</v>
+      </c>
+      <c r="E240" t="n">
+        <v>114.9248657226562</v>
+      </c>
+      <c r="F240" t="n">
+        <v>20675000</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>114.9148971425914</v>
+      </c>
+      <c r="C241" t="n">
+        <v>116.590885146559</v>
+      </c>
+      <c r="D241" t="n">
+        <v>113.7177585048011</v>
+      </c>
+      <c r="E241" t="n">
+        <v>114.0270233154297</v>
+      </c>
+      <c r="F241" t="n">
+        <v>34286600</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>106.1259298697332</v>
+      </c>
+      <c r="C242" t="n">
+        <v>106.7444518635443</v>
+      </c>
+      <c r="D242" t="n">
+        <v>102.6043617877236</v>
+      </c>
+      <c r="E242" t="n">
+        <v>103.5919952392578</v>
+      </c>
+      <c r="F242" t="n">
+        <v>83633100</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>103.6900024414062</v>
+      </c>
+      <c r="C243" t="n">
+        <v>104.2799987792969</v>
+      </c>
+      <c r="D243" t="n">
+        <v>102.1500015258789</v>
+      </c>
+      <c r="E243" t="n">
+        <v>103.6999969482422</v>
+      </c>
+      <c r="F243" t="n">
+        <v>44454200</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>104.1399993896484</v>
+      </c>
+      <c r="C244" t="n">
+        <v>106.5999984741211</v>
+      </c>
+      <c r="D244" t="n">
+        <v>104</v>
+      </c>
+      <c r="E244" t="n">
+        <v>106.4899978637695</v>
+      </c>
+      <c r="F244" t="n">
+        <v>35616300</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>105.5800018310547</v>
+      </c>
+      <c r="C245" t="n">
+        <v>106.0699996948242</v>
+      </c>
+      <c r="D245" t="n">
+        <v>104.4000015258789</v>
+      </c>
+      <c r="E245" t="n">
+        <v>105.379997253418</v>
+      </c>
+      <c r="F245" t="n">
+        <v>27032500</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>105.5100021362305</v>
+      </c>
+      <c r="C246" t="n">
+        <v>106.0899963378906</v>
+      </c>
+      <c r="D246" t="n">
+        <v>104.0800018310547</v>
+      </c>
+      <c r="E246" t="n">
+        <v>104.3399963378906</v>
+      </c>
+      <c r="F246" t="n">
+        <v>28409400</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>103.6100006103516</v>
+      </c>
+      <c r="C247" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="D247" t="n">
+        <v>102.2699966430664</v>
+      </c>
+      <c r="E247" t="n">
+        <v>102.629997253418</v>
+      </c>
+      <c r="F247" t="n">
+        <v>29816600</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>103.0899963378906</v>
+      </c>
+      <c r="C248" t="n">
+        <v>103.4000015258789</v>
+      </c>
+      <c r="D248" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="E248" t="n">
+        <v>103.0899963378906</v>
+      </c>
+      <c r="F248" t="n">
+        <v>19420800</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>103.0800018310547</v>
+      </c>
+      <c r="C249" t="n">
+        <v>104.9899978637695</v>
+      </c>
+      <c r="D249" t="n">
+        <v>102.8399963378906</v>
+      </c>
+      <c r="E249" t="n">
+        <v>104.870002746582</v>
+      </c>
+      <c r="F249" t="n">
+        <v>34188700</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>105.1100006103516</v>
+      </c>
+      <c r="C250" t="n">
+        <v>106.6399993896484</v>
+      </c>
+      <c r="D250" t="n">
+        <v>104.6600036621094</v>
+      </c>
+      <c r="E250" t="n">
+        <v>105.9199981689453</v>
+      </c>
+      <c r="F250" t="n">
+        <v>22074600</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>105.9700012207031</v>
+      </c>
+      <c r="C251" t="n">
+        <v>106.7799987792969</v>
+      </c>
+      <c r="D251" t="n">
+        <v>105.4599990844727</v>
+      </c>
+      <c r="E251" t="n">
+        <v>106.0899963378906</v>
+      </c>
+      <c r="F251" t="n">
+        <v>25181800</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>106.4199981689453</v>
+      </c>
+      <c r="C252" t="n">
+        <v>109.3499984741211</v>
+      </c>
+      <c r="D252" t="n">
+        <v>106.0199966430664</v>
+      </c>
+      <c r="E252" t="n">
+        <v>108.4199981689453</v>
+      </c>
+      <c r="F252" t="n">
+        <v>25541200</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>108.1999969482422</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>109.2300033569336</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>106.9300003051758</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>107.1399993896484</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>20527200</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4723,7 +10677,7 @@
         <v>106.935</v>
       </c>
       <c r="H2" t="n">
-        <v>19188931</v>
+        <v>20540472</v>
       </c>
       <c r="I2" t="n">
         <v>24355206</v>
@@ -4813,7 +10767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:42</t>
+          <t>2026-09-07 03:08:33</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -576,16 +576,16 @@
         <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>100.1468020683853</v>
+        <v>100.1468095744012</v>
       </c>
       <c r="C6" t="n">
-        <v>101.9218577291584</v>
+        <v>101.9218653682149</v>
       </c>
       <c r="D6" t="n">
-        <v>99.44273097931239</v>
+        <v>99.44273843255802</v>
       </c>
       <c r="E6" t="n">
-        <v>101.7929458618164</v>
+        <v>101.7929534912109</v>
       </c>
       <c r="F6" t="n">
         <v>15900800</v>
@@ -602,16 +602,16 @@
         <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>101.6838580700448</v>
+        <v>101.6838656294045</v>
       </c>
       <c r="C7" t="n">
-        <v>103.111837420202</v>
+        <v>103.1118450857203</v>
       </c>
       <c r="D7" t="n">
-        <v>101.5053606512752</v>
+        <v>101.5053681973651</v>
       </c>
       <c r="E7" t="n">
-        <v>102.6259231567383</v>
+        <v>102.6259307861328</v>
       </c>
       <c r="F7" t="n">
         <v>11641900</v>
@@ -654,16 +654,16 @@
         <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>102.9829210178903</v>
+        <v>102.9829286790064</v>
       </c>
       <c r="C9" t="n">
-        <v>103.3399158659111</v>
+        <v>103.3399235535848</v>
       </c>
       <c r="D9" t="n">
-        <v>102.2689313218488</v>
+        <v>102.2689389298496</v>
       </c>
       <c r="E9" t="n">
-        <v>102.556510925293</v>
+        <v>102.5565185546875</v>
       </c>
       <c r="F9" t="n">
         <v>14481900</v>
@@ -758,16 +758,16 @@
         <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>101.5946114796781</v>
+        <v>101.5946038777383</v>
       </c>
       <c r="C13" t="n">
-        <v>102.3383495068081</v>
+        <v>102.3383418492172</v>
       </c>
       <c r="D13" t="n">
-        <v>101.069037817684</v>
+        <v>101.0690302550709</v>
       </c>
       <c r="E13" t="n">
-        <v>101.9615249633789</v>
+        <v>101.9615173339844</v>
       </c>
       <c r="F13" t="n">
         <v>12861900</v>
@@ -784,16 +784,16 @@
         <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>101.5549649811181</v>
+        <v>101.5549573599091</v>
       </c>
       <c r="C14" t="n">
-        <v>101.8227073759147</v>
+        <v>101.822699734613</v>
       </c>
       <c r="D14" t="n">
-        <v>100.4839802705406</v>
+        <v>100.4839727297038</v>
       </c>
       <c r="E14" t="n">
-        <v>101.6640396118164</v>
+        <v>101.6640319824219</v>
       </c>
       <c r="F14" t="n">
         <v>13158700</v>
@@ -810,16 +810,16 @@
         <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>102.1796932441854</v>
+        <v>102.1796855917684</v>
       </c>
       <c r="C15" t="n">
-        <v>102.606103365375</v>
+        <v>102.6060956810235</v>
       </c>
       <c r="D15" t="n">
-        <v>101.6243712503365</v>
+        <v>101.6243636395086</v>
       </c>
       <c r="E15" t="n">
-        <v>101.8722839355469</v>
+        <v>101.8722763061523</v>
       </c>
       <c r="F15" t="n">
         <v>11391800</v>
@@ -836,16 +836,16 @@
         <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>102.3581921548903</v>
+        <v>102.3581845129098</v>
       </c>
       <c r="C16" t="n">
-        <v>102.645771781761</v>
+        <v>102.64576411831</v>
       </c>
       <c r="D16" t="n">
-        <v>101.7235362768635</v>
+        <v>101.7235286822659</v>
       </c>
       <c r="E16" t="n">
-        <v>102.1896133422852</v>
+        <v>102.1896057128906</v>
       </c>
       <c r="F16" t="n">
         <v>13366700</v>
@@ -888,16 +888,16 @@
         <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>102.1896196669732</v>
+        <v>102.189612039799</v>
       </c>
       <c r="C18" t="n">
-        <v>102.4474434319635</v>
+        <v>102.447435785546</v>
       </c>
       <c r="D18" t="n">
-        <v>101.2277171644534</v>
+        <v>101.2277096090732</v>
       </c>
       <c r="E18" t="n">
-        <v>102.219367980957</v>
+        <v>102.2193603515625</v>
       </c>
       <c r="F18" t="n">
         <v>15477200</v>
@@ -940,16 +940,16 @@
         <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>101.7036925151355</v>
+        <v>101.7037001894263</v>
       </c>
       <c r="C20" t="n">
-        <v>102.0011907489098</v>
+        <v>102.001198445649</v>
       </c>
       <c r="D20" t="n">
-        <v>99.71048007220848</v>
+        <v>99.71048759609677</v>
       </c>
       <c r="E20" t="n">
-        <v>101.1087036132812</v>
+        <v>101.1087112426758</v>
       </c>
       <c r="F20" t="n">
         <v>16142800</v>
@@ -966,16 +966,16 @@
         <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>100.6029707835176</v>
+        <v>100.6029631728777</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2872122575589</v>
+        <v>101.287204595156</v>
       </c>
       <c r="D21" t="n">
-        <v>99.036168267113</v>
+        <v>99.03616077500212</v>
       </c>
       <c r="E21" t="n">
-        <v>100.8508834838867</v>
+        <v>100.8508758544922</v>
       </c>
       <c r="F21" t="n">
         <v>15605400</v>
@@ -1070,16 +1070,16 @@
         <v>45938</v>
       </c>
       <c r="B25" t="n">
-        <v>102.1598562843055</v>
+        <v>102.1598486460141</v>
       </c>
       <c r="C25" t="n">
-        <v>102.3978579100873</v>
+        <v>102.397850254001</v>
       </c>
       <c r="D25" t="n">
-        <v>101.2971249793545</v>
+        <v>101.2971174055678</v>
       </c>
       <c r="E25" t="n">
-        <v>102.0408630371094</v>
+        <v>102.0408554077148</v>
       </c>
       <c r="F25" t="n">
         <v>13584100</v>
@@ -1174,16 +1174,16 @@
         <v>45944</v>
       </c>
       <c r="B29" t="n">
-        <v>103.1812529973676</v>
+        <v>103.1812604018871</v>
       </c>
       <c r="C29" t="n">
-        <v>107.01893616482</v>
+        <v>107.0189438447403</v>
       </c>
       <c r="D29" t="n">
-        <v>102.0309346136339</v>
+        <v>102.030941935604</v>
       </c>
       <c r="E29" t="n">
-        <v>106.3148651123047</v>
+        <v>106.3148727416992</v>
       </c>
       <c r="F29" t="n">
         <v>30859500</v>
@@ -1252,16 +1252,16 @@
         <v>45947</v>
       </c>
       <c r="B32" t="n">
-        <v>106.2752063382308</v>
+        <v>106.2751987484956</v>
       </c>
       <c r="C32" t="n">
-        <v>107.2966053740443</v>
+        <v>107.2965977113651</v>
       </c>
       <c r="D32" t="n">
-        <v>105.3331411761509</v>
+        <v>105.3331336536941</v>
       </c>
       <c r="E32" t="n">
-        <v>106.8305358886719</v>
+        <v>106.8305282592773</v>
       </c>
       <c r="F32" t="n">
         <v>13735600</v>
@@ -1408,16 +1408,16 @@
         <v>45957</v>
       </c>
       <c r="B38" t="n">
-        <v>105.452129733232</v>
+        <v>105.4521374991914</v>
       </c>
       <c r="C38" t="n">
-        <v>105.4719669836308</v>
+        <v>105.4719747510511</v>
       </c>
       <c r="D38" t="n">
-        <v>103.280419887601</v>
+        <v>103.2804274936261</v>
       </c>
       <c r="E38" t="n">
-        <v>103.5977478027344</v>
+        <v>103.5977554321289</v>
       </c>
       <c r="F38" t="n">
         <v>16375900</v>
@@ -1512,16 +1512,16 @@
         <v>45961</v>
       </c>
       <c r="B42" t="n">
-        <v>100.8508753833576</v>
+        <v>100.8508830519621</v>
       </c>
       <c r="C42" t="n">
-        <v>101.2475371852267</v>
+        <v>101.2475448839929</v>
       </c>
       <c r="D42" t="n">
-        <v>99.34356961508874</v>
+        <v>99.3435771690791</v>
       </c>
       <c r="E42" t="n">
-        <v>100.3352203369141</v>
+        <v>100.3352279663086</v>
       </c>
       <c r="F42" t="n">
         <v>20237000</v>
@@ -1564,16 +1564,16 @@
         <v>45965</v>
       </c>
       <c r="B44" t="n">
-        <v>101.2772919319017</v>
+        <v>101.2772843129512</v>
       </c>
       <c r="C44" t="n">
-        <v>101.763206263773</v>
+        <v>101.7631986082678</v>
       </c>
       <c r="D44" t="n">
-        <v>100.6128877218267</v>
+        <v>100.6128801528584</v>
       </c>
       <c r="E44" t="n">
-        <v>101.4161224365234</v>
+        <v>101.4161148071289</v>
       </c>
       <c r="F44" t="n">
         <v>12636400</v>
@@ -1798,16 +1798,16 @@
         <v>45978</v>
       </c>
       <c r="B53" t="n">
-        <v>101.7235329175373</v>
+        <v>101.7235405195123</v>
       </c>
       <c r="C53" t="n">
-        <v>102.4573523337042</v>
+        <v>102.4573599905188</v>
       </c>
       <c r="D53" t="n">
-        <v>101.2475372418891</v>
+        <v>101.2475448082921</v>
       </c>
       <c r="E53" t="n">
-        <v>102.0904388427734</v>
+        <v>102.090446472168</v>
       </c>
       <c r="F53" t="n">
         <v>15289400</v>
@@ -1876,16 +1876,16 @@
         <v>45981</v>
       </c>
       <c r="B56" t="n">
-        <v>103.0721824077765</v>
+        <v>103.0721750041795</v>
       </c>
       <c r="C56" t="n">
-        <v>107.0090371351957</v>
+        <v>107.0090294488173</v>
       </c>
       <c r="D56" t="n">
-        <v>101.8227003318746</v>
+        <v>101.8226930180269</v>
       </c>
       <c r="E56" t="n">
-        <v>106.2157135009766</v>
+        <v>106.215705871582</v>
       </c>
       <c r="F56" t="n">
         <v>50375900</v>
@@ -1928,16 +1928,16 @@
         <v>45985</v>
       </c>
       <c r="B58" t="n">
-        <v>104.4803186790174</v>
+        <v>104.4803264037246</v>
       </c>
       <c r="C58" t="n">
-        <v>105.3827168846354</v>
+        <v>105.382724676061</v>
       </c>
       <c r="D58" t="n">
-        <v>102.89367906727</v>
+        <v>102.8936866746697</v>
       </c>
       <c r="E58" t="n">
-        <v>103.1911697387695</v>
+        <v>103.1911773681641</v>
       </c>
       <c r="F58" t="n">
         <v>42519200</v>
@@ -1954,16 +1954,16 @@
         <v>45986</v>
       </c>
       <c r="B59" t="n">
-        <v>103.7365763126644</v>
+        <v>103.7365837716454</v>
       </c>
       <c r="C59" t="n">
-        <v>106.5231122506693</v>
+        <v>106.5231199100109</v>
       </c>
       <c r="D59" t="n">
-        <v>103.3597517849156</v>
+        <v>103.3597592168018</v>
       </c>
       <c r="E59" t="n">
-        <v>106.1066207885742</v>
+        <v>106.1066284179688</v>
       </c>
       <c r="F59" t="n">
         <v>20212900</v>
@@ -1980,16 +1980,16 @@
         <v>45987</v>
       </c>
       <c r="B60" t="n">
-        <v>106.3049641152269</v>
+        <v>106.3049566187</v>
       </c>
       <c r="C60" t="n">
-        <v>108.6750089527716</v>
+        <v>108.6750012891114</v>
       </c>
       <c r="D60" t="n">
-        <v>106.2752158013515</v>
+        <v>106.2752083069225</v>
       </c>
       <c r="E60" t="n">
-        <v>108.1891021728516</v>
+        <v>108.189094543457</v>
       </c>
       <c r="F60" t="n">
         <v>17783300</v>
@@ -2188,16 +2188,16 @@
         <v>46000</v>
       </c>
       <c r="B68" t="n">
-        <v>112.9985942054707</v>
+        <v>112.9986017612633</v>
       </c>
       <c r="C68" t="n">
-        <v>114.7538201807431</v>
+        <v>114.7538278539011</v>
       </c>
       <c r="D68" t="n">
-        <v>112.0763587521143</v>
+        <v>112.0763662462405</v>
       </c>
       <c r="E68" t="n">
-        <v>114.0993270874023</v>
+        <v>114.0993347167969</v>
       </c>
       <c r="F68" t="n">
         <v>24326700</v>
@@ -10689,7 +10689,7 @@
         <v>38.81884</v>
       </c>
       <c r="L2" t="n">
-        <v>33.16032</v>
+        <v>33.167812</v>
       </c>
       <c r="M2" t="n">
         <v>2.76</v>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:33</t>
+          <t>2026-09-08 08:52:24</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>100.2360551135878</v>
+        <v>101.1483716213974</v>
       </c>
       <c r="C2" t="n">
-        <v>100.6327169088708</v>
+        <v>101.6342783470665</v>
       </c>
       <c r="D2" t="n">
-        <v>98.71883074489759</v>
+        <v>100.7021318316984</v>
       </c>
       <c r="E2" t="n">
-        <v>99.67081451416016</v>
+        <v>101.4359512329102</v>
       </c>
       <c r="F2" t="n">
-        <v>13748500</v>
+        <v>11819700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>100.0079722075202</v>
+        <v>101.0987907680863</v>
       </c>
       <c r="C3" t="n">
-        <v>101.5053668922825</v>
+        <v>101.5946161422617</v>
       </c>
       <c r="D3" t="n">
-        <v>99.5815621012248</v>
+        <v>99.5518180216814</v>
       </c>
       <c r="E3" t="n">
-        <v>101.4260330200195</v>
+        <v>99.5716552734375</v>
       </c>
       <c r="F3" t="n">
-        <v>13685700</v>
+        <v>17934900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>101.1483716213974</v>
+        <v>100.1468095744012</v>
       </c>
       <c r="C4" t="n">
-        <v>101.6342783470665</v>
+        <v>101.9218653682149</v>
       </c>
       <c r="D4" t="n">
-        <v>100.7021318316984</v>
+        <v>99.44273843255802</v>
       </c>
       <c r="E4" t="n">
-        <v>101.4359512329102</v>
+        <v>101.7929534912109</v>
       </c>
       <c r="F4" t="n">
-        <v>11819700</v>
+        <v>15900800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>101.0987907680863</v>
+        <v>101.6838731887643</v>
       </c>
       <c r="C5" t="n">
-        <v>101.5946161422617</v>
+        <v>103.1118527512385</v>
       </c>
       <c r="D5" t="n">
-        <v>99.5518180216814</v>
+        <v>101.505375743455</v>
       </c>
       <c r="E5" t="n">
-        <v>99.5716552734375</v>
+        <v>102.6259384155273</v>
       </c>
       <c r="F5" t="n">
-        <v>17934900</v>
+        <v>11641900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>100.1468095744012</v>
+        <v>102.7845975900895</v>
       </c>
       <c r="C6" t="n">
-        <v>101.9218653682149</v>
+        <v>103.1118441401098</v>
       </c>
       <c r="D6" t="n">
-        <v>99.44273843255802</v>
+        <v>102.5466035381176</v>
       </c>
       <c r="E6" t="n">
-        <v>101.7929534912109</v>
+        <v>102.8242645263672</v>
       </c>
       <c r="F6" t="n">
-        <v>15900800</v>
+        <v>10756900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>101.6838656294045</v>
+        <v>102.9829286790064</v>
       </c>
       <c r="C7" t="n">
-        <v>103.1118450857203</v>
+        <v>103.3399235535848</v>
       </c>
       <c r="D7" t="n">
-        <v>101.5053681973651</v>
+        <v>102.2689389298496</v>
       </c>
       <c r="E7" t="n">
-        <v>102.6259307861328</v>
+        <v>102.5565185546875</v>
       </c>
       <c r="F7" t="n">
-        <v>11641900</v>
+        <v>14481900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>102.7845975900895</v>
+        <v>102.8639293479953</v>
       </c>
       <c r="C8" t="n">
-        <v>103.1118441401098</v>
+        <v>105.2240552652924</v>
       </c>
       <c r="D8" t="n">
-        <v>102.5466035381176</v>
+        <v>102.8639293479953</v>
       </c>
       <c r="E8" t="n">
-        <v>102.8242645263672</v>
+        <v>103.3994140625</v>
       </c>
       <c r="F8" t="n">
-        <v>10756900</v>
+        <v>25382000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>102.9829286790064</v>
+        <v>102.9135133062164</v>
       </c>
       <c r="C9" t="n">
-        <v>103.3399235535848</v>
+        <v>103.7663335538345</v>
       </c>
       <c r="D9" t="n">
-        <v>102.2689389298496</v>
+        <v>101.2673770004686</v>
       </c>
       <c r="E9" t="n">
-        <v>102.5565185546875</v>
+        <v>102.7350158691406</v>
       </c>
       <c r="F9" t="n">
-        <v>14481900</v>
+        <v>14869400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>102.8639369378787</v>
+        <v>102.9432629724532</v>
       </c>
       <c r="C10" t="n">
-        <v>105.2240630293193</v>
+        <v>103.0721824132953</v>
       </c>
       <c r="D10" t="n">
-        <v>102.8639369378787</v>
+        <v>101.2376224547773</v>
       </c>
       <c r="E10" t="n">
-        <v>103.3994216918945</v>
+        <v>101.4756240844727</v>
       </c>
       <c r="F10" t="n">
-        <v>25382000</v>
+        <v>34791600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>102.9135133062164</v>
+        <v>101.5946114796781</v>
       </c>
       <c r="C11" t="n">
-        <v>103.7663335538345</v>
+        <v>102.3383495068081</v>
       </c>
       <c r="D11" t="n">
-        <v>101.2673770004686</v>
+        <v>101.069037817684</v>
       </c>
       <c r="E11" t="n">
-        <v>102.7350158691406</v>
+        <v>101.9615249633789</v>
       </c>
       <c r="F11" t="n">
-        <v>14869400</v>
+        <v>12861900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>102.9432629724532</v>
+        <v>101.5549573599091</v>
       </c>
       <c r="C12" t="n">
-        <v>103.0721824132953</v>
+        <v>101.822699734613</v>
       </c>
       <c r="D12" t="n">
-        <v>101.2376224547773</v>
+        <v>100.4839727297038</v>
       </c>
       <c r="E12" t="n">
-        <v>101.4756240844727</v>
+        <v>101.6640319824219</v>
       </c>
       <c r="F12" t="n">
-        <v>34791600</v>
+        <v>13158700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>101.5946038777383</v>
+        <v>102.1796855917684</v>
       </c>
       <c r="C13" t="n">
-        <v>102.3383418492172</v>
+        <v>102.6060956810235</v>
       </c>
       <c r="D13" t="n">
-        <v>101.0690302550709</v>
+        <v>101.6243636395086</v>
       </c>
       <c r="E13" t="n">
-        <v>101.9615173339844</v>
+        <v>101.8722763061523</v>
       </c>
       <c r="F13" t="n">
-        <v>12861900</v>
+        <v>11391800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>101.5549573599091</v>
+        <v>102.3581921548903</v>
       </c>
       <c r="C14" t="n">
-        <v>101.822699734613</v>
+        <v>102.645771781761</v>
       </c>
       <c r="D14" t="n">
-        <v>100.4839727297038</v>
+        <v>101.7235362768635</v>
       </c>
       <c r="E14" t="n">
-        <v>101.6640319824219</v>
+        <v>102.1896133422852</v>
       </c>
       <c r="F14" t="n">
-        <v>13158700</v>
+        <v>13366700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>102.1796855917684</v>
+        <v>102.0210222421301</v>
       </c>
       <c r="C15" t="n">
-        <v>102.6060956810235</v>
+        <v>102.6259297800171</v>
       </c>
       <c r="D15" t="n">
-        <v>101.6243636395086</v>
+        <v>101.6144493855062</v>
       </c>
       <c r="E15" t="n">
-        <v>101.8722763061523</v>
+        <v>102.2986907958984</v>
       </c>
       <c r="F15" t="n">
-        <v>11391800</v>
+        <v>11859300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>102.3581845129098</v>
+        <v>102.189612039799</v>
       </c>
       <c r="C16" t="n">
-        <v>102.64576411831</v>
+        <v>102.447435785546</v>
       </c>
       <c r="D16" t="n">
-        <v>101.7235286822659</v>
+        <v>101.2277096090732</v>
       </c>
       <c r="E16" t="n">
-        <v>102.1896057128906</v>
+        <v>102.2193603515625</v>
       </c>
       <c r="F16" t="n">
-        <v>13366700</v>
+        <v>15477200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>102.0210298508162</v>
+        <v>102.1400273017734</v>
       </c>
       <c r="C17" t="n">
-        <v>102.625937433817</v>
+        <v>103.0721814282683</v>
       </c>
       <c r="D17" t="n">
-        <v>101.6144569638703</v>
+        <v>101.8623663021439</v>
       </c>
       <c r="E17" t="n">
-        <v>102.298698425293</v>
+        <v>102.1995239257812</v>
       </c>
       <c r="F17" t="n">
-        <v>11859300</v>
+        <v>13873400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>102.189612039799</v>
+        <v>101.7037001894263</v>
       </c>
       <c r="C18" t="n">
-        <v>102.447435785546</v>
+        <v>102.001198445649</v>
       </c>
       <c r="D18" t="n">
-        <v>101.2277096090732</v>
+        <v>99.71048759609677</v>
       </c>
       <c r="E18" t="n">
-        <v>102.2193603515625</v>
+        <v>101.1087112426758</v>
       </c>
       <c r="F18" t="n">
-        <v>15477200</v>
+        <v>16142800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>102.1400273017734</v>
+        <v>100.6029631728777</v>
       </c>
       <c r="C19" t="n">
-        <v>103.0721814282683</v>
+        <v>101.287204595156</v>
       </c>
       <c r="D19" t="n">
-        <v>101.8623663021439</v>
+        <v>99.03616077500212</v>
       </c>
       <c r="E19" t="n">
-        <v>102.1995239257812</v>
+        <v>100.8508758544922</v>
       </c>
       <c r="F19" t="n">
-        <v>13873400</v>
+        <v>15605400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>101.7037001894263</v>
+        <v>100.6128811517826</v>
       </c>
       <c r="C20" t="n">
-        <v>102.001198445649</v>
+        <v>101.9615267363516</v>
       </c>
       <c r="D20" t="n">
-        <v>99.71048759609677</v>
+        <v>100.3550498461664</v>
       </c>
       <c r="E20" t="n">
-        <v>101.1087112426758</v>
+        <v>101.2177886962891</v>
       </c>
       <c r="F20" t="n">
-        <v>16142800</v>
+        <v>11867500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>100.6029631728777</v>
+        <v>101.0293759821222</v>
       </c>
       <c r="C21" t="n">
-        <v>101.287204595156</v>
+        <v>102.2094427990993</v>
       </c>
       <c r="D21" t="n">
-        <v>99.03616077500212</v>
+        <v>100.7318852956682</v>
       </c>
       <c r="E21" t="n">
-        <v>100.8508758544922</v>
+        <v>101.842529296875</v>
       </c>
       <c r="F21" t="n">
-        <v>15605400</v>
+        <v>13303600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>100.6128811517826</v>
+        <v>101.5252009905733</v>
       </c>
       <c r="C22" t="n">
-        <v>101.9615267363516</v>
+        <v>102.387939866122</v>
       </c>
       <c r="D22" t="n">
-        <v>100.3550498461664</v>
+        <v>100.1071401164341</v>
       </c>
       <c r="E22" t="n">
-        <v>101.2177886962891</v>
+        <v>102.3780212402344</v>
       </c>
       <c r="F22" t="n">
-        <v>11867500</v>
+        <v>15538900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>101.029368413644</v>
+        <v>102.1598486460141</v>
       </c>
       <c r="C23" t="n">
-        <v>102.2094351422179</v>
+        <v>102.397850254001</v>
       </c>
       <c r="D23" t="n">
-        <v>100.731877749476</v>
+        <v>101.2971174055678</v>
       </c>
       <c r="E23" t="n">
-        <v>101.8425216674805</v>
+        <v>102.0408554077148</v>
       </c>
       <c r="F23" t="n">
-        <v>13303600</v>
+        <v>13584100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>101.5252009905733</v>
+        <v>102.2689336388612</v>
       </c>
       <c r="C24" t="n">
-        <v>102.387939866122</v>
+        <v>102.5862615592142</v>
       </c>
       <c r="D24" t="n">
-        <v>100.1071401164341</v>
+        <v>99.53198316295229</v>
       </c>
       <c r="E24" t="n">
-        <v>102.3780212402344</v>
+        <v>100.9202880859375</v>
       </c>
       <c r="F24" t="n">
-        <v>15538900</v>
+        <v>19508000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>102.1598486460141</v>
+        <v>101.1979612604356</v>
       </c>
       <c r="C25" t="n">
-        <v>102.397850254001</v>
+        <v>102.7647636830698</v>
       </c>
       <c r="D25" t="n">
-        <v>101.2971174055678</v>
+        <v>100.6723800119242</v>
       </c>
       <c r="E25" t="n">
-        <v>102.0408554077148</v>
+        <v>100.9897079467773</v>
       </c>
       <c r="F25" t="n">
-        <v>13584100</v>
+        <v>18519400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>102.2689413702109</v>
+        <v>100.523634106908</v>
       </c>
       <c r="C26" t="n">
-        <v>102.5862693145533</v>
+        <v>101.5946111121733</v>
       </c>
       <c r="D26" t="n">
-        <v>99.53199068739345</v>
+        <v>100.2261358708544</v>
       </c>
       <c r="E26" t="n">
-        <v>100.920295715332</v>
+        <v>101.2673721313477</v>
       </c>
       <c r="F26" t="n">
-        <v>19508000</v>
+        <v>10871200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>101.1979536153083</v>
+        <v>103.1812529973676</v>
       </c>
       <c r="C27" t="n">
-        <v>102.7647559195764</v>
+        <v>107.01893616482</v>
       </c>
       <c r="D27" t="n">
-        <v>100.6723724065026</v>
+        <v>102.0309346136339</v>
       </c>
       <c r="E27" t="n">
-        <v>100.9897003173828</v>
+        <v>106.3148651123047</v>
       </c>
       <c r="F27" t="n">
-        <v>18519400</v>
+        <v>30859500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>100.523634106908</v>
+        <v>106.4239528923693</v>
       </c>
       <c r="C28" t="n">
-        <v>101.5946111121733</v>
+        <v>108.6452483434567</v>
       </c>
       <c r="D28" t="n">
-        <v>100.2261358708544</v>
+        <v>106.4041232072616</v>
       </c>
       <c r="E28" t="n">
-        <v>101.2673721313477</v>
+        <v>108.1196746826172</v>
       </c>
       <c r="F28" t="n">
-        <v>10871200</v>
+        <v>21416300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>103.1812604018871</v>
+        <v>108.288256950121</v>
       </c>
       <c r="C29" t="n">
-        <v>107.0189438447403</v>
+        <v>108.6650890704717</v>
       </c>
       <c r="D29" t="n">
-        <v>102.030941935604</v>
+        <v>104.7778200152908</v>
       </c>
       <c r="E29" t="n">
-        <v>106.3148727416992</v>
+        <v>105.5810546875</v>
       </c>
       <c r="F29" t="n">
-        <v>30859500</v>
+        <v>16366200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>106.4239604021063</v>
+        <v>106.2752063382308</v>
       </c>
       <c r="C30" t="n">
-        <v>108.645256009938</v>
+        <v>107.2966053740443</v>
       </c>
       <c r="D30" t="n">
-        <v>106.4041307155994</v>
+        <v>105.3331411761509</v>
       </c>
       <c r="E30" t="n">
-        <v>108.1196823120117</v>
+        <v>106.8305358886719</v>
       </c>
       <c r="F30" t="n">
-        <v>21416300</v>
+        <v>13735600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>108.2882647751407</v>
+        <v>106.9495278840114</v>
       </c>
       <c r="C31" t="n">
-        <v>108.6650969227217</v>
+        <v>107.3461896823507</v>
       </c>
       <c r="D31" t="n">
-        <v>104.7778275866427</v>
+        <v>105.7198831182847</v>
       </c>
       <c r="E31" t="n">
-        <v>105.5810623168945</v>
+        <v>106.1562118530273</v>
       </c>
       <c r="F31" t="n">
-        <v>16366200</v>
+        <v>10581200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>106.2751987484956</v>
+        <v>106.4338780925878</v>
       </c>
       <c r="C32" t="n">
-        <v>107.2965977113651</v>
+        <v>106.5826272200147</v>
       </c>
       <c r="D32" t="n">
-        <v>105.3331336536941</v>
+        <v>105.2934782032414</v>
       </c>
       <c r="E32" t="n">
-        <v>106.8305282592773</v>
+        <v>105.3331451416016</v>
       </c>
       <c r="F32" t="n">
-        <v>13735600</v>
+        <v>10899700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>106.9495278840114</v>
+        <v>105.6603902006062</v>
       </c>
       <c r="C33" t="n">
-        <v>107.3461896823507</v>
+        <v>106.8701977576955</v>
       </c>
       <c r="D33" t="n">
-        <v>105.7198831182847</v>
+        <v>104.7778216403512</v>
       </c>
       <c r="E33" t="n">
-        <v>106.1562118530273</v>
+        <v>106.2454605102539</v>
       </c>
       <c r="F33" t="n">
-        <v>10581200</v>
+        <v>12296500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>106.4338780925878</v>
+        <v>106.4537107234644</v>
       </c>
       <c r="C34" t="n">
-        <v>106.5826272200147</v>
+        <v>106.6718751076324</v>
       </c>
       <c r="D34" t="n">
-        <v>105.2934782032414</v>
+        <v>104.8968192868145</v>
       </c>
       <c r="E34" t="n">
-        <v>105.3331451416016</v>
+        <v>105.9678039550781</v>
       </c>
       <c r="F34" t="n">
-        <v>10899700</v>
+        <v>11408200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>105.6603902006062</v>
+        <v>106.1760412293909</v>
       </c>
       <c r="C35" t="n">
-        <v>106.8701977576955</v>
+        <v>106.2752047872635</v>
       </c>
       <c r="D35" t="n">
-        <v>104.7778216403512</v>
+        <v>104.6290685426336</v>
       </c>
       <c r="E35" t="n">
-        <v>106.2454605102539</v>
+        <v>105.2835540771484</v>
       </c>
       <c r="F35" t="n">
-        <v>12296500</v>
+        <v>10318000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>106.4537107234644</v>
+        <v>105.4521374991914</v>
       </c>
       <c r="C36" t="n">
-        <v>106.6718751076324</v>
+        <v>105.4719747510511</v>
       </c>
       <c r="D36" t="n">
-        <v>104.8968192868145</v>
+        <v>103.2804274936261</v>
       </c>
       <c r="E36" t="n">
-        <v>105.9678039550781</v>
+        <v>103.5977554321289</v>
       </c>
       <c r="F36" t="n">
-        <v>11408200</v>
+        <v>16375900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>106.1760412293909</v>
+        <v>103.1911775964564</v>
       </c>
       <c r="C37" t="n">
-        <v>106.2752047872635</v>
+        <v>103.2705114745084</v>
       </c>
       <c r="D37" t="n">
-        <v>104.6290685426336</v>
+        <v>102.1896157574061</v>
       </c>
       <c r="E37" t="n">
-        <v>105.2835540771484</v>
+        <v>102.3086090087891</v>
       </c>
       <c r="F37" t="n">
-        <v>10318000</v>
+        <v>13323000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>105.4521374991914</v>
+        <v>102.0507853540776</v>
       </c>
       <c r="C38" t="n">
-        <v>105.4719747510511</v>
+        <v>102.8044344992282</v>
       </c>
       <c r="D38" t="n">
-        <v>103.2804274936261</v>
+        <v>101.2574617041669</v>
       </c>
       <c r="E38" t="n">
-        <v>103.5977554321289</v>
+        <v>101.6045379638672</v>
       </c>
       <c r="F38" t="n">
-        <v>16375900</v>
+        <v>11986400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>103.1911699012466</v>
+        <v>101.3467089644983</v>
       </c>
       <c r="C39" t="n">
-        <v>103.2705037733825</v>
+        <v>102.5069461530686</v>
       </c>
       <c r="D39" t="n">
-        <v>102.1896081368852</v>
+        <v>101.108714890351</v>
       </c>
       <c r="E39" t="n">
-        <v>102.3086013793945</v>
+        <v>101.37646484375</v>
       </c>
       <c r="F39" t="n">
-        <v>13323000</v>
+        <v>14065100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>102.0507853540776</v>
+        <v>100.8508753833576</v>
       </c>
       <c r="C40" t="n">
-        <v>102.8044344992282</v>
+        <v>101.2475371852267</v>
       </c>
       <c r="D40" t="n">
-        <v>101.2574617041669</v>
+        <v>99.34356961508874</v>
       </c>
       <c r="E40" t="n">
-        <v>101.6045379638672</v>
+        <v>100.3352203369141</v>
       </c>
       <c r="F40" t="n">
-        <v>11986400</v>
+        <v>20237000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>101.3467013373431</v>
+        <v>99.97822306298148</v>
       </c>
       <c r="C41" t="n">
-        <v>102.5069384385963</v>
+        <v>100.9500440758614</v>
       </c>
       <c r="D41" t="n">
-        <v>101.1087072811068</v>
+        <v>99.56173158561626</v>
       </c>
       <c r="E41" t="n">
-        <v>101.3764572143555</v>
+        <v>100.7417907714844</v>
       </c>
       <c r="F41" t="n">
-        <v>14065100</v>
+        <v>14811700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>100.8508830519621</v>
+        <v>101.2772843129512</v>
       </c>
       <c r="C42" t="n">
-        <v>101.2475448839929</v>
+        <v>101.7631986082678</v>
       </c>
       <c r="D42" t="n">
-        <v>99.3435771690791</v>
+        <v>100.6128801528584</v>
       </c>
       <c r="E42" t="n">
-        <v>100.3352279663086</v>
+        <v>101.4161148071289</v>
       </c>
       <c r="F42" t="n">
-        <v>20237000</v>
+        <v>12636400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>99.97822306298148</v>
+        <v>100.89054510776</v>
       </c>
       <c r="C43" t="n">
-        <v>100.9500440758614</v>
+        <v>101.8226992330539</v>
       </c>
       <c r="D43" t="n">
-        <v>99.56173158561626</v>
+        <v>100.0079765462054</v>
       </c>
       <c r="E43" t="n">
-        <v>100.7417907714844</v>
+        <v>100.622802734375</v>
       </c>
       <c r="F43" t="n">
-        <v>14811700</v>
+        <v>13356800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>101.2772843129512</v>
+        <v>100.493889477858</v>
       </c>
       <c r="C44" t="n">
-        <v>101.7631986082678</v>
+        <v>101.0789673900592</v>
       </c>
       <c r="D44" t="n">
-        <v>100.6128801528584</v>
+        <v>99.19482933747032</v>
       </c>
       <c r="E44" t="n">
-        <v>101.4161148071289</v>
+        <v>100.8310546875</v>
       </c>
       <c r="F44" t="n">
-        <v>12636400</v>
+        <v>14866000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>100.89054510776</v>
+        <v>101.2772781932102</v>
       </c>
       <c r="C45" t="n">
-        <v>101.8226992330539</v>
+        <v>102.1102686736373</v>
       </c>
       <c r="D45" t="n">
-        <v>100.0079765462054</v>
+        <v>100.8806239856387</v>
       </c>
       <c r="E45" t="n">
-        <v>100.622802734375</v>
+        <v>101.7334365844727</v>
       </c>
       <c r="F45" t="n">
-        <v>13356800</v>
+        <v>17248700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>100.4938818739751</v>
+        <v>101.2971227463208</v>
       </c>
       <c r="C46" t="n">
-        <v>101.0789597419063</v>
+        <v>101.8127777927579</v>
       </c>
       <c r="D46" t="n">
-        <v>99.19482183188099</v>
+        <v>100.7517118230459</v>
       </c>
       <c r="E46" t="n">
-        <v>100.8310470581055</v>
+        <v>101.5648651123047</v>
       </c>
       <c r="F46" t="n">
-        <v>14866000</v>
+        <v>14507600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>101.2772857883956</v>
+        <v>101.6441933036576</v>
       </c>
       <c r="C47" t="n">
-        <v>102.1102763312919</v>
+        <v>102.8738380115709</v>
       </c>
       <c r="D47" t="n">
-        <v>100.8806315510774</v>
+        <v>101.4656958810819</v>
       </c>
       <c r="E47" t="n">
-        <v>101.7334442138672</v>
+        <v>102.5763473510742</v>
       </c>
       <c r="F47" t="n">
-        <v>17248700</v>
+        <v>13182100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>101.297130355603</v>
+        <v>102.4870948569393</v>
       </c>
       <c r="C48" t="n">
-        <v>101.8127854407752</v>
+        <v>102.7350075235336</v>
       </c>
       <c r="D48" t="n">
-        <v>100.7517193913577</v>
+        <v>101.8028610418111</v>
       </c>
       <c r="E48" t="n">
-        <v>101.5648727416992</v>
+        <v>102.5763473510742</v>
       </c>
       <c r="F48" t="n">
-        <v>14507600</v>
+        <v>12084400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>101.6442008637206</v>
+        <v>102.7251048596608</v>
       </c>
       <c r="C49" t="n">
-        <v>102.8738456630921</v>
+        <v>103.062270072778</v>
       </c>
       <c r="D49" t="n">
-        <v>101.4657034278687</v>
+        <v>101.1682133741703</v>
       </c>
       <c r="E49" t="n">
-        <v>102.5763549804688</v>
+        <v>101.6838760375977</v>
       </c>
       <c r="F49" t="n">
-        <v>13182100</v>
+        <v>18088500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>102.4871024796954</v>
+        <v>99.36341173515544</v>
       </c>
       <c r="C50" t="n">
-        <v>102.7350151647289</v>
+        <v>101.6342930802014</v>
       </c>
       <c r="D50" t="n">
-        <v>101.8028686136755</v>
+        <v>98.05443292116557</v>
       </c>
       <c r="E50" t="n">
-        <v>102.5763549804688</v>
+        <v>101.624382019043</v>
       </c>
       <c r="F50" t="n">
-        <v>12084400</v>
+        <v>23424200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>102.7250971521424</v>
+        <v>101.7235329175373</v>
       </c>
       <c r="C51" t="n">
-        <v>103.0622623399618</v>
+        <v>102.4573523337042</v>
       </c>
       <c r="D51" t="n">
-        <v>101.1682057834663</v>
+        <v>101.2475372418891</v>
       </c>
       <c r="E51" t="n">
-        <v>101.6838684082031</v>
+        <v>102.0904388427734</v>
       </c>
       <c r="F51" t="n">
-        <v>18088500</v>
+        <v>15289400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>99.36340427550201</v>
+        <v>102.1201932202399</v>
       </c>
       <c r="C52" t="n">
-        <v>101.6342854500628</v>
+        <v>102.4771805146163</v>
       </c>
       <c r="D52" t="n">
-        <v>98.054425559783</v>
+        <v>100.5335460351719</v>
       </c>
       <c r="E52" t="n">
-        <v>101.6243743896484</v>
+        <v>100.5434646606445</v>
       </c>
       <c r="F52" t="n">
-        <v>23424200</v>
+        <v>17604500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>101.7235405195123</v>
+        <v>100.7318838109266</v>
       </c>
       <c r="C53" t="n">
-        <v>102.4573599905188</v>
+        <v>100.8607956832537</v>
       </c>
       <c r="D53" t="n">
-        <v>101.2475448082921</v>
+        <v>98.84774589504295</v>
       </c>
       <c r="E53" t="n">
-        <v>102.090446472168</v>
+        <v>99.76998138427734</v>
       </c>
       <c r="F53" t="n">
-        <v>15289400</v>
+        <v>22157000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>102.1202009692791</v>
+        <v>103.0721750041795</v>
       </c>
       <c r="C54" t="n">
-        <v>102.4771882907442</v>
+        <v>107.0090294488173</v>
       </c>
       <c r="D54" t="n">
-        <v>100.5335536638138</v>
+        <v>101.8226930180269</v>
       </c>
       <c r="E54" t="n">
-        <v>100.5434722900391</v>
+        <v>106.215705871582</v>
       </c>
       <c r="F54" t="n">
-        <v>17604500</v>
+        <v>50375900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>100.7318761079755</v>
+        <v>107.0784532434011</v>
       </c>
       <c r="C55" t="n">
-        <v>100.8607879704448</v>
+        <v>107.247032058172</v>
       </c>
       <c r="D55" t="n">
-        <v>98.84773833617163</v>
+        <v>103.8456696217535</v>
       </c>
       <c r="E55" t="n">
-        <v>99.76997375488281</v>
+        <v>104.4406585693359</v>
       </c>
       <c r="F55" t="n">
-        <v>22157000</v>
+        <v>41420800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>103.0721750041795</v>
+        <v>104.4803186790174</v>
       </c>
       <c r="C56" t="n">
-        <v>107.0090294488173</v>
+        <v>105.3827168846354</v>
       </c>
       <c r="D56" t="n">
-        <v>101.8226930180269</v>
+        <v>102.89367906727</v>
       </c>
       <c r="E56" t="n">
-        <v>106.215705871582</v>
+        <v>103.1911697387695</v>
       </c>
       <c r="F56" t="n">
-        <v>50375900</v>
+        <v>42519200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>107.0784454213155</v>
+        <v>103.7365912306264</v>
       </c>
       <c r="C57" t="n">
-        <v>107.2470242237718</v>
+        <v>106.5231275693524</v>
       </c>
       <c r="D57" t="n">
-        <v>103.845662035823</v>
+        <v>103.3597666486879</v>
       </c>
       <c r="E57" t="n">
-        <v>104.4406509399414</v>
+        <v>106.1066360473633</v>
       </c>
       <c r="F57" t="n">
-        <v>41420800</v>
+        <v>20212900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>104.4803264037246</v>
+        <v>106.3049566187</v>
       </c>
       <c r="C58" t="n">
-        <v>105.382724676061</v>
+        <v>108.6750012891114</v>
       </c>
       <c r="D58" t="n">
-        <v>102.8936866746697</v>
+        <v>106.2752083069225</v>
       </c>
       <c r="E58" t="n">
-        <v>103.1911773681641</v>
+        <v>108.189094543457</v>
       </c>
       <c r="F58" t="n">
-        <v>42519200</v>
+        <v>17783300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>103.7365837716454</v>
+        <v>108.3874295551272</v>
       </c>
       <c r="C59" t="n">
-        <v>106.5231199100109</v>
+        <v>109.7757345468567</v>
       </c>
       <c r="D59" t="n">
-        <v>103.3597592168018</v>
+        <v>108.0899313050738</v>
       </c>
       <c r="E59" t="n">
-        <v>106.1066284179688</v>
+        <v>109.5873260498047</v>
       </c>
       <c r="F59" t="n">
-        <v>20212900</v>
+        <v>9846500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>106.3049566187</v>
+        <v>109.587327840119</v>
       </c>
       <c r="C60" t="n">
-        <v>108.6750012891114</v>
+        <v>110.8268912927673</v>
       </c>
       <c r="D60" t="n">
-        <v>106.2752083069225</v>
+        <v>109.4385787126623</v>
       </c>
       <c r="E60" t="n">
-        <v>108.189094543457</v>
+        <v>110.5988082885742</v>
       </c>
       <c r="F60" t="n">
-        <v>17783300</v>
+        <v>17236800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>108.3874295551272</v>
+        <v>110.5393043592431</v>
       </c>
       <c r="C61" t="n">
-        <v>109.7757345468567</v>
+        <v>111.7094524838454</v>
       </c>
       <c r="D61" t="n">
-        <v>108.0899313050738</v>
+        <v>109.8649815829351</v>
       </c>
       <c r="E61" t="n">
-        <v>109.5873260498047</v>
+        <v>111.4714584350586</v>
       </c>
       <c r="F61" t="n">
-        <v>9846500</v>
+        <v>18711800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>109.587335399739</v>
+        <v>111.560708766128</v>
       </c>
       <c r="C62" t="n">
-        <v>110.8268989378955</v>
+        <v>113.9307534404373</v>
       </c>
       <c r="D62" t="n">
-        <v>109.4385862620211</v>
+        <v>111.2830477681546</v>
       </c>
       <c r="E62" t="n">
-        <v>110.5988159179688</v>
+        <v>113.4547653198242</v>
       </c>
       <c r="F62" t="n">
-        <v>17236800</v>
+        <v>24478300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>110.5393043592431</v>
+        <v>112.6713645812471</v>
       </c>
       <c r="C63" t="n">
-        <v>111.7094524838454</v>
+        <v>113.9307577455568</v>
       </c>
       <c r="D63" t="n">
-        <v>109.8649815829351</v>
+        <v>112.2152061293831</v>
       </c>
       <c r="E63" t="n">
-        <v>111.4714584350586</v>
+        <v>113.8811721801758</v>
       </c>
       <c r="F63" t="n">
-        <v>18711800</v>
+        <v>25905100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>111.560708766128</v>
+        <v>113.7720935914494</v>
       </c>
       <c r="C64" t="n">
-        <v>113.9307534404373</v>
+        <v>115.2992290848131</v>
       </c>
       <c r="D64" t="n">
-        <v>111.2830477681546</v>
+        <v>113.7225080277957</v>
       </c>
       <c r="E64" t="n">
-        <v>113.4547653198242</v>
+        <v>114.1489181518555</v>
       </c>
       <c r="F64" t="n">
-        <v>24478300</v>
+        <v>23956400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>112.6713645812471</v>
+        <v>113.6134239095882</v>
       </c>
       <c r="C65" t="n">
-        <v>113.9307577455568</v>
+        <v>114.0299154007005</v>
       </c>
       <c r="D65" t="n">
-        <v>112.2152061293831</v>
+        <v>111.3623800798857</v>
       </c>
       <c r="E65" t="n">
-        <v>113.8811721801758</v>
+        <v>112.6118545532227</v>
       </c>
       <c r="F65" t="n">
-        <v>25905100</v>
+        <v>22700700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>113.7720935914494</v>
+        <v>112.9985942054707</v>
       </c>
       <c r="C66" t="n">
-        <v>115.2992290848131</v>
+        <v>114.7538201807431</v>
       </c>
       <c r="D66" t="n">
-        <v>113.7225080277957</v>
+        <v>112.0763587521143</v>
       </c>
       <c r="E66" t="n">
-        <v>114.1489181518555</v>
+        <v>114.0993270874023</v>
       </c>
       <c r="F66" t="n">
-        <v>23956400</v>
+        <v>24326700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>113.6134239095882</v>
+        <v>114.3869191950181</v>
       </c>
       <c r="C67" t="n">
-        <v>114.0299154007005</v>
+        <v>115.259576748144</v>
       </c>
       <c r="D67" t="n">
-        <v>111.3623800798857</v>
+        <v>112.0466226827729</v>
       </c>
       <c r="E67" t="n">
-        <v>112.6118545532227</v>
+        <v>112.2350387573242</v>
       </c>
       <c r="F67" t="n">
-        <v>22700700</v>
+        <v>22859600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>112.9986017612633</v>
+        <v>112.195370053421</v>
       </c>
       <c r="C68" t="n">
-        <v>114.7538278539011</v>
+        <v>114.9025800457367</v>
       </c>
       <c r="D68" t="n">
-        <v>112.0763662462405</v>
+        <v>111.9077904157248</v>
       </c>
       <c r="E68" t="n">
-        <v>114.0993347167969</v>
+        <v>114.5554962158203</v>
       </c>
       <c r="F68" t="n">
-        <v>24326700</v>
+        <v>21586600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>114.3869114193454</v>
+        <v>114.5306574399956</v>
       </c>
       <c r="C69" t="n">
-        <v>115.2595689131506</v>
+        <v>116.2099582668437</v>
       </c>
       <c r="D69" t="n">
-        <v>112.0466150661863</v>
+        <v>114.2921706587026</v>
       </c>
       <c r="E69" t="n">
-        <v>112.2350311279297</v>
+        <v>115.961540222168</v>
       </c>
       <c r="F69" t="n">
-        <v>22859600</v>
+        <v>19092400</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>112.1953625812108</v>
+        <v>116.190085480185</v>
       </c>
       <c r="C70" t="n">
-        <v>114.9025723932263</v>
+        <v>116.7067916655062</v>
       </c>
       <c r="D70" t="n">
-        <v>111.9077829626674</v>
+        <v>114.9082474894773</v>
       </c>
       <c r="E70" t="n">
-        <v>114.5554885864258</v>
+        <v>116.0509719848633</v>
       </c>
       <c r="F70" t="n">
-        <v>21586600</v>
+        <v>18713700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,25 +2263,25 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>114.5306499047423</v>
+        <v>115.8423072543707</v>
       </c>
       <c r="C71" t="n">
-        <v>116.2099506211051</v>
+        <v>116.140404366624</v>
       </c>
       <c r="D71" t="n">
-        <v>114.29216313914</v>
+        <v>114.2226167114376</v>
       </c>
       <c r="E71" t="n">
-        <v>115.9615325927734</v>
+        <v>114.6896438598633</v>
       </c>
       <c r="F71" t="n">
-        <v>19092400</v>
+        <v>19642300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>116.190085480185</v>
+        <v>114.4710352169006</v>
       </c>
       <c r="C72" t="n">
-        <v>116.7067916655062</v>
+        <v>115.6535075692186</v>
       </c>
       <c r="D72" t="n">
-        <v>114.9082474894773</v>
+        <v>114.3418605591895</v>
       </c>
       <c r="E72" t="n">
-        <v>116.0509719848633</v>
+        <v>114.9281311035156</v>
       </c>
       <c r="F72" t="n">
-        <v>18713700</v>
+        <v>16177800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>115.8422995482986</v>
+        <v>114.2822472329707</v>
       </c>
       <c r="C73" t="n">
-        <v>116.1403966407218</v>
+        <v>115.7429466488196</v>
       </c>
       <c r="D73" t="n">
-        <v>114.2226091131107</v>
+        <v>113.8847768180071</v>
       </c>
       <c r="E73" t="n">
-        <v>114.6896362304688</v>
+        <v>114.103385925293</v>
       </c>
       <c r="F73" t="n">
-        <v>19642300</v>
+        <v>21476700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>114.4710352169006</v>
+        <v>114.411415636222</v>
       </c>
       <c r="C74" t="n">
-        <v>115.6535075692186</v>
+        <v>114.5505291366805</v>
       </c>
       <c r="D74" t="n">
-        <v>114.3418605591895</v>
+        <v>112.8116027998319</v>
       </c>
       <c r="E74" t="n">
-        <v>114.9281311035156</v>
+        <v>113.6363525390625</v>
       </c>
       <c r="F74" t="n">
-        <v>16177800</v>
+        <v>50043800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>114.2822395916168</v>
+        <v>113.2885707737471</v>
       </c>
       <c r="C75" t="n">
-        <v>115.7429389097976</v>
+        <v>113.5966067328595</v>
       </c>
       <c r="D75" t="n">
-        <v>113.8847692032296</v>
+        <v>111.5098966082868</v>
       </c>
       <c r="E75" t="n">
-        <v>114.1033782958984</v>
+        <v>111.8874893188477</v>
       </c>
       <c r="F75" t="n">
-        <v>21476700</v>
+        <v>21473900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>114.411415636222</v>
+        <v>111.2813411845575</v>
       </c>
       <c r="C76" t="n">
-        <v>114.5505291366805</v>
+        <v>111.6390637625677</v>
       </c>
       <c r="D76" t="n">
-        <v>112.8116027998319</v>
+        <v>109.9995032102072</v>
       </c>
       <c r="E76" t="n">
-        <v>113.6363525390625</v>
+        <v>110.1982421875</v>
       </c>
       <c r="F76" t="n">
-        <v>50043800</v>
+        <v>20319900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>113.2885630488155</v>
+        <v>110.1982488335626</v>
       </c>
       <c r="C77" t="n">
-        <v>113.5965989869235</v>
+        <v>111.003120892069</v>
       </c>
       <c r="D77" t="n">
-        <v>111.5098890046396</v>
+        <v>109.8504650787215</v>
       </c>
       <c r="E77" t="n">
-        <v>111.8874816894531</v>
+        <v>110.9037551879883</v>
       </c>
       <c r="F77" t="n">
-        <v>21473900</v>
+        <v>9009600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>111.2813488889387</v>
+        <v>111.0130583586743</v>
       </c>
       <c r="C78" t="n">
-        <v>111.6390714917152</v>
+        <v>111.2614764063509</v>
       </c>
       <c r="D78" t="n">
-        <v>109.9995108258424</v>
+        <v>110.6553357635307</v>
       </c>
       <c r="E78" t="n">
-        <v>110.1982498168945</v>
+        <v>111.0329284667969</v>
       </c>
       <c r="F78" t="n">
-        <v>20319900</v>
+        <v>9003800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>110.198241252702</v>
+        <v>110.8838702636393</v>
       </c>
       <c r="C79" t="n">
-        <v>111.0031132558388</v>
+        <v>112.0663425340636</v>
       </c>
       <c r="D79" t="n">
-        <v>109.8504575217858</v>
+        <v>110.8640001565665</v>
       </c>
       <c r="E79" t="n">
-        <v>110.9037475585938</v>
+        <v>111.8179244995117</v>
       </c>
       <c r="F79" t="n">
-        <v>9009600</v>
+        <v>12979600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>111.0130583586743</v>
+        <v>111.1819754114984</v>
       </c>
       <c r="C80" t="n">
-        <v>111.2614764063509</v>
+        <v>111.9769161578998</v>
       </c>
       <c r="D80" t="n">
-        <v>110.6553357635307</v>
+        <v>111.1322887719295</v>
       </c>
       <c r="E80" t="n">
-        <v>111.0329284667969</v>
+        <v>111.211784362793</v>
       </c>
       <c r="F80" t="n">
-        <v>9003800</v>
+        <v>11730600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>110.8838778293028</v>
+        <v>111.022991872357</v>
       </c>
       <c r="C81" t="n">
-        <v>112.0663501804078</v>
+        <v>111.5396980510222</v>
       </c>
       <c r="D81" t="n">
-        <v>110.8640077208743</v>
+        <v>110.6155826547936</v>
       </c>
       <c r="E81" t="n">
-        <v>111.8179321289062</v>
+        <v>110.7050170898438</v>
       </c>
       <c r="F81" t="n">
-        <v>12979600</v>
+        <v>11487400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>111.1819754114984</v>
+        <v>110.7248924392647</v>
       </c>
       <c r="C82" t="n">
-        <v>111.9769161578998</v>
+        <v>112.0762872242068</v>
       </c>
       <c r="D82" t="n">
-        <v>111.1322887719295</v>
+        <v>110.4168564863102</v>
       </c>
       <c r="E82" t="n">
-        <v>111.211784362793</v>
+        <v>112.0464782714844</v>
       </c>
       <c r="F82" t="n">
-        <v>11730600</v>
+        <v>14306600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>111.022991872357</v>
+        <v>112.106092568778</v>
       </c>
       <c r="C83" t="n">
-        <v>111.5396980510222</v>
+        <v>113.0103378715463</v>
       </c>
       <c r="D83" t="n">
-        <v>110.6155826547936</v>
+        <v>111.4403340423477</v>
       </c>
       <c r="E83" t="n">
-        <v>110.7050170898438</v>
+        <v>111.9967880249023</v>
       </c>
       <c r="F83" t="n">
-        <v>11487400</v>
+        <v>19557600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>110.7248924392647</v>
+        <v>111.6887590151699</v>
       </c>
       <c r="C84" t="n">
-        <v>112.0762872242068</v>
+        <v>114.0636350138627</v>
       </c>
       <c r="D84" t="n">
-        <v>110.4168564863102</v>
+        <v>111.2813497661395</v>
       </c>
       <c r="E84" t="n">
-        <v>112.0464782714844</v>
+        <v>113.6164779663086</v>
       </c>
       <c r="F84" t="n">
-        <v>14306600</v>
+        <v>20120800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>112.106092568778</v>
+        <v>113.4674284407305</v>
       </c>
       <c r="C85" t="n">
-        <v>113.0103378715463</v>
+        <v>114.0040123266269</v>
       </c>
       <c r="D85" t="n">
-        <v>111.4403340423477</v>
+        <v>111.3906496463658</v>
       </c>
       <c r="E85" t="n">
-        <v>111.9967880249023</v>
+        <v>112.0067291259766</v>
       </c>
       <c r="F85" t="n">
-        <v>19557600</v>
+        <v>23306000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>111.6887515152225</v>
+        <v>110.5857797769927</v>
       </c>
       <c r="C86" t="n">
-        <v>114.0636273544414</v>
+        <v>112.7519854709339</v>
       </c>
       <c r="D86" t="n">
-        <v>111.2813422935498</v>
+        <v>109.1151415889016</v>
       </c>
       <c r="E86" t="n">
-        <v>113.6164703369141</v>
+        <v>112.3545150756836</v>
       </c>
       <c r="F86" t="n">
-        <v>20120800</v>
+        <v>24058300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>113.4674284407305</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="C87" t="n">
-        <v>114.0040123266269</v>
+        <v>114.7293904053996</v>
       </c>
       <c r="D87" t="n">
-        <v>111.3906496463658</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="E87" t="n">
-        <v>112.0067291259766</v>
+        <v>113.8052749633789</v>
       </c>
       <c r="F87" t="n">
-        <v>23306000</v>
+        <v>21902900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>110.5857797769927</v>
+        <v>116.756475995831</v>
       </c>
       <c r="C88" t="n">
-        <v>112.7519854709339</v>
+        <v>118.0879930193155</v>
       </c>
       <c r="D88" t="n">
-        <v>109.1151415889016</v>
+        <v>115.6733770063802</v>
       </c>
       <c r="E88" t="n">
-        <v>112.3545150756836</v>
+        <v>117.223503112793</v>
       </c>
       <c r="F88" t="n">
-        <v>24058300</v>
+        <v>49182100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>111.5496424227033</v>
+        <v>117.1440096095209</v>
       </c>
       <c r="C89" t="n">
-        <v>114.7293904053996</v>
+        <v>119.7474333817796</v>
       </c>
       <c r="D89" t="n">
-        <v>111.5496424227033</v>
+        <v>116.9850260070875</v>
       </c>
       <c r="E89" t="n">
-        <v>113.8052749633789</v>
+        <v>119.5983810424805</v>
       </c>
       <c r="F89" t="n">
-        <v>21902900</v>
+        <v>31222100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>116.7564835948294</v>
+        <v>119.4294631115365</v>
       </c>
       <c r="C90" t="n">
-        <v>118.0880007049746</v>
+        <v>120.4728143638468</v>
       </c>
       <c r="D90" t="n">
-        <v>115.673384534886</v>
+        <v>118.2767997305645</v>
       </c>
       <c r="E90" t="n">
-        <v>117.2235107421875</v>
+        <v>119.2804107666016</v>
       </c>
       <c r="F90" t="n">
-        <v>49182100</v>
+        <v>32764000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>117.1440170823467</v>
+        <v>119.2207951798175</v>
       </c>
       <c r="C91" t="n">
-        <v>119.7474410206824</v>
+        <v>120.1051628408833</v>
       </c>
       <c r="D91" t="n">
-        <v>116.9850334697715</v>
+        <v>117.9787049163972</v>
       </c>
       <c r="E91" t="n">
-        <v>119.598388671875</v>
+        <v>118.4457244873047</v>
       </c>
       <c r="F91" t="n">
-        <v>31222100</v>
+        <v>34559400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>119.4294631115365</v>
+        <v>117.9190771443211</v>
       </c>
       <c r="C92" t="n">
-        <v>120.4728143638468</v>
+        <v>119.8368647771362</v>
       </c>
       <c r="D92" t="n">
-        <v>118.2767997305645</v>
+        <v>116.1602807010803</v>
       </c>
       <c r="E92" t="n">
-        <v>119.2804107666016</v>
+        <v>118.9425582885742</v>
       </c>
       <c r="F92" t="n">
-        <v>32764000</v>
+        <v>415144600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>119.2207951798175</v>
+        <v>120.1250298240042</v>
       </c>
       <c r="C93" t="n">
-        <v>120.1051628408833</v>
+        <v>120.8504138546603</v>
       </c>
       <c r="D93" t="n">
-        <v>117.9787049163972</v>
+        <v>116.8657862705671</v>
       </c>
       <c r="E93" t="n">
-        <v>118.4457244873047</v>
+        <v>117.9588241577148</v>
       </c>
       <c r="F93" t="n">
-        <v>34559400</v>
+        <v>45334000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>117.9190771443211</v>
+        <v>117.3328142471995</v>
       </c>
       <c r="C94" t="n">
-        <v>119.8368647771362</v>
+        <v>119.7275602876645</v>
       </c>
       <c r="D94" t="n">
-        <v>116.1602807010803</v>
+        <v>116.8061691984345</v>
       </c>
       <c r="E94" t="n">
-        <v>118.9425582885742</v>
+        <v>118.6047134399414</v>
       </c>
       <c r="F94" t="n">
-        <v>415144600</v>
+        <v>34811700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>120.1250298240042</v>
+        <v>118.5351568548667</v>
       </c>
       <c r="C95" t="n">
-        <v>120.8504138546603</v>
+        <v>118.7636972139123</v>
       </c>
       <c r="D95" t="n">
-        <v>116.8657862705671</v>
+        <v>116.9055350642564</v>
       </c>
       <c r="E95" t="n">
-        <v>117.9588241577148</v>
+        <v>117.0843963623047</v>
       </c>
       <c r="F95" t="n">
-        <v>45334000</v>
+        <v>24547300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>117.3328142471995</v>
+        <v>117.4222340816893</v>
       </c>
       <c r="C96" t="n">
-        <v>119.7275602876645</v>
+        <v>117.8594522459602</v>
       </c>
       <c r="D96" t="n">
-        <v>116.8061691984345</v>
+        <v>116.3987529981613</v>
       </c>
       <c r="E96" t="n">
-        <v>118.6047134399414</v>
+        <v>116.9850234985352</v>
       </c>
       <c r="F96" t="n">
-        <v>34811700</v>
+        <v>20806900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>118.5351568548667</v>
+        <v>117.064521823182</v>
       </c>
       <c r="C97" t="n">
-        <v>118.7636972139123</v>
+        <v>118.0979418418126</v>
       </c>
       <c r="D97" t="n">
-        <v>116.9055350642564</v>
+        <v>116.6471813102112</v>
       </c>
       <c r="E97" t="n">
-        <v>117.0843963623047</v>
+        <v>116.8955993652344</v>
       </c>
       <c r="F97" t="n">
-        <v>24547300</v>
+        <v>19552200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>117.4222340816893</v>
+        <v>116.7564814621505</v>
       </c>
       <c r="C98" t="n">
-        <v>117.8594522459602</v>
+        <v>116.8856561166937</v>
       </c>
       <c r="D98" t="n">
-        <v>116.3987529981613</v>
+        <v>114.7492669888757</v>
       </c>
       <c r="E98" t="n">
-        <v>116.9850234985352</v>
+        <v>116.2000274658203</v>
       </c>
       <c r="F98" t="n">
-        <v>20806900</v>
+        <v>22968600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>117.064521823182</v>
+        <v>115.9019236934497</v>
       </c>
       <c r="C99" t="n">
-        <v>118.0979418418126</v>
+        <v>116.7167345864151</v>
       </c>
       <c r="D99" t="n">
-        <v>116.6471813102112</v>
+        <v>115.1367994424561</v>
       </c>
       <c r="E99" t="n">
-        <v>116.8955993652344</v>
+        <v>115.8323669433594</v>
       </c>
       <c r="F99" t="n">
-        <v>19552200</v>
+        <v>16342000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>116.7564814621505</v>
+        <v>115.7131212672227</v>
       </c>
       <c r="C100" t="n">
-        <v>116.8856561166937</v>
+        <v>116.9154712653777</v>
       </c>
       <c r="D100" t="n">
-        <v>114.7492669888757</v>
+        <v>115.3355285714882</v>
       </c>
       <c r="E100" t="n">
-        <v>116.2000274658203</v>
+        <v>116.6670532226562</v>
       </c>
       <c r="F100" t="n">
-        <v>22968600</v>
+        <v>16381100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>115.9019236934497</v>
+        <v>116.1702235798966</v>
       </c>
       <c r="C101" t="n">
-        <v>116.7167345864151</v>
+        <v>118.6544041448817</v>
       </c>
       <c r="D101" t="n">
-        <v>115.1367994424561</v>
+        <v>115.8621800346786</v>
       </c>
       <c r="E101" t="n">
-        <v>115.8323669433594</v>
+        <v>118.3861083984375</v>
       </c>
       <c r="F101" t="n">
-        <v>16342000</v>
+        <v>22215400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>115.7131212672227</v>
+        <v>118.7438208421828</v>
       </c>
       <c r="C102" t="n">
-        <v>116.9154712653777</v>
+        <v>123.4140768721483</v>
       </c>
       <c r="D102" t="n">
-        <v>115.3355285714882</v>
+        <v>118.2966714112071</v>
       </c>
       <c r="E102" t="n">
-        <v>116.6670532226562</v>
+        <v>123.2749633789062</v>
       </c>
       <c r="F102" t="n">
-        <v>16381100</v>
+        <v>31210100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>116.1702235798966</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="C103" t="n">
-        <v>118.6544041448817</v>
+        <v>127.3589666685813</v>
       </c>
       <c r="D103" t="n">
-        <v>115.8621800346786</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="E103" t="n">
-        <v>118.3861083984375</v>
+        <v>126.9018783569336</v>
       </c>
       <c r="F103" t="n">
-        <v>22215400</v>
+        <v>32018700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>118.7438208421828</v>
+        <v>127.3192151881231</v>
       </c>
       <c r="C104" t="n">
-        <v>123.4140768721483</v>
+        <v>128.5911143047342</v>
       </c>
       <c r="D104" t="n">
-        <v>118.2966714112071</v>
+        <v>126.2857876794806</v>
       </c>
       <c r="E104" t="n">
-        <v>123.2749633789062</v>
+        <v>127.1900329589844</v>
       </c>
       <c r="F104" t="n">
-        <v>31210100</v>
+        <v>27531800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>122.8675715680868</v>
+        <v>127.7663710403251</v>
       </c>
       <c r="C105" t="n">
-        <v>127.3589666685813</v>
+        <v>128.779920911861</v>
       </c>
       <c r="D105" t="n">
-        <v>122.8675715680868</v>
+        <v>125.7591489863279</v>
       </c>
       <c r="E105" t="n">
-        <v>126.9018783569336</v>
+        <v>126.1367492675781</v>
       </c>
       <c r="F105" t="n">
-        <v>32018700</v>
+        <v>30517800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>127.3192228252665</v>
+        <v>126.4845378023196</v>
       </c>
       <c r="C106" t="n">
-        <v>128.5911220181715</v>
+        <v>130.8666283506429</v>
       </c>
       <c r="D106" t="n">
-        <v>126.2857952546346</v>
+        <v>126.2460585922159</v>
       </c>
       <c r="E106" t="n">
-        <v>127.1900405883789</v>
+        <v>130.3499145507812</v>
       </c>
       <c r="F106" t="n">
-        <v>27531800</v>
+        <v>26593400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>127.7663710403251</v>
+        <v>130.5884053590928</v>
       </c>
       <c r="C107" t="n">
-        <v>128.779920911861</v>
+        <v>130.9560592399128</v>
       </c>
       <c r="D107" t="n">
-        <v>125.7591489863279</v>
+        <v>127.2794749450073</v>
       </c>
       <c r="E107" t="n">
-        <v>126.1367492675781</v>
+        <v>128.2035980224609</v>
       </c>
       <c r="F107" t="n">
-        <v>30517800</v>
+        <v>27197300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>126.4845378023196</v>
+        <v>128.1240931628847</v>
       </c>
       <c r="C108" t="n">
-        <v>130.8666283506429</v>
+        <v>128.5215559695187</v>
       </c>
       <c r="D108" t="n">
-        <v>126.2460585922159</v>
+        <v>125.5902260744493</v>
       </c>
       <c r="E108" t="n">
-        <v>130.3499145507812</v>
+        <v>125.8982620239258</v>
       </c>
       <c r="F108" t="n">
-        <v>26593400</v>
+        <v>24662000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>130.5884053590928</v>
+        <v>125.8982685130821</v>
       </c>
       <c r="C109" t="n">
-        <v>130.9560592399128</v>
+        <v>128.9190405832424</v>
       </c>
       <c r="D109" t="n">
-        <v>127.2794749450073</v>
+        <v>125.8287117602243</v>
       </c>
       <c r="E109" t="n">
-        <v>128.2035980224609</v>
+        <v>127.9551773071289</v>
       </c>
       <c r="F109" t="n">
-        <v>27197300</v>
+        <v>19232100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>128.1240931628847</v>
+        <v>128.5613042513025</v>
       </c>
       <c r="C110" t="n">
-        <v>128.5215559695187</v>
+        <v>133.6389694112844</v>
       </c>
       <c r="D110" t="n">
-        <v>125.5902260744493</v>
+        <v>128.4917399247525</v>
       </c>
       <c r="E110" t="n">
-        <v>125.8982620239258</v>
+        <v>132.7943420410156</v>
       </c>
       <c r="F110" t="n">
-        <v>24662000</v>
+        <v>33382700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>125.8982534995816</v>
+        <v>131.8602980405916</v>
       </c>
       <c r="C111" t="n">
-        <v>128.9190252095116</v>
+        <v>133.7979558000997</v>
       </c>
       <c r="D111" t="n">
-        <v>125.8286967550185</v>
+        <v>130.9163124820861</v>
       </c>
       <c r="E111" t="n">
-        <v>127.9551620483398</v>
+        <v>133.0427703857422</v>
       </c>
       <c r="F111" t="n">
-        <v>19232100</v>
+        <v>24131200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>128.5613042513025</v>
+        <v>132.2677060470971</v>
       </c>
       <c r="C112" t="n">
-        <v>133.6389694112844</v>
+        <v>133.8377099294918</v>
       </c>
       <c r="D112" t="n">
-        <v>128.4917399247525</v>
+        <v>127.3490317305018</v>
       </c>
       <c r="E112" t="n">
-        <v>132.7943420410156</v>
+        <v>128.03466796875</v>
       </c>
       <c r="F112" t="n">
-        <v>33382700</v>
+        <v>37995900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>131.8602980405916</v>
+        <v>127.3192184434441</v>
       </c>
       <c r="C113" t="n">
-        <v>133.7979558000997</v>
+        <v>128.0545261364593</v>
       </c>
       <c r="D113" t="n">
-        <v>130.9163124820861</v>
+        <v>124.9741439631975</v>
       </c>
       <c r="E113" t="n">
-        <v>133.0427703857422</v>
+        <v>125.8187713623047</v>
       </c>
       <c r="F113" t="n">
-        <v>24131200</v>
+        <v>36485000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>132.2677060470971</v>
+        <v>127.6868765679835</v>
       </c>
       <c r="C114" t="n">
-        <v>133.8377099294918</v>
+        <v>129.2767581387821</v>
       </c>
       <c r="D114" t="n">
-        <v>127.3490317305018</v>
+        <v>123.6128221003258</v>
       </c>
       <c r="E114" t="n">
-        <v>128.03466796875</v>
+        <v>124.0798492431641</v>
       </c>
       <c r="F114" t="n">
-        <v>37995900</v>
+        <v>42993300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>127.3192261638227</v>
+        <v>122.2216774308809</v>
       </c>
       <c r="C115" t="n">
-        <v>128.0545339014254</v>
+        <v>122.6986434102051</v>
       </c>
       <c r="D115" t="n">
-        <v>124.9741515413755</v>
+        <v>120.2840197235699</v>
       </c>
       <c r="E115" t="n">
-        <v>125.8187789916992</v>
+        <v>122.2117385864258</v>
       </c>
       <c r="F115" t="n">
-        <v>36485000</v>
+        <v>35151000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>127.6868765679835</v>
+        <v>122.7383904417398</v>
       </c>
       <c r="C116" t="n">
-        <v>129.2767581387821</v>
+        <v>125.9976417223621</v>
       </c>
       <c r="D116" t="n">
-        <v>123.6128221003258</v>
+        <v>122.1819364192246</v>
       </c>
       <c r="E116" t="n">
-        <v>124.0798492431641</v>
+        <v>125.0139007568359</v>
       </c>
       <c r="F116" t="n">
-        <v>42993300</v>
+        <v>25662800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>122.2216774308809</v>
+        <v>125.1033248323272</v>
       </c>
       <c r="C117" t="n">
-        <v>122.6986434102051</v>
+        <v>127.2297750394507</v>
       </c>
       <c r="D117" t="n">
-        <v>120.2840197235699</v>
+        <v>124.1195915294407</v>
       </c>
       <c r="E117" t="n">
-        <v>122.2117385864258</v>
+        <v>125.9479446411133</v>
       </c>
       <c r="F117" t="n">
-        <v>35151000</v>
+        <v>20161200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>122.7383904417398</v>
+        <v>125.8088357226236</v>
       </c>
       <c r="C118" t="n">
-        <v>125.9976417223621</v>
+        <v>126.593837657093</v>
       </c>
       <c r="D118" t="n">
-        <v>122.1819364192246</v>
+        <v>124.626363398647</v>
       </c>
       <c r="E118" t="n">
-        <v>125.0139007568359</v>
+        <v>124.9542770385742</v>
       </c>
       <c r="F118" t="n">
-        <v>25662800</v>
+        <v>17345700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>125.1033248323272</v>
+        <v>125.1828241808018</v>
       </c>
       <c r="C119" t="n">
-        <v>127.2297750394507</v>
+        <v>126.5242801033853</v>
       </c>
       <c r="D119" t="n">
-        <v>124.1195915294407</v>
+        <v>123.1557320302039</v>
       </c>
       <c r="E119" t="n">
-        <v>125.9479446411133</v>
+        <v>123.6326904296875</v>
       </c>
       <c r="F119" t="n">
-        <v>20161200</v>
+        <v>18638300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>125.8088357226236</v>
+        <v>124.7257341647123</v>
       </c>
       <c r="C120" t="n">
-        <v>126.593837657093</v>
+        <v>127.7862540138419</v>
       </c>
       <c r="D120" t="n">
-        <v>124.626363398647</v>
+        <v>124.3580802939128</v>
       </c>
       <c r="E120" t="n">
-        <v>124.9542770385742</v>
+        <v>127.1403579711914</v>
       </c>
       <c r="F120" t="n">
-        <v>17345700</v>
+        <v>29205500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>125.1828241808018</v>
+        <v>126.6534531765271</v>
       </c>
       <c r="C121" t="n">
-        <v>126.5242801033853</v>
+        <v>127.9352911784569</v>
       </c>
       <c r="D121" t="n">
-        <v>123.1557320302039</v>
+        <v>126.2460515312658</v>
       </c>
       <c r="E121" t="n">
-        <v>123.6326904296875</v>
+        <v>126.2957305908203</v>
       </c>
       <c r="F121" t="n">
-        <v>18638300</v>
+        <v>17091500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>124.7257266802137</v>
+        <v>125.7193975573372</v>
       </c>
       <c r="C122" t="n">
-        <v>127.7862463456887</v>
+        <v>127.5576895255598</v>
       </c>
       <c r="D122" t="n">
-        <v>124.3580728314762</v>
+        <v>124.8747777428692</v>
       </c>
       <c r="E122" t="n">
-        <v>127.1403503417969</v>
+        <v>127.1006088256836</v>
       </c>
       <c r="F122" t="n">
-        <v>29205500</v>
+        <v>16480400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>126.6534531765271</v>
+        <v>126.3056684844515</v>
       </c>
       <c r="C123" t="n">
-        <v>127.9352911784569</v>
+        <v>127.3589585449282</v>
       </c>
       <c r="D123" t="n">
-        <v>126.2460515312658</v>
+        <v>125.4411709786478</v>
       </c>
       <c r="E123" t="n">
-        <v>126.2957305908203</v>
+        <v>127.0012359619141</v>
       </c>
       <c r="F123" t="n">
-        <v>17091500</v>
+        <v>16434100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>125.7193975573372</v>
+        <v>124.5866098839056</v>
       </c>
       <c r="C124" t="n">
-        <v>127.5576895255598</v>
+        <v>124.8847145576342</v>
       </c>
       <c r="D124" t="n">
-        <v>124.8747777428692</v>
+        <v>120.8802170560586</v>
       </c>
       <c r="E124" t="n">
-        <v>127.1006088256836</v>
+        <v>122.5297088623047</v>
       </c>
       <c r="F124" t="n">
-        <v>16480400</v>
+        <v>28604900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>126.3056684844515</v>
+        <v>121.7248399768431</v>
       </c>
       <c r="C125" t="n">
-        <v>127.3589585449282</v>
+        <v>123.4041483583995</v>
       </c>
       <c r="D125" t="n">
-        <v>125.4411709786478</v>
+        <v>120.8504112025381</v>
       </c>
       <c r="E125" t="n">
-        <v>127.0012359619141</v>
+        <v>123.0166168212891</v>
       </c>
       <c r="F125" t="n">
-        <v>16434100</v>
+        <v>21553000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>124.5866098839056</v>
+        <v>122.9073188921967</v>
       </c>
       <c r="C126" t="n">
-        <v>124.8847145576342</v>
+        <v>123.7221298065307</v>
       </c>
       <c r="D126" t="n">
-        <v>120.8802170560586</v>
+        <v>121.7248465285333</v>
       </c>
       <c r="E126" t="n">
-        <v>122.5297088623047</v>
+        <v>123.5531997680664</v>
       </c>
       <c r="F126" t="n">
-        <v>28604900</v>
+        <v>19375900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>121.7248475261227</v>
+        <v>123.4240246061754</v>
       </c>
       <c r="C127" t="n">
-        <v>123.4041560118284</v>
+        <v>125.3020644813305</v>
       </c>
       <c r="D127" t="n">
-        <v>120.8504186975863</v>
+        <v>122.5694658969271</v>
       </c>
       <c r="E127" t="n">
-        <v>123.0166244506836</v>
+        <v>124.3282699584961</v>
       </c>
       <c r="F127" t="n">
-        <v>21553000</v>
+        <v>18793600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>122.9073113026852</v>
+        <v>124.5170631497059</v>
       </c>
       <c r="C128" t="n">
-        <v>123.7221221667048</v>
+        <v>124.6959244521016</v>
       </c>
       <c r="D128" t="n">
-        <v>121.7248390120394</v>
+        <v>122.2713693965471</v>
       </c>
       <c r="E128" t="n">
-        <v>123.5531921386719</v>
+        <v>122.7085800170898</v>
       </c>
       <c r="F128" t="n">
-        <v>19375900</v>
+        <v>18176500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>123.4240170322698</v>
+        <v>121.5261084606577</v>
       </c>
       <c r="C129" t="n">
-        <v>125.3020567921792</v>
+        <v>124.596551802696</v>
       </c>
       <c r="D129" t="n">
-        <v>122.5694583754614</v>
+        <v>121.5062307719897</v>
       </c>
       <c r="E129" t="n">
-        <v>124.3282623291016</v>
+        <v>124.5369338989258</v>
       </c>
       <c r="F129" t="n">
-        <v>18793600</v>
+        <v>21751600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>124.5170631497059</v>
+        <v>124.5965516855884</v>
       </c>
       <c r="C130" t="n">
-        <v>124.6959244521016</v>
+        <v>125.888328527587</v>
       </c>
       <c r="D130" t="n">
-        <v>122.2713693965471</v>
+        <v>124.1792111973551</v>
       </c>
       <c r="E130" t="n">
-        <v>122.7085800170898</v>
+        <v>125.7193984985352</v>
       </c>
       <c r="F130" t="n">
-        <v>18176500</v>
+        <v>15194100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>121.5261084606577</v>
+        <v>125.9578884818529</v>
       </c>
       <c r="C131" t="n">
-        <v>124.596551802696</v>
+        <v>126.1764975758589</v>
       </c>
       <c r="D131" t="n">
-        <v>121.5062307719897</v>
+        <v>124.0401008586876</v>
       </c>
       <c r="E131" t="n">
-        <v>124.5369338989258</v>
+        <v>125.192756652832</v>
       </c>
       <c r="F131" t="n">
-        <v>21751600</v>
+        <v>20463200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>124.5965441243348</v>
+        <v>125.8485858664739</v>
       </c>
       <c r="C132" t="n">
-        <v>125.8883208879408</v>
+        <v>126.3851697651471</v>
       </c>
       <c r="D132" t="n">
-        <v>124.1792036614282</v>
+        <v>124.0699117156269</v>
       </c>
       <c r="E132" t="n">
-        <v>125.7193908691406</v>
+        <v>124.2885208129883</v>
       </c>
       <c r="F132" t="n">
-        <v>15194100</v>
+        <v>19895000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>125.9578808058303</v>
+        <v>123.5432578745883</v>
       </c>
       <c r="C133" t="n">
-        <v>126.176489886514</v>
+        <v>123.8214848583074</v>
       </c>
       <c r="D133" t="n">
-        <v>124.0400932995373</v>
+        <v>121.0590775469296</v>
       </c>
       <c r="E133" t="n">
-        <v>125.1927490234375</v>
+        <v>121.2081298828125</v>
       </c>
       <c r="F133" t="n">
-        <v>20463200</v>
+        <v>19734900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>125.8485781413155</v>
+        <v>121.6254689891314</v>
       </c>
       <c r="C134" t="n">
-        <v>126.3851620070507</v>
+        <v>121.9732527148649</v>
       </c>
       <c r="D134" t="n">
-        <v>124.0699040996516</v>
+        <v>118.5152704020027</v>
       </c>
       <c r="E134" t="n">
-        <v>124.2885131835938</v>
+        <v>120.3237533569336</v>
       </c>
       <c r="F134" t="n">
-        <v>19895000</v>
+        <v>17927700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,25 +3927,25 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>123.5432578745883</v>
+        <v>120.1126709520348</v>
       </c>
       <c r="C135" t="n">
-        <v>123.8214848583074</v>
+        <v>120.7798034051914</v>
       </c>
       <c r="D135" t="n">
-        <v>121.0590775469296</v>
+        <v>117.513863427923</v>
       </c>
       <c r="E135" t="n">
-        <v>121.2081298828125</v>
+        <v>118.5095748901367</v>
       </c>
       <c r="F135" t="n">
-        <v>19734900</v>
+        <v>57545600</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>121.6254767010641</v>
+        <v>119.9633247632631</v>
       </c>
       <c r="C136" t="n">
-        <v>121.9732604488496</v>
+        <v>120.6105311603868</v>
       </c>
       <c r="D136" t="n">
-        <v>118.5152779167263</v>
+        <v>118.5394570155744</v>
       </c>
       <c r="E136" t="n">
-        <v>120.3237609863281</v>
+        <v>120.2022933959961</v>
       </c>
       <c r="F136" t="n">
-        <v>17927700</v>
+        <v>22181500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,25 +3979,25 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>120.1126709520348</v>
+        <v>120.1126723733929</v>
       </c>
       <c r="C137" t="n">
-        <v>120.7798034051914</v>
+        <v>123.577751645438</v>
       </c>
       <c r="D137" t="n">
-        <v>117.513863427923</v>
+        <v>119.9732733747674</v>
       </c>
       <c r="E137" t="n">
-        <v>118.5095748901367</v>
+        <v>121.5265884399414</v>
       </c>
       <c r="F137" t="n">
-        <v>57545600</v>
+        <v>17269600</v>
       </c>
       <c r="G137" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>119.9633247632631</v>
+        <v>122.2833215864677</v>
       </c>
       <c r="C138" t="n">
-        <v>120.6105311603868</v>
+        <v>122.9604056810019</v>
       </c>
       <c r="D138" t="n">
-        <v>118.5394570155744</v>
+        <v>121.2577400013664</v>
       </c>
       <c r="E138" t="n">
-        <v>120.2022933959961</v>
+        <v>122.5322494506836</v>
       </c>
       <c r="F138" t="n">
-        <v>22181500</v>
+        <v>16597300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>120.1126723733929</v>
+        <v>123.0798964656872</v>
       </c>
       <c r="C139" t="n">
-        <v>123.577751645438</v>
+        <v>123.2690840775393</v>
       </c>
       <c r="D139" t="n">
-        <v>119.9732733747674</v>
+        <v>121.2677018786759</v>
       </c>
       <c r="E139" t="n">
-        <v>121.5265884399414</v>
+        <v>121.6560287475586</v>
       </c>
       <c r="F139" t="n">
-        <v>17269600</v>
+        <v>16442500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>122.2833215864677</v>
+        <v>121.5066712193412</v>
       </c>
       <c r="C140" t="n">
-        <v>122.9604056810019</v>
+        <v>123.7370628172082</v>
       </c>
       <c r="D140" t="n">
-        <v>121.2577400013664</v>
+        <v>121.2975727192295</v>
       </c>
       <c r="E140" t="n">
-        <v>122.5322494506836</v>
+        <v>122.3629837036133</v>
       </c>
       <c r="F140" t="n">
-        <v>16597300</v>
+        <v>16543300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>123.0798964656872</v>
+        <v>123.1794659302472</v>
       </c>
       <c r="C141" t="n">
-        <v>123.2690840775393</v>
+        <v>124.7228217585454</v>
       </c>
       <c r="D141" t="n">
-        <v>121.2677018786759</v>
+        <v>122.611910692122</v>
       </c>
       <c r="E141" t="n">
-        <v>121.6560287475586</v>
+        <v>122.9703674316406</v>
       </c>
       <c r="F141" t="n">
-        <v>16442500</v>
+        <v>20428900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>121.5066712193412</v>
+        <v>122.9006712768322</v>
       </c>
       <c r="C142" t="n">
-        <v>123.7370628172082</v>
+        <v>124.4639380346807</v>
       </c>
       <c r="D142" t="n">
-        <v>121.2975727192295</v>
+        <v>122.313197539037</v>
       </c>
       <c r="E142" t="n">
-        <v>122.3629837036133</v>
+        <v>123.7470245361328</v>
       </c>
       <c r="F142" t="n">
-        <v>16543300</v>
+        <v>21330400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>123.1794659302472</v>
+        <v>123.2690839840767</v>
       </c>
       <c r="C143" t="n">
-        <v>124.7228217585454</v>
+        <v>124.6929517011257</v>
       </c>
       <c r="D143" t="n">
-        <v>122.611910692122</v>
+        <v>122.6019515205109</v>
       </c>
       <c r="E143" t="n">
-        <v>122.9703674316406</v>
+        <v>124.2050476074219</v>
       </c>
       <c r="F143" t="n">
-        <v>20428900</v>
+        <v>17039700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>122.9006712768322</v>
+        <v>124.613294570145</v>
       </c>
       <c r="C144" t="n">
-        <v>124.4639380346807</v>
+        <v>125.3600781881083</v>
       </c>
       <c r="D144" t="n">
-        <v>122.313197539037</v>
+        <v>123.6175830795272</v>
       </c>
       <c r="E144" t="n">
-        <v>123.7470245361328</v>
+        <v>125.2505493164062</v>
       </c>
       <c r="F144" t="n">
-        <v>21330400</v>
+        <v>11898400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>123.2690839840767</v>
+        <v>125.2704609872334</v>
       </c>
       <c r="C145" t="n">
-        <v>124.6929517011257</v>
+        <v>126.4354492120167</v>
       </c>
       <c r="D145" t="n">
-        <v>122.6019515205109</v>
+        <v>124.8323530943609</v>
       </c>
       <c r="E145" t="n">
-        <v>124.2050476074219</v>
+        <v>126.2462615966797</v>
       </c>
       <c r="F145" t="n">
-        <v>17039700</v>
+        <v>10850400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>124.613294570145</v>
+        <v>125.6488358778686</v>
       </c>
       <c r="C146" t="n">
-        <v>125.3600781881083</v>
+        <v>125.8181050086721</v>
       </c>
       <c r="D146" t="n">
-        <v>123.6175830795272</v>
+        <v>121.2677037842684</v>
       </c>
       <c r="E146" t="n">
-        <v>125.2505493164062</v>
+        <v>121.9646987915039</v>
       </c>
       <c r="F146" t="n">
-        <v>11898400</v>
+        <v>16076000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>125.2704609872334</v>
+        <v>121.7556020039852</v>
       </c>
       <c r="C147" t="n">
-        <v>126.4354492120167</v>
+        <v>126.7540780291546</v>
       </c>
       <c r="D147" t="n">
-        <v>124.8323530943609</v>
+        <v>120.8096791098908</v>
       </c>
       <c r="E147" t="n">
-        <v>126.2462615966797</v>
+        <v>126.7142486572266</v>
       </c>
       <c r="F147" t="n">
-        <v>10850400</v>
+        <v>20194300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>125.6488358778686</v>
+        <v>126.5449729094413</v>
       </c>
       <c r="C148" t="n">
-        <v>125.8181050086721</v>
+        <v>129.1338289281244</v>
       </c>
       <c r="D148" t="n">
-        <v>121.2677037842684</v>
+        <v>126.2761341426855</v>
       </c>
       <c r="E148" t="n">
-        <v>121.9646987915039</v>
+        <v>128.5762329101562</v>
       </c>
       <c r="F148" t="n">
-        <v>16076000</v>
+        <v>13853100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>121.7556020039852</v>
+        <v>128.1679831957248</v>
       </c>
       <c r="C149" t="n">
-        <v>126.7540780291546</v>
+        <v>128.3770740986961</v>
       </c>
       <c r="D149" t="n">
-        <v>120.8096791098908</v>
+        <v>125.6787044903905</v>
       </c>
       <c r="E149" t="n">
-        <v>126.7142486572266</v>
+        <v>126.2263412475586</v>
       </c>
       <c r="F149" t="n">
-        <v>20194300</v>
+        <v>13894000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>126.5449729094413</v>
+        <v>125.7484068642315</v>
       </c>
       <c r="C150" t="n">
-        <v>129.1338289281244</v>
+        <v>125.7583661063497</v>
       </c>
       <c r="D150" t="n">
-        <v>126.2761341426855</v>
+        <v>123.4184379925161</v>
       </c>
       <c r="E150" t="n">
-        <v>128.5762329101562</v>
+        <v>124.0357818603516</v>
       </c>
       <c r="F150" t="n">
-        <v>13853100</v>
+        <v>14510600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>128.1679831957248</v>
+        <v>122.6218644106077</v>
       </c>
       <c r="C151" t="n">
-        <v>128.3770740986961</v>
+        <v>124.6630682888762</v>
       </c>
       <c r="D151" t="n">
-        <v>125.6787044903905</v>
+        <v>122.0244390705456</v>
       </c>
       <c r="E151" t="n">
-        <v>126.2263412475586</v>
+        <v>124.5137176513672</v>
       </c>
       <c r="F151" t="n">
-        <v>13894000</v>
+        <v>15320800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>125.7484068642315</v>
+        <v>124.0955129791748</v>
       </c>
       <c r="C152" t="n">
-        <v>125.7583661063497</v>
+        <v>124.5336284399926</v>
       </c>
       <c r="D152" t="n">
-        <v>123.4184379925161</v>
+        <v>122.6517344420986</v>
       </c>
       <c r="E152" t="n">
-        <v>124.0357818603516</v>
+        <v>124.2249603271484</v>
       </c>
       <c r="F152" t="n">
-        <v>14510600</v>
+        <v>17001400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>122.6218644106077</v>
+        <v>123.7968020201654</v>
       </c>
       <c r="C153" t="n">
-        <v>124.6630682888762</v>
+        <v>125.3998980056611</v>
       </c>
       <c r="D153" t="n">
-        <v>122.0244390705456</v>
+        <v>123.4383453031182</v>
       </c>
       <c r="E153" t="n">
-        <v>124.5137176513672</v>
+        <v>124.2846984863281</v>
       </c>
       <c r="F153" t="n">
-        <v>15320800</v>
+        <v>18324500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>124.0955129791748</v>
+        <v>124.0357815469104</v>
       </c>
       <c r="C154" t="n">
-        <v>124.5336284399926</v>
+        <v>127.0229160540335</v>
       </c>
       <c r="D154" t="n">
-        <v>122.6517344420986</v>
+        <v>122.8409307827315</v>
       </c>
       <c r="E154" t="n">
-        <v>124.2249603271484</v>
+        <v>126.9532165527344</v>
       </c>
       <c r="F154" t="n">
-        <v>17001400</v>
+        <v>24763700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>123.7968020201654</v>
+        <v>127.3216255408005</v>
       </c>
       <c r="C155" t="n">
-        <v>125.3998980056611</v>
+        <v>128.9147623376428</v>
       </c>
       <c r="D155" t="n">
-        <v>123.4383453031182</v>
+        <v>126.7739812059444</v>
       </c>
       <c r="E155" t="n">
-        <v>124.2846984863281</v>
+        <v>127.3714065551758</v>
       </c>
       <c r="F155" t="n">
-        <v>18324500</v>
+        <v>18933600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>124.0357815469104</v>
+        <v>127.2817912634612</v>
       </c>
       <c r="C156" t="n">
-        <v>127.0229160540335</v>
+        <v>129.213473828279</v>
       </c>
       <c r="D156" t="n">
-        <v>122.8409307827315</v>
+        <v>126.9332937895701</v>
       </c>
       <c r="E156" t="n">
-        <v>126.9532165527344</v>
+        <v>129.0442047119141</v>
       </c>
       <c r="F156" t="n">
-        <v>24763700</v>
+        <v>17312400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>127.3216255408005</v>
+        <v>129.4424953884951</v>
       </c>
       <c r="C157" t="n">
-        <v>128.9147623376428</v>
+        <v>129.8905625261696</v>
       </c>
       <c r="D157" t="n">
-        <v>126.7739812059444</v>
+        <v>128.2874663986241</v>
       </c>
       <c r="E157" t="n">
-        <v>127.3714065551758</v>
+        <v>129.4225769042969</v>
       </c>
       <c r="F157" t="n">
-        <v>18933600</v>
+        <v>17624500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>127.2817912634612</v>
+        <v>130.010060581267</v>
       </c>
       <c r="C158" t="n">
-        <v>129.213473828279</v>
+        <v>131.8919547480997</v>
       </c>
       <c r="D158" t="n">
-        <v>126.9332937895701</v>
+        <v>129.93040183639</v>
       </c>
       <c r="E158" t="n">
-        <v>129.0442047119141</v>
+        <v>131.4637908935547</v>
       </c>
       <c r="F158" t="n">
-        <v>17312400</v>
+        <v>16376000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>129.4424953884951</v>
+        <v>131.3741802679442</v>
       </c>
       <c r="C159" t="n">
-        <v>129.8905625261696</v>
+        <v>131.5534010485827</v>
       </c>
       <c r="D159" t="n">
-        <v>128.2874663986241</v>
+        <v>128.7255839805935</v>
       </c>
       <c r="E159" t="n">
-        <v>129.4225769042969</v>
+        <v>129.3628387451172</v>
       </c>
       <c r="F159" t="n">
-        <v>17624500</v>
+        <v>16016300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>130.010060581267</v>
+        <v>129.0641091249569</v>
       </c>
       <c r="C160" t="n">
-        <v>131.8919547480997</v>
+        <v>129.253296725292</v>
       </c>
       <c r="D160" t="n">
-        <v>129.93040183639</v>
+        <v>126.8536361584495</v>
       </c>
       <c r="E160" t="n">
-        <v>131.4637908935547</v>
+        <v>127.0428161621094</v>
       </c>
       <c r="F160" t="n">
-        <v>16376000</v>
+        <v>17029500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>131.3741802679442</v>
+        <v>128.7853111434159</v>
       </c>
       <c r="C161" t="n">
-        <v>131.5534010485827</v>
+        <v>129.2134749536506</v>
       </c>
       <c r="D161" t="n">
-        <v>128.7255839805935</v>
+        <v>126.236292344555</v>
       </c>
       <c r="E161" t="n">
-        <v>129.3628387451172</v>
+        <v>127.0428161621094</v>
       </c>
       <c r="F161" t="n">
-        <v>16016300</v>
+        <v>16341800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>129.0641091249569</v>
+        <v>126.1367309249001</v>
       </c>
       <c r="C162" t="n">
-        <v>129.253296725292</v>
+        <v>127.5307285199335</v>
       </c>
       <c r="D162" t="n">
-        <v>126.8536361584495</v>
+        <v>125.3700364258034</v>
       </c>
       <c r="E162" t="n">
-        <v>127.0428161621094</v>
+        <v>127.4610214233398</v>
       </c>
       <c r="F162" t="n">
-        <v>17029500</v>
+        <v>16538800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>128.7853111434159</v>
+        <v>127.470976777907</v>
       </c>
       <c r="C163" t="n">
-        <v>129.2134749536506</v>
+        <v>131.8620524738122</v>
       </c>
       <c r="D163" t="n">
-        <v>126.236292344555</v>
+        <v>127.4012696875933</v>
       </c>
       <c r="E163" t="n">
-        <v>127.0428161621094</v>
+        <v>131.3641967773438</v>
       </c>
       <c r="F163" t="n">
-        <v>16341800</v>
+        <v>19867700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>126.1367309249001</v>
+        <v>131.3542490271043</v>
       </c>
       <c r="C164" t="n">
-        <v>127.5307285199335</v>
+        <v>132.7980275509944</v>
       </c>
       <c r="D164" t="n">
-        <v>125.3700364258034</v>
+        <v>130.4182778590603</v>
       </c>
       <c r="E164" t="n">
-        <v>127.4610214233398</v>
+        <v>131.0356292724609</v>
       </c>
       <c r="F164" t="n">
-        <v>16538800</v>
+        <v>10480900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>127.470976777907</v>
+        <v>129.8507311252314</v>
       </c>
       <c r="C165" t="n">
-        <v>131.8620524738122</v>
+        <v>131.184980793923</v>
       </c>
       <c r="D165" t="n">
-        <v>127.4012696875933</v>
+        <v>129.1238508427206</v>
       </c>
       <c r="E165" t="n">
-        <v>131.3641967773438</v>
+        <v>129.7710723876953</v>
       </c>
       <c r="F165" t="n">
-        <v>19867700</v>
+        <v>10340700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>131.3542490271043</v>
+        <v>129.9502974650302</v>
       </c>
       <c r="C166" t="n">
-        <v>132.7980275509944</v>
+        <v>131.1650666644096</v>
       </c>
       <c r="D166" t="n">
-        <v>130.4182778590603</v>
+        <v>129.7412065662402</v>
       </c>
       <c r="E166" t="n">
-        <v>131.0356292724609</v>
+        <v>130.2290954589844</v>
       </c>
       <c r="F166" t="n">
-        <v>10480900</v>
+        <v>10637300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>129.8507311252314</v>
+        <v>130.2988095283542</v>
       </c>
       <c r="C167" t="n">
-        <v>131.184980793923</v>
+        <v>130.5875591827794</v>
       </c>
       <c r="D167" t="n">
-        <v>129.1238508427206</v>
+        <v>128.9745113895137</v>
       </c>
       <c r="E167" t="n">
-        <v>129.7710723876953</v>
+        <v>129.5221557617188</v>
       </c>
       <c r="F167" t="n">
-        <v>10340700</v>
+        <v>16371500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>129.9502974650302</v>
+        <v>129.3429155964338</v>
       </c>
       <c r="C168" t="n">
-        <v>131.1650666644096</v>
+        <v>130.0399257893878</v>
       </c>
       <c r="D168" t="n">
-        <v>129.7412065662402</v>
+        <v>128.1181947261785</v>
       </c>
       <c r="E168" t="n">
-        <v>130.2290954589844</v>
+        <v>129.6416320800781</v>
       </c>
       <c r="F168" t="n">
-        <v>10637300</v>
+        <v>14935400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,25 +4811,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>130.2988095283542</v>
+        <v>130.0087618254011</v>
       </c>
       <c r="C169" t="n">
-        <v>130.5875591827794</v>
+        <v>131.0961549064253</v>
       </c>
       <c r="D169" t="n">
-        <v>128.9745113895137</v>
+        <v>129.9389217008702</v>
       </c>
       <c r="E169" t="n">
-        <v>129.5221557617188</v>
+        <v>130.1184844970703</v>
       </c>
       <c r="F169" t="n">
-        <v>16371500</v>
+        <v>15183700</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>129.3429155964338</v>
+        <v>129.8690812906444</v>
       </c>
       <c r="C170" t="n">
-        <v>130.0399257893878</v>
+        <v>130.2880915922154</v>
       </c>
       <c r="D170" t="n">
-        <v>128.1181947261785</v>
+        <v>126.078161470576</v>
       </c>
       <c r="E170" t="n">
-        <v>129.6416320800781</v>
+        <v>127.285270690918</v>
       </c>
       <c r="F170" t="n">
-        <v>14935400</v>
+        <v>18699200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>130.0087618254011</v>
+        <v>127.7741133789013</v>
       </c>
       <c r="C171" t="n">
-        <v>131.0961549064253</v>
+        <v>130.8068463681294</v>
       </c>
       <c r="D171" t="n">
-        <v>129.9389217008702</v>
+        <v>127.4149725439082</v>
       </c>
       <c r="E171" t="n">
-        <v>130.1184844970703</v>
+        <v>130.0386962890625</v>
       </c>
       <c r="F171" t="n">
-        <v>15183700</v>
+        <v>17935400</v>
       </c>
       <c r="G171" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>129.8690812906444</v>
+        <v>128.8814524975413</v>
       </c>
       <c r="C172" t="n">
-        <v>130.2880915922154</v>
+        <v>132.2134717809921</v>
       </c>
       <c r="D172" t="n">
-        <v>126.078161470576</v>
+        <v>128.4624574279768</v>
       </c>
       <c r="E172" t="n">
-        <v>127.285270690918</v>
+        <v>131.156005859375</v>
       </c>
       <c r="F172" t="n">
-        <v>18699200</v>
+        <v>13786600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>127.7741133789013</v>
+        <v>131.0462673331121</v>
       </c>
       <c r="C173" t="n">
-        <v>130.8068463681294</v>
+        <v>132.4628740535408</v>
       </c>
       <c r="D173" t="n">
-        <v>127.4149725439082</v>
+        <v>130.5474615066649</v>
       </c>
       <c r="E173" t="n">
-        <v>130.0386962890625</v>
+        <v>132.1436462402344</v>
       </c>
       <c r="F173" t="n">
-        <v>17935400</v>
+        <v>14200400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>128.8814524975413</v>
+        <v>133.370718441355</v>
       </c>
       <c r="C174" t="n">
-        <v>132.2134717809921</v>
+        <v>133.6300920185431</v>
       </c>
       <c r="D174" t="n">
-        <v>128.4624574279768</v>
+        <v>130.4776352080381</v>
       </c>
       <c r="E174" t="n">
-        <v>131.156005859375</v>
+        <v>131.1360626220703</v>
       </c>
       <c r="F174" t="n">
-        <v>13786600</v>
+        <v>25323000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>131.0462673331121</v>
+        <v>131.2058999637278</v>
       </c>
       <c r="C175" t="n">
-        <v>132.4628740535408</v>
+        <v>133.1512398071679</v>
       </c>
       <c r="D175" t="n">
-        <v>130.5474615066649</v>
+        <v>130.8168319950398</v>
       </c>
       <c r="E175" t="n">
-        <v>132.1436462402344</v>
+        <v>133.0215454101562</v>
       </c>
       <c r="F175" t="n">
-        <v>14200400</v>
+        <v>17183200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>133.370718441355</v>
+        <v>132.6225008315265</v>
       </c>
       <c r="C176" t="n">
-        <v>133.6300920185431</v>
+        <v>134.8372000065807</v>
       </c>
       <c r="D176" t="n">
-        <v>130.4776352080381</v>
+        <v>131.7445976710087</v>
       </c>
       <c r="E176" t="n">
-        <v>131.1360626220703</v>
+        <v>133.8794860839844</v>
       </c>
       <c r="F176" t="n">
-        <v>25323000</v>
+        <v>16957100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>131.2058999637278</v>
+        <v>132.5925684137131</v>
       </c>
       <c r="C177" t="n">
-        <v>133.1512398071679</v>
+        <v>133.3307912944098</v>
       </c>
       <c r="D177" t="n">
-        <v>130.8168319950398</v>
+        <v>130.0187285230658</v>
       </c>
       <c r="E177" t="n">
-        <v>133.0215454101562</v>
+        <v>130.5374908447266</v>
       </c>
       <c r="F177" t="n">
-        <v>17183200</v>
+        <v>28471600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>132.6225008315265</v>
+        <v>124.112876676945</v>
       </c>
       <c r="C178" t="n">
-        <v>134.8372000065807</v>
+        <v>125.49955634699</v>
       </c>
       <c r="D178" t="n">
-        <v>131.7445976710087</v>
+        <v>120.1024733345915</v>
       </c>
       <c r="E178" t="n">
-        <v>133.8794860839844</v>
+        <v>121.0502014160156</v>
       </c>
       <c r="F178" t="n">
-        <v>16957100</v>
+        <v>53006600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>132.5925684137131</v>
+        <v>121.0502017985552</v>
       </c>
       <c r="C179" t="n">
-        <v>133.3307912944098</v>
+        <v>121.6587455533669</v>
       </c>
       <c r="D179" t="n">
-        <v>130.0187285230658</v>
+        <v>118.6260126387565</v>
       </c>
       <c r="E179" t="n">
-        <v>130.5374908447266</v>
+        <v>119.9827575683594</v>
       </c>
       <c r="F179" t="n">
-        <v>28471600</v>
+        <v>30330600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>124.112876676945</v>
+        <v>120.401759010853</v>
       </c>
       <c r="C180" t="n">
-        <v>125.49955634699</v>
+        <v>120.7608998332451</v>
       </c>
       <c r="D180" t="n">
-        <v>120.1024733345915</v>
+        <v>117.638370328068</v>
       </c>
       <c r="E180" t="n">
-        <v>121.0502014160156</v>
+        <v>118.2868194580078</v>
       </c>
       <c r="F180" t="n">
-        <v>53006600</v>
+        <v>28796600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>121.0502017985552</v>
+        <v>118.0473918040102</v>
       </c>
       <c r="C181" t="n">
-        <v>121.6587455533669</v>
+        <v>119.1447631286873</v>
       </c>
       <c r="D181" t="n">
-        <v>118.6260126387565</v>
+        <v>117.7580835037564</v>
       </c>
       <c r="E181" t="n">
-        <v>119.9827575683594</v>
+        <v>118.2568893432617</v>
       </c>
       <c r="F181" t="n">
-        <v>30330600</v>
+        <v>22062200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>120.401759010853</v>
+        <v>118.6758897292679</v>
       </c>
       <c r="C182" t="n">
-        <v>120.7608998332451</v>
+        <v>118.8853872778886</v>
       </c>
       <c r="D182" t="n">
-        <v>117.638370328068</v>
+        <v>117.0497853597791</v>
       </c>
       <c r="E182" t="n">
-        <v>118.2868194580078</v>
+        <v>118.6160354614258</v>
       </c>
       <c r="F182" t="n">
-        <v>28796600</v>
+        <v>21613100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>118.0473918040102</v>
+        <v>117.8279207851919</v>
       </c>
       <c r="C183" t="n">
-        <v>119.1447631286873</v>
+        <v>118.7956053707809</v>
       </c>
       <c r="D183" t="n">
-        <v>117.7580835037564</v>
+        <v>114.4360394170558</v>
       </c>
       <c r="E183" t="n">
-        <v>118.2568893432617</v>
+        <v>115.4735565185547</v>
       </c>
       <c r="F183" t="n">
-        <v>22062200</v>
+        <v>42191000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>118.6758897292679</v>
+        <v>114.4559959694409</v>
       </c>
       <c r="C184" t="n">
-        <v>118.8853872778886</v>
+        <v>115.7030106192767</v>
       </c>
       <c r="D184" t="n">
-        <v>117.0497853597791</v>
+        <v>113.2887844727029</v>
       </c>
       <c r="E184" t="n">
-        <v>118.6160354614258</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F184" t="n">
-        <v>21613100</v>
+        <v>26176200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>117.8279207851919</v>
+        <v>113.598048691841</v>
       </c>
       <c r="C185" t="n">
-        <v>118.7956053707809</v>
+        <v>114.2963738476551</v>
       </c>
       <c r="D185" t="n">
-        <v>114.4360394170558</v>
+        <v>112.4607719459876</v>
       </c>
       <c r="E185" t="n">
-        <v>115.4735565185547</v>
+        <v>112.7899780273438</v>
       </c>
       <c r="F185" t="n">
-        <v>42191000</v>
+        <v>27366400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>114.4559959694409</v>
+        <v>112.829882918774</v>
       </c>
       <c r="C186" t="n">
-        <v>115.7030106192767</v>
+        <v>117.0098784207316</v>
       </c>
       <c r="D186" t="n">
-        <v>113.2887844727029</v>
+        <v>112.6902178882183</v>
       </c>
       <c r="E186" t="n">
-        <v>114.326301574707</v>
+        <v>116.6108322143555</v>
       </c>
       <c r="F186" t="n">
-        <v>26176200</v>
+        <v>32880600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>113.598048691841</v>
+        <v>119.613646228699</v>
       </c>
       <c r="C187" t="n">
-        <v>114.2963738476551</v>
+        <v>119.6535516106658</v>
       </c>
       <c r="D187" t="n">
-        <v>112.4607719459876</v>
+        <v>117.009879041958</v>
       </c>
       <c r="E187" t="n">
-        <v>112.7899780273438</v>
+        <v>117.4588012695312</v>
       </c>
       <c r="F187" t="n">
-        <v>27366400</v>
+        <v>22870400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>112.829882918774</v>
+        <v>118.0673439785114</v>
       </c>
       <c r="C188" t="n">
-        <v>117.0098784207316</v>
+        <v>120.601278627145</v>
       </c>
       <c r="D188" t="n">
-        <v>112.6902178882183</v>
+        <v>117.8179410518094</v>
       </c>
       <c r="E188" t="n">
-        <v>116.6108322143555</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F188" t="n">
-        <v>32880600</v>
+        <v>36638100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>119.613646228699</v>
+        <v>117.9675872503352</v>
       </c>
       <c r="C189" t="n">
-        <v>119.6535516106658</v>
+        <v>119.8929781965846</v>
       </c>
       <c r="D189" t="n">
-        <v>117.009879041958</v>
+        <v>117.8678275994195</v>
       </c>
       <c r="E189" t="n">
-        <v>117.4588012695312</v>
+        <v>119.543815612793</v>
       </c>
       <c r="F189" t="n">
-        <v>22870400</v>
+        <v>19514100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>118.0673439785114</v>
+        <v>120.0924945255443</v>
       </c>
       <c r="C190" t="n">
-        <v>120.601278627145</v>
+        <v>120.2122106703836</v>
       </c>
       <c r="D190" t="n">
-        <v>117.8179410518094</v>
+        <v>117.7181814033632</v>
       </c>
       <c r="E190" t="n">
         <v>118.596076965332</v>
       </c>
       <c r="F190" t="n">
-        <v>36638100</v>
+        <v>23959000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>117.9675872503352</v>
+        <v>119.4240987453198</v>
       </c>
       <c r="C191" t="n">
-        <v>119.8929781965846</v>
+        <v>120.53144836951</v>
       </c>
       <c r="D191" t="n">
-        <v>117.8678275994195</v>
+        <v>117.2493048793001</v>
       </c>
       <c r="E191" t="n">
-        <v>119.543815612793</v>
+        <v>120.3019943237305</v>
       </c>
       <c r="F191" t="n">
-        <v>19514100</v>
+        <v>22414900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>120.0924945255443</v>
+        <v>120.2820441244615</v>
       </c>
       <c r="C192" t="n">
-        <v>120.2122106703836</v>
+        <v>121.5689641496319</v>
       </c>
       <c r="D192" t="n">
-        <v>117.7181814033632</v>
+        <v>119.1746945123655</v>
       </c>
       <c r="E192" t="n">
-        <v>118.596076965332</v>
+        <v>120.2122116088867</v>
       </c>
       <c r="F192" t="n">
-        <v>23959000</v>
+        <v>22438000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>119.4240987453198</v>
+        <v>120.3019933173184</v>
       </c>
       <c r="C193" t="n">
-        <v>120.53144836951</v>
+        <v>121.3195615310648</v>
       </c>
       <c r="D193" t="n">
-        <v>117.2493048793001</v>
+        <v>119.2445273327187</v>
       </c>
       <c r="E193" t="n">
-        <v>120.3019943237305</v>
+        <v>120.7509231567383</v>
       </c>
       <c r="F193" t="n">
-        <v>22414900</v>
+        <v>14753500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>120.2820441244615</v>
+        <v>119.4540258740917</v>
       </c>
       <c r="C194" t="n">
-        <v>121.5689641496319</v>
+        <v>121.1998463936268</v>
       </c>
       <c r="D194" t="n">
-        <v>119.1746945123655</v>
+        <v>118.2968002303814</v>
       </c>
       <c r="E194" t="n">
-        <v>120.2122116088867</v>
+        <v>120.5314483642578</v>
       </c>
       <c r="F194" t="n">
-        <v>22438000</v>
+        <v>20722500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>120.3019933173184</v>
+        <v>120.8506818055627</v>
       </c>
       <c r="C195" t="n">
-        <v>121.3195615310648</v>
+        <v>122.646385926027</v>
       </c>
       <c r="D195" t="n">
-        <v>119.2445273327187</v>
+        <v>119.5936889212378</v>
       </c>
       <c r="E195" t="n">
-        <v>120.7509231567383</v>
+        <v>120.7409439086914</v>
       </c>
       <c r="F195" t="n">
-        <v>14753500</v>
+        <v>23060700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>119.4540258740917</v>
+        <v>119.2944114353401</v>
       </c>
       <c r="C196" t="n">
-        <v>121.1998463936268</v>
+        <v>120.7209965009543</v>
       </c>
       <c r="D196" t="n">
-        <v>118.2968002303814</v>
+        <v>117.1694935982547</v>
       </c>
       <c r="E196" t="n">
-        <v>120.5314483642578</v>
+        <v>117.8478698730469</v>
       </c>
       <c r="F196" t="n">
-        <v>20722500</v>
+        <v>21711100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>120.8506818055627</v>
+        <v>117.9176994360996</v>
       </c>
       <c r="C197" t="n">
-        <v>122.646385926027</v>
+        <v>118.1970371043968</v>
       </c>
       <c r="D197" t="n">
-        <v>119.5936889212378</v>
+        <v>116.5210491504798</v>
       </c>
       <c r="E197" t="n">
-        <v>120.7409439086914</v>
+        <v>116.9001388549805</v>
       </c>
       <c r="F197" t="n">
-        <v>23060700</v>
+        <v>36526800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>119.2944114353401</v>
+        <v>116.6806630640479</v>
       </c>
       <c r="C198" t="n">
-        <v>120.7209965009543</v>
+        <v>118.1172263420262</v>
       </c>
       <c r="D198" t="n">
-        <v>117.1694935982547</v>
+        <v>116.6706848159582</v>
       </c>
       <c r="E198" t="n">
-        <v>117.8478698730469</v>
+        <v>116.9001388549805</v>
       </c>
       <c r="F198" t="n">
-        <v>21711100</v>
+        <v>17053900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>117.9176994360996</v>
+        <v>119.4240968222584</v>
       </c>
       <c r="C199" t="n">
-        <v>118.1970371043968</v>
+        <v>119.9628080586903</v>
       </c>
       <c r="D199" t="n">
-        <v>116.5210491504798</v>
+        <v>116.0621426214644</v>
       </c>
       <c r="E199" t="n">
-        <v>116.9001388549805</v>
+        <v>119.1347885131836</v>
       </c>
       <c r="F199" t="n">
-        <v>36526800</v>
+        <v>23411400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>116.6806630640479</v>
+        <v>119.2744498995579</v>
       </c>
       <c r="C200" t="n">
-        <v>118.1172263420262</v>
+        <v>120.112447667685</v>
       </c>
       <c r="D200" t="n">
-        <v>116.6706848159582</v>
+        <v>118.6459572818424</v>
       </c>
       <c r="E200" t="n">
-        <v>116.9001388549805</v>
+        <v>118.7157897949219</v>
       </c>
       <c r="F200" t="n">
-        <v>17053900</v>
+        <v>20600100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>119.4240968222584</v>
+        <v>117.1894451773868</v>
       </c>
       <c r="C201" t="n">
-        <v>119.9628080586903</v>
+        <v>118.2967947502302</v>
       </c>
       <c r="D201" t="n">
-        <v>116.0621426214644</v>
+        <v>115.1044328099781</v>
       </c>
       <c r="E201" t="n">
-        <v>119.1347885131836</v>
+        <v>115.5034790039062</v>
       </c>
       <c r="F201" t="n">
-        <v>23411400</v>
+        <v>20384700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>119.2744498995579</v>
+        <v>117.0098811702962</v>
       </c>
       <c r="C202" t="n">
-        <v>120.112447667685</v>
+        <v>117.5984684398727</v>
       </c>
       <c r="D202" t="n">
-        <v>118.6459572818424</v>
+        <v>114.8151307892405</v>
       </c>
       <c r="E202" t="n">
-        <v>118.7157897949219</v>
+        <v>115.413703918457</v>
       </c>
       <c r="F202" t="n">
-        <v>20600100</v>
+        <v>36636000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>117.1894451773868</v>
+        <v>116.1918382308837</v>
       </c>
       <c r="C203" t="n">
-        <v>118.2967947502302</v>
+        <v>116.521051925122</v>
       </c>
       <c r="D203" t="n">
-        <v>115.1044328099781</v>
+        <v>113.9272553645249</v>
       </c>
       <c r="E203" t="n">
-        <v>115.5034790039062</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F203" t="n">
-        <v>20384700</v>
+        <v>20367000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>117.0098811702962</v>
+        <v>113.6978053385094</v>
       </c>
       <c r="C204" t="n">
-        <v>117.5984684398727</v>
+        <v>114.3362762101566</v>
       </c>
       <c r="D204" t="n">
-        <v>114.8151307892405</v>
+        <v>112.6602882692895</v>
       </c>
       <c r="E204" t="n">
-        <v>115.413703918457</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F204" t="n">
-        <v>36636000</v>
+        <v>23034000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>116.1918382308837</v>
+        <v>109.8669732552887</v>
       </c>
       <c r="C205" t="n">
-        <v>116.521051925122</v>
+        <v>110.4455898652017</v>
       </c>
       <c r="D205" t="n">
-        <v>113.9272553645249</v>
+        <v>106.9938543130583</v>
       </c>
       <c r="E205" t="n">
-        <v>114.326301574707</v>
+        <v>108.5601043701172</v>
       </c>
       <c r="F205" t="n">
-        <v>20367000</v>
+        <v>40391400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>113.6978053385094</v>
+        <v>109.0688912954154</v>
       </c>
       <c r="C206" t="n">
-        <v>114.3362762101566</v>
+        <v>112.1814349941213</v>
       </c>
       <c r="D206" t="n">
-        <v>112.6602882692895</v>
+        <v>108.8992991295087</v>
       </c>
       <c r="E206" t="n">
-        <v>112.989501953125</v>
+        <v>111.5728912353516</v>
       </c>
       <c r="F206" t="n">
-        <v>23034000</v>
+        <v>29512200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>109.8669732552887</v>
+        <v>111.1339433224697</v>
       </c>
       <c r="C207" t="n">
-        <v>110.4455898652017</v>
+        <v>112.1016278755018</v>
       </c>
       <c r="D207" t="n">
-        <v>106.9938543130583</v>
+        <v>109.1087928180449</v>
       </c>
       <c r="E207" t="n">
-        <v>108.5601043701172</v>
+        <v>110.3857345581055</v>
       </c>
       <c r="F207" t="n">
-        <v>40391400</v>
+        <v>29523300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>109.0688912954154</v>
+        <v>112.7001980505562</v>
       </c>
       <c r="C208" t="n">
-        <v>112.1814349941213</v>
+        <v>113.228931048236</v>
       </c>
       <c r="D208" t="n">
-        <v>108.8992991295087</v>
+        <v>111.0341882926515</v>
       </c>
       <c r="E208" t="n">
-        <v>111.5728912353516</v>
+        <v>111.2736129760742</v>
       </c>
       <c r="F208" t="n">
-        <v>29512200</v>
+        <v>19941400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>111.1339433224697</v>
+        <v>112.879763389333</v>
       </c>
       <c r="C209" t="n">
-        <v>112.1016278755018</v>
+        <v>113.5880667705184</v>
       </c>
       <c r="D209" t="n">
-        <v>109.1087928180449</v>
+        <v>111.5429597770651</v>
       </c>
       <c r="E209" t="n">
-        <v>110.3857345581055</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F209" t="n">
-        <v>29523300</v>
+        <v>19892000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>112.7001980505562</v>
+        <v>110.9743243964893</v>
       </c>
       <c r="C210" t="n">
-        <v>113.228931048236</v>
+        <v>112.4906984566786</v>
       </c>
       <c r="D210" t="n">
-        <v>111.0341882926515</v>
+        <v>110.7748050991254</v>
       </c>
       <c r="E210" t="n">
-        <v>111.2736129760742</v>
+        <v>111.942008972168</v>
       </c>
       <c r="F210" t="n">
-        <v>19941400</v>
+        <v>20464500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>112.879763389333</v>
+        <v>111.6826280597077</v>
       </c>
       <c r="C211" t="n">
-        <v>113.5880667705184</v>
+        <v>113.8873566399898</v>
       </c>
       <c r="D211" t="n">
-        <v>111.5429597770651</v>
+        <v>111.6626791743936</v>
       </c>
       <c r="E211" t="n">
-        <v>112.8298797607422</v>
+        <v>113.6279754638672</v>
       </c>
       <c r="F211" t="n">
-        <v>19892000</v>
+        <v>12461700</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>110.9743243964893</v>
+        <v>114.4559909872762</v>
       </c>
       <c r="C212" t="n">
-        <v>112.4906984566786</v>
+        <v>115.26405400962</v>
       </c>
       <c r="D212" t="n">
-        <v>110.7748050991254</v>
+        <v>113.7377093624492</v>
       </c>
       <c r="E212" t="n">
-        <v>111.942008972168</v>
+        <v>114.5058670043945</v>
       </c>
       <c r="F212" t="n">
-        <v>20464500</v>
+        <v>17043400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>111.6826280597077</v>
+        <v>114.8051528853423</v>
       </c>
       <c r="C213" t="n">
-        <v>113.8873566399898</v>
+        <v>115.6032376551602</v>
       </c>
       <c r="D213" t="n">
-        <v>111.6626791743936</v>
+        <v>113.2289246190302</v>
       </c>
       <c r="E213" t="n">
-        <v>113.6279754638672</v>
+        <v>113.4284439086914</v>
       </c>
       <c r="F213" t="n">
-        <v>12461700</v>
+        <v>14682000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>114.4559909872762</v>
+        <v>112.9795273843265</v>
       </c>
       <c r="C214" t="n">
-        <v>115.26405400962</v>
+        <v>114.4559960800755</v>
       </c>
       <c r="D214" t="n">
-        <v>113.7377093624492</v>
+        <v>111.8023452492967</v>
       </c>
       <c r="E214" t="n">
-        <v>114.5058670043945</v>
+        <v>112.2612457275391</v>
       </c>
       <c r="F214" t="n">
-        <v>17043400</v>
+        <v>16467900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>114.8051528853423</v>
+        <v>113.4883080789502</v>
       </c>
       <c r="C215" t="n">
-        <v>115.6032376551602</v>
+        <v>115.3139316886614</v>
       </c>
       <c r="D215" t="n">
-        <v>113.2289246190302</v>
+        <v>113.288781174082</v>
       </c>
       <c r="E215" t="n">
-        <v>113.4284439086914</v>
+        <v>114.6754608154297</v>
       </c>
       <c r="F215" t="n">
-        <v>14682000</v>
+        <v>20777600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>112.9795273843265</v>
+        <v>116.6806604264181</v>
       </c>
       <c r="C216" t="n">
-        <v>114.4559960800755</v>
+        <v>117.8079588775203</v>
       </c>
       <c r="D216" t="n">
-        <v>111.8023452492967</v>
+        <v>113.3286845943574</v>
       </c>
       <c r="E216" t="n">
-        <v>112.2612457275391</v>
+        <v>113.967155456543</v>
       </c>
       <c r="F216" t="n">
-        <v>16467900</v>
+        <v>28289800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>113.4883080789502</v>
+        <v>113.6878284476981</v>
       </c>
       <c r="C217" t="n">
-        <v>115.3139316886614</v>
+        <v>114.1267800313856</v>
       </c>
       <c r="D217" t="n">
-        <v>113.288781174082</v>
+        <v>111.8721754576813</v>
       </c>
       <c r="E217" t="n">
-        <v>114.6754608154297</v>
+        <v>111.9320297241211</v>
       </c>
       <c r="F217" t="n">
-        <v>20777600</v>
+        <v>17738900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>116.6806604264181</v>
+        <v>111.2436859074791</v>
       </c>
       <c r="C218" t="n">
-        <v>117.8079588775203</v>
+        <v>111.5329942219063</v>
       </c>
       <c r="D218" t="n">
-        <v>113.3286845943574</v>
+        <v>109.6275521682845</v>
       </c>
       <c r="E218" t="n">
-        <v>113.967155456543</v>
+        <v>110.1263580322266</v>
       </c>
       <c r="F218" t="n">
-        <v>28289800</v>
+        <v>22717000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>113.6878284476981</v>
+        <v>109.268405092928</v>
       </c>
       <c r="C219" t="n">
-        <v>114.1267800313856</v>
+        <v>109.737283796026</v>
       </c>
       <c r="D219" t="n">
-        <v>111.8721754576813</v>
+        <v>108.4603420750963</v>
       </c>
       <c r="E219" t="n">
-        <v>111.9320297241211</v>
+        <v>109.0688858032227</v>
       </c>
       <c r="F219" t="n">
-        <v>17738900</v>
+        <v>23494800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>111.2436859074791</v>
+        <v>107.25323944858</v>
       </c>
       <c r="C220" t="n">
-        <v>111.5329942219063</v>
+        <v>108.3007272005749</v>
       </c>
       <c r="D220" t="n">
-        <v>109.6275521682845</v>
+        <v>106.5349577836844</v>
       </c>
       <c r="E220" t="n">
-        <v>110.1263580322266</v>
+        <v>108.14111328125</v>
       </c>
       <c r="F220" t="n">
-        <v>22717000</v>
+        <v>21516800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>109.268405092928</v>
+        <v>107.8617828177618</v>
       </c>
       <c r="C221" t="n">
-        <v>109.737283796026</v>
+        <v>109.3382439135796</v>
       </c>
       <c r="D221" t="n">
-        <v>108.4603420750963</v>
+        <v>107.7520449187408</v>
       </c>
       <c r="E221" t="n">
-        <v>109.0688858032227</v>
+        <v>109.2085571289062</v>
       </c>
       <c r="F221" t="n">
-        <v>23494800</v>
+        <v>18405900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>107.25323944858</v>
+        <v>109.6574762821653</v>
       </c>
       <c r="C222" t="n">
-        <v>108.3007272005749</v>
+        <v>112.2412945440321</v>
       </c>
       <c r="D222" t="n">
-        <v>106.5349577836844</v>
+        <v>109.6275491489408</v>
       </c>
       <c r="E222" t="n">
-        <v>108.14111328125</v>
+        <v>111.4731292724609</v>
       </c>
       <c r="F222" t="n">
-        <v>21516800</v>
+        <v>19008700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>107.8617828177618</v>
+        <v>113.6878264165269</v>
       </c>
       <c r="C223" t="n">
-        <v>109.3382439135796</v>
+        <v>115.7528822947127</v>
       </c>
       <c r="D223" t="n">
-        <v>107.7520449187408</v>
+        <v>112.5704985921816</v>
       </c>
       <c r="E223" t="n">
-        <v>109.2085571289062</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F223" t="n">
-        <v>18405900</v>
+        <v>24867900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>109.6574762821653</v>
+        <v>112.9595787445935</v>
       </c>
       <c r="C224" t="n">
-        <v>112.2412945440321</v>
+        <v>114.4160909468376</v>
       </c>
       <c r="D224" t="n">
-        <v>109.6275491489408</v>
+        <v>112.1814352072651</v>
       </c>
       <c r="E224" t="n">
-        <v>111.4731292724609</v>
+        <v>113.9472122192383</v>
       </c>
       <c r="F224" t="n">
-        <v>19008700</v>
+        <v>23480000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>113.6878264165269</v>
+        <v>111.3434398479761</v>
       </c>
       <c r="C225" t="n">
-        <v>115.7528822947127</v>
+        <v>112.7600466022415</v>
       </c>
       <c r="D225" t="n">
-        <v>112.5704985921816</v>
+        <v>110.1762360128914</v>
       </c>
       <c r="E225" t="n">
-        <v>112.8298797607422</v>
+        <v>110.8346557617188</v>
       </c>
       <c r="F225" t="n">
-        <v>24867900</v>
+        <v>28747000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>112.9595787445935</v>
+        <v>110.2560414658192</v>
       </c>
       <c r="C226" t="n">
-        <v>114.4160909468376</v>
+        <v>111.642728727712</v>
       </c>
       <c r="D226" t="n">
-        <v>112.1814352072651</v>
+        <v>109.6275488363764</v>
       </c>
       <c r="E226" t="n">
-        <v>113.9472122192383</v>
+        <v>110.9344177246094</v>
       </c>
       <c r="F226" t="n">
-        <v>23480000</v>
+        <v>22799100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>111.3434398479761</v>
+        <v>112.8298784424625</v>
       </c>
       <c r="C227" t="n">
-        <v>112.7600466022415</v>
+        <v>113.0194270954852</v>
       </c>
       <c r="D227" t="n">
-        <v>110.1762360128914</v>
+        <v>109.8969053059805</v>
       </c>
       <c r="E227" t="n">
-        <v>110.8346557617188</v>
+        <v>110.4455871582031</v>
       </c>
       <c r="F227" t="n">
-        <v>28747000</v>
+        <v>23942500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>110.2560414658192</v>
+        <v>108.7496500450106</v>
       </c>
       <c r="C228" t="n">
-        <v>111.642728727712</v>
+        <v>111.4132713715266</v>
       </c>
       <c r="D228" t="n">
-        <v>109.6275488363764</v>
+        <v>108.3007202277679</v>
       </c>
       <c r="E228" t="n">
-        <v>110.9344177246094</v>
+        <v>111.2835845947266</v>
       </c>
       <c r="F228" t="n">
-        <v>22799100</v>
+        <v>29620000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>112.8298784424625</v>
+        <v>112.181431315027</v>
       </c>
       <c r="C229" t="n">
-        <v>113.0194270954852</v>
+        <v>112.8897423116165</v>
       </c>
       <c r="D229" t="n">
-        <v>109.8969053059805</v>
+        <v>111.0940382280446</v>
       </c>
       <c r="E229" t="n">
-        <v>110.4455871582031</v>
+        <v>112.0716934204102</v>
       </c>
       <c r="F229" t="n">
-        <v>23942500</v>
+        <v>21446300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>108.7496500450106</v>
+        <v>113.7975687180191</v>
       </c>
       <c r="C230" t="n">
-        <v>111.4132713715266</v>
+        <v>114.2863963302149</v>
       </c>
       <c r="D230" t="n">
-        <v>108.3007202277679</v>
+        <v>110.7748064209645</v>
       </c>
       <c r="E230" t="n">
-        <v>111.2835845947266</v>
+        <v>111.8023452758789</v>
       </c>
       <c r="F230" t="n">
-        <v>29620000</v>
+        <v>23203100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>112.181431315027</v>
+        <v>110.3458340692701</v>
       </c>
       <c r="C231" t="n">
-        <v>112.8897423116165</v>
+        <v>112.0218220801941</v>
       </c>
       <c r="D231" t="n">
-        <v>111.0940382280446</v>
+        <v>110.2360961700712</v>
       </c>
       <c r="E231" t="n">
-        <v>112.0716934204102</v>
+        <v>111.5828704833984</v>
       </c>
       <c r="F231" t="n">
-        <v>21446300</v>
+        <v>18819300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>113.7975687180191</v>
+        <v>110.8147094920761</v>
       </c>
       <c r="C232" t="n">
-        <v>114.2863963302149</v>
+        <v>112.4308355753539</v>
       </c>
       <c r="D232" t="n">
-        <v>110.7748064209645</v>
+        <v>110.4954740524384</v>
       </c>
       <c r="E232" t="n">
-        <v>111.8023452758789</v>
+        <v>112.3909378051758</v>
       </c>
       <c r="F232" t="n">
-        <v>23203100</v>
+        <v>19144000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>110.3458340692701</v>
+        <v>112.1714606731287</v>
       </c>
       <c r="C233" t="n">
-        <v>112.0218220801941</v>
+        <v>113.069305103701</v>
       </c>
       <c r="D233" t="n">
-        <v>110.2360961700712</v>
+        <v>111.9220577510424</v>
       </c>
       <c r="E233" t="n">
-        <v>111.5828704833984</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F233" t="n">
-        <v>18819300</v>
+        <v>17005800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>110.8147094920761</v>
+        <v>112.1016271407472</v>
       </c>
       <c r="C234" t="n">
-        <v>112.4308355753539</v>
+        <v>115.7728384249456</v>
       </c>
       <c r="D234" t="n">
-        <v>110.4954740524384</v>
+        <v>112.011838131802</v>
       </c>
       <c r="E234" t="n">
-        <v>112.3909378051758</v>
+        <v>115.7329330444336</v>
       </c>
       <c r="F234" t="n">
-        <v>19144000</v>
+        <v>22054700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>112.1714606731287</v>
+        <v>115.8925486214695</v>
       </c>
       <c r="C235" t="n">
-        <v>113.069305103701</v>
+        <v>116.0421918977476</v>
       </c>
       <c r="D235" t="n">
-        <v>111.9220577510424</v>
+        <v>114.5357961092488</v>
       </c>
       <c r="E235" t="n">
-        <v>112.989501953125</v>
+        <v>115.4436264038086</v>
       </c>
       <c r="F235" t="n">
-        <v>17005800</v>
+        <v>16822200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>112.1016271407472</v>
+        <v>115.3837731369623</v>
       </c>
       <c r="C236" t="n">
-        <v>115.7728384249456</v>
+        <v>116.1718796839166</v>
       </c>
       <c r="D236" t="n">
-        <v>112.011838131802</v>
+        <v>114.3662049383982</v>
       </c>
       <c r="E236" t="n">
-        <v>115.7329330444336</v>
+        <v>114.9946975708008</v>
       </c>
       <c r="F236" t="n">
-        <v>22054700</v>
+        <v>14520000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>115.8925486214695</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="C237" t="n">
-        <v>116.0421918977476</v>
+        <v>114.9049142110052</v>
       </c>
       <c r="D237" t="n">
-        <v>114.5357961092488</v>
+        <v>113.6479213564676</v>
       </c>
       <c r="E237" t="n">
-        <v>115.4436264038086</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="F237" t="n">
-        <v>16822200</v>
+        <v>18131100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>115.3837731369623</v>
+        <v>116.0222446904477</v>
       </c>
       <c r="C238" t="n">
-        <v>116.1718796839166</v>
+        <v>116.0322153274834</v>
       </c>
       <c r="D238" t="n">
-        <v>114.3662049383982</v>
+        <v>114.2065916862473</v>
       </c>
       <c r="E238" t="n">
-        <v>114.9946975708008</v>
+        <v>114.9248657226562</v>
       </c>
       <c r="F238" t="n">
-        <v>14520000</v>
+        <v>20675000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>114.0569458007812</v>
+        <v>114.9148971425914</v>
       </c>
       <c r="C239" t="n">
-        <v>114.9049142110052</v>
+        <v>116.590885146559</v>
       </c>
       <c r="D239" t="n">
-        <v>113.6479213564676</v>
+        <v>113.7177585048011</v>
       </c>
       <c r="E239" t="n">
-        <v>114.0569458007812</v>
+        <v>114.0270233154297</v>
       </c>
       <c r="F239" t="n">
-        <v>18131100</v>
+        <v>34286600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>116.0222446904477</v>
+        <v>106.1259298697332</v>
       </c>
       <c r="C240" t="n">
-        <v>116.0322153274834</v>
+        <v>106.7444518635443</v>
       </c>
       <c r="D240" t="n">
-        <v>114.2065916862473</v>
+        <v>102.6043617877236</v>
       </c>
       <c r="E240" t="n">
-        <v>114.9248657226562</v>
+        <v>103.5919952392578</v>
       </c>
       <c r="F240" t="n">
-        <v>20675000</v>
+        <v>83633100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>114.9148971425914</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C241" t="n">
-        <v>116.590885146559</v>
+        <v>104.2799987792969</v>
       </c>
       <c r="D241" t="n">
-        <v>113.7177585048011</v>
+        <v>102.1500015258789</v>
       </c>
       <c r="E241" t="n">
-        <v>114.0270233154297</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="F241" t="n">
-        <v>34286600</v>
+        <v>44454200</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>106.1259298697332</v>
+        <v>104.1399993896484</v>
       </c>
       <c r="C242" t="n">
-        <v>106.7444518635443</v>
+        <v>106.5999984741211</v>
       </c>
       <c r="D242" t="n">
-        <v>102.6043617877236</v>
+        <v>104</v>
       </c>
       <c r="E242" t="n">
-        <v>103.5919952392578</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="F242" t="n">
-        <v>83633100</v>
+        <v>35616300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>103.6900024414062</v>
+        <v>105.5800018310547</v>
       </c>
       <c r="C243" t="n">
-        <v>104.2799987792969</v>
+        <v>106.0699996948242</v>
       </c>
       <c r="D243" t="n">
-        <v>102.1500015258789</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="E243" t="n">
-        <v>103.6999969482422</v>
+        <v>105.379997253418</v>
       </c>
       <c r="F243" t="n">
-        <v>44454200</v>
+        <v>27032500</v>
       </c>
       <c r="G243" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>104.1399993896484</v>
+        <v>105.5100021362305</v>
       </c>
       <c r="C244" t="n">
-        <v>106.5999984741211</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="D244" t="n">
-        <v>104</v>
+        <v>104.0800018310547</v>
       </c>
       <c r="E244" t="n">
-        <v>106.4899978637695</v>
+        <v>104.3399963378906</v>
       </c>
       <c r="F244" t="n">
-        <v>35616300</v>
+        <v>28409400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>105.5800018310547</v>
+        <v>103.6100006103516</v>
       </c>
       <c r="C245" t="n">
-        <v>106.0699996948242</v>
+        <v>103.75</v>
       </c>
       <c r="D245" t="n">
-        <v>104.4000015258789</v>
+        <v>102.2699966430664</v>
       </c>
       <c r="E245" t="n">
-        <v>105.379997253418</v>
+        <v>102.629997253418</v>
       </c>
       <c r="F245" t="n">
-        <v>27032500</v>
+        <v>29816600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>105.5100021362305</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="C246" t="n">
-        <v>106.0899963378906</v>
+        <v>103.4000015258789</v>
       </c>
       <c r="D246" t="n">
-        <v>104.0800018310547</v>
+        <v>102.5</v>
       </c>
       <c r="E246" t="n">
-        <v>104.3399963378906</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="F246" t="n">
-        <v>28409400</v>
+        <v>19420800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>103.6100006103516</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="C247" t="n">
-        <v>103.75</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="D247" t="n">
-        <v>102.2699966430664</v>
+        <v>102.8399963378906</v>
       </c>
       <c r="E247" t="n">
-        <v>102.629997253418</v>
+        <v>104.870002746582</v>
       </c>
       <c r="F247" t="n">
-        <v>29816600</v>
+        <v>34188700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>103.0899963378906</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="C248" t="n">
-        <v>103.4000015258789</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D248" t="n">
-        <v>102.5</v>
+        <v>104.6600036621094</v>
       </c>
       <c r="E248" t="n">
-        <v>103.0899963378906</v>
+        <v>105.9199981689453</v>
       </c>
       <c r="F248" t="n">
-        <v>19420800</v>
+        <v>22074600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>103.0800018310547</v>
+        <v>105.9700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>104.9899978637695</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="D249" t="n">
-        <v>102.8399963378906</v>
+        <v>105.4599990844727</v>
       </c>
       <c r="E249" t="n">
-        <v>104.870002746582</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="F249" t="n">
-        <v>34188700</v>
+        <v>25181800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>105.1100006103516</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="C250" t="n">
-        <v>106.6399993896484</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="D250" t="n">
-        <v>104.6600036621094</v>
+        <v>106.0199966430664</v>
       </c>
       <c r="E250" t="n">
-        <v>105.9199981689453</v>
+        <v>108.4199981689453</v>
       </c>
       <c r="F250" t="n">
-        <v>22074600</v>
+        <v>25541200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>105.9700012207031</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="C251" t="n">
-        <v>106.7799987792969</v>
+        <v>109.2300033569336</v>
       </c>
       <c r="D251" t="n">
-        <v>105.4599990844727</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="E251" t="n">
-        <v>106.0899963378906</v>
+        <v>107.1399993896484</v>
       </c>
       <c r="F251" t="n">
-        <v>25181800</v>
+        <v>20527200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>106.4199981689453</v>
-      </c>
-      <c r="C252" t="n">
-        <v>109.3499984741211</v>
-      </c>
-      <c r="D252" t="n">
-        <v>106.0199966430664</v>
-      </c>
-      <c r="E252" t="n">
-        <v>108.4199981689453</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>25541200</v>
+        <v>21478485</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>108.1999969482422</v>
-      </c>
-      <c r="C253" t="n">
-        <v>109.2300033569336</v>
-      </c>
-      <c r="D253" t="n">
-        <v>106.9300003051758</v>
-      </c>
-      <c r="E253" t="n">
-        <v>107.1399993896484</v>
-      </c>
-      <c r="F253" t="n">
-        <v>20527200</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10662,34 +10628,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="D2" t="n">
         <v>107.14</v>
       </c>
-      <c r="D2" t="n">
-        <v>108.42</v>
-      </c>
       <c r="E2" t="n">
-        <v>108.2</v>
+        <v>106.78</v>
       </c>
       <c r="F2" t="n">
-        <v>109.23</v>
+        <v>106.87</v>
       </c>
       <c r="G2" t="n">
-        <v>106.935</v>
+        <v>105.66</v>
       </c>
       <c r="H2" t="n">
-        <v>20540472</v>
+        <v>21478485</v>
       </c>
       <c r="I2" t="n">
-        <v>24355206</v>
+        <v>24433288</v>
       </c>
       <c r="J2" t="n">
-        <v>852628602880</v>
+        <v>843954323456</v>
       </c>
       <c r="K2" t="n">
-        <v>38.81884</v>
+        <v>38.423916</v>
       </c>
       <c r="L2" t="n">
-        <v>33.167812</v>
+        <v>32.82794</v>
       </c>
       <c r="M2" t="n">
         <v>2.76</v>
@@ -10728,7 +10694,7 @@
         <v>11.848</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.042876</v>
+        <v>8.950877999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.091</v>
@@ -10740,7 +10706,7 @@
         <v>735839977472</v>
       </c>
       <c r="AC2" t="n">
-        <v>920145559552</v>
+        <v>911497756672</v>
       </c>
       <c r="AD2" t="n">
         <v>44073000960</v>
@@ -10767,7 +10733,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:24</t>
+          <t>2026-09-09 09:15:21</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>101.1483716213974</v>
+        <v>101.0987907680863</v>
       </c>
       <c r="C2" t="n">
-        <v>101.6342783470665</v>
+        <v>101.5946161422617</v>
       </c>
       <c r="D2" t="n">
-        <v>100.7021318316984</v>
+        <v>99.5518180216814</v>
       </c>
       <c r="E2" t="n">
-        <v>101.4359512329102</v>
+        <v>99.5716552734375</v>
       </c>
       <c r="F2" t="n">
-        <v>11819700</v>
+        <v>17934900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>101.0987907680863</v>
+        <v>100.1468095744012</v>
       </c>
       <c r="C3" t="n">
-        <v>101.5946161422617</v>
+        <v>101.9218653682149</v>
       </c>
       <c r="D3" t="n">
-        <v>99.5518180216814</v>
+        <v>99.44273843255802</v>
       </c>
       <c r="E3" t="n">
-        <v>99.5716552734375</v>
+        <v>101.7929534912109</v>
       </c>
       <c r="F3" t="n">
-        <v>17934900</v>
+        <v>15900800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>100.1468095744012</v>
+        <v>101.6838731887643</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9218653682149</v>
+        <v>103.1118527512385</v>
       </c>
       <c r="D4" t="n">
-        <v>99.44273843255802</v>
+        <v>101.505375743455</v>
       </c>
       <c r="E4" t="n">
-        <v>101.7929534912109</v>
+        <v>102.6259384155273</v>
       </c>
       <c r="F4" t="n">
-        <v>15900800</v>
+        <v>11641900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>101.6838731887643</v>
+        <v>102.7845975900895</v>
       </c>
       <c r="C5" t="n">
-        <v>103.1118527512385</v>
+        <v>103.1118441401098</v>
       </c>
       <c r="D5" t="n">
-        <v>101.505375743455</v>
+        <v>102.5466035381176</v>
       </c>
       <c r="E5" t="n">
-        <v>102.6259384155273</v>
+        <v>102.8242645263672</v>
       </c>
       <c r="F5" t="n">
-        <v>11641900</v>
+        <v>10756900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>102.7845975900895</v>
+        <v>102.9829286790064</v>
       </c>
       <c r="C6" t="n">
-        <v>103.1118441401098</v>
+        <v>103.3399235535848</v>
       </c>
       <c r="D6" t="n">
-        <v>102.5466035381176</v>
+        <v>102.2689389298496</v>
       </c>
       <c r="E6" t="n">
-        <v>102.8242645263672</v>
+        <v>102.5565185546875</v>
       </c>
       <c r="F6" t="n">
-        <v>10756900</v>
+        <v>14481900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>102.9829286790064</v>
+        <v>102.8639293479953</v>
       </c>
       <c r="C7" t="n">
-        <v>103.3399235535848</v>
+        <v>105.2240552652924</v>
       </c>
       <c r="D7" t="n">
-        <v>102.2689389298496</v>
+        <v>102.8639293479953</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5565185546875</v>
+        <v>103.3994140625</v>
       </c>
       <c r="F7" t="n">
-        <v>14481900</v>
+        <v>25382000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>102.8639293479953</v>
+        <v>102.9135133062164</v>
       </c>
       <c r="C8" t="n">
-        <v>105.2240552652924</v>
+        <v>103.7663335538345</v>
       </c>
       <c r="D8" t="n">
-        <v>102.8639293479953</v>
+        <v>101.2673770004686</v>
       </c>
       <c r="E8" t="n">
-        <v>103.3994140625</v>
+        <v>102.7350158691406</v>
       </c>
       <c r="F8" t="n">
-        <v>25382000</v>
+        <v>14869400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>102.9135133062164</v>
+        <v>102.9432629724532</v>
       </c>
       <c r="C9" t="n">
-        <v>103.7663335538345</v>
+        <v>103.0721824132953</v>
       </c>
       <c r="D9" t="n">
-        <v>101.2673770004686</v>
+        <v>101.2376224547773</v>
       </c>
       <c r="E9" t="n">
-        <v>102.7350158691406</v>
+        <v>101.4756240844727</v>
       </c>
       <c r="F9" t="n">
-        <v>14869400</v>
+        <v>34791600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>102.9432629724532</v>
+        <v>101.5946114796781</v>
       </c>
       <c r="C10" t="n">
-        <v>103.0721824132953</v>
+        <v>102.3383495068081</v>
       </c>
       <c r="D10" t="n">
-        <v>101.2376224547773</v>
+        <v>101.069037817684</v>
       </c>
       <c r="E10" t="n">
-        <v>101.4756240844727</v>
+        <v>101.9615249633789</v>
       </c>
       <c r="F10" t="n">
-        <v>34791600</v>
+        <v>12861900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>101.5946114796781</v>
+        <v>101.5549573599091</v>
       </c>
       <c r="C11" t="n">
-        <v>102.3383495068081</v>
+        <v>101.822699734613</v>
       </c>
       <c r="D11" t="n">
-        <v>101.069037817684</v>
+        <v>100.4839727297038</v>
       </c>
       <c r="E11" t="n">
-        <v>101.9615249633789</v>
+        <v>101.6640319824219</v>
       </c>
       <c r="F11" t="n">
-        <v>12861900</v>
+        <v>13158700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>101.5549573599091</v>
+        <v>102.1796855917684</v>
       </c>
       <c r="C12" t="n">
-        <v>101.822699734613</v>
+        <v>102.6060956810235</v>
       </c>
       <c r="D12" t="n">
-        <v>100.4839727297038</v>
+        <v>101.6243636395086</v>
       </c>
       <c r="E12" t="n">
-        <v>101.6640319824219</v>
+        <v>101.8722763061523</v>
       </c>
       <c r="F12" t="n">
-        <v>13158700</v>
+        <v>11391800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>102.1796855917684</v>
+        <v>102.3581921548903</v>
       </c>
       <c r="C13" t="n">
-        <v>102.6060956810235</v>
+        <v>102.645771781761</v>
       </c>
       <c r="D13" t="n">
-        <v>101.6243636395086</v>
+        <v>101.7235362768635</v>
       </c>
       <c r="E13" t="n">
-        <v>101.8722763061523</v>
+        <v>102.1896133422852</v>
       </c>
       <c r="F13" t="n">
-        <v>11391800</v>
+        <v>13366700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>102.3581921548903</v>
+        <v>102.0210222421301</v>
       </c>
       <c r="C14" t="n">
-        <v>102.645771781761</v>
+        <v>102.6259297800171</v>
       </c>
       <c r="D14" t="n">
-        <v>101.7235362768635</v>
+        <v>101.6144493855062</v>
       </c>
       <c r="E14" t="n">
-        <v>102.1896133422852</v>
+        <v>102.2986907958984</v>
       </c>
       <c r="F14" t="n">
-        <v>13366700</v>
+        <v>11859300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>102.0210222421301</v>
+        <v>102.189612039799</v>
       </c>
       <c r="C15" t="n">
-        <v>102.6259297800171</v>
+        <v>102.447435785546</v>
       </c>
       <c r="D15" t="n">
-        <v>101.6144493855062</v>
+        <v>101.2277096090732</v>
       </c>
       <c r="E15" t="n">
-        <v>102.2986907958984</v>
+        <v>102.2193603515625</v>
       </c>
       <c r="F15" t="n">
-        <v>11859300</v>
+        <v>15477200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>102.189612039799</v>
+        <v>102.1400273017734</v>
       </c>
       <c r="C16" t="n">
-        <v>102.447435785546</v>
+        <v>103.0721814282683</v>
       </c>
       <c r="D16" t="n">
-        <v>101.2277096090732</v>
+        <v>101.8623663021439</v>
       </c>
       <c r="E16" t="n">
-        <v>102.2193603515625</v>
+        <v>102.1995239257812</v>
       </c>
       <c r="F16" t="n">
-        <v>15477200</v>
+        <v>13873400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>102.1400273017734</v>
+        <v>101.7037001894263</v>
       </c>
       <c r="C17" t="n">
-        <v>103.0721814282683</v>
+        <v>102.001198445649</v>
       </c>
       <c r="D17" t="n">
-        <v>101.8623663021439</v>
+        <v>99.71048759609677</v>
       </c>
       <c r="E17" t="n">
-        <v>102.1995239257812</v>
+        <v>101.1087112426758</v>
       </c>
       <c r="F17" t="n">
-        <v>13873400</v>
+        <v>16142800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>101.7037001894263</v>
+        <v>100.6029631728777</v>
       </c>
       <c r="C18" t="n">
-        <v>102.001198445649</v>
+        <v>101.287204595156</v>
       </c>
       <c r="D18" t="n">
-        <v>99.71048759609677</v>
+        <v>99.03616077500212</v>
       </c>
       <c r="E18" t="n">
-        <v>101.1087112426758</v>
+        <v>100.8508758544922</v>
       </c>
       <c r="F18" t="n">
-        <v>16142800</v>
+        <v>15605400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>100.6029631728777</v>
+        <v>100.6128811517826</v>
       </c>
       <c r="C19" t="n">
-        <v>101.287204595156</v>
+        <v>101.9615267363516</v>
       </c>
       <c r="D19" t="n">
-        <v>99.03616077500212</v>
+        <v>100.3550498461664</v>
       </c>
       <c r="E19" t="n">
-        <v>100.8508758544922</v>
+        <v>101.2177886962891</v>
       </c>
       <c r="F19" t="n">
-        <v>15605400</v>
+        <v>11867500</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>100.6128811517826</v>
+        <v>101.0293759821222</v>
       </c>
       <c r="C20" t="n">
-        <v>101.9615267363516</v>
+        <v>102.2094427990993</v>
       </c>
       <c r="D20" t="n">
-        <v>100.3550498461664</v>
+        <v>100.7318852956682</v>
       </c>
       <c r="E20" t="n">
-        <v>101.2177886962891</v>
+        <v>101.842529296875</v>
       </c>
       <c r="F20" t="n">
-        <v>11867500</v>
+        <v>13303600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>101.0293759821222</v>
+        <v>101.5252009905733</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2094427990993</v>
+        <v>102.387939866122</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7318852956682</v>
+        <v>100.1071401164341</v>
       </c>
       <c r="E21" t="n">
-        <v>101.842529296875</v>
+        <v>102.3780212402344</v>
       </c>
       <c r="F21" t="n">
-        <v>13303600</v>
+        <v>15538900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>101.5252009905733</v>
+        <v>102.1598486460141</v>
       </c>
       <c r="C22" t="n">
-        <v>102.387939866122</v>
+        <v>102.397850254001</v>
       </c>
       <c r="D22" t="n">
-        <v>100.1071401164341</v>
+        <v>101.2971174055678</v>
       </c>
       <c r="E22" t="n">
-        <v>102.3780212402344</v>
+        <v>102.0408554077148</v>
       </c>
       <c r="F22" t="n">
-        <v>15538900</v>
+        <v>13584100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>102.1598486460141</v>
+        <v>102.2689336388612</v>
       </c>
       <c r="C23" t="n">
-        <v>102.397850254001</v>
+        <v>102.5862615592142</v>
       </c>
       <c r="D23" t="n">
-        <v>101.2971174055678</v>
+        <v>99.53198316295229</v>
       </c>
       <c r="E23" t="n">
-        <v>102.0408554077148</v>
+        <v>100.9202880859375</v>
       </c>
       <c r="F23" t="n">
-        <v>13584100</v>
+        <v>19508000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>102.2689336388612</v>
+        <v>101.1979612604356</v>
       </c>
       <c r="C24" t="n">
-        <v>102.5862615592142</v>
+        <v>102.7647636830698</v>
       </c>
       <c r="D24" t="n">
-        <v>99.53198316295229</v>
+        <v>100.6723800119242</v>
       </c>
       <c r="E24" t="n">
-        <v>100.9202880859375</v>
+        <v>100.9897079467773</v>
       </c>
       <c r="F24" t="n">
-        <v>19508000</v>
+        <v>18519400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>101.1979612604356</v>
+        <v>100.523634106908</v>
       </c>
       <c r="C25" t="n">
-        <v>102.7647636830698</v>
+        <v>101.5946111121733</v>
       </c>
       <c r="D25" t="n">
-        <v>100.6723800119242</v>
+        <v>100.2261358708544</v>
       </c>
       <c r="E25" t="n">
-        <v>100.9897079467773</v>
+        <v>101.2673721313477</v>
       </c>
       <c r="F25" t="n">
-        <v>18519400</v>
+        <v>10871200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>100.523634106908</v>
+        <v>103.1812529973676</v>
       </c>
       <c r="C26" t="n">
-        <v>101.5946111121733</v>
+        <v>107.01893616482</v>
       </c>
       <c r="D26" t="n">
-        <v>100.2261358708544</v>
+        <v>102.0309346136339</v>
       </c>
       <c r="E26" t="n">
-        <v>101.2673721313477</v>
+        <v>106.3148651123047</v>
       </c>
       <c r="F26" t="n">
-        <v>10871200</v>
+        <v>30859500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>103.1812529973676</v>
+        <v>106.4239528923693</v>
       </c>
       <c r="C27" t="n">
-        <v>107.01893616482</v>
+        <v>108.6452483434567</v>
       </c>
       <c r="D27" t="n">
-        <v>102.0309346136339</v>
+        <v>106.4041232072616</v>
       </c>
       <c r="E27" t="n">
-        <v>106.3148651123047</v>
+        <v>108.1196746826172</v>
       </c>
       <c r="F27" t="n">
-        <v>30859500</v>
+        <v>21416300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>106.4239528923693</v>
+        <v>108.288256950121</v>
       </c>
       <c r="C28" t="n">
-        <v>108.6452483434567</v>
+        <v>108.6650890704717</v>
       </c>
       <c r="D28" t="n">
-        <v>106.4041232072616</v>
+        <v>104.7778200152908</v>
       </c>
       <c r="E28" t="n">
-        <v>108.1196746826172</v>
+        <v>105.5810546875</v>
       </c>
       <c r="F28" t="n">
-        <v>21416300</v>
+        <v>16366200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>108.288256950121</v>
+        <v>106.2752063382308</v>
       </c>
       <c r="C29" t="n">
-        <v>108.6650890704717</v>
+        <v>107.2966053740443</v>
       </c>
       <c r="D29" t="n">
-        <v>104.7778200152908</v>
+        <v>105.3331411761509</v>
       </c>
       <c r="E29" t="n">
-        <v>105.5810546875</v>
+        <v>106.8305358886719</v>
       </c>
       <c r="F29" t="n">
-        <v>16366200</v>
+        <v>13735600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>106.2752063382308</v>
+        <v>106.9495278840114</v>
       </c>
       <c r="C30" t="n">
-        <v>107.2966053740443</v>
+        <v>107.3461896823507</v>
       </c>
       <c r="D30" t="n">
-        <v>105.3331411761509</v>
+        <v>105.7198831182847</v>
       </c>
       <c r="E30" t="n">
-        <v>106.8305358886719</v>
+        <v>106.1562118530273</v>
       </c>
       <c r="F30" t="n">
-        <v>13735600</v>
+        <v>10581200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>106.9495278840114</v>
+        <v>106.4338780925878</v>
       </c>
       <c r="C31" t="n">
-        <v>107.3461896823507</v>
+        <v>106.5826272200147</v>
       </c>
       <c r="D31" t="n">
-        <v>105.7198831182847</v>
+        <v>105.2934782032414</v>
       </c>
       <c r="E31" t="n">
-        <v>106.1562118530273</v>
+        <v>105.3331451416016</v>
       </c>
       <c r="F31" t="n">
-        <v>10581200</v>
+        <v>10899700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>106.4338780925878</v>
+        <v>105.6603902006062</v>
       </c>
       <c r="C32" t="n">
-        <v>106.5826272200147</v>
+        <v>106.8701977576955</v>
       </c>
       <c r="D32" t="n">
-        <v>105.2934782032414</v>
+        <v>104.7778216403512</v>
       </c>
       <c r="E32" t="n">
-        <v>105.3331451416016</v>
+        <v>106.2454605102539</v>
       </c>
       <c r="F32" t="n">
-        <v>10899700</v>
+        <v>12296500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>105.6603902006062</v>
+        <v>106.4537107234644</v>
       </c>
       <c r="C33" t="n">
-        <v>106.8701977576955</v>
+        <v>106.6718751076324</v>
       </c>
       <c r="D33" t="n">
-        <v>104.7778216403512</v>
+        <v>104.8968192868145</v>
       </c>
       <c r="E33" t="n">
-        <v>106.2454605102539</v>
+        <v>105.9678039550781</v>
       </c>
       <c r="F33" t="n">
-        <v>12296500</v>
+        <v>11408200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>106.4537107234644</v>
+        <v>106.1760412293909</v>
       </c>
       <c r="C34" t="n">
-        <v>106.6718751076324</v>
+        <v>106.2752047872635</v>
       </c>
       <c r="D34" t="n">
-        <v>104.8968192868145</v>
+        <v>104.6290685426336</v>
       </c>
       <c r="E34" t="n">
-        <v>105.9678039550781</v>
+        <v>105.2835540771484</v>
       </c>
       <c r="F34" t="n">
-        <v>11408200</v>
+        <v>10318000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>106.1760412293909</v>
+        <v>105.4521374991914</v>
       </c>
       <c r="C35" t="n">
-        <v>106.2752047872635</v>
+        <v>105.4719747510511</v>
       </c>
       <c r="D35" t="n">
-        <v>104.6290685426336</v>
+        <v>103.2804274936261</v>
       </c>
       <c r="E35" t="n">
-        <v>105.2835540771484</v>
+        <v>103.5977554321289</v>
       </c>
       <c r="F35" t="n">
-        <v>10318000</v>
+        <v>16375900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>105.4521374991914</v>
+        <v>103.1911775964564</v>
       </c>
       <c r="C36" t="n">
-        <v>105.4719747510511</v>
+        <v>103.2705114745084</v>
       </c>
       <c r="D36" t="n">
-        <v>103.2804274936261</v>
+        <v>102.1896157574061</v>
       </c>
       <c r="E36" t="n">
-        <v>103.5977554321289</v>
+        <v>102.3086090087891</v>
       </c>
       <c r="F36" t="n">
-        <v>16375900</v>
+        <v>13323000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>103.1911775964564</v>
+        <v>102.0507853540776</v>
       </c>
       <c r="C37" t="n">
-        <v>103.2705114745084</v>
+        <v>102.8044344992282</v>
       </c>
       <c r="D37" t="n">
-        <v>102.1896157574061</v>
+        <v>101.2574617041669</v>
       </c>
       <c r="E37" t="n">
-        <v>102.3086090087891</v>
+        <v>101.6045379638672</v>
       </c>
       <c r="F37" t="n">
-        <v>13323000</v>
+        <v>11986400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>102.0507853540776</v>
+        <v>101.3467089644983</v>
       </c>
       <c r="C38" t="n">
-        <v>102.8044344992282</v>
+        <v>102.5069461530686</v>
       </c>
       <c r="D38" t="n">
-        <v>101.2574617041669</v>
+        <v>101.108714890351</v>
       </c>
       <c r="E38" t="n">
-        <v>101.6045379638672</v>
+        <v>101.37646484375</v>
       </c>
       <c r="F38" t="n">
-        <v>11986400</v>
+        <v>14065100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>101.3467089644983</v>
+        <v>100.8508753833576</v>
       </c>
       <c r="C39" t="n">
-        <v>102.5069461530686</v>
+        <v>101.2475371852267</v>
       </c>
       <c r="D39" t="n">
-        <v>101.108714890351</v>
+        <v>99.34356961508874</v>
       </c>
       <c r="E39" t="n">
-        <v>101.37646484375</v>
+        <v>100.3352203369141</v>
       </c>
       <c r="F39" t="n">
-        <v>14065100</v>
+        <v>20237000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>100.8508753833576</v>
+        <v>99.97822306298148</v>
       </c>
       <c r="C40" t="n">
-        <v>101.2475371852267</v>
+        <v>100.9500440758614</v>
       </c>
       <c r="D40" t="n">
-        <v>99.34356961508874</v>
+        <v>99.56173158561626</v>
       </c>
       <c r="E40" t="n">
-        <v>100.3352203369141</v>
+        <v>100.7417907714844</v>
       </c>
       <c r="F40" t="n">
-        <v>20237000</v>
+        <v>14811700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>99.97822306298148</v>
+        <v>101.2772843129512</v>
       </c>
       <c r="C41" t="n">
-        <v>100.9500440758614</v>
+        <v>101.7631986082678</v>
       </c>
       <c r="D41" t="n">
-        <v>99.56173158561626</v>
+        <v>100.6128801528584</v>
       </c>
       <c r="E41" t="n">
-        <v>100.7417907714844</v>
+        <v>101.4161148071289</v>
       </c>
       <c r="F41" t="n">
-        <v>14811700</v>
+        <v>12636400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>101.2772843129512</v>
+        <v>100.89054510776</v>
       </c>
       <c r="C42" t="n">
-        <v>101.7631986082678</v>
+        <v>101.8226992330539</v>
       </c>
       <c r="D42" t="n">
-        <v>100.6128801528584</v>
+        <v>100.0079765462054</v>
       </c>
       <c r="E42" t="n">
-        <v>101.4161148071289</v>
+        <v>100.622802734375</v>
       </c>
       <c r="F42" t="n">
-        <v>12636400</v>
+        <v>13356800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>100.89054510776</v>
+        <v>100.493889477858</v>
       </c>
       <c r="C43" t="n">
-        <v>101.8226992330539</v>
+        <v>101.0789673900592</v>
       </c>
       <c r="D43" t="n">
-        <v>100.0079765462054</v>
+        <v>99.19482933747032</v>
       </c>
       <c r="E43" t="n">
-        <v>100.622802734375</v>
+        <v>100.8310546875</v>
       </c>
       <c r="F43" t="n">
-        <v>13356800</v>
+        <v>14866000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>100.493889477858</v>
+        <v>101.2772781932102</v>
       </c>
       <c r="C44" t="n">
-        <v>101.0789673900592</v>
+        <v>102.1102686736373</v>
       </c>
       <c r="D44" t="n">
-        <v>99.19482933747032</v>
+        <v>100.8806239856387</v>
       </c>
       <c r="E44" t="n">
-        <v>100.8310546875</v>
+        <v>101.7334365844727</v>
       </c>
       <c r="F44" t="n">
-        <v>14866000</v>
+        <v>17248700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>101.2772781932102</v>
+        <v>101.2971227463208</v>
       </c>
       <c r="C45" t="n">
-        <v>102.1102686736373</v>
+        <v>101.8127777927579</v>
       </c>
       <c r="D45" t="n">
-        <v>100.8806239856387</v>
+        <v>100.7517118230459</v>
       </c>
       <c r="E45" t="n">
-        <v>101.7334365844727</v>
+        <v>101.5648651123047</v>
       </c>
       <c r="F45" t="n">
-        <v>17248700</v>
+        <v>14507600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>101.2971227463208</v>
+        <v>101.6441933036576</v>
       </c>
       <c r="C46" t="n">
-        <v>101.8127777927579</v>
+        <v>102.8738380115709</v>
       </c>
       <c r="D46" t="n">
-        <v>100.7517118230459</v>
+        <v>101.4656958810819</v>
       </c>
       <c r="E46" t="n">
-        <v>101.5648651123047</v>
+        <v>102.5763473510742</v>
       </c>
       <c r="F46" t="n">
-        <v>14507600</v>
+        <v>13182100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>101.6441933036576</v>
+        <v>102.4870948569393</v>
       </c>
       <c r="C47" t="n">
-        <v>102.8738380115709</v>
+        <v>102.7350075235336</v>
       </c>
       <c r="D47" t="n">
-        <v>101.4656958810819</v>
+        <v>101.8028610418111</v>
       </c>
       <c r="E47" t="n">
         <v>102.5763473510742</v>
       </c>
       <c r="F47" t="n">
-        <v>13182100</v>
+        <v>12084400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>102.4870948569393</v>
+        <v>102.7251048596608</v>
       </c>
       <c r="C48" t="n">
-        <v>102.7350075235336</v>
+        <v>103.062270072778</v>
       </c>
       <c r="D48" t="n">
-        <v>101.8028610418111</v>
+        <v>101.1682133741703</v>
       </c>
       <c r="E48" t="n">
-        <v>102.5763473510742</v>
+        <v>101.6838760375977</v>
       </c>
       <c r="F48" t="n">
-        <v>12084400</v>
+        <v>18088500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>102.7251048596608</v>
+        <v>99.36341173515544</v>
       </c>
       <c r="C49" t="n">
-        <v>103.062270072778</v>
+        <v>101.6342930802014</v>
       </c>
       <c r="D49" t="n">
-        <v>101.1682133741703</v>
+        <v>98.05443292116557</v>
       </c>
       <c r="E49" t="n">
-        <v>101.6838760375977</v>
+        <v>101.624382019043</v>
       </c>
       <c r="F49" t="n">
-        <v>18088500</v>
+        <v>23424200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>99.36341173515544</v>
+        <v>101.7235329175373</v>
       </c>
       <c r="C50" t="n">
-        <v>101.6342930802014</v>
+        <v>102.4573523337042</v>
       </c>
       <c r="D50" t="n">
-        <v>98.05443292116557</v>
+        <v>101.2475372418891</v>
       </c>
       <c r="E50" t="n">
-        <v>101.624382019043</v>
+        <v>102.0904388427734</v>
       </c>
       <c r="F50" t="n">
-        <v>23424200</v>
+        <v>15289400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>101.7235329175373</v>
+        <v>102.1201932202399</v>
       </c>
       <c r="C51" t="n">
-        <v>102.4573523337042</v>
+        <v>102.4771805146163</v>
       </c>
       <c r="D51" t="n">
-        <v>101.2475372418891</v>
+        <v>100.5335460351719</v>
       </c>
       <c r="E51" t="n">
-        <v>102.0904388427734</v>
+        <v>100.5434646606445</v>
       </c>
       <c r="F51" t="n">
-        <v>15289400</v>
+        <v>17604500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>102.1201932202399</v>
+        <v>100.7318838109266</v>
       </c>
       <c r="C52" t="n">
-        <v>102.4771805146163</v>
+        <v>100.8607956832537</v>
       </c>
       <c r="D52" t="n">
-        <v>100.5335460351719</v>
+        <v>98.84774589504295</v>
       </c>
       <c r="E52" t="n">
-        <v>100.5434646606445</v>
+        <v>99.76998138427734</v>
       </c>
       <c r="F52" t="n">
-        <v>17604500</v>
+        <v>22157000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>100.7318838109266</v>
+        <v>103.0721750041795</v>
       </c>
       <c r="C53" t="n">
-        <v>100.8607956832537</v>
+        <v>107.0090294488173</v>
       </c>
       <c r="D53" t="n">
-        <v>98.84774589504295</v>
+        <v>101.8226930180269</v>
       </c>
       <c r="E53" t="n">
-        <v>99.76998138427734</v>
+        <v>106.215705871582</v>
       </c>
       <c r="F53" t="n">
-        <v>22157000</v>
+        <v>50375900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>103.0721750041795</v>
+        <v>107.0784532434011</v>
       </c>
       <c r="C54" t="n">
-        <v>107.0090294488173</v>
+        <v>107.247032058172</v>
       </c>
       <c r="D54" t="n">
-        <v>101.8226930180269</v>
+        <v>103.8456696217535</v>
       </c>
       <c r="E54" t="n">
-        <v>106.215705871582</v>
+        <v>104.4406585693359</v>
       </c>
       <c r="F54" t="n">
-        <v>50375900</v>
+        <v>41420800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>107.0784532434011</v>
+        <v>104.4803186790174</v>
       </c>
       <c r="C55" t="n">
-        <v>107.247032058172</v>
+        <v>105.3827168846354</v>
       </c>
       <c r="D55" t="n">
-        <v>103.8456696217535</v>
+        <v>102.89367906727</v>
       </c>
       <c r="E55" t="n">
-        <v>104.4406585693359</v>
+        <v>103.1911697387695</v>
       </c>
       <c r="F55" t="n">
-        <v>41420800</v>
+        <v>42519200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>104.4803186790174</v>
+        <v>103.7365912306264</v>
       </c>
       <c r="C56" t="n">
-        <v>105.3827168846354</v>
+        <v>106.5231275693524</v>
       </c>
       <c r="D56" t="n">
-        <v>102.89367906727</v>
+        <v>103.3597666486879</v>
       </c>
       <c r="E56" t="n">
-        <v>103.1911697387695</v>
+        <v>106.1066360473633</v>
       </c>
       <c r="F56" t="n">
-        <v>42519200</v>
+        <v>20212900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>103.7365912306264</v>
+        <v>106.3049566187</v>
       </c>
       <c r="C57" t="n">
-        <v>106.5231275693524</v>
+        <v>108.6750012891114</v>
       </c>
       <c r="D57" t="n">
-        <v>103.3597666486879</v>
+        <v>106.2752083069225</v>
       </c>
       <c r="E57" t="n">
-        <v>106.1066360473633</v>
+        <v>108.189094543457</v>
       </c>
       <c r="F57" t="n">
-        <v>20212900</v>
+        <v>17783300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>106.3049566187</v>
+        <v>108.3874295551272</v>
       </c>
       <c r="C58" t="n">
-        <v>108.6750012891114</v>
+        <v>109.7757345468567</v>
       </c>
       <c r="D58" t="n">
-        <v>106.2752083069225</v>
+        <v>108.0899313050738</v>
       </c>
       <c r="E58" t="n">
-        <v>108.189094543457</v>
+        <v>109.5873260498047</v>
       </c>
       <c r="F58" t="n">
-        <v>17783300</v>
+        <v>9846500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>108.3874295551272</v>
+        <v>109.587327840119</v>
       </c>
       <c r="C59" t="n">
-        <v>109.7757345468567</v>
+        <v>110.8268912927673</v>
       </c>
       <c r="D59" t="n">
-        <v>108.0899313050738</v>
+        <v>109.4385787126623</v>
       </c>
       <c r="E59" t="n">
-        <v>109.5873260498047</v>
+        <v>110.5988082885742</v>
       </c>
       <c r="F59" t="n">
-        <v>9846500</v>
+        <v>17236800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>109.587327840119</v>
+        <v>110.5393043592431</v>
       </c>
       <c r="C60" t="n">
-        <v>110.8268912927673</v>
+        <v>111.7094524838454</v>
       </c>
       <c r="D60" t="n">
-        <v>109.4385787126623</v>
+        <v>109.8649815829351</v>
       </c>
       <c r="E60" t="n">
-        <v>110.5988082885742</v>
+        <v>111.4714584350586</v>
       </c>
       <c r="F60" t="n">
-        <v>17236800</v>
+        <v>18711800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>110.5393043592431</v>
+        <v>111.560708766128</v>
       </c>
       <c r="C61" t="n">
-        <v>111.7094524838454</v>
+        <v>113.9307534404373</v>
       </c>
       <c r="D61" t="n">
-        <v>109.8649815829351</v>
+        <v>111.2830477681546</v>
       </c>
       <c r="E61" t="n">
-        <v>111.4714584350586</v>
+        <v>113.4547653198242</v>
       </c>
       <c r="F61" t="n">
-        <v>18711800</v>
+        <v>24478300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>111.560708766128</v>
+        <v>112.6713645812471</v>
       </c>
       <c r="C62" t="n">
-        <v>113.9307534404373</v>
+        <v>113.9307577455568</v>
       </c>
       <c r="D62" t="n">
-        <v>111.2830477681546</v>
+        <v>112.2152061293831</v>
       </c>
       <c r="E62" t="n">
-        <v>113.4547653198242</v>
+        <v>113.8811721801758</v>
       </c>
       <c r="F62" t="n">
-        <v>24478300</v>
+        <v>25905100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>112.6713645812471</v>
+        <v>113.7720935914494</v>
       </c>
       <c r="C63" t="n">
-        <v>113.9307577455568</v>
+        <v>115.2992290848131</v>
       </c>
       <c r="D63" t="n">
-        <v>112.2152061293831</v>
+        <v>113.7225080277957</v>
       </c>
       <c r="E63" t="n">
-        <v>113.8811721801758</v>
+        <v>114.1489181518555</v>
       </c>
       <c r="F63" t="n">
-        <v>25905100</v>
+        <v>23956400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>113.7720935914494</v>
+        <v>113.6134239095882</v>
       </c>
       <c r="C64" t="n">
-        <v>115.2992290848131</v>
+        <v>114.0299154007005</v>
       </c>
       <c r="D64" t="n">
-        <v>113.7225080277957</v>
+        <v>111.3623800798857</v>
       </c>
       <c r="E64" t="n">
-        <v>114.1489181518555</v>
+        <v>112.6118545532227</v>
       </c>
       <c r="F64" t="n">
-        <v>23956400</v>
+        <v>22700700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>113.6134239095882</v>
+        <v>112.9985942054707</v>
       </c>
       <c r="C65" t="n">
-        <v>114.0299154007005</v>
+        <v>114.7538201807431</v>
       </c>
       <c r="D65" t="n">
-        <v>111.3623800798857</v>
+        <v>112.0763587521143</v>
       </c>
       <c r="E65" t="n">
-        <v>112.6118545532227</v>
+        <v>114.0993270874023</v>
       </c>
       <c r="F65" t="n">
-        <v>22700700</v>
+        <v>24326700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>112.9985942054707</v>
+        <v>114.3869191950181</v>
       </c>
       <c r="C66" t="n">
-        <v>114.7538201807431</v>
+        <v>115.259576748144</v>
       </c>
       <c r="D66" t="n">
-        <v>112.0763587521143</v>
+        <v>112.0466226827729</v>
       </c>
       <c r="E66" t="n">
-        <v>114.0993270874023</v>
+        <v>112.2350387573242</v>
       </c>
       <c r="F66" t="n">
-        <v>24326700</v>
+        <v>22859600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>114.3869191950181</v>
+        <v>112.195370053421</v>
       </c>
       <c r="C67" t="n">
-        <v>115.259576748144</v>
+        <v>114.9025800457367</v>
       </c>
       <c r="D67" t="n">
-        <v>112.0466226827729</v>
+        <v>111.9077904157248</v>
       </c>
       <c r="E67" t="n">
-        <v>112.2350387573242</v>
+        <v>114.5554962158203</v>
       </c>
       <c r="F67" t="n">
-        <v>22859600</v>
+        <v>21586600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>112.195370053421</v>
+        <v>114.5306574399956</v>
       </c>
       <c r="C68" t="n">
-        <v>114.9025800457367</v>
+        <v>116.2099582668437</v>
       </c>
       <c r="D68" t="n">
-        <v>111.9077904157248</v>
+        <v>114.2921706587026</v>
       </c>
       <c r="E68" t="n">
-        <v>114.5554962158203</v>
+        <v>115.961540222168</v>
       </c>
       <c r="F68" t="n">
-        <v>21586600</v>
+        <v>19092400</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>114.5306574399956</v>
+        <v>116.190085480185</v>
       </c>
       <c r="C69" t="n">
-        <v>116.2099582668437</v>
+        <v>116.7067916655062</v>
       </c>
       <c r="D69" t="n">
-        <v>114.2921706587026</v>
+        <v>114.9082474894773</v>
       </c>
       <c r="E69" t="n">
-        <v>115.961540222168</v>
+        <v>116.0509719848633</v>
       </c>
       <c r="F69" t="n">
-        <v>19092400</v>
+        <v>18713700</v>
       </c>
       <c r="G69" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>116.190085480185</v>
+        <v>115.8423072543707</v>
       </c>
       <c r="C70" t="n">
-        <v>116.7067916655062</v>
+        <v>116.140404366624</v>
       </c>
       <c r="D70" t="n">
-        <v>114.9082474894773</v>
+        <v>114.2226167114376</v>
       </c>
       <c r="E70" t="n">
-        <v>116.0509719848633</v>
+        <v>114.6896438598633</v>
       </c>
       <c r="F70" t="n">
-        <v>18713700</v>
+        <v>19642300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>115.8423072543707</v>
+        <v>114.4710352169006</v>
       </c>
       <c r="C71" t="n">
-        <v>116.140404366624</v>
+        <v>115.6535075692186</v>
       </c>
       <c r="D71" t="n">
-        <v>114.2226167114376</v>
+        <v>114.3418605591895</v>
       </c>
       <c r="E71" t="n">
-        <v>114.6896438598633</v>
+        <v>114.9281311035156</v>
       </c>
       <c r="F71" t="n">
-        <v>19642300</v>
+        <v>16177800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>114.4710352169006</v>
+        <v>114.2822472329707</v>
       </c>
       <c r="C72" t="n">
-        <v>115.6535075692186</v>
+        <v>115.7429466488196</v>
       </c>
       <c r="D72" t="n">
-        <v>114.3418605591895</v>
+        <v>113.8847768180071</v>
       </c>
       <c r="E72" t="n">
-        <v>114.9281311035156</v>
+        <v>114.103385925293</v>
       </c>
       <c r="F72" t="n">
-        <v>16177800</v>
+        <v>21476700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>114.2822472329707</v>
+        <v>114.411415636222</v>
       </c>
       <c r="C73" t="n">
-        <v>115.7429466488196</v>
+        <v>114.5505291366805</v>
       </c>
       <c r="D73" t="n">
-        <v>113.8847768180071</v>
+        <v>112.8116027998319</v>
       </c>
       <c r="E73" t="n">
-        <v>114.103385925293</v>
+        <v>113.6363525390625</v>
       </c>
       <c r="F73" t="n">
-        <v>21476700</v>
+        <v>50043800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>114.411415636222</v>
+        <v>113.2885707737471</v>
       </c>
       <c r="C74" t="n">
-        <v>114.5505291366805</v>
+        <v>113.5966067328595</v>
       </c>
       <c r="D74" t="n">
-        <v>112.8116027998319</v>
+        <v>111.5098966082868</v>
       </c>
       <c r="E74" t="n">
-        <v>113.6363525390625</v>
+        <v>111.8874893188477</v>
       </c>
       <c r="F74" t="n">
-        <v>50043800</v>
+        <v>21473900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>113.2885707737471</v>
+        <v>111.2813411845575</v>
       </c>
       <c r="C75" t="n">
-        <v>113.5966067328595</v>
+        <v>111.6390637625677</v>
       </c>
       <c r="D75" t="n">
-        <v>111.5098966082868</v>
+        <v>109.9995032102072</v>
       </c>
       <c r="E75" t="n">
-        <v>111.8874893188477</v>
+        <v>110.1982421875</v>
       </c>
       <c r="F75" t="n">
-        <v>21473900</v>
+        <v>20319900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>111.2813411845575</v>
+        <v>110.1982488335626</v>
       </c>
       <c r="C76" t="n">
-        <v>111.6390637625677</v>
+        <v>111.003120892069</v>
       </c>
       <c r="D76" t="n">
-        <v>109.9995032102072</v>
+        <v>109.8504650787215</v>
       </c>
       <c r="E76" t="n">
-        <v>110.1982421875</v>
+        <v>110.9037551879883</v>
       </c>
       <c r="F76" t="n">
-        <v>20319900</v>
+        <v>9009600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>110.1982488335626</v>
+        <v>111.0130583586743</v>
       </c>
       <c r="C77" t="n">
-        <v>111.003120892069</v>
+        <v>111.2614764063509</v>
       </c>
       <c r="D77" t="n">
-        <v>109.8504650787215</v>
+        <v>110.6553357635307</v>
       </c>
       <c r="E77" t="n">
-        <v>110.9037551879883</v>
+        <v>111.0329284667969</v>
       </c>
       <c r="F77" t="n">
-        <v>9009600</v>
+        <v>9003800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>111.0130583586743</v>
+        <v>110.8838702636393</v>
       </c>
       <c r="C78" t="n">
-        <v>111.2614764063509</v>
+        <v>112.0663425340636</v>
       </c>
       <c r="D78" t="n">
-        <v>110.6553357635307</v>
+        <v>110.8640001565665</v>
       </c>
       <c r="E78" t="n">
-        <v>111.0329284667969</v>
+        <v>111.8179244995117</v>
       </c>
       <c r="F78" t="n">
-        <v>9003800</v>
+        <v>12979600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>110.8838702636393</v>
+        <v>111.1819754114984</v>
       </c>
       <c r="C79" t="n">
-        <v>112.0663425340636</v>
+        <v>111.9769161578998</v>
       </c>
       <c r="D79" t="n">
-        <v>110.8640001565665</v>
+        <v>111.1322887719295</v>
       </c>
       <c r="E79" t="n">
-        <v>111.8179244995117</v>
+        <v>111.211784362793</v>
       </c>
       <c r="F79" t="n">
-        <v>12979600</v>
+        <v>11730600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>111.1819754114984</v>
+        <v>111.022991872357</v>
       </c>
       <c r="C80" t="n">
-        <v>111.9769161578998</v>
+        <v>111.5396980510222</v>
       </c>
       <c r="D80" t="n">
-        <v>111.1322887719295</v>
+        <v>110.6155826547936</v>
       </c>
       <c r="E80" t="n">
-        <v>111.211784362793</v>
+        <v>110.7050170898438</v>
       </c>
       <c r="F80" t="n">
-        <v>11730600</v>
+        <v>11487400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>111.022991872357</v>
+        <v>110.7248924392647</v>
       </c>
       <c r="C81" t="n">
-        <v>111.5396980510222</v>
+        <v>112.0762872242068</v>
       </c>
       <c r="D81" t="n">
-        <v>110.6155826547936</v>
+        <v>110.4168564863102</v>
       </c>
       <c r="E81" t="n">
-        <v>110.7050170898438</v>
+        <v>112.0464782714844</v>
       </c>
       <c r="F81" t="n">
-        <v>11487400</v>
+        <v>14306600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>110.7248924392647</v>
+        <v>112.106092568778</v>
       </c>
       <c r="C82" t="n">
-        <v>112.0762872242068</v>
+        <v>113.0103378715463</v>
       </c>
       <c r="D82" t="n">
-        <v>110.4168564863102</v>
+        <v>111.4403340423477</v>
       </c>
       <c r="E82" t="n">
-        <v>112.0464782714844</v>
+        <v>111.9967880249023</v>
       </c>
       <c r="F82" t="n">
-        <v>14306600</v>
+        <v>19557600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>112.106092568778</v>
+        <v>111.6887590151699</v>
       </c>
       <c r="C83" t="n">
-        <v>113.0103378715463</v>
+        <v>114.0636350138627</v>
       </c>
       <c r="D83" t="n">
-        <v>111.4403340423477</v>
+        <v>111.2813497661395</v>
       </c>
       <c r="E83" t="n">
-        <v>111.9967880249023</v>
+        <v>113.6164779663086</v>
       </c>
       <c r="F83" t="n">
-        <v>19557600</v>
+        <v>20120800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>111.6887590151699</v>
+        <v>113.4674284407305</v>
       </c>
       <c r="C84" t="n">
-        <v>114.0636350138627</v>
+        <v>114.0040123266269</v>
       </c>
       <c r="D84" t="n">
-        <v>111.2813497661395</v>
+        <v>111.3906496463658</v>
       </c>
       <c r="E84" t="n">
-        <v>113.6164779663086</v>
+        <v>112.0067291259766</v>
       </c>
       <c r="F84" t="n">
-        <v>20120800</v>
+        <v>23306000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>113.4674284407305</v>
+        <v>110.5857797769927</v>
       </c>
       <c r="C85" t="n">
-        <v>114.0040123266269</v>
+        <v>112.7519854709339</v>
       </c>
       <c r="D85" t="n">
-        <v>111.3906496463658</v>
+        <v>109.1151415889016</v>
       </c>
       <c r="E85" t="n">
-        <v>112.0067291259766</v>
+        <v>112.3545150756836</v>
       </c>
       <c r="F85" t="n">
-        <v>23306000</v>
+        <v>24058300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>110.5857797769927</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="C86" t="n">
-        <v>112.7519854709339</v>
+        <v>114.7293904053996</v>
       </c>
       <c r="D86" t="n">
-        <v>109.1151415889016</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="E86" t="n">
-        <v>112.3545150756836</v>
+        <v>113.8052749633789</v>
       </c>
       <c r="F86" t="n">
-        <v>24058300</v>
+        <v>21902900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>111.5496424227033</v>
+        <v>116.756475995831</v>
       </c>
       <c r="C87" t="n">
-        <v>114.7293904053996</v>
+        <v>118.0879930193155</v>
       </c>
       <c r="D87" t="n">
-        <v>111.5496424227033</v>
+        <v>115.6733770063802</v>
       </c>
       <c r="E87" t="n">
-        <v>113.8052749633789</v>
+        <v>117.223503112793</v>
       </c>
       <c r="F87" t="n">
-        <v>21902900</v>
+        <v>49182100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>116.756475995831</v>
+        <v>117.1440096095209</v>
       </c>
       <c r="C88" t="n">
-        <v>118.0879930193155</v>
+        <v>119.7474333817796</v>
       </c>
       <c r="D88" t="n">
-        <v>115.6733770063802</v>
+        <v>116.9850260070875</v>
       </c>
       <c r="E88" t="n">
-        <v>117.223503112793</v>
+        <v>119.5983810424805</v>
       </c>
       <c r="F88" t="n">
-        <v>49182100</v>
+        <v>31222100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>117.1440096095209</v>
+        <v>119.4294631115365</v>
       </c>
       <c r="C89" t="n">
-        <v>119.7474333817796</v>
+        <v>120.4728143638468</v>
       </c>
       <c r="D89" t="n">
-        <v>116.9850260070875</v>
+        <v>118.2767997305645</v>
       </c>
       <c r="E89" t="n">
-        <v>119.5983810424805</v>
+        <v>119.2804107666016</v>
       </c>
       <c r="F89" t="n">
-        <v>31222100</v>
+        <v>32764000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>119.4294631115365</v>
+        <v>119.2207951798175</v>
       </c>
       <c r="C90" t="n">
-        <v>120.4728143638468</v>
+        <v>120.1051628408833</v>
       </c>
       <c r="D90" t="n">
-        <v>118.2767997305645</v>
+        <v>117.9787049163972</v>
       </c>
       <c r="E90" t="n">
-        <v>119.2804107666016</v>
+        <v>118.4457244873047</v>
       </c>
       <c r="F90" t="n">
-        <v>32764000</v>
+        <v>34559400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>119.2207951798175</v>
+        <v>117.9190771443211</v>
       </c>
       <c r="C91" t="n">
-        <v>120.1051628408833</v>
+        <v>119.8368647771362</v>
       </c>
       <c r="D91" t="n">
-        <v>117.9787049163972</v>
+        <v>116.1602807010803</v>
       </c>
       <c r="E91" t="n">
-        <v>118.4457244873047</v>
+        <v>118.9425582885742</v>
       </c>
       <c r="F91" t="n">
-        <v>34559400</v>
+        <v>415144600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>117.9190771443211</v>
+        <v>120.1250298240042</v>
       </c>
       <c r="C92" t="n">
-        <v>119.8368647771362</v>
+        <v>120.8504138546603</v>
       </c>
       <c r="D92" t="n">
-        <v>116.1602807010803</v>
+        <v>116.8657862705671</v>
       </c>
       <c r="E92" t="n">
-        <v>118.9425582885742</v>
+        <v>117.9588241577148</v>
       </c>
       <c r="F92" t="n">
-        <v>415144600</v>
+        <v>45334000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>120.1250298240042</v>
+        <v>117.3328142471995</v>
       </c>
       <c r="C93" t="n">
-        <v>120.8504138546603</v>
+        <v>119.7275602876645</v>
       </c>
       <c r="D93" t="n">
-        <v>116.8657862705671</v>
+        <v>116.8061691984345</v>
       </c>
       <c r="E93" t="n">
-        <v>117.9588241577148</v>
+        <v>118.6047134399414</v>
       </c>
       <c r="F93" t="n">
-        <v>45334000</v>
+        <v>34811700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>117.3328142471995</v>
+        <v>118.5351568548667</v>
       </c>
       <c r="C94" t="n">
-        <v>119.7275602876645</v>
+        <v>118.7636972139123</v>
       </c>
       <c r="D94" t="n">
-        <v>116.8061691984345</v>
+        <v>116.9055350642564</v>
       </c>
       <c r="E94" t="n">
-        <v>118.6047134399414</v>
+        <v>117.0843963623047</v>
       </c>
       <c r="F94" t="n">
-        <v>34811700</v>
+        <v>24547300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>118.5351568548667</v>
+        <v>117.4222340816893</v>
       </c>
       <c r="C95" t="n">
-        <v>118.7636972139123</v>
+        <v>117.8594522459602</v>
       </c>
       <c r="D95" t="n">
-        <v>116.9055350642564</v>
+        <v>116.3987529981613</v>
       </c>
       <c r="E95" t="n">
-        <v>117.0843963623047</v>
+        <v>116.9850234985352</v>
       </c>
       <c r="F95" t="n">
-        <v>24547300</v>
+        <v>20806900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>117.4222340816893</v>
+        <v>117.064521823182</v>
       </c>
       <c r="C96" t="n">
-        <v>117.8594522459602</v>
+        <v>118.0979418418126</v>
       </c>
       <c r="D96" t="n">
-        <v>116.3987529981613</v>
+        <v>116.6471813102112</v>
       </c>
       <c r="E96" t="n">
-        <v>116.9850234985352</v>
+        <v>116.8955993652344</v>
       </c>
       <c r="F96" t="n">
-        <v>20806900</v>
+        <v>19552200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>117.064521823182</v>
+        <v>116.7564814621505</v>
       </c>
       <c r="C97" t="n">
-        <v>118.0979418418126</v>
+        <v>116.8856561166937</v>
       </c>
       <c r="D97" t="n">
-        <v>116.6471813102112</v>
+        <v>114.7492669888757</v>
       </c>
       <c r="E97" t="n">
-        <v>116.8955993652344</v>
+        <v>116.2000274658203</v>
       </c>
       <c r="F97" t="n">
-        <v>19552200</v>
+        <v>22968600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>116.7564814621505</v>
+        <v>115.9019236934497</v>
       </c>
       <c r="C98" t="n">
-        <v>116.8856561166937</v>
+        <v>116.7167345864151</v>
       </c>
       <c r="D98" t="n">
-        <v>114.7492669888757</v>
+        <v>115.1367994424561</v>
       </c>
       <c r="E98" t="n">
-        <v>116.2000274658203</v>
+        <v>115.8323669433594</v>
       </c>
       <c r="F98" t="n">
-        <v>22968600</v>
+        <v>16342000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>115.9019236934497</v>
+        <v>115.7131212672227</v>
       </c>
       <c r="C99" t="n">
-        <v>116.7167345864151</v>
+        <v>116.9154712653777</v>
       </c>
       <c r="D99" t="n">
-        <v>115.1367994424561</v>
+        <v>115.3355285714882</v>
       </c>
       <c r="E99" t="n">
-        <v>115.8323669433594</v>
+        <v>116.6670532226562</v>
       </c>
       <c r="F99" t="n">
-        <v>16342000</v>
+        <v>16381100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>115.7131212672227</v>
+        <v>116.1702235798966</v>
       </c>
       <c r="C100" t="n">
-        <v>116.9154712653777</v>
+        <v>118.6544041448817</v>
       </c>
       <c r="D100" t="n">
-        <v>115.3355285714882</v>
+        <v>115.8621800346786</v>
       </c>
       <c r="E100" t="n">
-        <v>116.6670532226562</v>
+        <v>118.3861083984375</v>
       </c>
       <c r="F100" t="n">
-        <v>16381100</v>
+        <v>22215400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>116.1702235798966</v>
+        <v>118.7438208421828</v>
       </c>
       <c r="C101" t="n">
-        <v>118.6544041448817</v>
+        <v>123.4140768721483</v>
       </c>
       <c r="D101" t="n">
-        <v>115.8621800346786</v>
+        <v>118.2966714112071</v>
       </c>
       <c r="E101" t="n">
-        <v>118.3861083984375</v>
+        <v>123.2749633789062</v>
       </c>
       <c r="F101" t="n">
-        <v>22215400</v>
+        <v>31210100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>118.7438208421828</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="C102" t="n">
-        <v>123.4140768721483</v>
+        <v>127.3589666685813</v>
       </c>
       <c r="D102" t="n">
-        <v>118.2966714112071</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="E102" t="n">
-        <v>123.2749633789062</v>
+        <v>126.9018783569336</v>
       </c>
       <c r="F102" t="n">
-        <v>31210100</v>
+        <v>32018700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>122.8675715680868</v>
+        <v>127.3192151881231</v>
       </c>
       <c r="C103" t="n">
-        <v>127.3589666685813</v>
+        <v>128.5911143047342</v>
       </c>
       <c r="D103" t="n">
-        <v>122.8675715680868</v>
+        <v>126.2857876794806</v>
       </c>
       <c r="E103" t="n">
-        <v>126.9018783569336</v>
+        <v>127.1900329589844</v>
       </c>
       <c r="F103" t="n">
-        <v>32018700</v>
+        <v>27531800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>127.3192151881231</v>
+        <v>127.7663710403251</v>
       </c>
       <c r="C104" t="n">
-        <v>128.5911143047342</v>
+        <v>128.779920911861</v>
       </c>
       <c r="D104" t="n">
-        <v>126.2857876794806</v>
+        <v>125.7591489863279</v>
       </c>
       <c r="E104" t="n">
-        <v>127.1900329589844</v>
+        <v>126.1367492675781</v>
       </c>
       <c r="F104" t="n">
-        <v>27531800</v>
+        <v>30517800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>127.7663710403251</v>
+        <v>126.4845378023196</v>
       </c>
       <c r="C105" t="n">
-        <v>128.779920911861</v>
+        <v>130.8666283506429</v>
       </c>
       <c r="D105" t="n">
-        <v>125.7591489863279</v>
+        <v>126.2460585922159</v>
       </c>
       <c r="E105" t="n">
-        <v>126.1367492675781</v>
+        <v>130.3499145507812</v>
       </c>
       <c r="F105" t="n">
-        <v>30517800</v>
+        <v>26593400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>126.4845378023196</v>
+        <v>130.5884053590928</v>
       </c>
       <c r="C106" t="n">
-        <v>130.8666283506429</v>
+        <v>130.9560592399128</v>
       </c>
       <c r="D106" t="n">
-        <v>126.2460585922159</v>
+        <v>127.2794749450073</v>
       </c>
       <c r="E106" t="n">
-        <v>130.3499145507812</v>
+        <v>128.2035980224609</v>
       </c>
       <c r="F106" t="n">
-        <v>26593400</v>
+        <v>27197300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>130.5884053590928</v>
+        <v>128.1240931628847</v>
       </c>
       <c r="C107" t="n">
-        <v>130.9560592399128</v>
+        <v>128.5215559695187</v>
       </c>
       <c r="D107" t="n">
-        <v>127.2794749450073</v>
+        <v>125.5902260744493</v>
       </c>
       <c r="E107" t="n">
-        <v>128.2035980224609</v>
+        <v>125.8982620239258</v>
       </c>
       <c r="F107" t="n">
-        <v>27197300</v>
+        <v>24662000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>128.1240931628847</v>
+        <v>125.8982685130821</v>
       </c>
       <c r="C108" t="n">
-        <v>128.5215559695187</v>
+        <v>128.9190405832424</v>
       </c>
       <c r="D108" t="n">
-        <v>125.5902260744493</v>
+        <v>125.8287117602243</v>
       </c>
       <c r="E108" t="n">
-        <v>125.8982620239258</v>
+        <v>127.9551773071289</v>
       </c>
       <c r="F108" t="n">
-        <v>24662000</v>
+        <v>19232100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>125.8982685130821</v>
+        <v>128.5613042513025</v>
       </c>
       <c r="C109" t="n">
-        <v>128.9190405832424</v>
+        <v>133.6389694112844</v>
       </c>
       <c r="D109" t="n">
-        <v>125.8287117602243</v>
+        <v>128.4917399247525</v>
       </c>
       <c r="E109" t="n">
-        <v>127.9551773071289</v>
+        <v>132.7943420410156</v>
       </c>
       <c r="F109" t="n">
-        <v>19232100</v>
+        <v>33382700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>128.5613042513025</v>
+        <v>131.8602980405916</v>
       </c>
       <c r="C110" t="n">
-        <v>133.6389694112844</v>
+        <v>133.7979558000997</v>
       </c>
       <c r="D110" t="n">
-        <v>128.4917399247525</v>
+        <v>130.9163124820861</v>
       </c>
       <c r="E110" t="n">
-        <v>132.7943420410156</v>
+        <v>133.0427703857422</v>
       </c>
       <c r="F110" t="n">
-        <v>33382700</v>
+        <v>24131200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>131.8602980405916</v>
+        <v>132.2677060470971</v>
       </c>
       <c r="C111" t="n">
-        <v>133.7979558000997</v>
+        <v>133.8377099294918</v>
       </c>
       <c r="D111" t="n">
-        <v>130.9163124820861</v>
+        <v>127.3490317305018</v>
       </c>
       <c r="E111" t="n">
-        <v>133.0427703857422</v>
+        <v>128.03466796875</v>
       </c>
       <c r="F111" t="n">
-        <v>24131200</v>
+        <v>37995900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>132.2677060470971</v>
+        <v>127.3192184434441</v>
       </c>
       <c r="C112" t="n">
-        <v>133.8377099294918</v>
+        <v>128.0545261364593</v>
       </c>
       <c r="D112" t="n">
-        <v>127.3490317305018</v>
+        <v>124.9741439631975</v>
       </c>
       <c r="E112" t="n">
-        <v>128.03466796875</v>
+        <v>125.8187713623047</v>
       </c>
       <c r="F112" t="n">
-        <v>37995900</v>
+        <v>36485000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>127.3192184434441</v>
+        <v>127.6868765679835</v>
       </c>
       <c r="C113" t="n">
-        <v>128.0545261364593</v>
+        <v>129.2767581387821</v>
       </c>
       <c r="D113" t="n">
-        <v>124.9741439631975</v>
+        <v>123.6128221003258</v>
       </c>
       <c r="E113" t="n">
-        <v>125.8187713623047</v>
+        <v>124.0798492431641</v>
       </c>
       <c r="F113" t="n">
-        <v>36485000</v>
+        <v>42993300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>127.6868765679835</v>
+        <v>122.2216774308809</v>
       </c>
       <c r="C114" t="n">
-        <v>129.2767581387821</v>
+        <v>122.6986434102051</v>
       </c>
       <c r="D114" t="n">
-        <v>123.6128221003258</v>
+        <v>120.2840197235699</v>
       </c>
       <c r="E114" t="n">
-        <v>124.0798492431641</v>
+        <v>122.2117385864258</v>
       </c>
       <c r="F114" t="n">
-        <v>42993300</v>
+        <v>35151000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>122.2216774308809</v>
+        <v>122.7383904417398</v>
       </c>
       <c r="C115" t="n">
-        <v>122.6986434102051</v>
+        <v>125.9976417223621</v>
       </c>
       <c r="D115" t="n">
-        <v>120.2840197235699</v>
+        <v>122.1819364192246</v>
       </c>
       <c r="E115" t="n">
-        <v>122.2117385864258</v>
+        <v>125.0139007568359</v>
       </c>
       <c r="F115" t="n">
-        <v>35151000</v>
+        <v>25662800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>122.7383904417398</v>
+        <v>125.1033248323272</v>
       </c>
       <c r="C116" t="n">
-        <v>125.9976417223621</v>
+        <v>127.2297750394507</v>
       </c>
       <c r="D116" t="n">
-        <v>122.1819364192246</v>
+        <v>124.1195915294407</v>
       </c>
       <c r="E116" t="n">
-        <v>125.0139007568359</v>
+        <v>125.9479446411133</v>
       </c>
       <c r="F116" t="n">
-        <v>25662800</v>
+        <v>20161200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>125.1033248323272</v>
+        <v>125.8088357226236</v>
       </c>
       <c r="C117" t="n">
-        <v>127.2297750394507</v>
+        <v>126.593837657093</v>
       </c>
       <c r="D117" t="n">
-        <v>124.1195915294407</v>
+        <v>124.626363398647</v>
       </c>
       <c r="E117" t="n">
-        <v>125.9479446411133</v>
+        <v>124.9542770385742</v>
       </c>
       <c r="F117" t="n">
-        <v>20161200</v>
+        <v>17345700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>125.8088357226236</v>
+        <v>125.1828241808018</v>
       </c>
       <c r="C118" t="n">
-        <v>126.593837657093</v>
+        <v>126.5242801033853</v>
       </c>
       <c r="D118" t="n">
-        <v>124.626363398647</v>
+        <v>123.1557320302039</v>
       </c>
       <c r="E118" t="n">
-        <v>124.9542770385742</v>
+        <v>123.6326904296875</v>
       </c>
       <c r="F118" t="n">
-        <v>17345700</v>
+        <v>18638300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>125.1828241808018</v>
+        <v>124.7257341647123</v>
       </c>
       <c r="C119" t="n">
-        <v>126.5242801033853</v>
+        <v>127.7862540138419</v>
       </c>
       <c r="D119" t="n">
-        <v>123.1557320302039</v>
+        <v>124.3580802939128</v>
       </c>
       <c r="E119" t="n">
-        <v>123.6326904296875</v>
+        <v>127.1403579711914</v>
       </c>
       <c r="F119" t="n">
-        <v>18638300</v>
+        <v>29205500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>124.7257341647123</v>
+        <v>126.6534531765271</v>
       </c>
       <c r="C120" t="n">
-        <v>127.7862540138419</v>
+        <v>127.9352911784569</v>
       </c>
       <c r="D120" t="n">
-        <v>124.3580802939128</v>
+        <v>126.2460515312658</v>
       </c>
       <c r="E120" t="n">
-        <v>127.1403579711914</v>
+        <v>126.2957305908203</v>
       </c>
       <c r="F120" t="n">
-        <v>29205500</v>
+        <v>17091500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>126.6534531765271</v>
+        <v>125.7193975573372</v>
       </c>
       <c r="C121" t="n">
-        <v>127.9352911784569</v>
+        <v>127.5576895255598</v>
       </c>
       <c r="D121" t="n">
-        <v>126.2460515312658</v>
+        <v>124.8747777428692</v>
       </c>
       <c r="E121" t="n">
-        <v>126.2957305908203</v>
+        <v>127.1006088256836</v>
       </c>
       <c r="F121" t="n">
-        <v>17091500</v>
+        <v>16480400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>125.7193975573372</v>
+        <v>126.3056684844515</v>
       </c>
       <c r="C122" t="n">
-        <v>127.5576895255598</v>
+        <v>127.3589585449282</v>
       </c>
       <c r="D122" t="n">
-        <v>124.8747777428692</v>
+        <v>125.4411709786478</v>
       </c>
       <c r="E122" t="n">
-        <v>127.1006088256836</v>
+        <v>127.0012359619141</v>
       </c>
       <c r="F122" t="n">
-        <v>16480400</v>
+        <v>16434100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>126.3056684844515</v>
+        <v>124.5866098839056</v>
       </c>
       <c r="C123" t="n">
-        <v>127.3589585449282</v>
+        <v>124.8847145576342</v>
       </c>
       <c r="D123" t="n">
-        <v>125.4411709786478</v>
+        <v>120.8802170560586</v>
       </c>
       <c r="E123" t="n">
-        <v>127.0012359619141</v>
+        <v>122.5297088623047</v>
       </c>
       <c r="F123" t="n">
-        <v>16434100</v>
+        <v>28604900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>124.5866098839056</v>
+        <v>121.7248399768431</v>
       </c>
       <c r="C124" t="n">
-        <v>124.8847145576342</v>
+        <v>123.4041483583995</v>
       </c>
       <c r="D124" t="n">
-        <v>120.8802170560586</v>
+        <v>120.8504112025381</v>
       </c>
       <c r="E124" t="n">
-        <v>122.5297088623047</v>
+        <v>123.0166168212891</v>
       </c>
       <c r="F124" t="n">
-        <v>28604900</v>
+        <v>21553000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>121.7248399768431</v>
+        <v>122.9073188921967</v>
       </c>
       <c r="C125" t="n">
-        <v>123.4041483583995</v>
+        <v>123.7221298065307</v>
       </c>
       <c r="D125" t="n">
-        <v>120.8504112025381</v>
+        <v>121.7248465285333</v>
       </c>
       <c r="E125" t="n">
-        <v>123.0166168212891</v>
+        <v>123.5531997680664</v>
       </c>
       <c r="F125" t="n">
-        <v>21553000</v>
+        <v>19375900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>122.9073188921967</v>
+        <v>123.4240246061754</v>
       </c>
       <c r="C126" t="n">
-        <v>123.7221298065307</v>
+        <v>125.3020644813305</v>
       </c>
       <c r="D126" t="n">
-        <v>121.7248465285333</v>
+        <v>122.5694658969271</v>
       </c>
       <c r="E126" t="n">
-        <v>123.5531997680664</v>
+        <v>124.3282699584961</v>
       </c>
       <c r="F126" t="n">
-        <v>19375900</v>
+        <v>18793600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>123.4240246061754</v>
+        <v>124.5170631497059</v>
       </c>
       <c r="C127" t="n">
-        <v>125.3020644813305</v>
+        <v>124.6959244521016</v>
       </c>
       <c r="D127" t="n">
-        <v>122.5694658969271</v>
+        <v>122.2713693965471</v>
       </c>
       <c r="E127" t="n">
-        <v>124.3282699584961</v>
+        <v>122.7085800170898</v>
       </c>
       <c r="F127" t="n">
-        <v>18793600</v>
+        <v>18176500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>124.5170631497059</v>
+        <v>121.5261084606577</v>
       </c>
       <c r="C128" t="n">
-        <v>124.6959244521016</v>
+        <v>124.596551802696</v>
       </c>
       <c r="D128" t="n">
-        <v>122.2713693965471</v>
+        <v>121.5062307719897</v>
       </c>
       <c r="E128" t="n">
-        <v>122.7085800170898</v>
+        <v>124.5369338989258</v>
       </c>
       <c r="F128" t="n">
-        <v>18176500</v>
+        <v>21751600</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>121.5261084606577</v>
+        <v>124.5965516855884</v>
       </c>
       <c r="C129" t="n">
-        <v>124.596551802696</v>
+        <v>125.888328527587</v>
       </c>
       <c r="D129" t="n">
-        <v>121.5062307719897</v>
+        <v>124.1792111973551</v>
       </c>
       <c r="E129" t="n">
-        <v>124.5369338989258</v>
+        <v>125.7193984985352</v>
       </c>
       <c r="F129" t="n">
-        <v>21751600</v>
+        <v>15194100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>124.5965516855884</v>
+        <v>125.9578884818529</v>
       </c>
       <c r="C130" t="n">
-        <v>125.888328527587</v>
+        <v>126.1764975758589</v>
       </c>
       <c r="D130" t="n">
-        <v>124.1792111973551</v>
+        <v>124.0401008586876</v>
       </c>
       <c r="E130" t="n">
-        <v>125.7193984985352</v>
+        <v>125.192756652832</v>
       </c>
       <c r="F130" t="n">
-        <v>15194100</v>
+        <v>20463200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>125.9578884818529</v>
+        <v>125.8485858664739</v>
       </c>
       <c r="C131" t="n">
-        <v>126.1764975758589</v>
+        <v>126.3851697651471</v>
       </c>
       <c r="D131" t="n">
-        <v>124.0401008586876</v>
+        <v>124.0699117156269</v>
       </c>
       <c r="E131" t="n">
-        <v>125.192756652832</v>
+        <v>124.2885208129883</v>
       </c>
       <c r="F131" t="n">
-        <v>20463200</v>
+        <v>19895000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>125.8485858664739</v>
+        <v>123.5432578745883</v>
       </c>
       <c r="C132" t="n">
-        <v>126.3851697651471</v>
+        <v>123.8214848583074</v>
       </c>
       <c r="D132" t="n">
-        <v>124.0699117156269</v>
+        <v>121.0590775469296</v>
       </c>
       <c r="E132" t="n">
-        <v>124.2885208129883</v>
+        <v>121.2081298828125</v>
       </c>
       <c r="F132" t="n">
-        <v>19895000</v>
+        <v>19734900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>123.5432578745883</v>
+        <v>121.6254689891314</v>
       </c>
       <c r="C133" t="n">
-        <v>123.8214848583074</v>
+        <v>121.9732527148649</v>
       </c>
       <c r="D133" t="n">
-        <v>121.0590775469296</v>
+        <v>118.5152704020027</v>
       </c>
       <c r="E133" t="n">
-        <v>121.2081298828125</v>
+        <v>120.3237533569336</v>
       </c>
       <c r="F133" t="n">
-        <v>19734900</v>
+        <v>17927700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>121.6254689891314</v>
+        <v>120.1126709520348</v>
       </c>
       <c r="C134" t="n">
-        <v>121.9732527148649</v>
+        <v>120.7798034051914</v>
       </c>
       <c r="D134" t="n">
-        <v>118.5152704020027</v>
+        <v>117.513863427923</v>
       </c>
       <c r="E134" t="n">
-        <v>120.3237533569336</v>
+        <v>118.5095748901367</v>
       </c>
       <c r="F134" t="n">
-        <v>17927700</v>
+        <v>57545600</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -3927,25 +3927,25 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>120.1126709520348</v>
+        <v>119.9633247632631</v>
       </c>
       <c r="C135" t="n">
-        <v>120.7798034051914</v>
+        <v>120.6105311603868</v>
       </c>
       <c r="D135" t="n">
-        <v>117.513863427923</v>
+        <v>118.5394570155744</v>
       </c>
       <c r="E135" t="n">
-        <v>118.5095748901367</v>
+        <v>120.2022933959961</v>
       </c>
       <c r="F135" t="n">
-        <v>57545600</v>
+        <v>22181500</v>
       </c>
       <c r="G135" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>119.9633247632631</v>
+        <v>120.1126723733929</v>
       </c>
       <c r="C136" t="n">
-        <v>120.6105311603868</v>
+        <v>123.577751645438</v>
       </c>
       <c r="D136" t="n">
-        <v>118.5394570155744</v>
+        <v>119.9732733747674</v>
       </c>
       <c r="E136" t="n">
-        <v>120.2022933959961</v>
+        <v>121.5265884399414</v>
       </c>
       <c r="F136" t="n">
-        <v>22181500</v>
+        <v>17269600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>120.1126723733929</v>
+        <v>122.2833215864677</v>
       </c>
       <c r="C137" t="n">
-        <v>123.577751645438</v>
+        <v>122.9604056810019</v>
       </c>
       <c r="D137" t="n">
-        <v>119.9732733747674</v>
+        <v>121.2577400013664</v>
       </c>
       <c r="E137" t="n">
-        <v>121.5265884399414</v>
+        <v>122.5322494506836</v>
       </c>
       <c r="F137" t="n">
-        <v>17269600</v>
+        <v>16597300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>122.2833215864677</v>
+        <v>123.0798964656872</v>
       </c>
       <c r="C138" t="n">
-        <v>122.9604056810019</v>
+        <v>123.2690840775393</v>
       </c>
       <c r="D138" t="n">
-        <v>121.2577400013664</v>
+        <v>121.2677018786759</v>
       </c>
       <c r="E138" t="n">
-        <v>122.5322494506836</v>
+        <v>121.6560287475586</v>
       </c>
       <c r="F138" t="n">
-        <v>16597300</v>
+        <v>16442500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>123.0798964656872</v>
+        <v>121.5066712193412</v>
       </c>
       <c r="C139" t="n">
-        <v>123.2690840775393</v>
+        <v>123.7370628172082</v>
       </c>
       <c r="D139" t="n">
-        <v>121.2677018786759</v>
+        <v>121.2975727192295</v>
       </c>
       <c r="E139" t="n">
-        <v>121.6560287475586</v>
+        <v>122.3629837036133</v>
       </c>
       <c r="F139" t="n">
-        <v>16442500</v>
+        <v>16543300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>121.5066712193412</v>
+        <v>123.1794659302472</v>
       </c>
       <c r="C140" t="n">
-        <v>123.7370628172082</v>
+        <v>124.7228217585454</v>
       </c>
       <c r="D140" t="n">
-        <v>121.2975727192295</v>
+        <v>122.611910692122</v>
       </c>
       <c r="E140" t="n">
-        <v>122.3629837036133</v>
+        <v>122.9703674316406</v>
       </c>
       <c r="F140" t="n">
-        <v>16543300</v>
+        <v>20428900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>123.1794659302472</v>
+        <v>122.9006712768322</v>
       </c>
       <c r="C141" t="n">
-        <v>124.7228217585454</v>
+        <v>124.4639380346807</v>
       </c>
       <c r="D141" t="n">
-        <v>122.611910692122</v>
+        <v>122.313197539037</v>
       </c>
       <c r="E141" t="n">
-        <v>122.9703674316406</v>
+        <v>123.7470245361328</v>
       </c>
       <c r="F141" t="n">
-        <v>20428900</v>
+        <v>21330400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>122.9006712768322</v>
+        <v>123.2690839840767</v>
       </c>
       <c r="C142" t="n">
-        <v>124.4639380346807</v>
+        <v>124.6929517011257</v>
       </c>
       <c r="D142" t="n">
-        <v>122.313197539037</v>
+        <v>122.6019515205109</v>
       </c>
       <c r="E142" t="n">
-        <v>123.7470245361328</v>
+        <v>124.2050476074219</v>
       </c>
       <c r="F142" t="n">
-        <v>21330400</v>
+        <v>17039700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>123.2690839840767</v>
+        <v>124.613294570145</v>
       </c>
       <c r="C143" t="n">
-        <v>124.6929517011257</v>
+        <v>125.3600781881083</v>
       </c>
       <c r="D143" t="n">
-        <v>122.6019515205109</v>
+        <v>123.6175830795272</v>
       </c>
       <c r="E143" t="n">
-        <v>124.2050476074219</v>
+        <v>125.2505493164062</v>
       </c>
       <c r="F143" t="n">
-        <v>17039700</v>
+        <v>11898400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>124.613294570145</v>
+        <v>125.2704609872334</v>
       </c>
       <c r="C144" t="n">
-        <v>125.3600781881083</v>
+        <v>126.4354492120167</v>
       </c>
       <c r="D144" t="n">
-        <v>123.6175830795272</v>
+        <v>124.8323530943609</v>
       </c>
       <c r="E144" t="n">
-        <v>125.2505493164062</v>
+        <v>126.2462615966797</v>
       </c>
       <c r="F144" t="n">
-        <v>11898400</v>
+        <v>10850400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>125.2704609872334</v>
+        <v>125.6488358778686</v>
       </c>
       <c r="C145" t="n">
-        <v>126.4354492120167</v>
+        <v>125.8181050086721</v>
       </c>
       <c r="D145" t="n">
-        <v>124.8323530943609</v>
+        <v>121.2677037842684</v>
       </c>
       <c r="E145" t="n">
-        <v>126.2462615966797</v>
+        <v>121.9646987915039</v>
       </c>
       <c r="F145" t="n">
-        <v>10850400</v>
+        <v>16076000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>125.6488358778686</v>
+        <v>121.7556020039852</v>
       </c>
       <c r="C146" t="n">
-        <v>125.8181050086721</v>
+        <v>126.7540780291546</v>
       </c>
       <c r="D146" t="n">
-        <v>121.2677037842684</v>
+        <v>120.8096791098908</v>
       </c>
       <c r="E146" t="n">
-        <v>121.9646987915039</v>
+        <v>126.7142486572266</v>
       </c>
       <c r="F146" t="n">
-        <v>16076000</v>
+        <v>20194300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>121.7556020039852</v>
+        <v>126.5449729094413</v>
       </c>
       <c r="C147" t="n">
-        <v>126.7540780291546</v>
+        <v>129.1338289281244</v>
       </c>
       <c r="D147" t="n">
-        <v>120.8096791098908</v>
+        <v>126.2761341426855</v>
       </c>
       <c r="E147" t="n">
-        <v>126.7142486572266</v>
+        <v>128.5762329101562</v>
       </c>
       <c r="F147" t="n">
-        <v>20194300</v>
+        <v>13853100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>126.5449729094413</v>
+        <v>128.1679831957248</v>
       </c>
       <c r="C148" t="n">
-        <v>129.1338289281244</v>
+        <v>128.3770740986961</v>
       </c>
       <c r="D148" t="n">
-        <v>126.2761341426855</v>
+        <v>125.6787044903905</v>
       </c>
       <c r="E148" t="n">
-        <v>128.5762329101562</v>
+        <v>126.2263412475586</v>
       </c>
       <c r="F148" t="n">
-        <v>13853100</v>
+        <v>13894000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>128.1679831957248</v>
+        <v>125.7484068642315</v>
       </c>
       <c r="C149" t="n">
-        <v>128.3770740986961</v>
+        <v>125.7583661063497</v>
       </c>
       <c r="D149" t="n">
-        <v>125.6787044903905</v>
+        <v>123.4184379925161</v>
       </c>
       <c r="E149" t="n">
-        <v>126.2263412475586</v>
+        <v>124.0357818603516</v>
       </c>
       <c r="F149" t="n">
-        <v>13894000</v>
+        <v>14510600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>125.7484068642315</v>
+        <v>122.6218644106077</v>
       </c>
       <c r="C150" t="n">
-        <v>125.7583661063497</v>
+        <v>124.6630682888762</v>
       </c>
       <c r="D150" t="n">
-        <v>123.4184379925161</v>
+        <v>122.0244390705456</v>
       </c>
       <c r="E150" t="n">
-        <v>124.0357818603516</v>
+        <v>124.5137176513672</v>
       </c>
       <c r="F150" t="n">
-        <v>14510600</v>
+        <v>15320800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>122.6218644106077</v>
+        <v>124.0955129791748</v>
       </c>
       <c r="C151" t="n">
-        <v>124.6630682888762</v>
+        <v>124.5336284399926</v>
       </c>
       <c r="D151" t="n">
-        <v>122.0244390705456</v>
+        <v>122.6517344420986</v>
       </c>
       <c r="E151" t="n">
-        <v>124.5137176513672</v>
+        <v>124.2249603271484</v>
       </c>
       <c r="F151" t="n">
-        <v>15320800</v>
+        <v>17001400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>124.0955129791748</v>
+        <v>123.7968020201654</v>
       </c>
       <c r="C152" t="n">
-        <v>124.5336284399926</v>
+        <v>125.3998980056611</v>
       </c>
       <c r="D152" t="n">
-        <v>122.6517344420986</v>
+        <v>123.4383453031182</v>
       </c>
       <c r="E152" t="n">
-        <v>124.2249603271484</v>
+        <v>124.2846984863281</v>
       </c>
       <c r="F152" t="n">
-        <v>17001400</v>
+        <v>18324500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>123.7968020201654</v>
+        <v>124.0357815469104</v>
       </c>
       <c r="C153" t="n">
-        <v>125.3998980056611</v>
+        <v>127.0229160540335</v>
       </c>
       <c r="D153" t="n">
-        <v>123.4383453031182</v>
+        <v>122.8409307827315</v>
       </c>
       <c r="E153" t="n">
-        <v>124.2846984863281</v>
+        <v>126.9532165527344</v>
       </c>
       <c r="F153" t="n">
-        <v>18324500</v>
+        <v>24763700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>124.0357815469104</v>
+        <v>127.3216255408005</v>
       </c>
       <c r="C154" t="n">
-        <v>127.0229160540335</v>
+        <v>128.9147623376428</v>
       </c>
       <c r="D154" t="n">
-        <v>122.8409307827315</v>
+        <v>126.7739812059444</v>
       </c>
       <c r="E154" t="n">
-        <v>126.9532165527344</v>
+        <v>127.3714065551758</v>
       </c>
       <c r="F154" t="n">
-        <v>24763700</v>
+        <v>18933600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>127.3216255408005</v>
+        <v>127.2817912634612</v>
       </c>
       <c r="C155" t="n">
-        <v>128.9147623376428</v>
+        <v>129.213473828279</v>
       </c>
       <c r="D155" t="n">
-        <v>126.7739812059444</v>
+        <v>126.9332937895701</v>
       </c>
       <c r="E155" t="n">
-        <v>127.3714065551758</v>
+        <v>129.0442047119141</v>
       </c>
       <c r="F155" t="n">
-        <v>18933600</v>
+        <v>17312400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>127.2817912634612</v>
+        <v>129.4424953884951</v>
       </c>
       <c r="C156" t="n">
-        <v>129.213473828279</v>
+        <v>129.8905625261696</v>
       </c>
       <c r="D156" t="n">
-        <v>126.9332937895701</v>
+        <v>128.2874663986241</v>
       </c>
       <c r="E156" t="n">
-        <v>129.0442047119141</v>
+        <v>129.4225769042969</v>
       </c>
       <c r="F156" t="n">
-        <v>17312400</v>
+        <v>17624500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>129.4424953884951</v>
+        <v>130.010060581267</v>
       </c>
       <c r="C157" t="n">
-        <v>129.8905625261696</v>
+        <v>131.8919547480997</v>
       </c>
       <c r="D157" t="n">
-        <v>128.2874663986241</v>
+        <v>129.93040183639</v>
       </c>
       <c r="E157" t="n">
-        <v>129.4225769042969</v>
+        <v>131.4637908935547</v>
       </c>
       <c r="F157" t="n">
-        <v>17624500</v>
+        <v>16376000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>130.010060581267</v>
+        <v>131.3741802679442</v>
       </c>
       <c r="C158" t="n">
-        <v>131.8919547480997</v>
+        <v>131.5534010485827</v>
       </c>
       <c r="D158" t="n">
-        <v>129.93040183639</v>
+        <v>128.7255839805935</v>
       </c>
       <c r="E158" t="n">
-        <v>131.4637908935547</v>
+        <v>129.3628387451172</v>
       </c>
       <c r="F158" t="n">
-        <v>16376000</v>
+        <v>16016300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>131.3741802679442</v>
+        <v>129.0641091249569</v>
       </c>
       <c r="C159" t="n">
-        <v>131.5534010485827</v>
+        <v>129.253296725292</v>
       </c>
       <c r="D159" t="n">
-        <v>128.7255839805935</v>
+        <v>126.8536361584495</v>
       </c>
       <c r="E159" t="n">
-        <v>129.3628387451172</v>
+        <v>127.0428161621094</v>
       </c>
       <c r="F159" t="n">
-        <v>16016300</v>
+        <v>17029500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>129.0641091249569</v>
+        <v>128.7853111434159</v>
       </c>
       <c r="C160" t="n">
-        <v>129.253296725292</v>
+        <v>129.2134749536506</v>
       </c>
       <c r="D160" t="n">
-        <v>126.8536361584495</v>
+        <v>126.236292344555</v>
       </c>
       <c r="E160" t="n">
         <v>127.0428161621094</v>
       </c>
       <c r="F160" t="n">
-        <v>17029500</v>
+        <v>16341800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>128.7853111434159</v>
+        <v>126.1367309249001</v>
       </c>
       <c r="C161" t="n">
-        <v>129.2134749536506</v>
+        <v>127.5307285199335</v>
       </c>
       <c r="D161" t="n">
-        <v>126.236292344555</v>
+        <v>125.3700364258034</v>
       </c>
       <c r="E161" t="n">
-        <v>127.0428161621094</v>
+        <v>127.4610214233398</v>
       </c>
       <c r="F161" t="n">
-        <v>16341800</v>
+        <v>16538800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>126.1367309249001</v>
+        <v>127.470976777907</v>
       </c>
       <c r="C162" t="n">
-        <v>127.5307285199335</v>
+        <v>131.8620524738122</v>
       </c>
       <c r="D162" t="n">
-        <v>125.3700364258034</v>
+        <v>127.4012696875933</v>
       </c>
       <c r="E162" t="n">
-        <v>127.4610214233398</v>
+        <v>131.3641967773438</v>
       </c>
       <c r="F162" t="n">
-        <v>16538800</v>
+        <v>19867700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>127.470976777907</v>
+        <v>131.3542490271043</v>
       </c>
       <c r="C163" t="n">
-        <v>131.8620524738122</v>
+        <v>132.7980275509944</v>
       </c>
       <c r="D163" t="n">
-        <v>127.4012696875933</v>
+        <v>130.4182778590603</v>
       </c>
       <c r="E163" t="n">
-        <v>131.3641967773438</v>
+        <v>131.0356292724609</v>
       </c>
       <c r="F163" t="n">
-        <v>19867700</v>
+        <v>10480900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>131.3542490271043</v>
+        <v>129.8507311252314</v>
       </c>
       <c r="C164" t="n">
-        <v>132.7980275509944</v>
+        <v>131.184980793923</v>
       </c>
       <c r="D164" t="n">
-        <v>130.4182778590603</v>
+        <v>129.1238508427206</v>
       </c>
       <c r="E164" t="n">
-        <v>131.0356292724609</v>
+        <v>129.7710723876953</v>
       </c>
       <c r="F164" t="n">
-        <v>10480900</v>
+        <v>10340700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>129.8507311252314</v>
+        <v>129.9502974650302</v>
       </c>
       <c r="C165" t="n">
-        <v>131.184980793923</v>
+        <v>131.1650666644096</v>
       </c>
       <c r="D165" t="n">
-        <v>129.1238508427206</v>
+        <v>129.7412065662402</v>
       </c>
       <c r="E165" t="n">
-        <v>129.7710723876953</v>
+        <v>130.2290954589844</v>
       </c>
       <c r="F165" t="n">
-        <v>10340700</v>
+        <v>10637300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>129.9502974650302</v>
+        <v>130.2988095283542</v>
       </c>
       <c r="C166" t="n">
-        <v>131.1650666644096</v>
+        <v>130.5875591827794</v>
       </c>
       <c r="D166" t="n">
-        <v>129.7412065662402</v>
+        <v>128.9745113895137</v>
       </c>
       <c r="E166" t="n">
-        <v>130.2290954589844</v>
+        <v>129.5221557617188</v>
       </c>
       <c r="F166" t="n">
-        <v>10637300</v>
+        <v>16371500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>130.2988095283542</v>
+        <v>129.3429155964338</v>
       </c>
       <c r="C167" t="n">
-        <v>130.5875591827794</v>
+        <v>130.0399257893878</v>
       </c>
       <c r="D167" t="n">
-        <v>128.9745113895137</v>
+        <v>128.1181947261785</v>
       </c>
       <c r="E167" t="n">
-        <v>129.5221557617188</v>
+        <v>129.6416320800781</v>
       </c>
       <c r="F167" t="n">
-        <v>16371500</v>
+        <v>14935400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,25 +4785,25 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>129.3429155964338</v>
+        <v>130.0087618254011</v>
       </c>
       <c r="C168" t="n">
-        <v>130.0399257893878</v>
+        <v>131.0961549064253</v>
       </c>
       <c r="D168" t="n">
-        <v>128.1181947261785</v>
+        <v>129.9389217008702</v>
       </c>
       <c r="E168" t="n">
-        <v>129.6416320800781</v>
+        <v>130.1184844970703</v>
       </c>
       <c r="F168" t="n">
-        <v>14935400</v>
+        <v>15183700</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -4811,25 +4811,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>130.0087618254011</v>
+        <v>129.8690812906444</v>
       </c>
       <c r="C169" t="n">
-        <v>131.0961549064253</v>
+        <v>130.2880915922154</v>
       </c>
       <c r="D169" t="n">
-        <v>129.9389217008702</v>
+        <v>126.078161470576</v>
       </c>
       <c r="E169" t="n">
-        <v>130.1184844970703</v>
+        <v>127.285270690918</v>
       </c>
       <c r="F169" t="n">
-        <v>15183700</v>
+        <v>18699200</v>
       </c>
       <c r="G169" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>129.8690812906444</v>
+        <v>127.7741133789013</v>
       </c>
       <c r="C170" t="n">
-        <v>130.2880915922154</v>
+        <v>130.8068463681294</v>
       </c>
       <c r="D170" t="n">
-        <v>126.078161470576</v>
+        <v>127.4149725439082</v>
       </c>
       <c r="E170" t="n">
-        <v>127.285270690918</v>
+        <v>130.0386962890625</v>
       </c>
       <c r="F170" t="n">
-        <v>18699200</v>
+        <v>17935400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>127.7741133789013</v>
+        <v>128.8814524975413</v>
       </c>
       <c r="C171" t="n">
-        <v>130.8068463681294</v>
+        <v>132.2134717809921</v>
       </c>
       <c r="D171" t="n">
-        <v>127.4149725439082</v>
+        <v>128.4624574279768</v>
       </c>
       <c r="E171" t="n">
-        <v>130.0386962890625</v>
+        <v>131.156005859375</v>
       </c>
       <c r="F171" t="n">
-        <v>17935400</v>
+        <v>13786600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>128.8814524975413</v>
+        <v>131.0462673331121</v>
       </c>
       <c r="C172" t="n">
-        <v>132.2134717809921</v>
+        <v>132.4628740535408</v>
       </c>
       <c r="D172" t="n">
-        <v>128.4624574279768</v>
+        <v>130.5474615066649</v>
       </c>
       <c r="E172" t="n">
-        <v>131.156005859375</v>
+        <v>132.1436462402344</v>
       </c>
       <c r="F172" t="n">
-        <v>13786600</v>
+        <v>14200400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>131.0462673331121</v>
+        <v>133.370718441355</v>
       </c>
       <c r="C173" t="n">
-        <v>132.4628740535408</v>
+        <v>133.6300920185431</v>
       </c>
       <c r="D173" t="n">
-        <v>130.5474615066649</v>
+        <v>130.4776352080381</v>
       </c>
       <c r="E173" t="n">
-        <v>132.1436462402344</v>
+        <v>131.1360626220703</v>
       </c>
       <c r="F173" t="n">
-        <v>14200400</v>
+        <v>25323000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>133.370718441355</v>
+        <v>131.2058999637278</v>
       </c>
       <c r="C174" t="n">
-        <v>133.6300920185431</v>
+        <v>133.1512398071679</v>
       </c>
       <c r="D174" t="n">
-        <v>130.4776352080381</v>
+        <v>130.8168319950398</v>
       </c>
       <c r="E174" t="n">
-        <v>131.1360626220703</v>
+        <v>133.0215454101562</v>
       </c>
       <c r="F174" t="n">
-        <v>25323000</v>
+        <v>17183200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>131.2058999637278</v>
+        <v>132.6225008315265</v>
       </c>
       <c r="C175" t="n">
-        <v>133.1512398071679</v>
+        <v>134.8372000065807</v>
       </c>
       <c r="D175" t="n">
-        <v>130.8168319950398</v>
+        <v>131.7445976710087</v>
       </c>
       <c r="E175" t="n">
-        <v>133.0215454101562</v>
+        <v>133.8794860839844</v>
       </c>
       <c r="F175" t="n">
-        <v>17183200</v>
+        <v>16957100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>132.6225008315265</v>
+        <v>132.5925684137131</v>
       </c>
       <c r="C176" t="n">
-        <v>134.8372000065807</v>
+        <v>133.3307912944098</v>
       </c>
       <c r="D176" t="n">
-        <v>131.7445976710087</v>
+        <v>130.0187285230658</v>
       </c>
       <c r="E176" t="n">
-        <v>133.8794860839844</v>
+        <v>130.5374908447266</v>
       </c>
       <c r="F176" t="n">
-        <v>16957100</v>
+        <v>28471600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>132.5925684137131</v>
+        <v>124.112876676945</v>
       </c>
       <c r="C177" t="n">
-        <v>133.3307912944098</v>
+        <v>125.49955634699</v>
       </c>
       <c r="D177" t="n">
-        <v>130.0187285230658</v>
+        <v>120.1024733345915</v>
       </c>
       <c r="E177" t="n">
-        <v>130.5374908447266</v>
+        <v>121.0502014160156</v>
       </c>
       <c r="F177" t="n">
-        <v>28471600</v>
+        <v>53006600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>124.112876676945</v>
+        <v>121.0502017985552</v>
       </c>
       <c r="C178" t="n">
-        <v>125.49955634699</v>
+        <v>121.6587455533669</v>
       </c>
       <c r="D178" t="n">
-        <v>120.1024733345915</v>
+        <v>118.6260126387565</v>
       </c>
       <c r="E178" t="n">
-        <v>121.0502014160156</v>
+        <v>119.9827575683594</v>
       </c>
       <c r="F178" t="n">
-        <v>53006600</v>
+        <v>30330600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>121.0502017985552</v>
+        <v>120.401759010853</v>
       </c>
       <c r="C179" t="n">
-        <v>121.6587455533669</v>
+        <v>120.7608998332451</v>
       </c>
       <c r="D179" t="n">
-        <v>118.6260126387565</v>
+        <v>117.638370328068</v>
       </c>
       <c r="E179" t="n">
-        <v>119.9827575683594</v>
+        <v>118.2868194580078</v>
       </c>
       <c r="F179" t="n">
-        <v>30330600</v>
+        <v>28796600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>120.401759010853</v>
+        <v>118.0473918040102</v>
       </c>
       <c r="C180" t="n">
-        <v>120.7608998332451</v>
+        <v>119.1447631286873</v>
       </c>
       <c r="D180" t="n">
-        <v>117.638370328068</v>
+        <v>117.7580835037564</v>
       </c>
       <c r="E180" t="n">
-        <v>118.2868194580078</v>
+        <v>118.2568893432617</v>
       </c>
       <c r="F180" t="n">
-        <v>28796600</v>
+        <v>22062200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>118.0473918040102</v>
+        <v>118.6758897292679</v>
       </c>
       <c r="C181" t="n">
-        <v>119.1447631286873</v>
+        <v>118.8853872778886</v>
       </c>
       <c r="D181" t="n">
-        <v>117.7580835037564</v>
+        <v>117.0497853597791</v>
       </c>
       <c r="E181" t="n">
-        <v>118.2568893432617</v>
+        <v>118.6160354614258</v>
       </c>
       <c r="F181" t="n">
-        <v>22062200</v>
+        <v>21613100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>118.6758897292679</v>
+        <v>117.8279207851919</v>
       </c>
       <c r="C182" t="n">
-        <v>118.8853872778886</v>
+        <v>118.7956053707809</v>
       </c>
       <c r="D182" t="n">
-        <v>117.0497853597791</v>
+        <v>114.4360394170558</v>
       </c>
       <c r="E182" t="n">
-        <v>118.6160354614258</v>
+        <v>115.4735565185547</v>
       </c>
       <c r="F182" t="n">
-        <v>21613100</v>
+        <v>42191000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>117.8279207851919</v>
+        <v>114.4559959694409</v>
       </c>
       <c r="C183" t="n">
-        <v>118.7956053707809</v>
+        <v>115.7030106192767</v>
       </c>
       <c r="D183" t="n">
-        <v>114.4360394170558</v>
+        <v>113.2887844727029</v>
       </c>
       <c r="E183" t="n">
-        <v>115.4735565185547</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F183" t="n">
-        <v>42191000</v>
+        <v>26176200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>114.4559959694409</v>
+        <v>113.598048691841</v>
       </c>
       <c r="C184" t="n">
-        <v>115.7030106192767</v>
+        <v>114.2963738476551</v>
       </c>
       <c r="D184" t="n">
-        <v>113.2887844727029</v>
+        <v>112.4607719459876</v>
       </c>
       <c r="E184" t="n">
-        <v>114.326301574707</v>
+        <v>112.7899780273438</v>
       </c>
       <c r="F184" t="n">
-        <v>26176200</v>
+        <v>27366400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>113.598048691841</v>
+        <v>112.829882918774</v>
       </c>
       <c r="C185" t="n">
-        <v>114.2963738476551</v>
+        <v>117.0098784207316</v>
       </c>
       <c r="D185" t="n">
-        <v>112.4607719459876</v>
+        <v>112.6902178882183</v>
       </c>
       <c r="E185" t="n">
-        <v>112.7899780273438</v>
+        <v>116.6108322143555</v>
       </c>
       <c r="F185" t="n">
-        <v>27366400</v>
+        <v>32880600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>112.829882918774</v>
+        <v>119.613646228699</v>
       </c>
       <c r="C186" t="n">
-        <v>117.0098784207316</v>
+        <v>119.6535516106658</v>
       </c>
       <c r="D186" t="n">
-        <v>112.6902178882183</v>
+        <v>117.009879041958</v>
       </c>
       <c r="E186" t="n">
-        <v>116.6108322143555</v>
+        <v>117.4588012695312</v>
       </c>
       <c r="F186" t="n">
-        <v>32880600</v>
+        <v>22870400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>119.613646228699</v>
+        <v>118.0673439785114</v>
       </c>
       <c r="C187" t="n">
-        <v>119.6535516106658</v>
+        <v>120.601278627145</v>
       </c>
       <c r="D187" t="n">
-        <v>117.009879041958</v>
+        <v>117.8179410518094</v>
       </c>
       <c r="E187" t="n">
-        <v>117.4588012695312</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F187" t="n">
-        <v>22870400</v>
+        <v>36638100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>118.0673439785114</v>
+        <v>117.9675872503352</v>
       </c>
       <c r="C188" t="n">
-        <v>120.601278627145</v>
+        <v>119.8929781965846</v>
       </c>
       <c r="D188" t="n">
-        <v>117.8179410518094</v>
+        <v>117.8678275994195</v>
       </c>
       <c r="E188" t="n">
-        <v>118.596076965332</v>
+        <v>119.543815612793</v>
       </c>
       <c r="F188" t="n">
-        <v>36638100</v>
+        <v>19514100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>117.9675872503352</v>
+        <v>120.0924945255443</v>
       </c>
       <c r="C189" t="n">
-        <v>119.8929781965846</v>
+        <v>120.2122106703836</v>
       </c>
       <c r="D189" t="n">
-        <v>117.8678275994195</v>
+        <v>117.7181814033632</v>
       </c>
       <c r="E189" t="n">
-        <v>119.543815612793</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F189" t="n">
-        <v>19514100</v>
+        <v>23959000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>120.0924945255443</v>
+        <v>119.4240987453198</v>
       </c>
       <c r="C190" t="n">
-        <v>120.2122106703836</v>
+        <v>120.53144836951</v>
       </c>
       <c r="D190" t="n">
-        <v>117.7181814033632</v>
+        <v>117.2493048793001</v>
       </c>
       <c r="E190" t="n">
-        <v>118.596076965332</v>
+        <v>120.3019943237305</v>
       </c>
       <c r="F190" t="n">
-        <v>23959000</v>
+        <v>22414900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>119.4240987453198</v>
+        <v>120.2820441244615</v>
       </c>
       <c r="C191" t="n">
-        <v>120.53144836951</v>
+        <v>121.5689641496319</v>
       </c>
       <c r="D191" t="n">
-        <v>117.2493048793001</v>
+        <v>119.1746945123655</v>
       </c>
       <c r="E191" t="n">
-        <v>120.3019943237305</v>
+        <v>120.2122116088867</v>
       </c>
       <c r="F191" t="n">
-        <v>22414900</v>
+        <v>22438000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>120.2820441244615</v>
+        <v>120.3019933173184</v>
       </c>
       <c r="C192" t="n">
-        <v>121.5689641496319</v>
+        <v>121.3195615310648</v>
       </c>
       <c r="D192" t="n">
-        <v>119.1746945123655</v>
+        <v>119.2445273327187</v>
       </c>
       <c r="E192" t="n">
-        <v>120.2122116088867</v>
+        <v>120.7509231567383</v>
       </c>
       <c r="F192" t="n">
-        <v>22438000</v>
+        <v>14753500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>120.3019933173184</v>
+        <v>119.4540258740917</v>
       </c>
       <c r="C193" t="n">
-        <v>121.3195615310648</v>
+        <v>121.1998463936268</v>
       </c>
       <c r="D193" t="n">
-        <v>119.2445273327187</v>
+        <v>118.2968002303814</v>
       </c>
       <c r="E193" t="n">
-        <v>120.7509231567383</v>
+        <v>120.5314483642578</v>
       </c>
       <c r="F193" t="n">
-        <v>14753500</v>
+        <v>20722500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>119.4540258740917</v>
+        <v>120.8506818055627</v>
       </c>
       <c r="C194" t="n">
-        <v>121.1998463936268</v>
+        <v>122.646385926027</v>
       </c>
       <c r="D194" t="n">
-        <v>118.2968002303814</v>
+        <v>119.5936889212378</v>
       </c>
       <c r="E194" t="n">
-        <v>120.5314483642578</v>
+        <v>120.7409439086914</v>
       </c>
       <c r="F194" t="n">
-        <v>20722500</v>
+        <v>23060700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>120.8506818055627</v>
+        <v>119.2944114353401</v>
       </c>
       <c r="C195" t="n">
-        <v>122.646385926027</v>
+        <v>120.7209965009543</v>
       </c>
       <c r="D195" t="n">
-        <v>119.5936889212378</v>
+        <v>117.1694935982547</v>
       </c>
       <c r="E195" t="n">
-        <v>120.7409439086914</v>
+        <v>117.8478698730469</v>
       </c>
       <c r="F195" t="n">
-        <v>23060700</v>
+        <v>21711100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>119.2944114353401</v>
+        <v>117.9176994360996</v>
       </c>
       <c r="C196" t="n">
-        <v>120.7209965009543</v>
+        <v>118.1970371043968</v>
       </c>
       <c r="D196" t="n">
-        <v>117.1694935982547</v>
+        <v>116.5210491504798</v>
       </c>
       <c r="E196" t="n">
-        <v>117.8478698730469</v>
+        <v>116.9001388549805</v>
       </c>
       <c r="F196" t="n">
-        <v>21711100</v>
+        <v>36526800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>117.9176994360996</v>
+        <v>116.6806630640479</v>
       </c>
       <c r="C197" t="n">
-        <v>118.1970371043968</v>
+        <v>118.1172263420262</v>
       </c>
       <c r="D197" t="n">
-        <v>116.5210491504798</v>
+        <v>116.6706848159582</v>
       </c>
       <c r="E197" t="n">
         <v>116.9001388549805</v>
       </c>
       <c r="F197" t="n">
-        <v>36526800</v>
+        <v>17053900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>116.6806630640479</v>
+        <v>119.4240968222584</v>
       </c>
       <c r="C198" t="n">
-        <v>118.1172263420262</v>
+        <v>119.9628080586903</v>
       </c>
       <c r="D198" t="n">
-        <v>116.6706848159582</v>
+        <v>116.0621426214644</v>
       </c>
       <c r="E198" t="n">
-        <v>116.9001388549805</v>
+        <v>119.1347885131836</v>
       </c>
       <c r="F198" t="n">
-        <v>17053900</v>
+        <v>23411400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>119.4240968222584</v>
+        <v>119.2744498995579</v>
       </c>
       <c r="C199" t="n">
-        <v>119.9628080586903</v>
+        <v>120.112447667685</v>
       </c>
       <c r="D199" t="n">
-        <v>116.0621426214644</v>
+        <v>118.6459572818424</v>
       </c>
       <c r="E199" t="n">
-        <v>119.1347885131836</v>
+        <v>118.7157897949219</v>
       </c>
       <c r="F199" t="n">
-        <v>23411400</v>
+        <v>20600100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>119.2744498995579</v>
+        <v>117.1894451773868</v>
       </c>
       <c r="C200" t="n">
-        <v>120.112447667685</v>
+        <v>118.2967947502302</v>
       </c>
       <c r="D200" t="n">
-        <v>118.6459572818424</v>
+        <v>115.1044328099781</v>
       </c>
       <c r="E200" t="n">
-        <v>118.7157897949219</v>
+        <v>115.5034790039062</v>
       </c>
       <c r="F200" t="n">
-        <v>20600100</v>
+        <v>20384700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>117.1894451773868</v>
+        <v>117.0098811702962</v>
       </c>
       <c r="C201" t="n">
-        <v>118.2967947502302</v>
+        <v>117.5984684398727</v>
       </c>
       <c r="D201" t="n">
-        <v>115.1044328099781</v>
+        <v>114.8151307892405</v>
       </c>
       <c r="E201" t="n">
-        <v>115.5034790039062</v>
+        <v>115.413703918457</v>
       </c>
       <c r="F201" t="n">
-        <v>20384700</v>
+        <v>36636000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>117.0098811702962</v>
+        <v>116.1918382308837</v>
       </c>
       <c r="C202" t="n">
-        <v>117.5984684398727</v>
+        <v>116.521051925122</v>
       </c>
       <c r="D202" t="n">
-        <v>114.8151307892405</v>
+        <v>113.9272553645249</v>
       </c>
       <c r="E202" t="n">
-        <v>115.413703918457</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F202" t="n">
-        <v>36636000</v>
+        <v>20367000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>116.1918382308837</v>
+        <v>113.6978053385094</v>
       </c>
       <c r="C203" t="n">
-        <v>116.521051925122</v>
+        <v>114.3362762101566</v>
       </c>
       <c r="D203" t="n">
-        <v>113.9272553645249</v>
+        <v>112.6602882692895</v>
       </c>
       <c r="E203" t="n">
-        <v>114.326301574707</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F203" t="n">
-        <v>20367000</v>
+        <v>23034000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>113.6978053385094</v>
+        <v>109.8669732552887</v>
       </c>
       <c r="C204" t="n">
-        <v>114.3362762101566</v>
+        <v>110.4455898652017</v>
       </c>
       <c r="D204" t="n">
-        <v>112.6602882692895</v>
+        <v>106.9938543130583</v>
       </c>
       <c r="E204" t="n">
-        <v>112.989501953125</v>
+        <v>108.5601043701172</v>
       </c>
       <c r="F204" t="n">
-        <v>23034000</v>
+        <v>40391400</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>109.8669732552887</v>
+        <v>109.0688912954154</v>
       </c>
       <c r="C205" t="n">
-        <v>110.4455898652017</v>
+        <v>112.1814349941213</v>
       </c>
       <c r="D205" t="n">
-        <v>106.9938543130583</v>
+        <v>108.8992991295087</v>
       </c>
       <c r="E205" t="n">
-        <v>108.5601043701172</v>
+        <v>111.5728912353516</v>
       </c>
       <c r="F205" t="n">
-        <v>40391400</v>
+        <v>29512200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>109.0688912954154</v>
+        <v>111.1339433224697</v>
       </c>
       <c r="C206" t="n">
-        <v>112.1814349941213</v>
+        <v>112.1016278755018</v>
       </c>
       <c r="D206" t="n">
-        <v>108.8992991295087</v>
+        <v>109.1087928180449</v>
       </c>
       <c r="E206" t="n">
-        <v>111.5728912353516</v>
+        <v>110.3857345581055</v>
       </c>
       <c r="F206" t="n">
-        <v>29512200</v>
+        <v>29523300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>111.1339433224697</v>
+        <v>112.7001980505562</v>
       </c>
       <c r="C207" t="n">
-        <v>112.1016278755018</v>
+        <v>113.228931048236</v>
       </c>
       <c r="D207" t="n">
-        <v>109.1087928180449</v>
+        <v>111.0341882926515</v>
       </c>
       <c r="E207" t="n">
-        <v>110.3857345581055</v>
+        <v>111.2736129760742</v>
       </c>
       <c r="F207" t="n">
-        <v>29523300</v>
+        <v>19941400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>112.7001980505562</v>
+        <v>112.879763389333</v>
       </c>
       <c r="C208" t="n">
-        <v>113.228931048236</v>
+        <v>113.5880667705184</v>
       </c>
       <c r="D208" t="n">
-        <v>111.0341882926515</v>
+        <v>111.5429597770651</v>
       </c>
       <c r="E208" t="n">
-        <v>111.2736129760742</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F208" t="n">
-        <v>19941400</v>
+        <v>19892000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>112.879763389333</v>
+        <v>110.9743243964893</v>
       </c>
       <c r="C209" t="n">
-        <v>113.5880667705184</v>
+        <v>112.4906984566786</v>
       </c>
       <c r="D209" t="n">
-        <v>111.5429597770651</v>
+        <v>110.7748050991254</v>
       </c>
       <c r="E209" t="n">
-        <v>112.8298797607422</v>
+        <v>111.942008972168</v>
       </c>
       <c r="F209" t="n">
-        <v>19892000</v>
+        <v>20464500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>110.9743243964893</v>
+        <v>111.6826280597077</v>
       </c>
       <c r="C210" t="n">
-        <v>112.4906984566786</v>
+        <v>113.8873566399898</v>
       </c>
       <c r="D210" t="n">
-        <v>110.7748050991254</v>
+        <v>111.6626791743936</v>
       </c>
       <c r="E210" t="n">
-        <v>111.942008972168</v>
+        <v>113.6279754638672</v>
       </c>
       <c r="F210" t="n">
-        <v>20464500</v>
+        <v>12461700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>111.6826280597077</v>
+        <v>114.4559909872762</v>
       </c>
       <c r="C211" t="n">
-        <v>113.8873566399898</v>
+        <v>115.26405400962</v>
       </c>
       <c r="D211" t="n">
-        <v>111.6626791743936</v>
+        <v>113.7377093624492</v>
       </c>
       <c r="E211" t="n">
-        <v>113.6279754638672</v>
+        <v>114.5058670043945</v>
       </c>
       <c r="F211" t="n">
-        <v>12461700</v>
+        <v>17043400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>114.4559909872762</v>
+        <v>114.8051528853423</v>
       </c>
       <c r="C212" t="n">
-        <v>115.26405400962</v>
+        <v>115.6032376551602</v>
       </c>
       <c r="D212" t="n">
-        <v>113.7377093624492</v>
+        <v>113.2289246190302</v>
       </c>
       <c r="E212" t="n">
-        <v>114.5058670043945</v>
+        <v>113.4284439086914</v>
       </c>
       <c r="F212" t="n">
-        <v>17043400</v>
+        <v>14682000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>114.8051528853423</v>
+        <v>112.9795273843265</v>
       </c>
       <c r="C213" t="n">
-        <v>115.6032376551602</v>
+        <v>114.4559960800755</v>
       </c>
       <c r="D213" t="n">
-        <v>113.2289246190302</v>
+        <v>111.8023452492967</v>
       </c>
       <c r="E213" t="n">
-        <v>113.4284439086914</v>
+        <v>112.2612457275391</v>
       </c>
       <c r="F213" t="n">
-        <v>14682000</v>
+        <v>16467900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>112.9795273843265</v>
+        <v>113.4883080789502</v>
       </c>
       <c r="C214" t="n">
-        <v>114.4559960800755</v>
+        <v>115.3139316886614</v>
       </c>
       <c r="D214" t="n">
-        <v>111.8023452492967</v>
+        <v>113.288781174082</v>
       </c>
       <c r="E214" t="n">
-        <v>112.2612457275391</v>
+        <v>114.6754608154297</v>
       </c>
       <c r="F214" t="n">
-        <v>16467900</v>
+        <v>20777600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>113.4883080789502</v>
+        <v>116.6806604264181</v>
       </c>
       <c r="C215" t="n">
-        <v>115.3139316886614</v>
+        <v>117.8079588775203</v>
       </c>
       <c r="D215" t="n">
-        <v>113.288781174082</v>
+        <v>113.3286845943574</v>
       </c>
       <c r="E215" t="n">
-        <v>114.6754608154297</v>
+        <v>113.967155456543</v>
       </c>
       <c r="F215" t="n">
-        <v>20777600</v>
+        <v>28289800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>116.6806604264181</v>
+        <v>113.6878284476981</v>
       </c>
       <c r="C216" t="n">
-        <v>117.8079588775203</v>
+        <v>114.1267800313856</v>
       </c>
       <c r="D216" t="n">
-        <v>113.3286845943574</v>
+        <v>111.8721754576813</v>
       </c>
       <c r="E216" t="n">
-        <v>113.967155456543</v>
+        <v>111.9320297241211</v>
       </c>
       <c r="F216" t="n">
-        <v>28289800</v>
+        <v>17738900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>113.6878284476981</v>
+        <v>111.2436859074791</v>
       </c>
       <c r="C217" t="n">
-        <v>114.1267800313856</v>
+        <v>111.5329942219063</v>
       </c>
       <c r="D217" t="n">
-        <v>111.8721754576813</v>
+        <v>109.6275521682845</v>
       </c>
       <c r="E217" t="n">
-        <v>111.9320297241211</v>
+        <v>110.1263580322266</v>
       </c>
       <c r="F217" t="n">
-        <v>17738900</v>
+        <v>22717000</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>111.2436859074791</v>
+        <v>109.268405092928</v>
       </c>
       <c r="C218" t="n">
-        <v>111.5329942219063</v>
+        <v>109.737283796026</v>
       </c>
       <c r="D218" t="n">
-        <v>109.6275521682845</v>
+        <v>108.4603420750963</v>
       </c>
       <c r="E218" t="n">
-        <v>110.1263580322266</v>
+        <v>109.0688858032227</v>
       </c>
       <c r="F218" t="n">
-        <v>22717000</v>
+        <v>23494800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>109.268405092928</v>
+        <v>107.25323944858</v>
       </c>
       <c r="C219" t="n">
-        <v>109.737283796026</v>
+        <v>108.3007272005749</v>
       </c>
       <c r="D219" t="n">
-        <v>108.4603420750963</v>
+        <v>106.5349577836844</v>
       </c>
       <c r="E219" t="n">
-        <v>109.0688858032227</v>
+        <v>108.14111328125</v>
       </c>
       <c r="F219" t="n">
-        <v>23494800</v>
+        <v>21516800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>107.25323944858</v>
+        <v>107.8617828177618</v>
       </c>
       <c r="C220" t="n">
-        <v>108.3007272005749</v>
+        <v>109.3382439135796</v>
       </c>
       <c r="D220" t="n">
-        <v>106.5349577836844</v>
+        <v>107.7520449187408</v>
       </c>
       <c r="E220" t="n">
-        <v>108.14111328125</v>
+        <v>109.2085571289062</v>
       </c>
       <c r="F220" t="n">
-        <v>21516800</v>
+        <v>18405900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>107.8617828177618</v>
+        <v>109.6574762821653</v>
       </c>
       <c r="C221" t="n">
-        <v>109.3382439135796</v>
+        <v>112.2412945440321</v>
       </c>
       <c r="D221" t="n">
-        <v>107.7520449187408</v>
+        <v>109.6275491489408</v>
       </c>
       <c r="E221" t="n">
-        <v>109.2085571289062</v>
+        <v>111.4731292724609</v>
       </c>
       <c r="F221" t="n">
-        <v>18405900</v>
+        <v>19008700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>109.6574762821653</v>
+        <v>113.6878264165269</v>
       </c>
       <c r="C222" t="n">
-        <v>112.2412945440321</v>
+        <v>115.7528822947127</v>
       </c>
       <c r="D222" t="n">
-        <v>109.6275491489408</v>
+        <v>112.5704985921816</v>
       </c>
       <c r="E222" t="n">
-        <v>111.4731292724609</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F222" t="n">
-        <v>19008700</v>
+        <v>24867900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>113.6878264165269</v>
+        <v>112.9595787445935</v>
       </c>
       <c r="C223" t="n">
-        <v>115.7528822947127</v>
+        <v>114.4160909468376</v>
       </c>
       <c r="D223" t="n">
-        <v>112.5704985921816</v>
+        <v>112.1814352072651</v>
       </c>
       <c r="E223" t="n">
-        <v>112.8298797607422</v>
+        <v>113.9472122192383</v>
       </c>
       <c r="F223" t="n">
-        <v>24867900</v>
+        <v>23480000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>112.9595787445935</v>
+        <v>111.3434398479761</v>
       </c>
       <c r="C224" t="n">
-        <v>114.4160909468376</v>
+        <v>112.7600466022415</v>
       </c>
       <c r="D224" t="n">
-        <v>112.1814352072651</v>
+        <v>110.1762360128914</v>
       </c>
       <c r="E224" t="n">
-        <v>113.9472122192383</v>
+        <v>110.8346557617188</v>
       </c>
       <c r="F224" t="n">
-        <v>23480000</v>
+        <v>28747000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>111.3434398479761</v>
+        <v>110.2560414658192</v>
       </c>
       <c r="C225" t="n">
-        <v>112.7600466022415</v>
+        <v>111.642728727712</v>
       </c>
       <c r="D225" t="n">
-        <v>110.1762360128914</v>
+        <v>109.6275488363764</v>
       </c>
       <c r="E225" t="n">
-        <v>110.8346557617188</v>
+        <v>110.9344177246094</v>
       </c>
       <c r="F225" t="n">
-        <v>28747000</v>
+        <v>22799100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>110.2560414658192</v>
+        <v>112.8298784424625</v>
       </c>
       <c r="C226" t="n">
-        <v>111.642728727712</v>
+        <v>113.0194270954852</v>
       </c>
       <c r="D226" t="n">
-        <v>109.6275488363764</v>
+        <v>109.8969053059805</v>
       </c>
       <c r="E226" t="n">
-        <v>110.9344177246094</v>
+        <v>110.4455871582031</v>
       </c>
       <c r="F226" t="n">
-        <v>22799100</v>
+        <v>23942500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>112.8298784424625</v>
+        <v>108.7496500450106</v>
       </c>
       <c r="C227" t="n">
-        <v>113.0194270954852</v>
+        <v>111.4132713715266</v>
       </c>
       <c r="D227" t="n">
-        <v>109.8969053059805</v>
+        <v>108.3007202277679</v>
       </c>
       <c r="E227" t="n">
-        <v>110.4455871582031</v>
+        <v>111.2835845947266</v>
       </c>
       <c r="F227" t="n">
-        <v>23942500</v>
+        <v>29620000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>108.7496500450106</v>
+        <v>112.181431315027</v>
       </c>
       <c r="C228" t="n">
-        <v>111.4132713715266</v>
+        <v>112.8897423116165</v>
       </c>
       <c r="D228" t="n">
-        <v>108.3007202277679</v>
+        <v>111.0940382280446</v>
       </c>
       <c r="E228" t="n">
-        <v>111.2835845947266</v>
+        <v>112.0716934204102</v>
       </c>
       <c r="F228" t="n">
-        <v>29620000</v>
+        <v>21446300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>112.181431315027</v>
+        <v>113.7975687180191</v>
       </c>
       <c r="C229" t="n">
-        <v>112.8897423116165</v>
+        <v>114.2863963302149</v>
       </c>
       <c r="D229" t="n">
-        <v>111.0940382280446</v>
+        <v>110.7748064209645</v>
       </c>
       <c r="E229" t="n">
-        <v>112.0716934204102</v>
+        <v>111.8023452758789</v>
       </c>
       <c r="F229" t="n">
-        <v>21446300</v>
+        <v>23203100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>113.7975687180191</v>
+        <v>110.3458340692701</v>
       </c>
       <c r="C230" t="n">
-        <v>114.2863963302149</v>
+        <v>112.0218220801941</v>
       </c>
       <c r="D230" t="n">
-        <v>110.7748064209645</v>
+        <v>110.2360961700712</v>
       </c>
       <c r="E230" t="n">
-        <v>111.8023452758789</v>
+        <v>111.5828704833984</v>
       </c>
       <c r="F230" t="n">
-        <v>23203100</v>
+        <v>18819300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>110.3458340692701</v>
+        <v>110.8147094920761</v>
       </c>
       <c r="C231" t="n">
-        <v>112.0218220801941</v>
+        <v>112.4308355753539</v>
       </c>
       <c r="D231" t="n">
-        <v>110.2360961700712</v>
+        <v>110.4954740524384</v>
       </c>
       <c r="E231" t="n">
-        <v>111.5828704833984</v>
+        <v>112.3909378051758</v>
       </c>
       <c r="F231" t="n">
-        <v>18819300</v>
+        <v>19144000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>110.8147094920761</v>
+        <v>112.1714606731287</v>
       </c>
       <c r="C232" t="n">
-        <v>112.4308355753539</v>
+        <v>113.069305103701</v>
       </c>
       <c r="D232" t="n">
-        <v>110.4954740524384</v>
+        <v>111.9220577510424</v>
       </c>
       <c r="E232" t="n">
-        <v>112.3909378051758</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F232" t="n">
-        <v>19144000</v>
+        <v>17005800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>112.1714606731287</v>
+        <v>112.1016271407472</v>
       </c>
       <c r="C233" t="n">
-        <v>113.069305103701</v>
+        <v>115.7728384249456</v>
       </c>
       <c r="D233" t="n">
-        <v>111.9220577510424</v>
+        <v>112.011838131802</v>
       </c>
       <c r="E233" t="n">
-        <v>112.989501953125</v>
+        <v>115.7329330444336</v>
       </c>
       <c r="F233" t="n">
-        <v>17005800</v>
+        <v>22054700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>112.1016271407472</v>
+        <v>115.8925486214695</v>
       </c>
       <c r="C234" t="n">
-        <v>115.7728384249456</v>
+        <v>116.0421918977476</v>
       </c>
       <c r="D234" t="n">
-        <v>112.011838131802</v>
+        <v>114.5357961092488</v>
       </c>
       <c r="E234" t="n">
-        <v>115.7329330444336</v>
+        <v>115.4436264038086</v>
       </c>
       <c r="F234" t="n">
-        <v>22054700</v>
+        <v>16822200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>115.8925486214695</v>
+        <v>115.3837731369623</v>
       </c>
       <c r="C235" t="n">
-        <v>116.0421918977476</v>
+        <v>116.1718796839166</v>
       </c>
       <c r="D235" t="n">
-        <v>114.5357961092488</v>
+        <v>114.3662049383982</v>
       </c>
       <c r="E235" t="n">
-        <v>115.4436264038086</v>
+        <v>114.9946975708008</v>
       </c>
       <c r="F235" t="n">
-        <v>16822200</v>
+        <v>14520000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>115.3837731369623</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="C236" t="n">
-        <v>116.1718796839166</v>
+        <v>114.9049142110052</v>
       </c>
       <c r="D236" t="n">
-        <v>114.3662049383982</v>
+        <v>113.6479213564676</v>
       </c>
       <c r="E236" t="n">
-        <v>114.9946975708008</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="F236" t="n">
-        <v>14520000</v>
+        <v>18131100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>114.0569458007812</v>
+        <v>116.0222446904477</v>
       </c>
       <c r="C237" t="n">
-        <v>114.9049142110052</v>
+        <v>116.0322153274834</v>
       </c>
       <c r="D237" t="n">
-        <v>113.6479213564676</v>
+        <v>114.2065916862473</v>
       </c>
       <c r="E237" t="n">
-        <v>114.0569458007812</v>
+        <v>114.9248657226562</v>
       </c>
       <c r="F237" t="n">
-        <v>18131100</v>
+        <v>20675000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>116.0222446904477</v>
+        <v>114.9148971425914</v>
       </c>
       <c r="C238" t="n">
-        <v>116.0322153274834</v>
+        <v>116.590885146559</v>
       </c>
       <c r="D238" t="n">
-        <v>114.2065916862473</v>
+        <v>113.7177585048011</v>
       </c>
       <c r="E238" t="n">
-        <v>114.9248657226562</v>
+        <v>114.0270233154297</v>
       </c>
       <c r="F238" t="n">
-        <v>20675000</v>
+        <v>34286600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>114.9148971425914</v>
+        <v>106.1259298697332</v>
       </c>
       <c r="C239" t="n">
-        <v>116.590885146559</v>
+        <v>106.7444518635443</v>
       </c>
       <c r="D239" t="n">
-        <v>113.7177585048011</v>
+        <v>102.6043617877236</v>
       </c>
       <c r="E239" t="n">
-        <v>114.0270233154297</v>
+        <v>103.5919952392578</v>
       </c>
       <c r="F239" t="n">
-        <v>34286600</v>
+        <v>83633100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>106.1259298697332</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C240" t="n">
-        <v>106.7444518635443</v>
+        <v>104.2799987792969</v>
       </c>
       <c r="D240" t="n">
-        <v>102.6043617877236</v>
+        <v>102.1500015258789</v>
       </c>
       <c r="E240" t="n">
-        <v>103.5919952392578</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="F240" t="n">
-        <v>83633100</v>
+        <v>44454200</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>103.6900024414062</v>
+        <v>104.1399993896484</v>
       </c>
       <c r="C241" t="n">
-        <v>104.2799987792969</v>
+        <v>106.5999984741211</v>
       </c>
       <c r="D241" t="n">
-        <v>102.1500015258789</v>
+        <v>104</v>
       </c>
       <c r="E241" t="n">
-        <v>103.6999969482422</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="F241" t="n">
-        <v>44454200</v>
+        <v>35616300</v>
       </c>
       <c r="G241" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>104.1399993896484</v>
+        <v>105.5800018310547</v>
       </c>
       <c r="C242" t="n">
-        <v>106.5999984741211</v>
+        <v>106.0699996948242</v>
       </c>
       <c r="D242" t="n">
-        <v>104</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="E242" t="n">
-        <v>106.4899978637695</v>
+        <v>105.379997253418</v>
       </c>
       <c r="F242" t="n">
-        <v>35616300</v>
+        <v>27032500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>105.5800018310547</v>
+        <v>105.5100021362305</v>
       </c>
       <c r="C243" t="n">
-        <v>106.0699996948242</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="D243" t="n">
-        <v>104.4000015258789</v>
+        <v>104.0800018310547</v>
       </c>
       <c r="E243" t="n">
-        <v>105.379997253418</v>
+        <v>104.3399963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>27032500</v>
+        <v>28409400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>105.5100021362305</v>
+        <v>103.6100006103516</v>
       </c>
       <c r="C244" t="n">
-        <v>106.0899963378906</v>
+        <v>103.75</v>
       </c>
       <c r="D244" t="n">
-        <v>104.0800018310547</v>
+        <v>102.2699966430664</v>
       </c>
       <c r="E244" t="n">
-        <v>104.3399963378906</v>
+        <v>102.629997253418</v>
       </c>
       <c r="F244" t="n">
-        <v>28409400</v>
+        <v>29816600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>103.6100006103516</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="C245" t="n">
-        <v>103.75</v>
+        <v>103.4000015258789</v>
       </c>
       <c r="D245" t="n">
-        <v>102.2699966430664</v>
+        <v>102.5</v>
       </c>
       <c r="E245" t="n">
-        <v>102.629997253418</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="F245" t="n">
-        <v>29816600</v>
+        <v>19420800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>103.0899963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="C246" t="n">
-        <v>103.4000015258789</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="D246" t="n">
-        <v>102.5</v>
+        <v>102.8399963378906</v>
       </c>
       <c r="E246" t="n">
-        <v>103.0899963378906</v>
+        <v>104.870002746582</v>
       </c>
       <c r="F246" t="n">
-        <v>19420800</v>
+        <v>34188700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>103.0800018310547</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="C247" t="n">
-        <v>104.9899978637695</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D247" t="n">
-        <v>102.8399963378906</v>
+        <v>104.6600036621094</v>
       </c>
       <c r="E247" t="n">
-        <v>104.870002746582</v>
+        <v>105.9199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>34188700</v>
+        <v>22074600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>105.1100006103516</v>
+        <v>105.9700012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>106.6399993896484</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="D248" t="n">
-        <v>104.6600036621094</v>
+        <v>105.4599990844727</v>
       </c>
       <c r="E248" t="n">
-        <v>105.9199981689453</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="F248" t="n">
-        <v>22074600</v>
+        <v>25181800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>105.9700012207031</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="C249" t="n">
-        <v>106.7799987792969</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="D249" t="n">
-        <v>105.4599990844727</v>
+        <v>106.0199966430664</v>
       </c>
       <c r="E249" t="n">
-        <v>106.0899963378906</v>
+        <v>108.4199981689453</v>
       </c>
       <c r="F249" t="n">
-        <v>25181800</v>
+        <v>25541200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>106.4199981689453</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="C250" t="n">
-        <v>109.3499984741211</v>
+        <v>109.2300033569336</v>
       </c>
       <c r="D250" t="n">
-        <v>106.0199966430664</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="E250" t="n">
-        <v>108.4199981689453</v>
+        <v>107.1399993896484</v>
       </c>
       <c r="F250" t="n">
-        <v>25541200</v>
+        <v>20540500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>108.1999969482422</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>109.2300033569336</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="D251" t="n">
-        <v>106.9300003051758</v>
+        <v>105.6600036621094</v>
       </c>
       <c r="E251" t="n">
-        <v>107.1399993896484</v>
+        <v>106.0500030517578</v>
       </c>
       <c r="F251" t="n">
-        <v>20527200</v>
+        <v>22664800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>105.6900024414062</v>
+      </c>
+      <c r="C252" t="n">
+        <v>106.1500015258789</v>
+      </c>
+      <c r="D252" t="n">
+        <v>105.1600036621094</v>
+      </c>
+      <c r="E252" t="n">
+        <v>105.8300018310547</v>
+      </c>
       <c r="F252" t="n">
-        <v>21478485</v>
+        <v>15450700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10628,37 +10636,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>105.83</v>
+      </c>
+      <c r="D2" t="n">
         <v>106.05</v>
       </c>
-      <c r="D2" t="n">
-        <v>107.14</v>
-      </c>
       <c r="E2" t="n">
-        <v>106.78</v>
+        <v>105.69</v>
       </c>
       <c r="F2" t="n">
-        <v>106.87</v>
+        <v>106.145</v>
       </c>
       <c r="G2" t="n">
-        <v>105.66</v>
+        <v>105.16</v>
       </c>
       <c r="H2" t="n">
-        <v>21478485</v>
+        <v>15347532</v>
       </c>
       <c r="I2" t="n">
-        <v>24433288</v>
+        <v>24445378</v>
       </c>
       <c r="J2" t="n">
-        <v>843954323456</v>
+        <v>842203529216</v>
       </c>
       <c r="K2" t="n">
-        <v>38.423916</v>
+        <v>38.48364</v>
       </c>
       <c r="L2" t="n">
-        <v>32.82794</v>
+        <v>32.75984</v>
       </c>
       <c r="M2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
         <v>135.16</v>
@@ -10670,7 +10678,7 @@
         <v>0.595</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R2" t="n">
         <v>0.03</v>
@@ -10694,7 +10702,7 @@
         <v>11.848</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.950877999999999</v>
+        <v>8.932309999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.091</v>
@@ -10706,7 +10714,7 @@
         <v>735839977472</v>
       </c>
       <c r="AC2" t="n">
-        <v>911497756672</v>
+        <v>909752336384</v>
       </c>
       <c r="AD2" t="n">
         <v>44073000960</v>
@@ -10733,7 +10741,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:21</t>
+          <t>2026-09-10 18:59:38</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>101.0987907680863</v>
+        <v>100.1468020683853</v>
       </c>
       <c r="C2" t="n">
-        <v>101.5946161422617</v>
+        <v>101.9218577291584</v>
       </c>
       <c r="D2" t="n">
-        <v>99.5518180216814</v>
+        <v>99.44273097931239</v>
       </c>
       <c r="E2" t="n">
-        <v>99.5716552734375</v>
+        <v>101.7929458618164</v>
       </c>
       <c r="F2" t="n">
-        <v>17934900</v>
+        <v>15900800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>100.1468095744012</v>
+        <v>101.6838580700448</v>
       </c>
       <c r="C3" t="n">
-        <v>101.9218653682149</v>
+        <v>103.111837420202</v>
       </c>
       <c r="D3" t="n">
-        <v>99.44273843255802</v>
+        <v>101.5053606512752</v>
       </c>
       <c r="E3" t="n">
-        <v>101.7929534912109</v>
+        <v>102.6259231567383</v>
       </c>
       <c r="F3" t="n">
-        <v>15900800</v>
+        <v>11641900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>101.6838731887643</v>
+        <v>102.7846052165408</v>
       </c>
       <c r="C4" t="n">
-        <v>103.1118527512385</v>
+        <v>103.1118517908423</v>
       </c>
       <c r="D4" t="n">
-        <v>101.505375743455</v>
+        <v>102.5466111469101</v>
       </c>
       <c r="E4" t="n">
-        <v>102.6259384155273</v>
+        <v>102.8242721557617</v>
       </c>
       <c r="F4" t="n">
-        <v>11641900</v>
+        <v>10756900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>102.7845975900895</v>
+        <v>102.9829286790064</v>
       </c>
       <c r="C5" t="n">
-        <v>103.1118441401098</v>
+        <v>103.3399235535848</v>
       </c>
       <c r="D5" t="n">
-        <v>102.5466035381176</v>
+        <v>102.2689389298496</v>
       </c>
       <c r="E5" t="n">
-        <v>102.8242645263672</v>
+        <v>102.5565185546875</v>
       </c>
       <c r="F5" t="n">
-        <v>10756900</v>
+        <v>14481900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>102.9829286790064</v>
+        <v>102.8639369378787</v>
       </c>
       <c r="C6" t="n">
-        <v>103.3399235535848</v>
+        <v>105.2240630293193</v>
       </c>
       <c r="D6" t="n">
-        <v>102.2689389298496</v>
+        <v>102.8639369378787</v>
       </c>
       <c r="E6" t="n">
-        <v>102.5565185546875</v>
+        <v>103.3994216918945</v>
       </c>
       <c r="F6" t="n">
-        <v>14481900</v>
+        <v>25382000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>102.8639293479953</v>
+        <v>102.9135133062164</v>
       </c>
       <c r="C7" t="n">
-        <v>105.2240552652924</v>
+        <v>103.7663335538345</v>
       </c>
       <c r="D7" t="n">
-        <v>102.8639293479953</v>
+        <v>101.2673770004686</v>
       </c>
       <c r="E7" t="n">
-        <v>103.3994140625</v>
+        <v>102.7350158691406</v>
       </c>
       <c r="F7" t="n">
-        <v>25382000</v>
+        <v>14869400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>102.9135133062164</v>
+        <v>102.9432629724532</v>
       </c>
       <c r="C8" t="n">
-        <v>103.7663335538345</v>
+        <v>103.0721824132953</v>
       </c>
       <c r="D8" t="n">
-        <v>101.2673770004686</v>
+        <v>101.2376224547773</v>
       </c>
       <c r="E8" t="n">
-        <v>102.7350158691406</v>
+        <v>101.4756240844727</v>
       </c>
       <c r="F8" t="n">
-        <v>14869400</v>
+        <v>34791600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>102.9432629724532</v>
+        <v>101.5946190816179</v>
       </c>
       <c r="C9" t="n">
-        <v>103.0721824132953</v>
+        <v>102.338357164399</v>
       </c>
       <c r="D9" t="n">
-        <v>101.2376224547773</v>
+        <v>101.0690453802971</v>
       </c>
       <c r="E9" t="n">
-        <v>101.4756240844727</v>
+        <v>101.9615325927734</v>
       </c>
       <c r="F9" t="n">
-        <v>34791600</v>
+        <v>12861900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>101.5946114796781</v>
+        <v>101.5549649811181</v>
       </c>
       <c r="C10" t="n">
-        <v>102.3383495068081</v>
+        <v>101.8227073759147</v>
       </c>
       <c r="D10" t="n">
-        <v>101.069037817684</v>
+        <v>100.4839802705406</v>
       </c>
       <c r="E10" t="n">
-        <v>101.9615249633789</v>
+        <v>101.6640396118164</v>
       </c>
       <c r="F10" t="n">
-        <v>12861900</v>
+        <v>13158700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>101.5549573599091</v>
+        <v>102.1796932441854</v>
       </c>
       <c r="C11" t="n">
-        <v>101.822699734613</v>
+        <v>102.606103365375</v>
       </c>
       <c r="D11" t="n">
-        <v>100.4839727297038</v>
+        <v>101.6243712503365</v>
       </c>
       <c r="E11" t="n">
-        <v>101.6640319824219</v>
+        <v>101.8722839355469</v>
       </c>
       <c r="F11" t="n">
-        <v>13158700</v>
+        <v>11391800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>102.1796855917684</v>
+        <v>102.3581921548903</v>
       </c>
       <c r="C12" t="n">
-        <v>102.6060956810235</v>
+        <v>102.645771781761</v>
       </c>
       <c r="D12" t="n">
-        <v>101.6243636395086</v>
+        <v>101.7235362768635</v>
       </c>
       <c r="E12" t="n">
-        <v>101.8722763061523</v>
+        <v>102.1896133422852</v>
       </c>
       <c r="F12" t="n">
-        <v>11391800</v>
+        <v>13366700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>102.3581921548903</v>
+        <v>102.0210222421301</v>
       </c>
       <c r="C13" t="n">
-        <v>102.645771781761</v>
+        <v>102.6259297800171</v>
       </c>
       <c r="D13" t="n">
-        <v>101.7235362768635</v>
+        <v>101.6144493855062</v>
       </c>
       <c r="E13" t="n">
-        <v>102.1896133422852</v>
+        <v>102.2986907958984</v>
       </c>
       <c r="F13" t="n">
-        <v>13366700</v>
+        <v>11859300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>102.0210222421301</v>
+        <v>102.189612039799</v>
       </c>
       <c r="C14" t="n">
-        <v>102.6259297800171</v>
+        <v>102.447435785546</v>
       </c>
       <c r="D14" t="n">
-        <v>101.6144493855062</v>
+        <v>101.2277096090732</v>
       </c>
       <c r="E14" t="n">
-        <v>102.2986907958984</v>
+        <v>102.2193603515625</v>
       </c>
       <c r="F14" t="n">
-        <v>11859300</v>
+        <v>15477200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>102.189612039799</v>
+        <v>102.1400273017734</v>
       </c>
       <c r="C15" t="n">
-        <v>102.447435785546</v>
+        <v>103.0721814282683</v>
       </c>
       <c r="D15" t="n">
-        <v>101.2277096090732</v>
+        <v>101.8623663021439</v>
       </c>
       <c r="E15" t="n">
-        <v>102.2193603515625</v>
+        <v>102.1995239257812</v>
       </c>
       <c r="F15" t="n">
-        <v>15477200</v>
+        <v>13873400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>102.1400273017734</v>
+        <v>101.7036925151355</v>
       </c>
       <c r="C16" t="n">
-        <v>103.0721814282683</v>
+        <v>102.0011907489098</v>
       </c>
       <c r="D16" t="n">
-        <v>101.8623663021439</v>
+        <v>99.71048007220848</v>
       </c>
       <c r="E16" t="n">
-        <v>102.1995239257812</v>
+        <v>101.1087036132812</v>
       </c>
       <c r="F16" t="n">
-        <v>13873400</v>
+        <v>16142800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>101.7037001894263</v>
+        <v>100.6029631728777</v>
       </c>
       <c r="C17" t="n">
-        <v>102.001198445649</v>
+        <v>101.287204595156</v>
       </c>
       <c r="D17" t="n">
-        <v>99.71048759609677</v>
+        <v>99.03616077500212</v>
       </c>
       <c r="E17" t="n">
-        <v>101.1087112426758</v>
+        <v>100.8508758544922</v>
       </c>
       <c r="F17" t="n">
-        <v>16142800</v>
+        <v>15605400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>100.6029631728777</v>
+        <v>100.6128811517826</v>
       </c>
       <c r="C18" t="n">
-        <v>101.287204595156</v>
+        <v>101.9615267363516</v>
       </c>
       <c r="D18" t="n">
-        <v>99.03616077500212</v>
+        <v>100.3550498461664</v>
       </c>
       <c r="E18" t="n">
-        <v>100.8508758544922</v>
+        <v>101.2177886962891</v>
       </c>
       <c r="F18" t="n">
-        <v>15605400</v>
+        <v>11867500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>100.6128811517826</v>
+        <v>101.0293759821222</v>
       </c>
       <c r="C19" t="n">
-        <v>101.9615267363516</v>
+        <v>102.2094427990993</v>
       </c>
       <c r="D19" t="n">
-        <v>100.3550498461664</v>
+        <v>100.7318852956682</v>
       </c>
       <c r="E19" t="n">
-        <v>101.2177886962891</v>
+        <v>101.842529296875</v>
       </c>
       <c r="F19" t="n">
-        <v>11867500</v>
+        <v>13303600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>101.0293759821222</v>
+        <v>101.5252085564141</v>
       </c>
       <c r="C20" t="n">
-        <v>102.2094427990993</v>
+        <v>102.3879474962557</v>
       </c>
       <c r="D20" t="n">
-        <v>100.7318852956682</v>
+        <v>100.1071475765985</v>
       </c>
       <c r="E20" t="n">
-        <v>101.842529296875</v>
+        <v>102.3780288696289</v>
       </c>
       <c r="F20" t="n">
-        <v>13303600</v>
+        <v>15538900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>101.5252009905733</v>
+        <v>102.1598562843055</v>
       </c>
       <c r="C21" t="n">
-        <v>102.387939866122</v>
+        <v>102.3978579100873</v>
       </c>
       <c r="D21" t="n">
-        <v>100.1071401164341</v>
+        <v>101.2971249793545</v>
       </c>
       <c r="E21" t="n">
-        <v>102.3780212402344</v>
+        <v>102.0408630371094</v>
       </c>
       <c r="F21" t="n">
-        <v>15538900</v>
+        <v>13584100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>102.1598486460141</v>
+        <v>102.2689413702109</v>
       </c>
       <c r="C22" t="n">
-        <v>102.397850254001</v>
+        <v>102.5862693145533</v>
       </c>
       <c r="D22" t="n">
-        <v>101.2971174055678</v>
+        <v>99.53199068739345</v>
       </c>
       <c r="E22" t="n">
-        <v>102.0408554077148</v>
+        <v>100.920295715332</v>
       </c>
       <c r="F22" t="n">
-        <v>13584100</v>
+        <v>19508000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>102.2689336388612</v>
+        <v>101.1979612604356</v>
       </c>
       <c r="C23" t="n">
-        <v>102.5862615592142</v>
+        <v>102.7647636830698</v>
       </c>
       <c r="D23" t="n">
-        <v>99.53198316295229</v>
+        <v>100.6723800119242</v>
       </c>
       <c r="E23" t="n">
-        <v>100.9202880859375</v>
+        <v>100.9897079467773</v>
       </c>
       <c r="F23" t="n">
-        <v>19508000</v>
+        <v>18519400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>101.1979612604356</v>
+        <v>100.523634106908</v>
       </c>
       <c r="C24" t="n">
-        <v>102.7647636830698</v>
+        <v>101.5946111121733</v>
       </c>
       <c r="D24" t="n">
-        <v>100.6723800119242</v>
+        <v>100.2261358708544</v>
       </c>
       <c r="E24" t="n">
-        <v>100.9897079467773</v>
+        <v>101.2673721313477</v>
       </c>
       <c r="F24" t="n">
-        <v>18519400</v>
+        <v>10871200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>100.523634106908</v>
+        <v>103.1812604018871</v>
       </c>
       <c r="C25" t="n">
-        <v>101.5946111121733</v>
+        <v>107.0189438447403</v>
       </c>
       <c r="D25" t="n">
-        <v>100.2261358708544</v>
+        <v>102.030941935604</v>
       </c>
       <c r="E25" t="n">
-        <v>101.2673721313477</v>
+        <v>106.3148727416992</v>
       </c>
       <c r="F25" t="n">
-        <v>10871200</v>
+        <v>30859500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>103.1812529973676</v>
+        <v>106.4239528923693</v>
       </c>
       <c r="C26" t="n">
-        <v>107.01893616482</v>
+        <v>108.6452483434567</v>
       </c>
       <c r="D26" t="n">
-        <v>102.0309346136339</v>
+        <v>106.4041232072616</v>
       </c>
       <c r="E26" t="n">
-        <v>106.3148651123047</v>
+        <v>108.1196746826172</v>
       </c>
       <c r="F26" t="n">
-        <v>30859500</v>
+        <v>21416300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>106.4239528923693</v>
+        <v>108.2882647751407</v>
       </c>
       <c r="C27" t="n">
-        <v>108.6452483434567</v>
+        <v>108.6650969227217</v>
       </c>
       <c r="D27" t="n">
-        <v>106.4041232072616</v>
+        <v>104.7778275866427</v>
       </c>
       <c r="E27" t="n">
-        <v>108.1196746826172</v>
+        <v>105.5810623168945</v>
       </c>
       <c r="F27" t="n">
-        <v>21416300</v>
+        <v>16366200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>108.288256950121</v>
+        <v>106.275213927966</v>
       </c>
       <c r="C28" t="n">
-        <v>108.6650890704717</v>
+        <v>107.2966130367236</v>
       </c>
       <c r="D28" t="n">
-        <v>104.7778200152908</v>
+        <v>105.3331486986077</v>
       </c>
       <c r="E28" t="n">
-        <v>105.5810546875</v>
+        <v>106.8305435180664</v>
       </c>
       <c r="F28" t="n">
-        <v>16366200</v>
+        <v>13735600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>106.2752063382308</v>
+        <v>106.9495278840114</v>
       </c>
       <c r="C29" t="n">
-        <v>107.2966053740443</v>
+        <v>107.3461896823507</v>
       </c>
       <c r="D29" t="n">
-        <v>105.3331411761509</v>
+        <v>105.7198831182847</v>
       </c>
       <c r="E29" t="n">
-        <v>106.8305358886719</v>
+        <v>106.1562118530273</v>
       </c>
       <c r="F29" t="n">
-        <v>13735600</v>
+        <v>10581200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>106.9495278840114</v>
+        <v>106.4338780925878</v>
       </c>
       <c r="C30" t="n">
-        <v>107.3461896823507</v>
+        <v>106.5826272200147</v>
       </c>
       <c r="D30" t="n">
-        <v>105.7198831182847</v>
+        <v>105.2934782032414</v>
       </c>
       <c r="E30" t="n">
-        <v>106.1562118530273</v>
+        <v>105.3331451416016</v>
       </c>
       <c r="F30" t="n">
-        <v>10581200</v>
+        <v>10899700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>106.4338780925878</v>
+        <v>105.6603826132251</v>
       </c>
       <c r="C31" t="n">
-        <v>106.5826272200147</v>
+        <v>106.8701900834392</v>
       </c>
       <c r="D31" t="n">
-        <v>105.2934782032414</v>
+        <v>104.7778141163466</v>
       </c>
       <c r="E31" t="n">
-        <v>105.3331451416016</v>
+        <v>106.2454528808594</v>
       </c>
       <c r="F31" t="n">
-        <v>10899700</v>
+        <v>12296500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>105.6603902006062</v>
+        <v>106.4537107234644</v>
       </c>
       <c r="C32" t="n">
-        <v>106.8701977576955</v>
+        <v>106.6718751076324</v>
       </c>
       <c r="D32" t="n">
-        <v>104.7778216403512</v>
+        <v>104.8968192868145</v>
       </c>
       <c r="E32" t="n">
-        <v>106.2454605102539</v>
+        <v>105.9678039550781</v>
       </c>
       <c r="F32" t="n">
-        <v>12296500</v>
+        <v>11408200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>106.4537107234644</v>
+        <v>106.1760412293909</v>
       </c>
       <c r="C33" t="n">
-        <v>106.6718751076324</v>
+        <v>106.2752047872635</v>
       </c>
       <c r="D33" t="n">
-        <v>104.8968192868145</v>
+        <v>104.6290685426336</v>
       </c>
       <c r="E33" t="n">
-        <v>105.9678039550781</v>
+        <v>105.2835540771484</v>
       </c>
       <c r="F33" t="n">
-        <v>11408200</v>
+        <v>10318000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>106.1760412293909</v>
+        <v>105.4521374991914</v>
       </c>
       <c r="C34" t="n">
-        <v>106.2752047872635</v>
+        <v>105.4719747510511</v>
       </c>
       <c r="D34" t="n">
-        <v>104.6290685426336</v>
+        <v>103.2804274936261</v>
       </c>
       <c r="E34" t="n">
-        <v>105.2835540771484</v>
+        <v>103.5977554321289</v>
       </c>
       <c r="F34" t="n">
-        <v>10318000</v>
+        <v>16375900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>105.4521374991914</v>
+        <v>103.1911699012466</v>
       </c>
       <c r="C35" t="n">
-        <v>105.4719747510511</v>
+        <v>103.2705037733825</v>
       </c>
       <c r="D35" t="n">
-        <v>103.2804274936261</v>
+        <v>102.1896081368852</v>
       </c>
       <c r="E35" t="n">
-        <v>103.5977554321289</v>
+        <v>102.3086013793945</v>
       </c>
       <c r="F35" t="n">
-        <v>16375900</v>
+        <v>13323000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>103.1911775964564</v>
+        <v>102.0507776911747</v>
       </c>
       <c r="C36" t="n">
-        <v>103.2705114745084</v>
+        <v>102.8044267797345</v>
       </c>
       <c r="D36" t="n">
-        <v>102.1896157574061</v>
+        <v>101.257454100834</v>
       </c>
       <c r="E36" t="n">
-        <v>102.3086090087891</v>
+        <v>101.6045303344727</v>
       </c>
       <c r="F36" t="n">
-        <v>13323000</v>
+        <v>11986400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>102.0507853540776</v>
+        <v>101.3467013373431</v>
       </c>
       <c r="C37" t="n">
-        <v>102.8044344992282</v>
+        <v>102.5069384385963</v>
       </c>
       <c r="D37" t="n">
-        <v>101.2574617041669</v>
+        <v>101.1087072811068</v>
       </c>
       <c r="E37" t="n">
-        <v>101.6045379638672</v>
+        <v>101.3764572143555</v>
       </c>
       <c r="F37" t="n">
-        <v>11986400</v>
+        <v>14065100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>101.3467089644983</v>
+        <v>100.8508753833576</v>
       </c>
       <c r="C38" t="n">
-        <v>102.5069461530686</v>
+        <v>101.2475371852267</v>
       </c>
       <c r="D38" t="n">
-        <v>101.108714890351</v>
+        <v>99.34356961508874</v>
       </c>
       <c r="E38" t="n">
-        <v>101.37646484375</v>
+        <v>100.3352203369141</v>
       </c>
       <c r="F38" t="n">
-        <v>14065100</v>
+        <v>20237000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>100.8508753833576</v>
+        <v>99.97823063454936</v>
       </c>
       <c r="C39" t="n">
-        <v>101.2475371852267</v>
+        <v>100.9500517210274</v>
       </c>
       <c r="D39" t="n">
-        <v>99.34356961508874</v>
+        <v>99.56173912564235</v>
       </c>
       <c r="E39" t="n">
-        <v>100.3352203369141</v>
+        <v>100.7417984008789</v>
       </c>
       <c r="F39" t="n">
-        <v>20237000</v>
+        <v>14811700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>99.97822306298148</v>
+        <v>101.2772919319017</v>
       </c>
       <c r="C40" t="n">
-        <v>100.9500440758614</v>
+        <v>101.763206263773</v>
       </c>
       <c r="D40" t="n">
-        <v>99.56173158561626</v>
+        <v>100.6128877218267</v>
       </c>
       <c r="E40" t="n">
-        <v>100.7417907714844</v>
+        <v>101.4161224365234</v>
       </c>
       <c r="F40" t="n">
-        <v>14811700</v>
+        <v>12636400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>101.2772843129512</v>
+        <v>100.8905527574553</v>
       </c>
       <c r="C41" t="n">
-        <v>101.7631986082678</v>
+        <v>101.8227069534267</v>
       </c>
       <c r="D41" t="n">
-        <v>100.6128801528584</v>
+        <v>100.0079841289827</v>
       </c>
       <c r="E41" t="n">
-        <v>101.4161148071289</v>
+        <v>100.6228103637695</v>
       </c>
       <c r="F41" t="n">
-        <v>12636400</v>
+        <v>13356800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>100.89054510776</v>
+        <v>100.4938818739751</v>
       </c>
       <c r="C42" t="n">
-        <v>101.8226992330539</v>
+        <v>101.0789597419063</v>
       </c>
       <c r="D42" t="n">
-        <v>100.0079765462054</v>
+        <v>99.19482183188099</v>
       </c>
       <c r="E42" t="n">
-        <v>100.622802734375</v>
+        <v>100.8310470581055</v>
       </c>
       <c r="F42" t="n">
-        <v>13356800</v>
+        <v>14866000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>100.493889477858</v>
+        <v>101.2772857883956</v>
       </c>
       <c r="C43" t="n">
-        <v>101.0789673900592</v>
+        <v>102.1102763312919</v>
       </c>
       <c r="D43" t="n">
-        <v>99.19482933747032</v>
+        <v>100.8806315510774</v>
       </c>
       <c r="E43" t="n">
-        <v>100.8310546875</v>
+        <v>101.7334442138672</v>
       </c>
       <c r="F43" t="n">
-        <v>14866000</v>
+        <v>17248700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>101.2772781932102</v>
+        <v>101.2971227463208</v>
       </c>
       <c r="C44" t="n">
-        <v>102.1102686736373</v>
+        <v>101.8127777927579</v>
       </c>
       <c r="D44" t="n">
-        <v>100.8806239856387</v>
+        <v>100.7517118230459</v>
       </c>
       <c r="E44" t="n">
-        <v>101.7334365844727</v>
+        <v>101.5648651123047</v>
       </c>
       <c r="F44" t="n">
-        <v>17248700</v>
+        <v>14507600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>101.2971227463208</v>
+        <v>101.6442008637206</v>
       </c>
       <c r="C45" t="n">
-        <v>101.8127777927579</v>
+        <v>102.8738456630921</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7517118230459</v>
+        <v>101.4657034278687</v>
       </c>
       <c r="E45" t="n">
-        <v>101.5648651123047</v>
+        <v>102.5763549804688</v>
       </c>
       <c r="F45" t="n">
-        <v>14507600</v>
+        <v>13182100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>101.6441933036576</v>
+        <v>102.4871024796954</v>
       </c>
       <c r="C46" t="n">
-        <v>102.8738380115709</v>
+        <v>102.7350151647289</v>
       </c>
       <c r="D46" t="n">
-        <v>101.4656958810819</v>
+        <v>101.8028686136755</v>
       </c>
       <c r="E46" t="n">
-        <v>102.5763473510742</v>
+        <v>102.5763549804688</v>
       </c>
       <c r="F46" t="n">
-        <v>13182100</v>
+        <v>12084400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>102.4870948569393</v>
+        <v>102.7250971521424</v>
       </c>
       <c r="C47" t="n">
-        <v>102.7350075235336</v>
+        <v>103.0622623399618</v>
       </c>
       <c r="D47" t="n">
-        <v>101.8028610418111</v>
+        <v>101.1682057834663</v>
       </c>
       <c r="E47" t="n">
-        <v>102.5763473510742</v>
+        <v>101.6838684082031</v>
       </c>
       <c r="F47" t="n">
-        <v>12084400</v>
+        <v>18088500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>102.7251048596608</v>
+        <v>99.36339681584856</v>
       </c>
       <c r="C48" t="n">
-        <v>103.062270072778</v>
+        <v>101.6342778199242</v>
       </c>
       <c r="D48" t="n">
-        <v>101.1682133741703</v>
+        <v>98.05441819840043</v>
       </c>
       <c r="E48" t="n">
-        <v>101.6838760375977</v>
+        <v>101.6243667602539</v>
       </c>
       <c r="F48" t="n">
-        <v>18088500</v>
+        <v>23424200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>99.36341173515544</v>
+        <v>101.7235329175373</v>
       </c>
       <c r="C49" t="n">
-        <v>101.6342930802014</v>
+        <v>102.4573523337042</v>
       </c>
       <c r="D49" t="n">
-        <v>98.05443292116557</v>
+        <v>101.2475372418891</v>
       </c>
       <c r="E49" t="n">
-        <v>101.624382019043</v>
+        <v>102.0904388427734</v>
       </c>
       <c r="F49" t="n">
-        <v>23424200</v>
+        <v>15289400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>101.7235329175373</v>
+        <v>102.1201932202399</v>
       </c>
       <c r="C50" t="n">
-        <v>102.4573523337042</v>
+        <v>102.4771805146163</v>
       </c>
       <c r="D50" t="n">
-        <v>101.2475372418891</v>
+        <v>100.5335460351719</v>
       </c>
       <c r="E50" t="n">
-        <v>102.0904388427734</v>
+        <v>100.5434646606445</v>
       </c>
       <c r="F50" t="n">
-        <v>15289400</v>
+        <v>17604500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>102.1201932202399</v>
+        <v>100.7318761079755</v>
       </c>
       <c r="C51" t="n">
-        <v>102.4771805146163</v>
+        <v>100.8607879704448</v>
       </c>
       <c r="D51" t="n">
-        <v>100.5335460351719</v>
+        <v>98.84773833617163</v>
       </c>
       <c r="E51" t="n">
-        <v>100.5434646606445</v>
+        <v>99.76997375488281</v>
       </c>
       <c r="F51" t="n">
-        <v>17604500</v>
+        <v>22157000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>100.7318838109266</v>
+        <v>103.0721824077765</v>
       </c>
       <c r="C52" t="n">
-        <v>100.8607956832537</v>
+        <v>107.0090371351957</v>
       </c>
       <c r="D52" t="n">
-        <v>98.84774589504295</v>
+        <v>101.8227003318746</v>
       </c>
       <c r="E52" t="n">
-        <v>99.76998138427734</v>
+        <v>106.2157135009766</v>
       </c>
       <c r="F52" t="n">
-        <v>22157000</v>
+        <v>50375900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>103.0721750041795</v>
+        <v>107.0784532434011</v>
       </c>
       <c r="C53" t="n">
-        <v>107.0090294488173</v>
+        <v>107.247032058172</v>
       </c>
       <c r="D53" t="n">
-        <v>101.8226930180269</v>
+        <v>103.8456696217535</v>
       </c>
       <c r="E53" t="n">
-        <v>106.215705871582</v>
+        <v>104.4406585693359</v>
       </c>
       <c r="F53" t="n">
-        <v>50375900</v>
+        <v>41420800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>107.0784532434011</v>
+        <v>104.4803186790174</v>
       </c>
       <c r="C54" t="n">
-        <v>107.247032058172</v>
+        <v>105.3827168846354</v>
       </c>
       <c r="D54" t="n">
-        <v>103.8456696217535</v>
+        <v>102.89367906727</v>
       </c>
       <c r="E54" t="n">
-        <v>104.4406585693359</v>
+        <v>103.1911697387695</v>
       </c>
       <c r="F54" t="n">
-        <v>41420800</v>
+        <v>42519200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>104.4803186790174</v>
+        <v>103.7365837716454</v>
       </c>
       <c r="C55" t="n">
-        <v>105.3827168846354</v>
+        <v>106.5231199100109</v>
       </c>
       <c r="D55" t="n">
-        <v>102.89367906727</v>
+        <v>103.3597592168018</v>
       </c>
       <c r="E55" t="n">
-        <v>103.1911697387695</v>
+        <v>106.1066284179688</v>
       </c>
       <c r="F55" t="n">
-        <v>42519200</v>
+        <v>20212900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>103.7365912306264</v>
+        <v>106.3049641152269</v>
       </c>
       <c r="C56" t="n">
-        <v>106.5231275693524</v>
+        <v>108.6750089527716</v>
       </c>
       <c r="D56" t="n">
-        <v>103.3597666486879</v>
+        <v>106.2752158013515</v>
       </c>
       <c r="E56" t="n">
-        <v>106.1066360473633</v>
+        <v>108.1891021728516</v>
       </c>
       <c r="F56" t="n">
-        <v>20212900</v>
+        <v>17783300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>106.3049566187</v>
+        <v>108.3874295551272</v>
       </c>
       <c r="C57" t="n">
-        <v>108.6750012891114</v>
+        <v>109.7757345468567</v>
       </c>
       <c r="D57" t="n">
-        <v>106.2752083069225</v>
+        <v>108.0899313050738</v>
       </c>
       <c r="E57" t="n">
-        <v>108.189094543457</v>
+        <v>109.5873260498047</v>
       </c>
       <c r="F57" t="n">
-        <v>17783300</v>
+        <v>9846500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>108.3874295551272</v>
+        <v>109.587327840119</v>
       </c>
       <c r="C58" t="n">
-        <v>109.7757345468567</v>
+        <v>110.8268912927673</v>
       </c>
       <c r="D58" t="n">
-        <v>108.0899313050738</v>
+        <v>109.4385787126623</v>
       </c>
       <c r="E58" t="n">
-        <v>109.5873260498047</v>
+        <v>110.5988082885742</v>
       </c>
       <c r="F58" t="n">
-        <v>9846500</v>
+        <v>17236800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>109.587327840119</v>
+        <v>110.5393119248386</v>
       </c>
       <c r="C59" t="n">
-        <v>110.8268912927673</v>
+        <v>111.7094601295289</v>
       </c>
       <c r="D59" t="n">
-        <v>109.4385787126623</v>
+        <v>109.8649891023782</v>
       </c>
       <c r="E59" t="n">
-        <v>110.5988082885742</v>
+        <v>111.4714660644531</v>
       </c>
       <c r="F59" t="n">
-        <v>17236800</v>
+        <v>18711800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>110.5393043592431</v>
+        <v>111.560708766128</v>
       </c>
       <c r="C60" t="n">
-        <v>111.7094524838454</v>
+        <v>113.9307534404373</v>
       </c>
       <c r="D60" t="n">
-        <v>109.8649815829351</v>
+        <v>111.2830477681546</v>
       </c>
       <c r="E60" t="n">
-        <v>111.4714584350586</v>
+        <v>113.4547653198242</v>
       </c>
       <c r="F60" t="n">
-        <v>18711800</v>
+        <v>24478300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>111.560708766128</v>
+        <v>112.6713570329028</v>
       </c>
       <c r="C61" t="n">
-        <v>113.9307534404373</v>
+        <v>113.9307501128403</v>
       </c>
       <c r="D61" t="n">
-        <v>111.2830477681546</v>
+        <v>112.2151986115989</v>
       </c>
       <c r="E61" t="n">
-        <v>113.4547653198242</v>
+        <v>113.8811645507812</v>
       </c>
       <c r="F61" t="n">
-        <v>24478300</v>
+        <v>25905100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>112.6713645812471</v>
+        <v>113.7720859872408</v>
       </c>
       <c r="C62" t="n">
-        <v>113.9307577455568</v>
+        <v>115.299221378535</v>
       </c>
       <c r="D62" t="n">
-        <v>112.2152061293831</v>
+        <v>113.7225004269012</v>
       </c>
       <c r="E62" t="n">
-        <v>113.8811721801758</v>
+        <v>114.1489105224609</v>
       </c>
       <c r="F62" t="n">
-        <v>25905100</v>
+        <v>23956400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>113.7720935914494</v>
+        <v>113.6134239095882</v>
       </c>
       <c r="C63" t="n">
-        <v>115.2992290848131</v>
+        <v>114.0299154007005</v>
       </c>
       <c r="D63" t="n">
-        <v>113.7225080277957</v>
+        <v>111.3623800798857</v>
       </c>
       <c r="E63" t="n">
-        <v>114.1489181518555</v>
+        <v>112.6118545532227</v>
       </c>
       <c r="F63" t="n">
-        <v>23956400</v>
+        <v>22700700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>113.6134239095882</v>
+        <v>112.9986017612633</v>
       </c>
       <c r="C64" t="n">
-        <v>114.0299154007005</v>
+        <v>114.7538278539011</v>
       </c>
       <c r="D64" t="n">
-        <v>111.3623800798857</v>
+        <v>112.0763662462405</v>
       </c>
       <c r="E64" t="n">
-        <v>112.6118545532227</v>
+        <v>114.0993347167969</v>
       </c>
       <c r="F64" t="n">
-        <v>22700700</v>
+        <v>24326700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>112.9985942054707</v>
+        <v>114.3869114193454</v>
       </c>
       <c r="C65" t="n">
-        <v>114.7538201807431</v>
+        <v>115.2595689131506</v>
       </c>
       <c r="D65" t="n">
-        <v>112.0763587521143</v>
+        <v>112.0466150661863</v>
       </c>
       <c r="E65" t="n">
-        <v>114.0993270874023</v>
+        <v>112.2350311279297</v>
       </c>
       <c r="F65" t="n">
-        <v>24326700</v>
+        <v>22859600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>114.3869191950181</v>
+        <v>112.1953625812108</v>
       </c>
       <c r="C66" t="n">
-        <v>115.259576748144</v>
+        <v>114.9025723932263</v>
       </c>
       <c r="D66" t="n">
-        <v>112.0466226827729</v>
+        <v>111.9077829626674</v>
       </c>
       <c r="E66" t="n">
-        <v>112.2350387573242</v>
+        <v>114.5554885864258</v>
       </c>
       <c r="F66" t="n">
-        <v>22859600</v>
+        <v>21586600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>112.195370053421</v>
+        <v>114.5306574399956</v>
       </c>
       <c r="C67" t="n">
-        <v>114.9025800457367</v>
+        <v>116.2099582668437</v>
       </c>
       <c r="D67" t="n">
-        <v>111.9077904157248</v>
+        <v>114.2921706587026</v>
       </c>
       <c r="E67" t="n">
-        <v>114.5554962158203</v>
+        <v>115.961540222168</v>
       </c>
       <c r="F67" t="n">
-        <v>21586600</v>
+        <v>19092400</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>114.5306574399956</v>
+        <v>116.190085480185</v>
       </c>
       <c r="C68" t="n">
-        <v>116.2099582668437</v>
+        <v>116.7067916655062</v>
       </c>
       <c r="D68" t="n">
-        <v>114.2921706587026</v>
+        <v>114.9082474894773</v>
       </c>
       <c r="E68" t="n">
-        <v>115.961540222168</v>
+        <v>116.0509719848633</v>
       </c>
       <c r="F68" t="n">
-        <v>19092400</v>
+        <v>18713700</v>
       </c>
       <c r="G68" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>116.190085480185</v>
+        <v>115.8423072543707</v>
       </c>
       <c r="C69" t="n">
-        <v>116.7067916655062</v>
+        <v>116.140404366624</v>
       </c>
       <c r="D69" t="n">
-        <v>114.9082474894773</v>
+        <v>114.2226167114376</v>
       </c>
       <c r="E69" t="n">
-        <v>116.0509719848633</v>
+        <v>114.6896438598633</v>
       </c>
       <c r="F69" t="n">
-        <v>18713700</v>
+        <v>19642300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>115.8423072543707</v>
+        <v>114.4710352169006</v>
       </c>
       <c r="C70" t="n">
-        <v>116.140404366624</v>
+        <v>115.6535075692186</v>
       </c>
       <c r="D70" t="n">
-        <v>114.2226167114376</v>
+        <v>114.3418605591895</v>
       </c>
       <c r="E70" t="n">
-        <v>114.6896438598633</v>
+        <v>114.9281311035156</v>
       </c>
       <c r="F70" t="n">
-        <v>19642300</v>
+        <v>16177800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>114.4710352169006</v>
+        <v>114.2822472329707</v>
       </c>
       <c r="C71" t="n">
-        <v>115.6535075692186</v>
+        <v>115.7429466488196</v>
       </c>
       <c r="D71" t="n">
-        <v>114.3418605591895</v>
+        <v>113.8847768180071</v>
       </c>
       <c r="E71" t="n">
-        <v>114.9281311035156</v>
+        <v>114.103385925293</v>
       </c>
       <c r="F71" t="n">
-        <v>16177800</v>
+        <v>21476700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>114.2822472329707</v>
+        <v>114.411415636222</v>
       </c>
       <c r="C72" t="n">
-        <v>115.7429466488196</v>
+        <v>114.5505291366805</v>
       </c>
       <c r="D72" t="n">
-        <v>113.8847768180071</v>
+        <v>112.8116027998319</v>
       </c>
       <c r="E72" t="n">
-        <v>114.103385925293</v>
+        <v>113.6363525390625</v>
       </c>
       <c r="F72" t="n">
-        <v>21476700</v>
+        <v>50043800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>114.411415636222</v>
+        <v>113.2885707737471</v>
       </c>
       <c r="C73" t="n">
-        <v>114.5505291366805</v>
+        <v>113.5966067328595</v>
       </c>
       <c r="D73" t="n">
-        <v>112.8116027998319</v>
+        <v>111.5098966082868</v>
       </c>
       <c r="E73" t="n">
-        <v>113.6363525390625</v>
+        <v>111.8874893188477</v>
       </c>
       <c r="F73" t="n">
-        <v>50043800</v>
+        <v>21473900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>113.2885707737471</v>
+        <v>111.2813411845575</v>
       </c>
       <c r="C74" t="n">
-        <v>113.5966067328595</v>
+        <v>111.6390637625677</v>
       </c>
       <c r="D74" t="n">
-        <v>111.5098966082868</v>
+        <v>109.9995032102072</v>
       </c>
       <c r="E74" t="n">
-        <v>111.8874893188477</v>
+        <v>110.1982421875</v>
       </c>
       <c r="F74" t="n">
-        <v>21473900</v>
+        <v>20319900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>111.2813411845575</v>
+        <v>110.1982488335626</v>
       </c>
       <c r="C75" t="n">
-        <v>111.6390637625677</v>
+        <v>111.003120892069</v>
       </c>
       <c r="D75" t="n">
-        <v>109.9995032102072</v>
+        <v>109.8504650787215</v>
       </c>
       <c r="E75" t="n">
-        <v>110.1982421875</v>
+        <v>110.9037551879883</v>
       </c>
       <c r="F75" t="n">
-        <v>20319900</v>
+        <v>9009600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>110.1982488335626</v>
+        <v>111.0130583586743</v>
       </c>
       <c r="C76" t="n">
-        <v>111.003120892069</v>
+        <v>111.2614764063509</v>
       </c>
       <c r="D76" t="n">
-        <v>109.8504650787215</v>
+        <v>110.6553357635307</v>
       </c>
       <c r="E76" t="n">
-        <v>110.9037551879883</v>
+        <v>111.0329284667969</v>
       </c>
       <c r="F76" t="n">
-        <v>9009600</v>
+        <v>9003800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>111.0130583586743</v>
+        <v>110.8838702636393</v>
       </c>
       <c r="C77" t="n">
-        <v>111.2614764063509</v>
+        <v>112.0663425340636</v>
       </c>
       <c r="D77" t="n">
-        <v>110.6553357635307</v>
+        <v>110.8640001565665</v>
       </c>
       <c r="E77" t="n">
-        <v>111.0329284667969</v>
+        <v>111.8179244995117</v>
       </c>
       <c r="F77" t="n">
-        <v>9003800</v>
+        <v>12979600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>110.8838702636393</v>
+        <v>111.1819754114984</v>
       </c>
       <c r="C78" t="n">
-        <v>112.0663425340636</v>
+        <v>111.9769161578998</v>
       </c>
       <c r="D78" t="n">
-        <v>110.8640001565665</v>
+        <v>111.1322887719295</v>
       </c>
       <c r="E78" t="n">
-        <v>111.8179244995117</v>
+        <v>111.211784362793</v>
       </c>
       <c r="F78" t="n">
-        <v>12979600</v>
+        <v>11730600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>111.1819754114984</v>
+        <v>111.022991872357</v>
       </c>
       <c r="C79" t="n">
-        <v>111.9769161578998</v>
+        <v>111.5396980510222</v>
       </c>
       <c r="D79" t="n">
-        <v>111.1322887719295</v>
+        <v>110.6155826547936</v>
       </c>
       <c r="E79" t="n">
-        <v>111.211784362793</v>
+        <v>110.7050170898438</v>
       </c>
       <c r="F79" t="n">
-        <v>11730600</v>
+        <v>11487400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>111.022991872357</v>
+        <v>110.7248924392647</v>
       </c>
       <c r="C80" t="n">
-        <v>111.5396980510222</v>
+        <v>112.0762872242068</v>
       </c>
       <c r="D80" t="n">
-        <v>110.6155826547936</v>
+        <v>110.4168564863102</v>
       </c>
       <c r="E80" t="n">
-        <v>110.7050170898438</v>
+        <v>112.0464782714844</v>
       </c>
       <c r="F80" t="n">
-        <v>11487400</v>
+        <v>14306600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>110.7248924392647</v>
+        <v>112.106092568778</v>
       </c>
       <c r="C81" t="n">
-        <v>112.0762872242068</v>
+        <v>113.0103378715463</v>
       </c>
       <c r="D81" t="n">
-        <v>110.4168564863102</v>
+        <v>111.4403340423477</v>
       </c>
       <c r="E81" t="n">
-        <v>112.0464782714844</v>
+        <v>111.9967880249023</v>
       </c>
       <c r="F81" t="n">
-        <v>14306600</v>
+        <v>19557600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>112.106092568778</v>
+        <v>111.6887590151699</v>
       </c>
       <c r="C82" t="n">
-        <v>113.0103378715463</v>
+        <v>114.0636350138627</v>
       </c>
       <c r="D82" t="n">
-        <v>111.4403340423477</v>
+        <v>111.2813497661395</v>
       </c>
       <c r="E82" t="n">
-        <v>111.9967880249023</v>
+        <v>113.6164779663086</v>
       </c>
       <c r="F82" t="n">
-        <v>19557600</v>
+        <v>20120800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>111.6887590151699</v>
+        <v>113.4674284407305</v>
       </c>
       <c r="C83" t="n">
-        <v>114.0636350138627</v>
+        <v>114.0040123266269</v>
       </c>
       <c r="D83" t="n">
-        <v>111.2813497661395</v>
+        <v>111.3906496463658</v>
       </c>
       <c r="E83" t="n">
-        <v>113.6164779663086</v>
+        <v>112.0067291259766</v>
       </c>
       <c r="F83" t="n">
-        <v>20120800</v>
+        <v>23306000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>113.4674284407305</v>
+        <v>110.5857797769927</v>
       </c>
       <c r="C84" t="n">
-        <v>114.0040123266269</v>
+        <v>112.7519854709339</v>
       </c>
       <c r="D84" t="n">
-        <v>111.3906496463658</v>
+        <v>109.1151415889016</v>
       </c>
       <c r="E84" t="n">
-        <v>112.0067291259766</v>
+        <v>112.3545150756836</v>
       </c>
       <c r="F84" t="n">
-        <v>23306000</v>
+        <v>24058300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>110.5857797769927</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="C85" t="n">
-        <v>112.7519854709339</v>
+        <v>114.7293904053996</v>
       </c>
       <c r="D85" t="n">
-        <v>109.1151415889016</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="E85" t="n">
-        <v>112.3545150756836</v>
+        <v>113.8052749633789</v>
       </c>
       <c r="F85" t="n">
-        <v>24058300</v>
+        <v>21902900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>111.5496424227033</v>
+        <v>116.756475995831</v>
       </c>
       <c r="C86" t="n">
-        <v>114.7293904053996</v>
+        <v>118.0879930193155</v>
       </c>
       <c r="D86" t="n">
-        <v>111.5496424227033</v>
+        <v>115.6733770063802</v>
       </c>
       <c r="E86" t="n">
-        <v>113.8052749633789</v>
+        <v>117.223503112793</v>
       </c>
       <c r="F86" t="n">
-        <v>21902900</v>
+        <v>49182100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>116.756475995831</v>
+        <v>117.1440096095209</v>
       </c>
       <c r="C87" t="n">
-        <v>118.0879930193155</v>
+        <v>119.7474333817796</v>
       </c>
       <c r="D87" t="n">
-        <v>115.6733770063802</v>
+        <v>116.9850260070875</v>
       </c>
       <c r="E87" t="n">
-        <v>117.223503112793</v>
+        <v>119.5983810424805</v>
       </c>
       <c r="F87" t="n">
-        <v>49182100</v>
+        <v>31222100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>117.1440096095209</v>
+        <v>119.4294631115365</v>
       </c>
       <c r="C88" t="n">
-        <v>119.7474333817796</v>
+        <v>120.4728143638468</v>
       </c>
       <c r="D88" t="n">
-        <v>116.9850260070875</v>
+        <v>118.2767997305645</v>
       </c>
       <c r="E88" t="n">
-        <v>119.5983810424805</v>
+        <v>119.2804107666016</v>
       </c>
       <c r="F88" t="n">
-        <v>31222100</v>
+        <v>32764000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>119.4294631115365</v>
+        <v>119.2207951798175</v>
       </c>
       <c r="C89" t="n">
-        <v>120.4728143638468</v>
+        <v>120.1051628408833</v>
       </c>
       <c r="D89" t="n">
-        <v>118.2767997305645</v>
+        <v>117.9787049163972</v>
       </c>
       <c r="E89" t="n">
-        <v>119.2804107666016</v>
+        <v>118.4457244873047</v>
       </c>
       <c r="F89" t="n">
-        <v>32764000</v>
+        <v>34559400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>119.2207951798175</v>
+        <v>117.9190771443211</v>
       </c>
       <c r="C90" t="n">
-        <v>120.1051628408833</v>
+        <v>119.8368647771362</v>
       </c>
       <c r="D90" t="n">
-        <v>117.9787049163972</v>
+        <v>116.1602807010803</v>
       </c>
       <c r="E90" t="n">
-        <v>118.4457244873047</v>
+        <v>118.9425582885742</v>
       </c>
       <c r="F90" t="n">
-        <v>34559400</v>
+        <v>415144600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>117.9190771443211</v>
+        <v>120.1250298240042</v>
       </c>
       <c r="C91" t="n">
-        <v>119.8368647771362</v>
+        <v>120.8504138546603</v>
       </c>
       <c r="D91" t="n">
-        <v>116.1602807010803</v>
+        <v>116.8657862705671</v>
       </c>
       <c r="E91" t="n">
-        <v>118.9425582885742</v>
+        <v>117.9588241577148</v>
       </c>
       <c r="F91" t="n">
-        <v>415144600</v>
+        <v>45334000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>120.1250298240042</v>
+        <v>117.3328142471995</v>
       </c>
       <c r="C92" t="n">
-        <v>120.8504138546603</v>
+        <v>119.7275602876645</v>
       </c>
       <c r="D92" t="n">
-        <v>116.8657862705671</v>
+        <v>116.8061691984345</v>
       </c>
       <c r="E92" t="n">
-        <v>117.9588241577148</v>
+        <v>118.6047134399414</v>
       </c>
       <c r="F92" t="n">
-        <v>45334000</v>
+        <v>34811700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>117.3328142471995</v>
+        <v>118.5351568548667</v>
       </c>
       <c r="C93" t="n">
-        <v>119.7275602876645</v>
+        <v>118.7636972139123</v>
       </c>
       <c r="D93" t="n">
-        <v>116.8061691984345</v>
+        <v>116.9055350642564</v>
       </c>
       <c r="E93" t="n">
-        <v>118.6047134399414</v>
+        <v>117.0843963623047</v>
       </c>
       <c r="F93" t="n">
-        <v>34811700</v>
+        <v>24547300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>118.5351568548667</v>
+        <v>117.4222340816893</v>
       </c>
       <c r="C94" t="n">
-        <v>118.7636972139123</v>
+        <v>117.8594522459602</v>
       </c>
       <c r="D94" t="n">
-        <v>116.9055350642564</v>
+        <v>116.3987529981613</v>
       </c>
       <c r="E94" t="n">
-        <v>117.0843963623047</v>
+        <v>116.9850234985352</v>
       </c>
       <c r="F94" t="n">
-        <v>24547300</v>
+        <v>20806900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>117.4222340816893</v>
+        <v>117.064521823182</v>
       </c>
       <c r="C95" t="n">
-        <v>117.8594522459602</v>
+        <v>118.0979418418126</v>
       </c>
       <c r="D95" t="n">
-        <v>116.3987529981613</v>
+        <v>116.6471813102112</v>
       </c>
       <c r="E95" t="n">
-        <v>116.9850234985352</v>
+        <v>116.8955993652344</v>
       </c>
       <c r="F95" t="n">
-        <v>20806900</v>
+        <v>19552200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>117.064521823182</v>
+        <v>116.7564814621505</v>
       </c>
       <c r="C96" t="n">
-        <v>118.0979418418126</v>
+        <v>116.8856561166937</v>
       </c>
       <c r="D96" t="n">
-        <v>116.6471813102112</v>
+        <v>114.7492669888757</v>
       </c>
       <c r="E96" t="n">
-        <v>116.8955993652344</v>
+        <v>116.2000274658203</v>
       </c>
       <c r="F96" t="n">
-        <v>19552200</v>
+        <v>22968600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>116.7564814621505</v>
+        <v>115.9019236934497</v>
       </c>
       <c r="C97" t="n">
-        <v>116.8856561166937</v>
+        <v>116.7167345864151</v>
       </c>
       <c r="D97" t="n">
-        <v>114.7492669888757</v>
+        <v>115.1367994424561</v>
       </c>
       <c r="E97" t="n">
-        <v>116.2000274658203</v>
+        <v>115.8323669433594</v>
       </c>
       <c r="F97" t="n">
-        <v>22968600</v>
+        <v>16342000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>115.9019236934497</v>
+        <v>115.7131212672227</v>
       </c>
       <c r="C98" t="n">
-        <v>116.7167345864151</v>
+        <v>116.9154712653777</v>
       </c>
       <c r="D98" t="n">
-        <v>115.1367994424561</v>
+        <v>115.3355285714882</v>
       </c>
       <c r="E98" t="n">
-        <v>115.8323669433594</v>
+        <v>116.6670532226562</v>
       </c>
       <c r="F98" t="n">
-        <v>16342000</v>
+        <v>16381100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>115.7131212672227</v>
+        <v>116.1702235798966</v>
       </c>
       <c r="C99" t="n">
-        <v>116.9154712653777</v>
+        <v>118.6544041448817</v>
       </c>
       <c r="D99" t="n">
-        <v>115.3355285714882</v>
+        <v>115.8621800346786</v>
       </c>
       <c r="E99" t="n">
-        <v>116.6670532226562</v>
+        <v>118.3861083984375</v>
       </c>
       <c r="F99" t="n">
-        <v>16381100</v>
+        <v>22215400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>116.1702235798966</v>
+        <v>118.7438208421828</v>
       </c>
       <c r="C100" t="n">
-        <v>118.6544041448817</v>
+        <v>123.4140768721483</v>
       </c>
       <c r="D100" t="n">
-        <v>115.8621800346786</v>
+        <v>118.2966714112071</v>
       </c>
       <c r="E100" t="n">
-        <v>118.3861083984375</v>
+        <v>123.2749633789062</v>
       </c>
       <c r="F100" t="n">
-        <v>22215400</v>
+        <v>31210100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>118.7438208421828</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="C101" t="n">
-        <v>123.4140768721483</v>
+        <v>127.3589666685813</v>
       </c>
       <c r="D101" t="n">
-        <v>118.2966714112071</v>
+        <v>122.8675715680868</v>
       </c>
       <c r="E101" t="n">
-        <v>123.2749633789062</v>
+        <v>126.9018783569336</v>
       </c>
       <c r="F101" t="n">
-        <v>31210100</v>
+        <v>32018700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>122.8675715680868</v>
+        <v>127.3192151881231</v>
       </c>
       <c r="C102" t="n">
-        <v>127.3589666685813</v>
+        <v>128.5911143047342</v>
       </c>
       <c r="D102" t="n">
-        <v>122.8675715680868</v>
+        <v>126.2857876794806</v>
       </c>
       <c r="E102" t="n">
-        <v>126.9018783569336</v>
+        <v>127.1900329589844</v>
       </c>
       <c r="F102" t="n">
-        <v>32018700</v>
+        <v>27531800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>127.3192151881231</v>
+        <v>127.7663710403251</v>
       </c>
       <c r="C103" t="n">
-        <v>128.5911143047342</v>
+        <v>128.779920911861</v>
       </c>
       <c r="D103" t="n">
-        <v>126.2857876794806</v>
+        <v>125.7591489863279</v>
       </c>
       <c r="E103" t="n">
-        <v>127.1900329589844</v>
+        <v>126.1367492675781</v>
       </c>
       <c r="F103" t="n">
-        <v>27531800</v>
+        <v>30517800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>127.7663710403251</v>
+        <v>126.4845378023196</v>
       </c>
       <c r="C104" t="n">
-        <v>128.779920911861</v>
+        <v>130.8666283506429</v>
       </c>
       <c r="D104" t="n">
-        <v>125.7591489863279</v>
+        <v>126.2460585922159</v>
       </c>
       <c r="E104" t="n">
-        <v>126.1367492675781</v>
+        <v>130.3499145507812</v>
       </c>
       <c r="F104" t="n">
-        <v>30517800</v>
+        <v>26593400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>126.4845378023196</v>
+        <v>130.5884053590928</v>
       </c>
       <c r="C105" t="n">
-        <v>130.8666283506429</v>
+        <v>130.9560592399128</v>
       </c>
       <c r="D105" t="n">
-        <v>126.2460585922159</v>
+        <v>127.2794749450073</v>
       </c>
       <c r="E105" t="n">
-        <v>130.3499145507812</v>
+        <v>128.2035980224609</v>
       </c>
       <c r="F105" t="n">
-        <v>26593400</v>
+        <v>27197300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>130.5884053590928</v>
+        <v>128.1240931628847</v>
       </c>
       <c r="C106" t="n">
-        <v>130.9560592399128</v>
+        <v>128.5215559695187</v>
       </c>
       <c r="D106" t="n">
-        <v>127.2794749450073</v>
+        <v>125.5902260744493</v>
       </c>
       <c r="E106" t="n">
-        <v>128.2035980224609</v>
+        <v>125.8982620239258</v>
       </c>
       <c r="F106" t="n">
-        <v>27197300</v>
+        <v>24662000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>128.1240931628847</v>
+        <v>125.8982685130821</v>
       </c>
       <c r="C107" t="n">
-        <v>128.5215559695187</v>
+        <v>128.9190405832424</v>
       </c>
       <c r="D107" t="n">
-        <v>125.5902260744493</v>
+        <v>125.8287117602243</v>
       </c>
       <c r="E107" t="n">
-        <v>125.8982620239258</v>
+        <v>127.9551773071289</v>
       </c>
       <c r="F107" t="n">
-        <v>24662000</v>
+        <v>19232100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>125.8982685130821</v>
+        <v>128.5613042513025</v>
       </c>
       <c r="C108" t="n">
-        <v>128.9190405832424</v>
+        <v>133.6389694112844</v>
       </c>
       <c r="D108" t="n">
-        <v>125.8287117602243</v>
+        <v>128.4917399247525</v>
       </c>
       <c r="E108" t="n">
-        <v>127.9551773071289</v>
+        <v>132.7943420410156</v>
       </c>
       <c r="F108" t="n">
-        <v>19232100</v>
+        <v>33382700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>128.5613042513025</v>
+        <v>131.8602980405916</v>
       </c>
       <c r="C109" t="n">
-        <v>133.6389694112844</v>
+        <v>133.7979558000997</v>
       </c>
       <c r="D109" t="n">
-        <v>128.4917399247525</v>
+        <v>130.9163124820861</v>
       </c>
       <c r="E109" t="n">
-        <v>132.7943420410156</v>
+        <v>133.0427703857422</v>
       </c>
       <c r="F109" t="n">
-        <v>33382700</v>
+        <v>24131200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>131.8602980405916</v>
+        <v>132.2677060470971</v>
       </c>
       <c r="C110" t="n">
-        <v>133.7979558000997</v>
+        <v>133.8377099294918</v>
       </c>
       <c r="D110" t="n">
-        <v>130.9163124820861</v>
+        <v>127.3490317305018</v>
       </c>
       <c r="E110" t="n">
-        <v>133.0427703857422</v>
+        <v>128.03466796875</v>
       </c>
       <c r="F110" t="n">
-        <v>24131200</v>
+        <v>37995900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>132.2677060470971</v>
+        <v>127.3192184434441</v>
       </c>
       <c r="C111" t="n">
-        <v>133.8377099294918</v>
+        <v>128.0545261364593</v>
       </c>
       <c r="D111" t="n">
-        <v>127.3490317305018</v>
+        <v>124.9741439631975</v>
       </c>
       <c r="E111" t="n">
-        <v>128.03466796875</v>
+        <v>125.8187713623047</v>
       </c>
       <c r="F111" t="n">
-        <v>37995900</v>
+        <v>36485000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>127.3192184434441</v>
+        <v>127.6868765679835</v>
       </c>
       <c r="C112" t="n">
-        <v>128.0545261364593</v>
+        <v>129.2767581387821</v>
       </c>
       <c r="D112" t="n">
-        <v>124.9741439631975</v>
+        <v>123.6128221003258</v>
       </c>
       <c r="E112" t="n">
-        <v>125.8187713623047</v>
+        <v>124.0798492431641</v>
       </c>
       <c r="F112" t="n">
-        <v>36485000</v>
+        <v>42993300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>127.6868765679835</v>
+        <v>122.2216774308809</v>
       </c>
       <c r="C113" t="n">
-        <v>129.2767581387821</v>
+        <v>122.6986434102051</v>
       </c>
       <c r="D113" t="n">
-        <v>123.6128221003258</v>
+        <v>120.2840197235699</v>
       </c>
       <c r="E113" t="n">
-        <v>124.0798492431641</v>
+        <v>122.2117385864258</v>
       </c>
       <c r="F113" t="n">
-        <v>42993300</v>
+        <v>35151000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>122.2216774308809</v>
+        <v>122.7383904417398</v>
       </c>
       <c r="C114" t="n">
-        <v>122.6986434102051</v>
+        <v>125.9976417223621</v>
       </c>
       <c r="D114" t="n">
-        <v>120.2840197235699</v>
+        <v>122.1819364192246</v>
       </c>
       <c r="E114" t="n">
-        <v>122.2117385864258</v>
+        <v>125.0139007568359</v>
       </c>
       <c r="F114" t="n">
-        <v>35151000</v>
+        <v>25662800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>122.7383904417398</v>
+        <v>125.1033248323272</v>
       </c>
       <c r="C115" t="n">
-        <v>125.9976417223621</v>
+        <v>127.2297750394507</v>
       </c>
       <c r="D115" t="n">
-        <v>122.1819364192246</v>
+        <v>124.1195915294407</v>
       </c>
       <c r="E115" t="n">
-        <v>125.0139007568359</v>
+        <v>125.9479446411133</v>
       </c>
       <c r="F115" t="n">
-        <v>25662800</v>
+        <v>20161200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>125.1033248323272</v>
+        <v>125.8088357226236</v>
       </c>
       <c r="C116" t="n">
-        <v>127.2297750394507</v>
+        <v>126.593837657093</v>
       </c>
       <c r="D116" t="n">
-        <v>124.1195915294407</v>
+        <v>124.626363398647</v>
       </c>
       <c r="E116" t="n">
-        <v>125.9479446411133</v>
+        <v>124.9542770385742</v>
       </c>
       <c r="F116" t="n">
-        <v>20161200</v>
+        <v>17345700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>125.8088357226236</v>
+        <v>125.1828241808018</v>
       </c>
       <c r="C117" t="n">
-        <v>126.593837657093</v>
+        <v>126.5242801033853</v>
       </c>
       <c r="D117" t="n">
-        <v>124.626363398647</v>
+        <v>123.1557320302039</v>
       </c>
       <c r="E117" t="n">
-        <v>124.9542770385742</v>
+        <v>123.6326904296875</v>
       </c>
       <c r="F117" t="n">
-        <v>17345700</v>
+        <v>18638300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>125.1828241808018</v>
+        <v>124.7257341647123</v>
       </c>
       <c r="C118" t="n">
-        <v>126.5242801033853</v>
+        <v>127.7862540138419</v>
       </c>
       <c r="D118" t="n">
-        <v>123.1557320302039</v>
+        <v>124.3580802939128</v>
       </c>
       <c r="E118" t="n">
-        <v>123.6326904296875</v>
+        <v>127.1403579711914</v>
       </c>
       <c r="F118" t="n">
-        <v>18638300</v>
+        <v>29205500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>124.7257341647123</v>
+        <v>126.6534531765271</v>
       </c>
       <c r="C119" t="n">
-        <v>127.7862540138419</v>
+        <v>127.9352911784569</v>
       </c>
       <c r="D119" t="n">
-        <v>124.3580802939128</v>
+        <v>126.2460515312658</v>
       </c>
       <c r="E119" t="n">
-        <v>127.1403579711914</v>
+        <v>126.2957305908203</v>
       </c>
       <c r="F119" t="n">
-        <v>29205500</v>
+        <v>17091500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>126.6534531765271</v>
+        <v>125.7193975573372</v>
       </c>
       <c r="C120" t="n">
-        <v>127.9352911784569</v>
+        <v>127.5576895255598</v>
       </c>
       <c r="D120" t="n">
-        <v>126.2460515312658</v>
+        <v>124.8747777428692</v>
       </c>
       <c r="E120" t="n">
-        <v>126.2957305908203</v>
+        <v>127.1006088256836</v>
       </c>
       <c r="F120" t="n">
-        <v>17091500</v>
+        <v>16480400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>125.7193975573372</v>
+        <v>126.3056684844515</v>
       </c>
       <c r="C121" t="n">
-        <v>127.5576895255598</v>
+        <v>127.3589585449282</v>
       </c>
       <c r="D121" t="n">
-        <v>124.8747777428692</v>
+        <v>125.4411709786478</v>
       </c>
       <c r="E121" t="n">
-        <v>127.1006088256836</v>
+        <v>127.0012359619141</v>
       </c>
       <c r="F121" t="n">
-        <v>16480400</v>
+        <v>16434100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>126.3056684844515</v>
+        <v>124.5866098839056</v>
       </c>
       <c r="C122" t="n">
-        <v>127.3589585449282</v>
+        <v>124.8847145576342</v>
       </c>
       <c r="D122" t="n">
-        <v>125.4411709786478</v>
+        <v>120.8802170560586</v>
       </c>
       <c r="E122" t="n">
-        <v>127.0012359619141</v>
+        <v>122.5297088623047</v>
       </c>
       <c r="F122" t="n">
-        <v>16434100</v>
+        <v>28604900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>124.5866098839056</v>
+        <v>121.7248399768431</v>
       </c>
       <c r="C123" t="n">
-        <v>124.8847145576342</v>
+        <v>123.4041483583995</v>
       </c>
       <c r="D123" t="n">
-        <v>120.8802170560586</v>
+        <v>120.8504112025381</v>
       </c>
       <c r="E123" t="n">
-        <v>122.5297088623047</v>
+        <v>123.0166168212891</v>
       </c>
       <c r="F123" t="n">
-        <v>28604900</v>
+        <v>21553000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>121.7248399768431</v>
+        <v>122.9073188921967</v>
       </c>
       <c r="C124" t="n">
-        <v>123.4041483583995</v>
+        <v>123.7221298065307</v>
       </c>
       <c r="D124" t="n">
-        <v>120.8504112025381</v>
+        <v>121.7248465285333</v>
       </c>
       <c r="E124" t="n">
-        <v>123.0166168212891</v>
+        <v>123.5531997680664</v>
       </c>
       <c r="F124" t="n">
-        <v>21553000</v>
+        <v>19375900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>122.9073188921967</v>
+        <v>123.4240246061754</v>
       </c>
       <c r="C125" t="n">
-        <v>123.7221298065307</v>
+        <v>125.3020644813305</v>
       </c>
       <c r="D125" t="n">
-        <v>121.7248465285333</v>
+        <v>122.5694658969271</v>
       </c>
       <c r="E125" t="n">
-        <v>123.5531997680664</v>
+        <v>124.3282699584961</v>
       </c>
       <c r="F125" t="n">
-        <v>19375900</v>
+        <v>18793600</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>123.4240246061754</v>
+        <v>124.5170631497059</v>
       </c>
       <c r="C126" t="n">
-        <v>125.3020644813305</v>
+        <v>124.6959244521016</v>
       </c>
       <c r="D126" t="n">
-        <v>122.5694658969271</v>
+        <v>122.2713693965471</v>
       </c>
       <c r="E126" t="n">
-        <v>124.3282699584961</v>
+        <v>122.7085800170898</v>
       </c>
       <c r="F126" t="n">
-        <v>18793600</v>
+        <v>18176500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>124.5170631497059</v>
+        <v>121.5261084606577</v>
       </c>
       <c r="C127" t="n">
-        <v>124.6959244521016</v>
+        <v>124.596551802696</v>
       </c>
       <c r="D127" t="n">
-        <v>122.2713693965471</v>
+        <v>121.5062307719897</v>
       </c>
       <c r="E127" t="n">
-        <v>122.7085800170898</v>
+        <v>124.5369338989258</v>
       </c>
       <c r="F127" t="n">
-        <v>18176500</v>
+        <v>21751600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>121.5261084606577</v>
+        <v>124.5965516855884</v>
       </c>
       <c r="C128" t="n">
-        <v>124.596551802696</v>
+        <v>125.888328527587</v>
       </c>
       <c r="D128" t="n">
-        <v>121.5062307719897</v>
+        <v>124.1792111973551</v>
       </c>
       <c r="E128" t="n">
-        <v>124.5369338989258</v>
+        <v>125.7193984985352</v>
       </c>
       <c r="F128" t="n">
-        <v>21751600</v>
+        <v>15194100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>124.5965516855884</v>
+        <v>125.9578884818529</v>
       </c>
       <c r="C129" t="n">
-        <v>125.888328527587</v>
+        <v>126.1764975758589</v>
       </c>
       <c r="D129" t="n">
-        <v>124.1792111973551</v>
+        <v>124.0401008586876</v>
       </c>
       <c r="E129" t="n">
-        <v>125.7193984985352</v>
+        <v>125.192756652832</v>
       </c>
       <c r="F129" t="n">
-        <v>15194100</v>
+        <v>20463200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>125.9578884818529</v>
+        <v>125.8485858664739</v>
       </c>
       <c r="C130" t="n">
-        <v>126.1764975758589</v>
+        <v>126.3851697651471</v>
       </c>
       <c r="D130" t="n">
-        <v>124.0401008586876</v>
+        <v>124.0699117156269</v>
       </c>
       <c r="E130" t="n">
-        <v>125.192756652832</v>
+        <v>124.2885208129883</v>
       </c>
       <c r="F130" t="n">
-        <v>20463200</v>
+        <v>19895000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>125.8485858664739</v>
+        <v>123.5432578745883</v>
       </c>
       <c r="C131" t="n">
-        <v>126.3851697651471</v>
+        <v>123.8214848583074</v>
       </c>
       <c r="D131" t="n">
-        <v>124.0699117156269</v>
+        <v>121.0590775469296</v>
       </c>
       <c r="E131" t="n">
-        <v>124.2885208129883</v>
+        <v>121.2081298828125</v>
       </c>
       <c r="F131" t="n">
-        <v>19895000</v>
+        <v>19734900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>123.5432578745883</v>
+        <v>121.6254689891314</v>
       </c>
       <c r="C132" t="n">
-        <v>123.8214848583074</v>
+        <v>121.9732527148649</v>
       </c>
       <c r="D132" t="n">
-        <v>121.0590775469296</v>
+        <v>118.5152704020027</v>
       </c>
       <c r="E132" t="n">
-        <v>121.2081298828125</v>
+        <v>120.3237533569336</v>
       </c>
       <c r="F132" t="n">
-        <v>19734900</v>
+        <v>17927700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>121.6254689891314</v>
+        <v>120.1126709520348</v>
       </c>
       <c r="C133" t="n">
-        <v>121.9732527148649</v>
+        <v>120.7798034051914</v>
       </c>
       <c r="D133" t="n">
-        <v>118.5152704020027</v>
+        <v>117.513863427923</v>
       </c>
       <c r="E133" t="n">
-        <v>120.3237533569336</v>
+        <v>118.5095748901367</v>
       </c>
       <c r="F133" t="n">
-        <v>17927700</v>
+        <v>57545600</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>120.1126709520348</v>
+        <v>119.9633247632631</v>
       </c>
       <c r="C134" t="n">
-        <v>120.7798034051914</v>
+        <v>120.6105311603868</v>
       </c>
       <c r="D134" t="n">
-        <v>117.513863427923</v>
+        <v>118.5394570155744</v>
       </c>
       <c r="E134" t="n">
-        <v>118.5095748901367</v>
+        <v>120.2022933959961</v>
       </c>
       <c r="F134" t="n">
-        <v>57545600</v>
+        <v>22181500</v>
       </c>
       <c r="G134" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>119.9633247632631</v>
+        <v>120.1126723733929</v>
       </c>
       <c r="C135" t="n">
-        <v>120.6105311603868</v>
+        <v>123.577751645438</v>
       </c>
       <c r="D135" t="n">
-        <v>118.5394570155744</v>
+        <v>119.9732733747674</v>
       </c>
       <c r="E135" t="n">
-        <v>120.2022933959961</v>
+        <v>121.5265884399414</v>
       </c>
       <c r="F135" t="n">
-        <v>22181500</v>
+        <v>17269600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>120.1126723733929</v>
+        <v>122.2833215864677</v>
       </c>
       <c r="C136" t="n">
-        <v>123.577751645438</v>
+        <v>122.9604056810019</v>
       </c>
       <c r="D136" t="n">
-        <v>119.9732733747674</v>
+        <v>121.2577400013664</v>
       </c>
       <c r="E136" t="n">
-        <v>121.5265884399414</v>
+        <v>122.5322494506836</v>
       </c>
       <c r="F136" t="n">
-        <v>17269600</v>
+        <v>16597300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>122.2833215864677</v>
+        <v>123.0798964656872</v>
       </c>
       <c r="C137" t="n">
-        <v>122.9604056810019</v>
+        <v>123.2690840775393</v>
       </c>
       <c r="D137" t="n">
-        <v>121.2577400013664</v>
+        <v>121.2677018786759</v>
       </c>
       <c r="E137" t="n">
-        <v>122.5322494506836</v>
+        <v>121.6560287475586</v>
       </c>
       <c r="F137" t="n">
-        <v>16597300</v>
+        <v>16442500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>123.0798964656872</v>
+        <v>121.5066712193412</v>
       </c>
       <c r="C138" t="n">
-        <v>123.2690840775393</v>
+        <v>123.7370628172082</v>
       </c>
       <c r="D138" t="n">
-        <v>121.2677018786759</v>
+        <v>121.2975727192295</v>
       </c>
       <c r="E138" t="n">
-        <v>121.6560287475586</v>
+        <v>122.3629837036133</v>
       </c>
       <c r="F138" t="n">
-        <v>16442500</v>
+        <v>16543300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>121.5066712193412</v>
+        <v>123.1794659302472</v>
       </c>
       <c r="C139" t="n">
-        <v>123.7370628172082</v>
+        <v>124.7228217585454</v>
       </c>
       <c r="D139" t="n">
-        <v>121.2975727192295</v>
+        <v>122.611910692122</v>
       </c>
       <c r="E139" t="n">
-        <v>122.3629837036133</v>
+        <v>122.9703674316406</v>
       </c>
       <c r="F139" t="n">
-        <v>16543300</v>
+        <v>20428900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>123.1794659302472</v>
+        <v>122.9006712768322</v>
       </c>
       <c r="C140" t="n">
-        <v>124.7228217585454</v>
+        <v>124.4639380346807</v>
       </c>
       <c r="D140" t="n">
-        <v>122.611910692122</v>
+        <v>122.313197539037</v>
       </c>
       <c r="E140" t="n">
-        <v>122.9703674316406</v>
+        <v>123.7470245361328</v>
       </c>
       <c r="F140" t="n">
-        <v>20428900</v>
+        <v>21330400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>122.9006712768322</v>
+        <v>123.2690839840767</v>
       </c>
       <c r="C141" t="n">
-        <v>124.4639380346807</v>
+        <v>124.6929517011257</v>
       </c>
       <c r="D141" t="n">
-        <v>122.313197539037</v>
+        <v>122.6019515205109</v>
       </c>
       <c r="E141" t="n">
-        <v>123.7470245361328</v>
+        <v>124.2050476074219</v>
       </c>
       <c r="F141" t="n">
-        <v>21330400</v>
+        <v>17039700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>123.2690839840767</v>
+        <v>124.613294570145</v>
       </c>
       <c r="C142" t="n">
-        <v>124.6929517011257</v>
+        <v>125.3600781881083</v>
       </c>
       <c r="D142" t="n">
-        <v>122.6019515205109</v>
+        <v>123.6175830795272</v>
       </c>
       <c r="E142" t="n">
-        <v>124.2050476074219</v>
+        <v>125.2505493164062</v>
       </c>
       <c r="F142" t="n">
-        <v>17039700</v>
+        <v>11898400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>124.613294570145</v>
+        <v>125.2704609872334</v>
       </c>
       <c r="C143" t="n">
-        <v>125.3600781881083</v>
+        <v>126.4354492120167</v>
       </c>
       <c r="D143" t="n">
-        <v>123.6175830795272</v>
+        <v>124.8323530943609</v>
       </c>
       <c r="E143" t="n">
-        <v>125.2505493164062</v>
+        <v>126.2462615966797</v>
       </c>
       <c r="F143" t="n">
-        <v>11898400</v>
+        <v>10850400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>125.2704609872334</v>
+        <v>125.6488358778686</v>
       </c>
       <c r="C144" t="n">
-        <v>126.4354492120167</v>
+        <v>125.8181050086721</v>
       </c>
       <c r="D144" t="n">
-        <v>124.8323530943609</v>
+        <v>121.2677037842684</v>
       </c>
       <c r="E144" t="n">
-        <v>126.2462615966797</v>
+        <v>121.9646987915039</v>
       </c>
       <c r="F144" t="n">
-        <v>10850400</v>
+        <v>16076000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>125.6488358778686</v>
+        <v>121.7556020039852</v>
       </c>
       <c r="C145" t="n">
-        <v>125.8181050086721</v>
+        <v>126.7540780291546</v>
       </c>
       <c r="D145" t="n">
-        <v>121.2677037842684</v>
+        <v>120.8096791098908</v>
       </c>
       <c r="E145" t="n">
-        <v>121.9646987915039</v>
+        <v>126.7142486572266</v>
       </c>
       <c r="F145" t="n">
-        <v>16076000</v>
+        <v>20194300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>121.7556020039852</v>
+        <v>126.5449729094413</v>
       </c>
       <c r="C146" t="n">
-        <v>126.7540780291546</v>
+        <v>129.1338289281244</v>
       </c>
       <c r="D146" t="n">
-        <v>120.8096791098908</v>
+        <v>126.2761341426855</v>
       </c>
       <c r="E146" t="n">
-        <v>126.7142486572266</v>
+        <v>128.5762329101562</v>
       </c>
       <c r="F146" t="n">
-        <v>20194300</v>
+        <v>13853100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>126.5449729094413</v>
+        <v>128.1679831957248</v>
       </c>
       <c r="C147" t="n">
-        <v>129.1338289281244</v>
+        <v>128.3770740986961</v>
       </c>
       <c r="D147" t="n">
-        <v>126.2761341426855</v>
+        <v>125.6787044903905</v>
       </c>
       <c r="E147" t="n">
-        <v>128.5762329101562</v>
+        <v>126.2263412475586</v>
       </c>
       <c r="F147" t="n">
-        <v>13853100</v>
+        <v>13894000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>128.1679831957248</v>
+        <v>125.7484068642315</v>
       </c>
       <c r="C148" t="n">
-        <v>128.3770740986961</v>
+        <v>125.7583661063497</v>
       </c>
       <c r="D148" t="n">
-        <v>125.6787044903905</v>
+        <v>123.4184379925161</v>
       </c>
       <c r="E148" t="n">
-        <v>126.2263412475586</v>
+        <v>124.0357818603516</v>
       </c>
       <c r="F148" t="n">
-        <v>13894000</v>
+        <v>14510600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>125.7484068642315</v>
+        <v>122.6218644106077</v>
       </c>
       <c r="C149" t="n">
-        <v>125.7583661063497</v>
+        <v>124.6630682888762</v>
       </c>
       <c r="D149" t="n">
-        <v>123.4184379925161</v>
+        <v>122.0244390705456</v>
       </c>
       <c r="E149" t="n">
-        <v>124.0357818603516</v>
+        <v>124.5137176513672</v>
       </c>
       <c r="F149" t="n">
-        <v>14510600</v>
+        <v>15320800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>122.6218644106077</v>
+        <v>124.0955129791748</v>
       </c>
       <c r="C150" t="n">
-        <v>124.6630682888762</v>
+        <v>124.5336284399926</v>
       </c>
       <c r="D150" t="n">
-        <v>122.0244390705456</v>
+        <v>122.6517344420986</v>
       </c>
       <c r="E150" t="n">
-        <v>124.5137176513672</v>
+        <v>124.2249603271484</v>
       </c>
       <c r="F150" t="n">
-        <v>15320800</v>
+        <v>17001400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>124.0955129791748</v>
+        <v>123.7968020201654</v>
       </c>
       <c r="C151" t="n">
-        <v>124.5336284399926</v>
+        <v>125.3998980056611</v>
       </c>
       <c r="D151" t="n">
-        <v>122.6517344420986</v>
+        <v>123.4383453031182</v>
       </c>
       <c r="E151" t="n">
-        <v>124.2249603271484</v>
+        <v>124.2846984863281</v>
       </c>
       <c r="F151" t="n">
-        <v>17001400</v>
+        <v>18324500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>123.7968020201654</v>
+        <v>124.0357815469104</v>
       </c>
       <c r="C152" t="n">
-        <v>125.3998980056611</v>
+        <v>127.0229160540335</v>
       </c>
       <c r="D152" t="n">
-        <v>123.4383453031182</v>
+        <v>122.8409307827315</v>
       </c>
       <c r="E152" t="n">
-        <v>124.2846984863281</v>
+        <v>126.9532165527344</v>
       </c>
       <c r="F152" t="n">
-        <v>18324500</v>
+        <v>24763700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>124.0357815469104</v>
+        <v>127.3216255408005</v>
       </c>
       <c r="C153" t="n">
-        <v>127.0229160540335</v>
+        <v>128.9147623376428</v>
       </c>
       <c r="D153" t="n">
-        <v>122.8409307827315</v>
+        <v>126.7739812059444</v>
       </c>
       <c r="E153" t="n">
-        <v>126.9532165527344</v>
+        <v>127.3714065551758</v>
       </c>
       <c r="F153" t="n">
-        <v>24763700</v>
+        <v>18933600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>127.3216255408005</v>
+        <v>127.2817912634612</v>
       </c>
       <c r="C154" t="n">
-        <v>128.9147623376428</v>
+        <v>129.213473828279</v>
       </c>
       <c r="D154" t="n">
-        <v>126.7739812059444</v>
+        <v>126.9332937895701</v>
       </c>
       <c r="E154" t="n">
-        <v>127.3714065551758</v>
+        <v>129.0442047119141</v>
       </c>
       <c r="F154" t="n">
-        <v>18933600</v>
+        <v>17312400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>127.2817912634612</v>
+        <v>129.4424953884951</v>
       </c>
       <c r="C155" t="n">
-        <v>129.213473828279</v>
+        <v>129.8905625261696</v>
       </c>
       <c r="D155" t="n">
-        <v>126.9332937895701</v>
+        <v>128.2874663986241</v>
       </c>
       <c r="E155" t="n">
-        <v>129.0442047119141</v>
+        <v>129.4225769042969</v>
       </c>
       <c r="F155" t="n">
-        <v>17312400</v>
+        <v>17624500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>129.4424953884951</v>
+        <v>130.010060581267</v>
       </c>
       <c r="C156" t="n">
-        <v>129.8905625261696</v>
+        <v>131.8919547480997</v>
       </c>
       <c r="D156" t="n">
-        <v>128.2874663986241</v>
+        <v>129.93040183639</v>
       </c>
       <c r="E156" t="n">
-        <v>129.4225769042969</v>
+        <v>131.4637908935547</v>
       </c>
       <c r="F156" t="n">
-        <v>17624500</v>
+        <v>16376000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>130.010060581267</v>
+        <v>131.3741802679442</v>
       </c>
       <c r="C157" t="n">
-        <v>131.8919547480997</v>
+        <v>131.5534010485827</v>
       </c>
       <c r="D157" t="n">
-        <v>129.93040183639</v>
+        <v>128.7255839805935</v>
       </c>
       <c r="E157" t="n">
-        <v>131.4637908935547</v>
+        <v>129.3628387451172</v>
       </c>
       <c r="F157" t="n">
-        <v>16376000</v>
+        <v>16016300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>131.3741802679442</v>
+        <v>129.0641091249569</v>
       </c>
       <c r="C158" t="n">
-        <v>131.5534010485827</v>
+        <v>129.253296725292</v>
       </c>
       <c r="D158" t="n">
-        <v>128.7255839805935</v>
+        <v>126.8536361584495</v>
       </c>
       <c r="E158" t="n">
-        <v>129.3628387451172</v>
+        <v>127.0428161621094</v>
       </c>
       <c r="F158" t="n">
-        <v>16016300</v>
+        <v>17029500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>129.0641091249569</v>
+        <v>128.7853111434159</v>
       </c>
       <c r="C159" t="n">
-        <v>129.253296725292</v>
+        <v>129.2134749536506</v>
       </c>
       <c r="D159" t="n">
-        <v>126.8536361584495</v>
+        <v>126.236292344555</v>
       </c>
       <c r="E159" t="n">
         <v>127.0428161621094</v>
       </c>
       <c r="F159" t="n">
-        <v>17029500</v>
+        <v>16341800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>128.7853111434159</v>
+        <v>126.1367309249001</v>
       </c>
       <c r="C160" t="n">
-        <v>129.2134749536506</v>
+        <v>127.5307285199335</v>
       </c>
       <c r="D160" t="n">
-        <v>126.236292344555</v>
+        <v>125.3700364258034</v>
       </c>
       <c r="E160" t="n">
-        <v>127.0428161621094</v>
+        <v>127.4610214233398</v>
       </c>
       <c r="F160" t="n">
-        <v>16341800</v>
+        <v>16538800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>126.1367309249001</v>
+        <v>127.470976777907</v>
       </c>
       <c r="C161" t="n">
-        <v>127.5307285199335</v>
+        <v>131.8620524738122</v>
       </c>
       <c r="D161" t="n">
-        <v>125.3700364258034</v>
+        <v>127.4012696875933</v>
       </c>
       <c r="E161" t="n">
-        <v>127.4610214233398</v>
+        <v>131.3641967773438</v>
       </c>
       <c r="F161" t="n">
-        <v>16538800</v>
+        <v>19867700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>127.470976777907</v>
+        <v>131.3542490271043</v>
       </c>
       <c r="C162" t="n">
-        <v>131.8620524738122</v>
+        <v>132.7980275509944</v>
       </c>
       <c r="D162" t="n">
-        <v>127.4012696875933</v>
+        <v>130.4182778590603</v>
       </c>
       <c r="E162" t="n">
-        <v>131.3641967773438</v>
+        <v>131.0356292724609</v>
       </c>
       <c r="F162" t="n">
-        <v>19867700</v>
+        <v>10480900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>131.3542490271043</v>
+        <v>129.8507311252314</v>
       </c>
       <c r="C163" t="n">
-        <v>132.7980275509944</v>
+        <v>131.184980793923</v>
       </c>
       <c r="D163" t="n">
-        <v>130.4182778590603</v>
+        <v>129.1238508427206</v>
       </c>
       <c r="E163" t="n">
-        <v>131.0356292724609</v>
+        <v>129.7710723876953</v>
       </c>
       <c r="F163" t="n">
-        <v>10480900</v>
+        <v>10340700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>129.8507311252314</v>
+        <v>129.9502974650302</v>
       </c>
       <c r="C164" t="n">
-        <v>131.184980793923</v>
+        <v>131.1650666644096</v>
       </c>
       <c r="D164" t="n">
-        <v>129.1238508427206</v>
+        <v>129.7412065662402</v>
       </c>
       <c r="E164" t="n">
-        <v>129.7710723876953</v>
+        <v>130.2290954589844</v>
       </c>
       <c r="F164" t="n">
-        <v>10340700</v>
+        <v>10637300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>129.9502974650302</v>
+        <v>130.2988095283542</v>
       </c>
       <c r="C165" t="n">
-        <v>131.1650666644096</v>
+        <v>130.5875591827794</v>
       </c>
       <c r="D165" t="n">
-        <v>129.7412065662402</v>
+        <v>128.9745113895137</v>
       </c>
       <c r="E165" t="n">
-        <v>130.2290954589844</v>
+        <v>129.5221557617188</v>
       </c>
       <c r="F165" t="n">
-        <v>10637300</v>
+        <v>16371500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>130.2988095283542</v>
+        <v>129.3429155964338</v>
       </c>
       <c r="C166" t="n">
-        <v>130.5875591827794</v>
+        <v>130.0399257893878</v>
       </c>
       <c r="D166" t="n">
-        <v>128.9745113895137</v>
+        <v>128.1181947261785</v>
       </c>
       <c r="E166" t="n">
-        <v>129.5221557617188</v>
+        <v>129.6416320800781</v>
       </c>
       <c r="F166" t="n">
-        <v>16371500</v>
+        <v>14935400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,25 +4759,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>129.3429155964338</v>
+        <v>130.0087618254011</v>
       </c>
       <c r="C167" t="n">
-        <v>130.0399257893878</v>
+        <v>131.0961549064253</v>
       </c>
       <c r="D167" t="n">
-        <v>128.1181947261785</v>
+        <v>129.9389217008702</v>
       </c>
       <c r="E167" t="n">
-        <v>129.6416320800781</v>
+        <v>130.1184844970703</v>
       </c>
       <c r="F167" t="n">
-        <v>14935400</v>
+        <v>15183700</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -4785,25 +4785,25 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>130.0087618254011</v>
+        <v>129.8690812906444</v>
       </c>
       <c r="C168" t="n">
-        <v>131.0961549064253</v>
+        <v>130.2880915922154</v>
       </c>
       <c r="D168" t="n">
-        <v>129.9389217008702</v>
+        <v>126.078161470576</v>
       </c>
       <c r="E168" t="n">
-        <v>130.1184844970703</v>
+        <v>127.285270690918</v>
       </c>
       <c r="F168" t="n">
-        <v>15183700</v>
+        <v>18699200</v>
       </c>
       <c r="G168" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>129.8690812906444</v>
+        <v>127.7741133789013</v>
       </c>
       <c r="C169" t="n">
-        <v>130.2880915922154</v>
+        <v>130.8068463681294</v>
       </c>
       <c r="D169" t="n">
-        <v>126.078161470576</v>
+        <v>127.4149725439082</v>
       </c>
       <c r="E169" t="n">
-        <v>127.285270690918</v>
+        <v>130.0386962890625</v>
       </c>
       <c r="F169" t="n">
-        <v>18699200</v>
+        <v>17935400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>127.7741133789013</v>
+        <v>128.8814524975413</v>
       </c>
       <c r="C170" t="n">
-        <v>130.8068463681294</v>
+        <v>132.2134717809921</v>
       </c>
       <c r="D170" t="n">
-        <v>127.4149725439082</v>
+        <v>128.4624574279768</v>
       </c>
       <c r="E170" t="n">
-        <v>130.0386962890625</v>
+        <v>131.156005859375</v>
       </c>
       <c r="F170" t="n">
-        <v>17935400</v>
+        <v>13786600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>128.8814524975413</v>
+        <v>131.0462673331121</v>
       </c>
       <c r="C171" t="n">
-        <v>132.2134717809921</v>
+        <v>132.4628740535408</v>
       </c>
       <c r="D171" t="n">
-        <v>128.4624574279768</v>
+        <v>130.5474615066649</v>
       </c>
       <c r="E171" t="n">
-        <v>131.156005859375</v>
+        <v>132.1436462402344</v>
       </c>
       <c r="F171" t="n">
-        <v>13786600</v>
+        <v>14200400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>131.0462673331121</v>
+        <v>133.370718441355</v>
       </c>
       <c r="C172" t="n">
-        <v>132.4628740535408</v>
+        <v>133.6300920185431</v>
       </c>
       <c r="D172" t="n">
-        <v>130.5474615066649</v>
+        <v>130.4776352080381</v>
       </c>
       <c r="E172" t="n">
-        <v>132.1436462402344</v>
+        <v>131.1360626220703</v>
       </c>
       <c r="F172" t="n">
-        <v>14200400</v>
+        <v>25323000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>133.370718441355</v>
+        <v>131.2058999637278</v>
       </c>
       <c r="C173" t="n">
-        <v>133.6300920185431</v>
+        <v>133.1512398071679</v>
       </c>
       <c r="D173" t="n">
-        <v>130.4776352080381</v>
+        <v>130.8168319950398</v>
       </c>
       <c r="E173" t="n">
-        <v>131.1360626220703</v>
+        <v>133.0215454101562</v>
       </c>
       <c r="F173" t="n">
-        <v>25323000</v>
+        <v>17183200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>131.2058999637278</v>
+        <v>132.6225008315265</v>
       </c>
       <c r="C174" t="n">
-        <v>133.1512398071679</v>
+        <v>134.8372000065807</v>
       </c>
       <c r="D174" t="n">
-        <v>130.8168319950398</v>
+        <v>131.7445976710087</v>
       </c>
       <c r="E174" t="n">
-        <v>133.0215454101562</v>
+        <v>133.8794860839844</v>
       </c>
       <c r="F174" t="n">
-        <v>17183200</v>
+        <v>16957100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>132.6225008315265</v>
+        <v>132.5925684137131</v>
       </c>
       <c r="C175" t="n">
-        <v>134.8372000065807</v>
+        <v>133.3307912944098</v>
       </c>
       <c r="D175" t="n">
-        <v>131.7445976710087</v>
+        <v>130.0187285230658</v>
       </c>
       <c r="E175" t="n">
-        <v>133.8794860839844</v>
+        <v>130.5374908447266</v>
       </c>
       <c r="F175" t="n">
-        <v>16957100</v>
+        <v>28471600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>132.5925684137131</v>
+        <v>124.112876676945</v>
       </c>
       <c r="C176" t="n">
-        <v>133.3307912944098</v>
+        <v>125.49955634699</v>
       </c>
       <c r="D176" t="n">
-        <v>130.0187285230658</v>
+        <v>120.1024733345915</v>
       </c>
       <c r="E176" t="n">
-        <v>130.5374908447266</v>
+        <v>121.0502014160156</v>
       </c>
       <c r="F176" t="n">
-        <v>28471600</v>
+        <v>53006600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>124.112876676945</v>
+        <v>121.0502017985552</v>
       </c>
       <c r="C177" t="n">
-        <v>125.49955634699</v>
+        <v>121.6587455533669</v>
       </c>
       <c r="D177" t="n">
-        <v>120.1024733345915</v>
+        <v>118.6260126387565</v>
       </c>
       <c r="E177" t="n">
-        <v>121.0502014160156</v>
+        <v>119.9827575683594</v>
       </c>
       <c r="F177" t="n">
-        <v>53006600</v>
+        <v>30330600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>121.0502017985552</v>
+        <v>120.401759010853</v>
       </c>
       <c r="C178" t="n">
-        <v>121.6587455533669</v>
+        <v>120.7608998332451</v>
       </c>
       <c r="D178" t="n">
-        <v>118.6260126387565</v>
+        <v>117.638370328068</v>
       </c>
       <c r="E178" t="n">
-        <v>119.9827575683594</v>
+        <v>118.2868194580078</v>
       </c>
       <c r="F178" t="n">
-        <v>30330600</v>
+        <v>28796600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>120.401759010853</v>
+        <v>118.0473918040102</v>
       </c>
       <c r="C179" t="n">
-        <v>120.7608998332451</v>
+        <v>119.1447631286873</v>
       </c>
       <c r="D179" t="n">
-        <v>117.638370328068</v>
+        <v>117.7580835037564</v>
       </c>
       <c r="E179" t="n">
-        <v>118.2868194580078</v>
+        <v>118.2568893432617</v>
       </c>
       <c r="F179" t="n">
-        <v>28796600</v>
+        <v>22062200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>118.0473918040102</v>
+        <v>118.6758897292679</v>
       </c>
       <c r="C180" t="n">
-        <v>119.1447631286873</v>
+        <v>118.8853872778886</v>
       </c>
       <c r="D180" t="n">
-        <v>117.7580835037564</v>
+        <v>117.0497853597791</v>
       </c>
       <c r="E180" t="n">
-        <v>118.2568893432617</v>
+        <v>118.6160354614258</v>
       </c>
       <c r="F180" t="n">
-        <v>22062200</v>
+        <v>21613100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>118.6758897292679</v>
+        <v>117.8279207851919</v>
       </c>
       <c r="C181" t="n">
-        <v>118.8853872778886</v>
+        <v>118.7956053707809</v>
       </c>
       <c r="D181" t="n">
-        <v>117.0497853597791</v>
+        <v>114.4360394170558</v>
       </c>
       <c r="E181" t="n">
-        <v>118.6160354614258</v>
+        <v>115.4735565185547</v>
       </c>
       <c r="F181" t="n">
-        <v>21613100</v>
+        <v>42191000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>117.8279207851919</v>
+        <v>114.4559959694409</v>
       </c>
       <c r="C182" t="n">
-        <v>118.7956053707809</v>
+        <v>115.7030106192767</v>
       </c>
       <c r="D182" t="n">
-        <v>114.4360394170558</v>
+        <v>113.2887844727029</v>
       </c>
       <c r="E182" t="n">
-        <v>115.4735565185547</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F182" t="n">
-        <v>42191000</v>
+        <v>26176200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>114.4559959694409</v>
+        <v>113.598048691841</v>
       </c>
       <c r="C183" t="n">
-        <v>115.7030106192767</v>
+        <v>114.2963738476551</v>
       </c>
       <c r="D183" t="n">
-        <v>113.2887844727029</v>
+        <v>112.4607719459876</v>
       </c>
       <c r="E183" t="n">
-        <v>114.326301574707</v>
+        <v>112.7899780273438</v>
       </c>
       <c r="F183" t="n">
-        <v>26176200</v>
+        <v>27366400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>113.598048691841</v>
+        <v>112.829882918774</v>
       </c>
       <c r="C184" t="n">
-        <v>114.2963738476551</v>
+        <v>117.0098784207316</v>
       </c>
       <c r="D184" t="n">
-        <v>112.4607719459876</v>
+        <v>112.6902178882183</v>
       </c>
       <c r="E184" t="n">
-        <v>112.7899780273438</v>
+        <v>116.6108322143555</v>
       </c>
       <c r="F184" t="n">
-        <v>27366400</v>
+        <v>32880600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>112.829882918774</v>
+        <v>119.613646228699</v>
       </c>
       <c r="C185" t="n">
-        <v>117.0098784207316</v>
+        <v>119.6535516106658</v>
       </c>
       <c r="D185" t="n">
-        <v>112.6902178882183</v>
+        <v>117.009879041958</v>
       </c>
       <c r="E185" t="n">
-        <v>116.6108322143555</v>
+        <v>117.4588012695312</v>
       </c>
       <c r="F185" t="n">
-        <v>32880600</v>
+        <v>22870400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>119.613646228699</v>
+        <v>118.0673439785114</v>
       </c>
       <c r="C186" t="n">
-        <v>119.6535516106658</v>
+        <v>120.601278627145</v>
       </c>
       <c r="D186" t="n">
-        <v>117.009879041958</v>
+        <v>117.8179410518094</v>
       </c>
       <c r="E186" t="n">
-        <v>117.4588012695312</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F186" t="n">
-        <v>22870400</v>
+        <v>36638100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>118.0673439785114</v>
+        <v>117.9675872503352</v>
       </c>
       <c r="C187" t="n">
-        <v>120.601278627145</v>
+        <v>119.8929781965846</v>
       </c>
       <c r="D187" t="n">
-        <v>117.8179410518094</v>
+        <v>117.8678275994195</v>
       </c>
       <c r="E187" t="n">
-        <v>118.596076965332</v>
+        <v>119.543815612793</v>
       </c>
       <c r="F187" t="n">
-        <v>36638100</v>
+        <v>19514100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>117.9675872503352</v>
+        <v>120.0924945255443</v>
       </c>
       <c r="C188" t="n">
-        <v>119.8929781965846</v>
+        <v>120.2122106703836</v>
       </c>
       <c r="D188" t="n">
-        <v>117.8678275994195</v>
+        <v>117.7181814033632</v>
       </c>
       <c r="E188" t="n">
-        <v>119.543815612793</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F188" t="n">
-        <v>19514100</v>
+        <v>23959000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>120.0924945255443</v>
+        <v>119.4240987453198</v>
       </c>
       <c r="C189" t="n">
-        <v>120.2122106703836</v>
+        <v>120.53144836951</v>
       </c>
       <c r="D189" t="n">
-        <v>117.7181814033632</v>
+        <v>117.2493048793001</v>
       </c>
       <c r="E189" t="n">
-        <v>118.596076965332</v>
+        <v>120.3019943237305</v>
       </c>
       <c r="F189" t="n">
-        <v>23959000</v>
+        <v>22414900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>119.4240987453198</v>
+        <v>120.2820441244615</v>
       </c>
       <c r="C190" t="n">
-        <v>120.53144836951</v>
+        <v>121.5689641496319</v>
       </c>
       <c r="D190" t="n">
-        <v>117.2493048793001</v>
+        <v>119.1746945123655</v>
       </c>
       <c r="E190" t="n">
-        <v>120.3019943237305</v>
+        <v>120.2122116088867</v>
       </c>
       <c r="F190" t="n">
-        <v>22414900</v>
+        <v>22438000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>120.2820441244615</v>
+        <v>120.3019933173184</v>
       </c>
       <c r="C191" t="n">
-        <v>121.5689641496319</v>
+        <v>121.3195615310648</v>
       </c>
       <c r="D191" t="n">
-        <v>119.1746945123655</v>
+        <v>119.2445273327187</v>
       </c>
       <c r="E191" t="n">
-        <v>120.2122116088867</v>
+        <v>120.7509231567383</v>
       </c>
       <c r="F191" t="n">
-        <v>22438000</v>
+        <v>14753500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>120.3019933173184</v>
+        <v>119.4540258740917</v>
       </c>
       <c r="C192" t="n">
-        <v>121.3195615310648</v>
+        <v>121.1998463936268</v>
       </c>
       <c r="D192" t="n">
-        <v>119.2445273327187</v>
+        <v>118.2968002303814</v>
       </c>
       <c r="E192" t="n">
-        <v>120.7509231567383</v>
+        <v>120.5314483642578</v>
       </c>
       <c r="F192" t="n">
-        <v>14753500</v>
+        <v>20722500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>119.4540258740917</v>
+        <v>120.8506818055627</v>
       </c>
       <c r="C193" t="n">
-        <v>121.1998463936268</v>
+        <v>122.646385926027</v>
       </c>
       <c r="D193" t="n">
-        <v>118.2968002303814</v>
+        <v>119.5936889212378</v>
       </c>
       <c r="E193" t="n">
-        <v>120.5314483642578</v>
+        <v>120.7409439086914</v>
       </c>
       <c r="F193" t="n">
-        <v>20722500</v>
+        <v>23060700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>120.8506818055627</v>
+        <v>119.2944114353401</v>
       </c>
       <c r="C194" t="n">
-        <v>122.646385926027</v>
+        <v>120.7209965009543</v>
       </c>
       <c r="D194" t="n">
-        <v>119.5936889212378</v>
+        <v>117.1694935982547</v>
       </c>
       <c r="E194" t="n">
-        <v>120.7409439086914</v>
+        <v>117.8478698730469</v>
       </c>
       <c r="F194" t="n">
-        <v>23060700</v>
+        <v>21711100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>119.2944114353401</v>
+        <v>117.9176994360996</v>
       </c>
       <c r="C195" t="n">
-        <v>120.7209965009543</v>
+        <v>118.1970371043968</v>
       </c>
       <c r="D195" t="n">
-        <v>117.1694935982547</v>
+        <v>116.5210491504798</v>
       </c>
       <c r="E195" t="n">
-        <v>117.8478698730469</v>
+        <v>116.9001388549805</v>
       </c>
       <c r="F195" t="n">
-        <v>21711100</v>
+        <v>36526800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>117.9176994360996</v>
+        <v>116.6806630640479</v>
       </c>
       <c r="C196" t="n">
-        <v>118.1970371043968</v>
+        <v>118.1172263420262</v>
       </c>
       <c r="D196" t="n">
-        <v>116.5210491504798</v>
+        <v>116.6706848159582</v>
       </c>
       <c r="E196" t="n">
         <v>116.9001388549805</v>
       </c>
       <c r="F196" t="n">
-        <v>36526800</v>
+        <v>17053900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>116.6806630640479</v>
+        <v>119.4240968222584</v>
       </c>
       <c r="C197" t="n">
-        <v>118.1172263420262</v>
+        <v>119.9628080586903</v>
       </c>
       <c r="D197" t="n">
-        <v>116.6706848159582</v>
+        <v>116.0621426214644</v>
       </c>
       <c r="E197" t="n">
-        <v>116.9001388549805</v>
+        <v>119.1347885131836</v>
       </c>
       <c r="F197" t="n">
-        <v>17053900</v>
+        <v>23411400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>119.4240968222584</v>
+        <v>119.2744498995579</v>
       </c>
       <c r="C198" t="n">
-        <v>119.9628080586903</v>
+        <v>120.112447667685</v>
       </c>
       <c r="D198" t="n">
-        <v>116.0621426214644</v>
+        <v>118.6459572818424</v>
       </c>
       <c r="E198" t="n">
-        <v>119.1347885131836</v>
+        <v>118.7157897949219</v>
       </c>
       <c r="F198" t="n">
-        <v>23411400</v>
+        <v>20600100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>119.2744498995579</v>
+        <v>117.1894451773868</v>
       </c>
       <c r="C199" t="n">
-        <v>120.112447667685</v>
+        <v>118.2967947502302</v>
       </c>
       <c r="D199" t="n">
-        <v>118.6459572818424</v>
+        <v>115.1044328099781</v>
       </c>
       <c r="E199" t="n">
-        <v>118.7157897949219</v>
+        <v>115.5034790039062</v>
       </c>
       <c r="F199" t="n">
-        <v>20600100</v>
+        <v>20384700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>117.1894451773868</v>
+        <v>117.0098811702962</v>
       </c>
       <c r="C200" t="n">
-        <v>118.2967947502302</v>
+        <v>117.5984684398727</v>
       </c>
       <c r="D200" t="n">
-        <v>115.1044328099781</v>
+        <v>114.8151307892405</v>
       </c>
       <c r="E200" t="n">
-        <v>115.5034790039062</v>
+        <v>115.413703918457</v>
       </c>
       <c r="F200" t="n">
-        <v>20384700</v>
+        <v>36636000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>117.0098811702962</v>
+        <v>116.1918382308837</v>
       </c>
       <c r="C201" t="n">
-        <v>117.5984684398727</v>
+        <v>116.521051925122</v>
       </c>
       <c r="D201" t="n">
-        <v>114.8151307892405</v>
+        <v>113.9272553645249</v>
       </c>
       <c r="E201" t="n">
-        <v>115.413703918457</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F201" t="n">
-        <v>36636000</v>
+        <v>20367000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>116.1918382308837</v>
+        <v>113.6978053385094</v>
       </c>
       <c r="C202" t="n">
-        <v>116.521051925122</v>
+        <v>114.3362762101566</v>
       </c>
       <c r="D202" t="n">
-        <v>113.9272553645249</v>
+        <v>112.6602882692895</v>
       </c>
       <c r="E202" t="n">
-        <v>114.326301574707</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F202" t="n">
-        <v>20367000</v>
+        <v>23034000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>113.6978053385094</v>
+        <v>109.8669732552887</v>
       </c>
       <c r="C203" t="n">
-        <v>114.3362762101566</v>
+        <v>110.4455898652017</v>
       </c>
       <c r="D203" t="n">
-        <v>112.6602882692895</v>
+        <v>106.9938543130583</v>
       </c>
       <c r="E203" t="n">
-        <v>112.989501953125</v>
+        <v>108.5601043701172</v>
       </c>
       <c r="F203" t="n">
-        <v>23034000</v>
+        <v>40391400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>109.8669732552887</v>
+        <v>109.0688912954154</v>
       </c>
       <c r="C204" t="n">
-        <v>110.4455898652017</v>
+        <v>112.1814349941213</v>
       </c>
       <c r="D204" t="n">
-        <v>106.9938543130583</v>
+        <v>108.8992991295087</v>
       </c>
       <c r="E204" t="n">
-        <v>108.5601043701172</v>
+        <v>111.5728912353516</v>
       </c>
       <c r="F204" t="n">
-        <v>40391400</v>
+        <v>29512200</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>109.0688912954154</v>
+        <v>111.1339433224697</v>
       </c>
       <c r="C205" t="n">
-        <v>112.1814349941213</v>
+        <v>112.1016278755018</v>
       </c>
       <c r="D205" t="n">
-        <v>108.8992991295087</v>
+        <v>109.1087928180449</v>
       </c>
       <c r="E205" t="n">
-        <v>111.5728912353516</v>
+        <v>110.3857345581055</v>
       </c>
       <c r="F205" t="n">
-        <v>29512200</v>
+        <v>29523300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>111.1339433224697</v>
+        <v>112.7001980505562</v>
       </c>
       <c r="C206" t="n">
-        <v>112.1016278755018</v>
+        <v>113.228931048236</v>
       </c>
       <c r="D206" t="n">
-        <v>109.1087928180449</v>
+        <v>111.0341882926515</v>
       </c>
       <c r="E206" t="n">
-        <v>110.3857345581055</v>
+        <v>111.2736129760742</v>
       </c>
       <c r="F206" t="n">
-        <v>29523300</v>
+        <v>19941400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>112.7001980505562</v>
+        <v>112.879763389333</v>
       </c>
       <c r="C207" t="n">
-        <v>113.228931048236</v>
+        <v>113.5880667705184</v>
       </c>
       <c r="D207" t="n">
-        <v>111.0341882926515</v>
+        <v>111.5429597770651</v>
       </c>
       <c r="E207" t="n">
-        <v>111.2736129760742</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F207" t="n">
-        <v>19941400</v>
+        <v>19892000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>112.879763389333</v>
+        <v>110.9743243964893</v>
       </c>
       <c r="C208" t="n">
-        <v>113.5880667705184</v>
+        <v>112.4906984566786</v>
       </c>
       <c r="D208" t="n">
-        <v>111.5429597770651</v>
+        <v>110.7748050991254</v>
       </c>
       <c r="E208" t="n">
-        <v>112.8298797607422</v>
+        <v>111.942008972168</v>
       </c>
       <c r="F208" t="n">
-        <v>19892000</v>
+        <v>20464500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>110.9743243964893</v>
+        <v>111.6826280597077</v>
       </c>
       <c r="C209" t="n">
-        <v>112.4906984566786</v>
+        <v>113.8873566399898</v>
       </c>
       <c r="D209" t="n">
-        <v>110.7748050991254</v>
+        <v>111.6626791743936</v>
       </c>
       <c r="E209" t="n">
-        <v>111.942008972168</v>
+        <v>113.6279754638672</v>
       </c>
       <c r="F209" t="n">
-        <v>20464500</v>
+        <v>12461700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>111.6826280597077</v>
+        <v>114.4559909872762</v>
       </c>
       <c r="C210" t="n">
-        <v>113.8873566399898</v>
+        <v>115.26405400962</v>
       </c>
       <c r="D210" t="n">
-        <v>111.6626791743936</v>
+        <v>113.7377093624492</v>
       </c>
       <c r="E210" t="n">
-        <v>113.6279754638672</v>
+        <v>114.5058670043945</v>
       </c>
       <c r="F210" t="n">
-        <v>12461700</v>
+        <v>17043400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>114.4559909872762</v>
+        <v>114.8051528853423</v>
       </c>
       <c r="C211" t="n">
-        <v>115.26405400962</v>
+        <v>115.6032376551602</v>
       </c>
       <c r="D211" t="n">
-        <v>113.7377093624492</v>
+        <v>113.2289246190302</v>
       </c>
       <c r="E211" t="n">
-        <v>114.5058670043945</v>
+        <v>113.4284439086914</v>
       </c>
       <c r="F211" t="n">
-        <v>17043400</v>
+        <v>14682000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>114.8051528853423</v>
+        <v>112.9795273843265</v>
       </c>
       <c r="C212" t="n">
-        <v>115.6032376551602</v>
+        <v>114.4559960800755</v>
       </c>
       <c r="D212" t="n">
-        <v>113.2289246190302</v>
+        <v>111.8023452492967</v>
       </c>
       <c r="E212" t="n">
-        <v>113.4284439086914</v>
+        <v>112.2612457275391</v>
       </c>
       <c r="F212" t="n">
-        <v>14682000</v>
+        <v>16467900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>112.9795273843265</v>
+        <v>113.4883080789502</v>
       </c>
       <c r="C213" t="n">
-        <v>114.4559960800755</v>
+        <v>115.3139316886614</v>
       </c>
       <c r="D213" t="n">
-        <v>111.8023452492967</v>
+        <v>113.288781174082</v>
       </c>
       <c r="E213" t="n">
-        <v>112.2612457275391</v>
+        <v>114.6754608154297</v>
       </c>
       <c r="F213" t="n">
-        <v>16467900</v>
+        <v>20777600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>113.4883080789502</v>
+        <v>116.6806604264181</v>
       </c>
       <c r="C214" t="n">
-        <v>115.3139316886614</v>
+        <v>117.8079588775203</v>
       </c>
       <c r="D214" t="n">
-        <v>113.288781174082</v>
+        <v>113.3286845943574</v>
       </c>
       <c r="E214" t="n">
-        <v>114.6754608154297</v>
+        <v>113.967155456543</v>
       </c>
       <c r="F214" t="n">
-        <v>20777600</v>
+        <v>28289800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>116.6806604264181</v>
+        <v>113.6878284476981</v>
       </c>
       <c r="C215" t="n">
-        <v>117.8079588775203</v>
+        <v>114.1267800313856</v>
       </c>
       <c r="D215" t="n">
-        <v>113.3286845943574</v>
+        <v>111.8721754576813</v>
       </c>
       <c r="E215" t="n">
-        <v>113.967155456543</v>
+        <v>111.9320297241211</v>
       </c>
       <c r="F215" t="n">
-        <v>28289800</v>
+        <v>17738900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>113.6878284476981</v>
+        <v>111.2436859074791</v>
       </c>
       <c r="C216" t="n">
-        <v>114.1267800313856</v>
+        <v>111.5329942219063</v>
       </c>
       <c r="D216" t="n">
-        <v>111.8721754576813</v>
+        <v>109.6275521682845</v>
       </c>
       <c r="E216" t="n">
-        <v>111.9320297241211</v>
+        <v>110.1263580322266</v>
       </c>
       <c r="F216" t="n">
-        <v>17738900</v>
+        <v>22717000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>111.2436859074791</v>
+        <v>109.268405092928</v>
       </c>
       <c r="C217" t="n">
-        <v>111.5329942219063</v>
+        <v>109.737283796026</v>
       </c>
       <c r="D217" t="n">
-        <v>109.6275521682845</v>
+        <v>108.4603420750963</v>
       </c>
       <c r="E217" t="n">
-        <v>110.1263580322266</v>
+        <v>109.0688858032227</v>
       </c>
       <c r="F217" t="n">
-        <v>22717000</v>
+        <v>23494800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>109.268405092928</v>
+        <v>107.25323944858</v>
       </c>
       <c r="C218" t="n">
-        <v>109.737283796026</v>
+        <v>108.3007272005749</v>
       </c>
       <c r="D218" t="n">
-        <v>108.4603420750963</v>
+        <v>106.5349577836844</v>
       </c>
       <c r="E218" t="n">
-        <v>109.0688858032227</v>
+        <v>108.14111328125</v>
       </c>
       <c r="F218" t="n">
-        <v>23494800</v>
+        <v>21516800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>107.25323944858</v>
+        <v>107.8617828177618</v>
       </c>
       <c r="C219" t="n">
-        <v>108.3007272005749</v>
+        <v>109.3382439135796</v>
       </c>
       <c r="D219" t="n">
-        <v>106.5349577836844</v>
+        <v>107.7520449187408</v>
       </c>
       <c r="E219" t="n">
-        <v>108.14111328125</v>
+        <v>109.2085571289062</v>
       </c>
       <c r="F219" t="n">
-        <v>21516800</v>
+        <v>18405900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>107.8617828177618</v>
+        <v>109.6574762821653</v>
       </c>
       <c r="C220" t="n">
-        <v>109.3382439135796</v>
+        <v>112.2412945440321</v>
       </c>
       <c r="D220" t="n">
-        <v>107.7520449187408</v>
+        <v>109.6275491489408</v>
       </c>
       <c r="E220" t="n">
-        <v>109.2085571289062</v>
+        <v>111.4731292724609</v>
       </c>
       <c r="F220" t="n">
-        <v>18405900</v>
+        <v>19008700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>109.6574762821653</v>
+        <v>113.6878264165269</v>
       </c>
       <c r="C221" t="n">
-        <v>112.2412945440321</v>
+        <v>115.7528822947127</v>
       </c>
       <c r="D221" t="n">
-        <v>109.6275491489408</v>
+        <v>112.5704985921816</v>
       </c>
       <c r="E221" t="n">
-        <v>111.4731292724609</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F221" t="n">
-        <v>19008700</v>
+        <v>24867900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>113.6878264165269</v>
+        <v>112.9595787445935</v>
       </c>
       <c r="C222" t="n">
-        <v>115.7528822947127</v>
+        <v>114.4160909468376</v>
       </c>
       <c r="D222" t="n">
-        <v>112.5704985921816</v>
+        <v>112.1814352072651</v>
       </c>
       <c r="E222" t="n">
-        <v>112.8298797607422</v>
+        <v>113.9472122192383</v>
       </c>
       <c r="F222" t="n">
-        <v>24867900</v>
+        <v>23480000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>112.9595787445935</v>
+        <v>111.3434398479761</v>
       </c>
       <c r="C223" t="n">
-        <v>114.4160909468376</v>
+        <v>112.7600466022415</v>
       </c>
       <c r="D223" t="n">
-        <v>112.1814352072651</v>
+        <v>110.1762360128914</v>
       </c>
       <c r="E223" t="n">
-        <v>113.9472122192383</v>
+        <v>110.8346557617188</v>
       </c>
       <c r="F223" t="n">
-        <v>23480000</v>
+        <v>28747000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>111.3434398479761</v>
+        <v>110.2560414658192</v>
       </c>
       <c r="C224" t="n">
-        <v>112.7600466022415</v>
+        <v>111.642728727712</v>
       </c>
       <c r="D224" t="n">
-        <v>110.1762360128914</v>
+        <v>109.6275488363764</v>
       </c>
       <c r="E224" t="n">
-        <v>110.8346557617188</v>
+        <v>110.9344177246094</v>
       </c>
       <c r="F224" t="n">
-        <v>28747000</v>
+        <v>22799100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>110.2560414658192</v>
+        <v>112.8298784424625</v>
       </c>
       <c r="C225" t="n">
-        <v>111.642728727712</v>
+        <v>113.0194270954852</v>
       </c>
       <c r="D225" t="n">
-        <v>109.6275488363764</v>
+        <v>109.8969053059805</v>
       </c>
       <c r="E225" t="n">
-        <v>110.9344177246094</v>
+        <v>110.4455871582031</v>
       </c>
       <c r="F225" t="n">
-        <v>22799100</v>
+        <v>23942500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>112.8298784424625</v>
+        <v>108.7496500450106</v>
       </c>
       <c r="C226" t="n">
-        <v>113.0194270954852</v>
+        <v>111.4132713715266</v>
       </c>
       <c r="D226" t="n">
-        <v>109.8969053059805</v>
+        <v>108.3007202277679</v>
       </c>
       <c r="E226" t="n">
-        <v>110.4455871582031</v>
+        <v>111.2835845947266</v>
       </c>
       <c r="F226" t="n">
-        <v>23942500</v>
+        <v>29620000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>108.7496500450106</v>
+        <v>112.181431315027</v>
       </c>
       <c r="C227" t="n">
-        <v>111.4132713715266</v>
+        <v>112.8897423116165</v>
       </c>
       <c r="D227" t="n">
-        <v>108.3007202277679</v>
+        <v>111.0940382280446</v>
       </c>
       <c r="E227" t="n">
-        <v>111.2835845947266</v>
+        <v>112.0716934204102</v>
       </c>
       <c r="F227" t="n">
-        <v>29620000</v>
+        <v>21446300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>112.181431315027</v>
+        <v>113.7975687180191</v>
       </c>
       <c r="C228" t="n">
-        <v>112.8897423116165</v>
+        <v>114.2863963302149</v>
       </c>
       <c r="D228" t="n">
-        <v>111.0940382280446</v>
+        <v>110.7748064209645</v>
       </c>
       <c r="E228" t="n">
-        <v>112.0716934204102</v>
+        <v>111.8023452758789</v>
       </c>
       <c r="F228" t="n">
-        <v>21446300</v>
+        <v>23203100</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>113.7975687180191</v>
+        <v>110.3458340692701</v>
       </c>
       <c r="C229" t="n">
-        <v>114.2863963302149</v>
+        <v>112.0218220801941</v>
       </c>
       <c r="D229" t="n">
-        <v>110.7748064209645</v>
+        <v>110.2360961700712</v>
       </c>
       <c r="E229" t="n">
-        <v>111.8023452758789</v>
+        <v>111.5828704833984</v>
       </c>
       <c r="F229" t="n">
-        <v>23203100</v>
+        <v>18819300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>110.3458340692701</v>
+        <v>110.8147094920761</v>
       </c>
       <c r="C230" t="n">
-        <v>112.0218220801941</v>
+        <v>112.4308355753539</v>
       </c>
       <c r="D230" t="n">
-        <v>110.2360961700712</v>
+        <v>110.4954740524384</v>
       </c>
       <c r="E230" t="n">
-        <v>111.5828704833984</v>
+        <v>112.3909378051758</v>
       </c>
       <c r="F230" t="n">
-        <v>18819300</v>
+        <v>19144000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>110.8147094920761</v>
+        <v>112.1714606731287</v>
       </c>
       <c r="C231" t="n">
-        <v>112.4308355753539</v>
+        <v>113.069305103701</v>
       </c>
       <c r="D231" t="n">
-        <v>110.4954740524384</v>
+        <v>111.9220577510424</v>
       </c>
       <c r="E231" t="n">
-        <v>112.3909378051758</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F231" t="n">
-        <v>19144000</v>
+        <v>17005800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>112.1714606731287</v>
+        <v>112.1016271407472</v>
       </c>
       <c r="C232" t="n">
-        <v>113.069305103701</v>
+        <v>115.7728384249456</v>
       </c>
       <c r="D232" t="n">
-        <v>111.9220577510424</v>
+        <v>112.011838131802</v>
       </c>
       <c r="E232" t="n">
-        <v>112.989501953125</v>
+        <v>115.7329330444336</v>
       </c>
       <c r="F232" t="n">
-        <v>17005800</v>
+        <v>22054700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>112.1016271407472</v>
+        <v>115.8925486214695</v>
       </c>
       <c r="C233" t="n">
-        <v>115.7728384249456</v>
+        <v>116.0421918977476</v>
       </c>
       <c r="D233" t="n">
-        <v>112.011838131802</v>
+        <v>114.5357961092488</v>
       </c>
       <c r="E233" t="n">
-        <v>115.7329330444336</v>
+        <v>115.4436264038086</v>
       </c>
       <c r="F233" t="n">
-        <v>22054700</v>
+        <v>16822200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>115.8925486214695</v>
+        <v>115.3837731369623</v>
       </c>
       <c r="C234" t="n">
-        <v>116.0421918977476</v>
+        <v>116.1718796839166</v>
       </c>
       <c r="D234" t="n">
-        <v>114.5357961092488</v>
+        <v>114.3662049383982</v>
       </c>
       <c r="E234" t="n">
-        <v>115.4436264038086</v>
+        <v>114.9946975708008</v>
       </c>
       <c r="F234" t="n">
-        <v>16822200</v>
+        <v>14520000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>115.3837731369623</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="C235" t="n">
-        <v>116.1718796839166</v>
+        <v>114.9049142110052</v>
       </c>
       <c r="D235" t="n">
-        <v>114.3662049383982</v>
+        <v>113.6479213564676</v>
       </c>
       <c r="E235" t="n">
-        <v>114.9946975708008</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="F235" t="n">
-        <v>14520000</v>
+        <v>18131100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>114.0569458007812</v>
+        <v>116.0222446904477</v>
       </c>
       <c r="C236" t="n">
-        <v>114.9049142110052</v>
+        <v>116.0322153274834</v>
       </c>
       <c r="D236" t="n">
-        <v>113.6479213564676</v>
+        <v>114.2065916862473</v>
       </c>
       <c r="E236" t="n">
-        <v>114.0569458007812</v>
+        <v>114.9248657226562</v>
       </c>
       <c r="F236" t="n">
-        <v>18131100</v>
+        <v>20675000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>116.0222446904477</v>
+        <v>114.9148971425914</v>
       </c>
       <c r="C237" t="n">
-        <v>116.0322153274834</v>
+        <v>116.590885146559</v>
       </c>
       <c r="D237" t="n">
-        <v>114.2065916862473</v>
+        <v>113.7177585048011</v>
       </c>
       <c r="E237" t="n">
-        <v>114.9248657226562</v>
+        <v>114.0270233154297</v>
       </c>
       <c r="F237" t="n">
-        <v>20675000</v>
+        <v>34286600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>114.9148971425914</v>
+        <v>106.1259298697332</v>
       </c>
       <c r="C238" t="n">
-        <v>116.590885146559</v>
+        <v>106.7444518635443</v>
       </c>
       <c r="D238" t="n">
-        <v>113.7177585048011</v>
+        <v>102.6043617877236</v>
       </c>
       <c r="E238" t="n">
-        <v>114.0270233154297</v>
+        <v>103.5919952392578</v>
       </c>
       <c r="F238" t="n">
-        <v>34286600</v>
+        <v>83633100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>106.1259298697332</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C239" t="n">
-        <v>106.7444518635443</v>
+        <v>104.2799987792969</v>
       </c>
       <c r="D239" t="n">
-        <v>102.6043617877236</v>
+        <v>102.1500015258789</v>
       </c>
       <c r="E239" t="n">
-        <v>103.5919952392578</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="F239" t="n">
-        <v>83633100</v>
+        <v>44454200</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>103.6900024414062</v>
+        <v>104.1399993896484</v>
       </c>
       <c r="C240" t="n">
-        <v>104.2799987792969</v>
+        <v>106.5999984741211</v>
       </c>
       <c r="D240" t="n">
-        <v>102.1500015258789</v>
+        <v>104</v>
       </c>
       <c r="E240" t="n">
-        <v>103.6999969482422</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="F240" t="n">
-        <v>44454200</v>
+        <v>35616300</v>
       </c>
       <c r="G240" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>104.1399993896484</v>
+        <v>105.5800018310547</v>
       </c>
       <c r="C241" t="n">
-        <v>106.5999984741211</v>
+        <v>106.0699996948242</v>
       </c>
       <c r="D241" t="n">
-        <v>104</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="E241" t="n">
-        <v>106.4899978637695</v>
+        <v>105.379997253418</v>
       </c>
       <c r="F241" t="n">
-        <v>35616300</v>
+        <v>27032500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>105.5800018310547</v>
+        <v>105.5100021362305</v>
       </c>
       <c r="C242" t="n">
-        <v>106.0699996948242</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="D242" t="n">
-        <v>104.4000015258789</v>
+        <v>104.0800018310547</v>
       </c>
       <c r="E242" t="n">
-        <v>105.379997253418</v>
+        <v>104.3399963378906</v>
       </c>
       <c r="F242" t="n">
-        <v>27032500</v>
+        <v>28409400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>105.5100021362305</v>
+        <v>103.6100006103516</v>
       </c>
       <c r="C243" t="n">
-        <v>106.0899963378906</v>
+        <v>103.75</v>
       </c>
       <c r="D243" t="n">
-        <v>104.0800018310547</v>
+        <v>102.2699966430664</v>
       </c>
       <c r="E243" t="n">
-        <v>104.3399963378906</v>
+        <v>102.629997253418</v>
       </c>
       <c r="F243" t="n">
-        <v>28409400</v>
+        <v>29816600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>103.6100006103516</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="C244" t="n">
-        <v>103.75</v>
+        <v>103.4000015258789</v>
       </c>
       <c r="D244" t="n">
-        <v>102.2699966430664</v>
+        <v>102.5</v>
       </c>
       <c r="E244" t="n">
-        <v>102.629997253418</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="F244" t="n">
-        <v>29816600</v>
+        <v>19420800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>103.0899963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="C245" t="n">
-        <v>103.4000015258789</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="D245" t="n">
-        <v>102.5</v>
+        <v>102.8399963378906</v>
       </c>
       <c r="E245" t="n">
-        <v>103.0899963378906</v>
+        <v>104.870002746582</v>
       </c>
       <c r="F245" t="n">
-        <v>19420800</v>
+        <v>34188700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>103.0800018310547</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="C246" t="n">
-        <v>104.9899978637695</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D246" t="n">
-        <v>102.8399963378906</v>
+        <v>104.6600036621094</v>
       </c>
       <c r="E246" t="n">
-        <v>104.870002746582</v>
+        <v>105.9199981689453</v>
       </c>
       <c r="F246" t="n">
-        <v>34188700</v>
+        <v>22074600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>105.1100006103516</v>
+        <v>105.9700012207031</v>
       </c>
       <c r="C247" t="n">
-        <v>106.6399993896484</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="D247" t="n">
-        <v>104.6600036621094</v>
+        <v>105.4599990844727</v>
       </c>
       <c r="E247" t="n">
-        <v>105.9199981689453</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="F247" t="n">
-        <v>22074600</v>
+        <v>25181800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>105.9700012207031</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="C248" t="n">
-        <v>106.7799987792969</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="D248" t="n">
-        <v>105.4599990844727</v>
+        <v>106.0199966430664</v>
       </c>
       <c r="E248" t="n">
-        <v>106.0899963378906</v>
+        <v>108.4199981689453</v>
       </c>
       <c r="F248" t="n">
-        <v>25181800</v>
+        <v>25541200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>106.4199981689453</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="C249" t="n">
-        <v>109.3499984741211</v>
+        <v>109.2300033569336</v>
       </c>
       <c r="D249" t="n">
-        <v>106.0199966430664</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="E249" t="n">
-        <v>108.4199981689453</v>
+        <v>107.1399993896484</v>
       </c>
       <c r="F249" t="n">
-        <v>25541200</v>
+        <v>20540500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>108.1999969482422</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>109.2300033569336</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="D250" t="n">
-        <v>106.9300003051758</v>
+        <v>105.6600036621094</v>
       </c>
       <c r="E250" t="n">
-        <v>107.1399993896484</v>
+        <v>106.0500030517578</v>
       </c>
       <c r="F250" t="n">
-        <v>20540500</v>
+        <v>22664800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>106.7799987792969</v>
+        <v>105.6900024414062</v>
       </c>
       <c r="C251" t="n">
-        <v>106.9000015258789</v>
+        <v>106.1500015258789</v>
       </c>
       <c r="D251" t="n">
-        <v>105.6600036621094</v>
+        <v>105.1600036621094</v>
       </c>
       <c r="E251" t="n">
-        <v>106.0500030517578</v>
+        <v>105.8300018310547</v>
       </c>
       <c r="F251" t="n">
-        <v>22664800</v>
+        <v>15460800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>105.6900024414062</v>
+        <v>106.1699981689453</v>
       </c>
       <c r="C252" t="n">
-        <v>106.1500015258789</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="D252" t="n">
-        <v>105.1600036621094</v>
+        <v>105.5899963378906</v>
       </c>
       <c r="E252" t="n">
-        <v>105.8300018310547</v>
+        <v>105.7300033569336</v>
       </c>
       <c r="F252" t="n">
-        <v>15450700</v>
+        <v>17164500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10636,37 +10636,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="D2" t="n">
         <v>105.83</v>
       </c>
-      <c r="D2" t="n">
-        <v>106.05</v>
-      </c>
       <c r="E2" t="n">
-        <v>105.69</v>
+        <v>106.17</v>
       </c>
       <c r="F2" t="n">
-        <v>106.145</v>
+        <v>107.155</v>
       </c>
       <c r="G2" t="n">
-        <v>105.16</v>
+        <v>105.59</v>
       </c>
       <c r="H2" t="n">
-        <v>15347532</v>
+        <v>16410703</v>
       </c>
       <c r="I2" t="n">
-        <v>24445378</v>
+        <v>24330998</v>
       </c>
       <c r="J2" t="n">
-        <v>842203529216</v>
+        <v>841407725568</v>
       </c>
       <c r="K2" t="n">
-        <v>38.48364</v>
+        <v>38.307972</v>
       </c>
       <c r="L2" t="n">
-        <v>32.75984</v>
+        <v>32.728886</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="N2" t="n">
         <v>135.16</v>
@@ -10702,7 +10702,7 @@
         <v>11.848</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.932309999999999</v>
+        <v>8.923870000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.091</v>
@@ -10714,7 +10714,7 @@
         <v>735839977472</v>
       </c>
       <c r="AC2" t="n">
-        <v>909752336384</v>
+        <v>908958957568</v>
       </c>
       <c r="AD2" t="n">
         <v>44073000960</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:38</t>
+          <t>2026-09-11 19:03:14</t>
         </is>
       </c>
     </row>

--- a/data/WMT_data.xlsx
+++ b/data/WMT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>100.1468020683853</v>
+        <v>101.6838656294045</v>
       </c>
       <c r="C2" t="n">
-        <v>101.9218577291584</v>
+        <v>103.1118450857203</v>
       </c>
       <c r="D2" t="n">
-        <v>99.44273097931239</v>
+        <v>101.5053681973651</v>
       </c>
       <c r="E2" t="n">
-        <v>101.7929458618164</v>
+        <v>102.6259307861328</v>
       </c>
       <c r="F2" t="n">
-        <v>15900800</v>
+        <v>11641900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>101.6838580700448</v>
+        <v>102.7845975900895</v>
       </c>
       <c r="C3" t="n">
-        <v>103.111837420202</v>
+        <v>103.1118441401098</v>
       </c>
       <c r="D3" t="n">
-        <v>101.5053606512752</v>
+        <v>102.5466035381176</v>
       </c>
       <c r="E3" t="n">
-        <v>102.6259231567383</v>
+        <v>102.8242645263672</v>
       </c>
       <c r="F3" t="n">
-        <v>11641900</v>
+        <v>10756900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>102.7846052165408</v>
+        <v>102.9829286790064</v>
       </c>
       <c r="C4" t="n">
-        <v>103.1118517908423</v>
+        <v>103.3399235535848</v>
       </c>
       <c r="D4" t="n">
-        <v>102.5466111469101</v>
+        <v>102.2689389298496</v>
       </c>
       <c r="E4" t="n">
-        <v>102.8242721557617</v>
+        <v>102.5565185546875</v>
       </c>
       <c r="F4" t="n">
-        <v>10756900</v>
+        <v>14481900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>102.9829286790064</v>
+        <v>102.8639217581119</v>
       </c>
       <c r="C5" t="n">
-        <v>103.3399235535848</v>
+        <v>105.2240475012655</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2689389298496</v>
+        <v>102.8639217581119</v>
       </c>
       <c r="E5" t="n">
-        <v>102.5565185546875</v>
+        <v>103.3994064331055</v>
       </c>
       <c r="F5" t="n">
-        <v>14481900</v>
+        <v>25382000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>102.8639369378787</v>
+        <v>102.9135133062164</v>
       </c>
       <c r="C6" t="n">
-        <v>105.2240630293193</v>
+        <v>103.7663335538345</v>
       </c>
       <c r="D6" t="n">
-        <v>102.8639369378787</v>
+        <v>101.2673770004686</v>
       </c>
       <c r="E6" t="n">
-        <v>103.3994216918945</v>
+        <v>102.7350158691406</v>
       </c>
       <c r="F6" t="n">
-        <v>25382000</v>
+        <v>14869400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>102.9135133062164</v>
+        <v>102.9432629724532</v>
       </c>
       <c r="C7" t="n">
-        <v>103.7663335538345</v>
+        <v>103.0721824132953</v>
       </c>
       <c r="D7" t="n">
-        <v>101.2673770004686</v>
+        <v>101.2376224547773</v>
       </c>
       <c r="E7" t="n">
-        <v>102.7350158691406</v>
+        <v>101.4756240844727</v>
       </c>
       <c r="F7" t="n">
-        <v>14869400</v>
+        <v>34791600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>102.9432629724532</v>
+        <v>101.5946190816179</v>
       </c>
       <c r="C8" t="n">
-        <v>103.0721824132953</v>
+        <v>102.338357164399</v>
       </c>
       <c r="D8" t="n">
-        <v>101.2376224547773</v>
+        <v>101.0690453802971</v>
       </c>
       <c r="E8" t="n">
-        <v>101.4756240844727</v>
+        <v>101.9615325927734</v>
       </c>
       <c r="F8" t="n">
-        <v>34791600</v>
+        <v>12861900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>101.5946190816179</v>
+        <v>101.5549573599091</v>
       </c>
       <c r="C9" t="n">
-        <v>102.338357164399</v>
+        <v>101.822699734613</v>
       </c>
       <c r="D9" t="n">
-        <v>101.0690453802971</v>
+        <v>100.4839727297038</v>
       </c>
       <c r="E9" t="n">
-        <v>101.9615325927734</v>
+        <v>101.6640319824219</v>
       </c>
       <c r="F9" t="n">
-        <v>12861900</v>
+        <v>13158700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>101.5549649811181</v>
+        <v>102.1796932441854</v>
       </c>
       <c r="C10" t="n">
-        <v>101.8227073759147</v>
+        <v>102.606103365375</v>
       </c>
       <c r="D10" t="n">
-        <v>100.4839802705406</v>
+        <v>101.6243712503365</v>
       </c>
       <c r="E10" t="n">
-        <v>101.6640396118164</v>
+        <v>101.8722839355469</v>
       </c>
       <c r="F10" t="n">
-        <v>13158700</v>
+        <v>11391800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>102.1796932441854</v>
+        <v>102.3581921548903</v>
       </c>
       <c r="C11" t="n">
-        <v>102.606103365375</v>
+        <v>102.645771781761</v>
       </c>
       <c r="D11" t="n">
-        <v>101.6243712503365</v>
+        <v>101.7235362768635</v>
       </c>
       <c r="E11" t="n">
-        <v>101.8722839355469</v>
+        <v>102.1896133422852</v>
       </c>
       <c r="F11" t="n">
-        <v>11391800</v>
+        <v>13366700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>102.3581921548903</v>
+        <v>102.0210222421301</v>
       </c>
       <c r="C12" t="n">
-        <v>102.645771781761</v>
+        <v>102.6259297800171</v>
       </c>
       <c r="D12" t="n">
-        <v>101.7235362768635</v>
+        <v>101.6144493855062</v>
       </c>
       <c r="E12" t="n">
-        <v>102.1896133422852</v>
+        <v>102.2986907958984</v>
       </c>
       <c r="F12" t="n">
-        <v>13366700</v>
+        <v>11859300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>102.0210222421301</v>
+        <v>102.1896196669732</v>
       </c>
       <c r="C13" t="n">
-        <v>102.6259297800171</v>
+        <v>102.4474434319635</v>
       </c>
       <c r="D13" t="n">
-        <v>101.6144493855062</v>
+        <v>101.2277171644534</v>
       </c>
       <c r="E13" t="n">
-        <v>102.2986907958984</v>
+        <v>102.219367980957</v>
       </c>
       <c r="F13" t="n">
-        <v>11859300</v>
+        <v>15477200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>102.189612039799</v>
+        <v>102.1400273017734</v>
       </c>
       <c r="C14" t="n">
-        <v>102.447435785546</v>
+        <v>103.0721814282683</v>
       </c>
       <c r="D14" t="n">
-        <v>101.2277096090732</v>
+        <v>101.8623663021439</v>
       </c>
       <c r="E14" t="n">
-        <v>102.2193603515625</v>
+        <v>102.1995239257812</v>
       </c>
       <c r="F14" t="n">
-        <v>15477200</v>
+        <v>13873400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>102.1400273017734</v>
+        <v>101.7036925151355</v>
       </c>
       <c r="C15" t="n">
-        <v>103.0721814282683</v>
+        <v>102.0011907489098</v>
       </c>
       <c r="D15" t="n">
-        <v>101.8623663021439</v>
+        <v>99.71048007220848</v>
       </c>
       <c r="E15" t="n">
-        <v>102.1995239257812</v>
+        <v>101.1087036132812</v>
       </c>
       <c r="F15" t="n">
-        <v>13873400</v>
+        <v>16142800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>101.7036925151355</v>
+        <v>100.6029707835176</v>
       </c>
       <c r="C16" t="n">
-        <v>102.0011907489098</v>
+        <v>101.2872122575589</v>
       </c>
       <c r="D16" t="n">
-        <v>99.71048007220848</v>
+        <v>99.036168267113</v>
       </c>
       <c r="E16" t="n">
-        <v>101.1087036132812</v>
+        <v>100.8508834838867</v>
       </c>
       <c r="F16" t="n">
-        <v>16142800</v>
+        <v>15605400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>100.6029631728777</v>
+        <v>100.6128887355816</v>
       </c>
       <c r="C17" t="n">
-        <v>101.287204595156</v>
+        <v>101.9615344218062</v>
       </c>
       <c r="D17" t="n">
-        <v>99.03616077500212</v>
+        <v>100.3550574105311</v>
       </c>
       <c r="E17" t="n">
-        <v>100.8508758544922</v>
+        <v>101.2177963256836</v>
       </c>
       <c r="F17" t="n">
-        <v>15605400</v>
+        <v>11867500</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>100.6128811517826</v>
+        <v>101.0293759821222</v>
       </c>
       <c r="C18" t="n">
-        <v>101.9615267363516</v>
+        <v>102.2094427990993</v>
       </c>
       <c r="D18" t="n">
-        <v>100.3550498461664</v>
+        <v>100.7318852956682</v>
       </c>
       <c r="E18" t="n">
-        <v>101.2177886962891</v>
+        <v>101.842529296875</v>
       </c>
       <c r="F18" t="n">
-        <v>11867500</v>
+        <v>13303600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>101.0293759821222</v>
+        <v>101.5252009905733</v>
       </c>
       <c r="C19" t="n">
-        <v>102.2094427990993</v>
+        <v>102.387939866122</v>
       </c>
       <c r="D19" t="n">
-        <v>100.7318852956682</v>
+        <v>100.1071401164341</v>
       </c>
       <c r="E19" t="n">
-        <v>101.842529296875</v>
+        <v>102.3780212402344</v>
       </c>
       <c r="F19" t="n">
-        <v>13303600</v>
+        <v>15538900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>101.5252085564141</v>
+        <v>102.1598639225969</v>
       </c>
       <c r="C20" t="n">
-        <v>102.3879474962557</v>
+        <v>102.3978655661736</v>
       </c>
       <c r="D20" t="n">
-        <v>100.1071475765985</v>
+        <v>101.2971325531412</v>
       </c>
       <c r="E20" t="n">
-        <v>102.3780288696289</v>
+        <v>102.0408706665039</v>
       </c>
       <c r="F20" t="n">
-        <v>15538900</v>
+        <v>13584100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>102.1598562843055</v>
+        <v>102.2689336388612</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3978579100873</v>
+        <v>102.5862615592142</v>
       </c>
       <c r="D21" t="n">
-        <v>101.2971249793545</v>
+        <v>99.53198316295229</v>
       </c>
       <c r="E21" t="n">
-        <v>102.0408630371094</v>
+        <v>100.9202880859375</v>
       </c>
       <c r="F21" t="n">
-        <v>13584100</v>
+        <v>19508000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>102.2689413702109</v>
+        <v>101.1979612604356</v>
       </c>
       <c r="C22" t="n">
-        <v>102.5862693145533</v>
+        <v>102.7647636830698</v>
       </c>
       <c r="D22" t="n">
-        <v>99.53199068739345</v>
+        <v>100.6723800119242</v>
       </c>
       <c r="E22" t="n">
-        <v>100.920295715332</v>
+        <v>100.9897079467773</v>
       </c>
       <c r="F22" t="n">
-        <v>19508000</v>
+        <v>18519400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>101.1979612604356</v>
+        <v>100.523634106908</v>
       </c>
       <c r="C23" t="n">
-        <v>102.7647636830698</v>
+        <v>101.5946111121733</v>
       </c>
       <c r="D23" t="n">
-        <v>100.6723800119242</v>
+        <v>100.2261358708544</v>
       </c>
       <c r="E23" t="n">
-        <v>100.9897079467773</v>
+        <v>101.2673721313477</v>
       </c>
       <c r="F23" t="n">
-        <v>18519400</v>
+        <v>10871200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>100.523634106908</v>
+        <v>103.1812604018871</v>
       </c>
       <c r="C24" t="n">
-        <v>101.5946111121733</v>
+        <v>107.0189438447403</v>
       </c>
       <c r="D24" t="n">
-        <v>100.2261358708544</v>
+        <v>102.030941935604</v>
       </c>
       <c r="E24" t="n">
-        <v>101.2673721313477</v>
+        <v>106.3148727416992</v>
       </c>
       <c r="F24" t="n">
-        <v>10871200</v>
+        <v>30859500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>103.1812604018871</v>
+        <v>106.4239604021063</v>
       </c>
       <c r="C25" t="n">
-        <v>107.0189438447403</v>
+        <v>108.645256009938</v>
       </c>
       <c r="D25" t="n">
-        <v>102.030941935604</v>
+        <v>106.4041307155994</v>
       </c>
       <c r="E25" t="n">
-        <v>106.3148727416992</v>
+        <v>108.1196823120117</v>
       </c>
       <c r="F25" t="n">
-        <v>30859500</v>
+        <v>21416300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>106.4239528923693</v>
+        <v>108.288256950121</v>
       </c>
       <c r="C26" t="n">
-        <v>108.6452483434567</v>
+        <v>108.6650890704717</v>
       </c>
       <c r="D26" t="n">
-        <v>106.4041232072616</v>
+        <v>104.7778200152908</v>
       </c>
       <c r="E26" t="n">
-        <v>108.1196746826172</v>
+        <v>105.5810546875</v>
       </c>
       <c r="F26" t="n">
-        <v>21416300</v>
+        <v>16366200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>108.2882647751407</v>
+        <v>106.2752063382308</v>
       </c>
       <c r="C27" t="n">
-        <v>108.6650969227217</v>
+        <v>107.2966053740443</v>
       </c>
       <c r="D27" t="n">
-        <v>104.7778275866427</v>
+        <v>105.3331411761509</v>
       </c>
       <c r="E27" t="n">
-        <v>105.5810623168945</v>
+        <v>106.8305358886719</v>
       </c>
       <c r="F27" t="n">
-        <v>16366200</v>
+        <v>13735600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>106.275213927966</v>
+        <v>106.9495278840114</v>
       </c>
       <c r="C28" t="n">
-        <v>107.2966130367236</v>
+        <v>107.3461896823507</v>
       </c>
       <c r="D28" t="n">
-        <v>105.3331486986077</v>
+        <v>105.7198831182847</v>
       </c>
       <c r="E28" t="n">
-        <v>106.8305435180664</v>
+        <v>106.1562118530273</v>
       </c>
       <c r="F28" t="n">
-        <v>13735600</v>
+        <v>10581200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>106.9495278840114</v>
+        <v>106.4338780925878</v>
       </c>
       <c r="C29" t="n">
-        <v>107.3461896823507</v>
+        <v>106.5826272200147</v>
       </c>
       <c r="D29" t="n">
-        <v>105.7198831182847</v>
+        <v>105.2934782032414</v>
       </c>
       <c r="E29" t="n">
-        <v>106.1562118530273</v>
+        <v>105.3331451416016</v>
       </c>
       <c r="F29" t="n">
-        <v>10581200</v>
+        <v>10899700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>106.4338780925878</v>
+        <v>105.6603826132251</v>
       </c>
       <c r="C30" t="n">
-        <v>106.5826272200147</v>
+        <v>106.8701900834392</v>
       </c>
       <c r="D30" t="n">
-        <v>105.2934782032414</v>
+        <v>104.7778141163466</v>
       </c>
       <c r="E30" t="n">
-        <v>105.3331451416016</v>
+        <v>106.2454528808594</v>
       </c>
       <c r="F30" t="n">
-        <v>10899700</v>
+        <v>12296500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>105.6603826132251</v>
+        <v>106.4537107234644</v>
       </c>
       <c r="C31" t="n">
-        <v>106.8701900834392</v>
+        <v>106.6718751076324</v>
       </c>
       <c r="D31" t="n">
-        <v>104.7778141163466</v>
+        <v>104.8968192868145</v>
       </c>
       <c r="E31" t="n">
-        <v>106.2454528808594</v>
+        <v>105.9678039550781</v>
       </c>
       <c r="F31" t="n">
-        <v>12296500</v>
+        <v>11408200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>106.4537107234644</v>
+        <v>106.1760412293909</v>
       </c>
       <c r="C32" t="n">
-        <v>106.6718751076324</v>
+        <v>106.2752047872635</v>
       </c>
       <c r="D32" t="n">
-        <v>104.8968192868145</v>
+        <v>104.6290685426336</v>
       </c>
       <c r="E32" t="n">
-        <v>105.9678039550781</v>
+        <v>105.2835540771484</v>
       </c>
       <c r="F32" t="n">
-        <v>11408200</v>
+        <v>10318000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>106.1760412293909</v>
+        <v>105.4521374991914</v>
       </c>
       <c r="C33" t="n">
-        <v>106.2752047872635</v>
+        <v>105.4719747510511</v>
       </c>
       <c r="D33" t="n">
-        <v>104.6290685426336</v>
+        <v>103.2804274936261</v>
       </c>
       <c r="E33" t="n">
-        <v>105.2835540771484</v>
+        <v>103.5977554321289</v>
       </c>
       <c r="F33" t="n">
-        <v>10318000</v>
+        <v>16375900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>105.4521374991914</v>
+        <v>103.1911775964564</v>
       </c>
       <c r="C34" t="n">
-        <v>105.4719747510511</v>
+        <v>103.2705114745084</v>
       </c>
       <c r="D34" t="n">
-        <v>103.2804274936261</v>
+        <v>102.1896157574061</v>
       </c>
       <c r="E34" t="n">
-        <v>103.5977554321289</v>
+        <v>102.3086090087891</v>
       </c>
       <c r="F34" t="n">
-        <v>16375900</v>
+        <v>13323000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>103.1911699012466</v>
+        <v>102.0507776911747</v>
       </c>
       <c r="C35" t="n">
-        <v>103.2705037733825</v>
+        <v>102.8044267797345</v>
       </c>
       <c r="D35" t="n">
-        <v>102.1896081368852</v>
+        <v>101.257454100834</v>
       </c>
       <c r="E35" t="n">
-        <v>102.3086013793945</v>
+        <v>101.6045303344727</v>
       </c>
       <c r="F35" t="n">
-        <v>13323000</v>
+        <v>11986400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>102.0507776911747</v>
+        <v>101.3467013373431</v>
       </c>
       <c r="C36" t="n">
-        <v>102.8044267797345</v>
+        <v>102.5069384385963</v>
       </c>
       <c r="D36" t="n">
-        <v>101.257454100834</v>
+        <v>101.1087072811068</v>
       </c>
       <c r="E36" t="n">
-        <v>101.6045303344727</v>
+        <v>101.3764572143555</v>
       </c>
       <c r="F36" t="n">
-        <v>11986400</v>
+        <v>14065100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>101.3467013373431</v>
+        <v>100.8508753833576</v>
       </c>
       <c r="C37" t="n">
-        <v>102.5069384385963</v>
+        <v>101.2475371852267</v>
       </c>
       <c r="D37" t="n">
-        <v>101.1087072811068</v>
+        <v>99.34356961508874</v>
       </c>
       <c r="E37" t="n">
-        <v>101.3764572143555</v>
+        <v>100.3352203369141</v>
       </c>
       <c r="F37" t="n">
-        <v>14065100</v>
+        <v>20237000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>100.8508753833576</v>
+        <v>99.97822306298148</v>
       </c>
       <c r="C38" t="n">
-        <v>101.2475371852267</v>
+        <v>100.9500440758614</v>
       </c>
       <c r="D38" t="n">
-        <v>99.34356961508874</v>
+        <v>99.56173158561626</v>
       </c>
       <c r="E38" t="n">
-        <v>100.3352203369141</v>
+        <v>100.7417907714844</v>
       </c>
       <c r="F38" t="n">
-        <v>20237000</v>
+        <v>14811700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>99.97823063454936</v>
+        <v>101.2772919319017</v>
       </c>
       <c r="C39" t="n">
-        <v>100.9500517210274</v>
+        <v>101.763206263773</v>
       </c>
       <c r="D39" t="n">
-        <v>99.56173912564235</v>
+        <v>100.6128877218267</v>
       </c>
       <c r="E39" t="n">
-        <v>100.7417984008789</v>
+        <v>101.4161224365234</v>
       </c>
       <c r="F39" t="n">
-        <v>14811700</v>
+        <v>12636400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>101.2772919319017</v>
+        <v>100.89054510776</v>
       </c>
       <c r="C40" t="n">
-        <v>101.763206263773</v>
+        <v>101.8226992330539</v>
       </c>
       <c r="D40" t="n">
-        <v>100.6128877218267</v>
+        <v>100.0079765462054</v>
       </c>
       <c r="E40" t="n">
-        <v>101.4161224365234</v>
+        <v>100.622802734375</v>
       </c>
       <c r="F40" t="n">
-        <v>12636400</v>
+        <v>13356800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>100.8905527574553</v>
+        <v>100.4938818739751</v>
       </c>
       <c r="C41" t="n">
-        <v>101.8227069534267</v>
+        <v>101.0789597419063</v>
       </c>
       <c r="D41" t="n">
-        <v>100.0079841289827</v>
+        <v>99.19482183188099</v>
       </c>
       <c r="E41" t="n">
-        <v>100.6228103637695</v>
+        <v>100.8310470581055</v>
       </c>
       <c r="F41" t="n">
-        <v>13356800</v>
+        <v>14866000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>100.4938818739751</v>
+        <v>101.2772857883956</v>
       </c>
       <c r="C42" t="n">
-        <v>101.0789597419063</v>
+        <v>102.1102763312919</v>
       </c>
       <c r="D42" t="n">
-        <v>99.19482183188099</v>
+        <v>100.8806315510774</v>
       </c>
       <c r="E42" t="n">
-        <v>100.8310470581055</v>
+        <v>101.7334442138672</v>
       </c>
       <c r="F42" t="n">
-        <v>14866000</v>
+        <v>17248700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>101.2772857883956</v>
+        <v>101.2971227463208</v>
       </c>
       <c r="C43" t="n">
-        <v>102.1102763312919</v>
+        <v>101.8127777927579</v>
       </c>
       <c r="D43" t="n">
-        <v>100.8806315510774</v>
+        <v>100.7517118230459</v>
       </c>
       <c r="E43" t="n">
-        <v>101.7334442138672</v>
+        <v>101.5648651123047</v>
       </c>
       <c r="F43" t="n">
-        <v>17248700</v>
+        <v>14507600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>101.2971227463208</v>
+        <v>101.6442008637206</v>
       </c>
       <c r="C44" t="n">
-        <v>101.8127777927579</v>
+        <v>102.8738456630921</v>
       </c>
       <c r="D44" t="n">
-        <v>100.7517118230459</v>
+        <v>101.4657034278687</v>
       </c>
       <c r="E44" t="n">
-        <v>101.5648651123047</v>
+        <v>102.5763549804688</v>
       </c>
       <c r="F44" t="n">
-        <v>14507600</v>
+        <v>13182100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>101.6442008637206</v>
+        <v>102.4871024796954</v>
       </c>
       <c r="C45" t="n">
-        <v>102.8738456630921</v>
+        <v>102.7350151647289</v>
       </c>
       <c r="D45" t="n">
-        <v>101.4657034278687</v>
+        <v>101.8028686136755</v>
       </c>
       <c r="E45" t="n">
         <v>102.5763549804688</v>
       </c>
       <c r="F45" t="n">
-        <v>13182100</v>
+        <v>12084400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>102.4871024796954</v>
+        <v>102.7251048596608</v>
       </c>
       <c r="C46" t="n">
-        <v>102.7350151647289</v>
+        <v>103.062270072778</v>
       </c>
       <c r="D46" t="n">
-        <v>101.8028686136755</v>
+        <v>101.1682133741703</v>
       </c>
       <c r="E46" t="n">
-        <v>102.5763549804688</v>
+        <v>101.6838760375977</v>
       </c>
       <c r="F46" t="n">
-        <v>12084400</v>
+        <v>18088500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>102.7250971521424</v>
+        <v>99.36339681584856</v>
       </c>
       <c r="C47" t="n">
-        <v>103.0622623399618</v>
+        <v>101.6342778199242</v>
       </c>
       <c r="D47" t="n">
-        <v>101.1682057834663</v>
+        <v>98.05441819840043</v>
       </c>
       <c r="E47" t="n">
-        <v>101.6838684082031</v>
+        <v>101.6243667602539</v>
       </c>
       <c r="F47" t="n">
-        <v>18088500</v>
+        <v>23424200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>99.36339681584856</v>
+        <v>101.7235253155623</v>
       </c>
       <c r="C48" t="n">
-        <v>101.6342778199242</v>
+        <v>102.4573446768896</v>
       </c>
       <c r="D48" t="n">
-        <v>98.05441819840043</v>
+        <v>101.2475296754861</v>
       </c>
       <c r="E48" t="n">
-        <v>101.6243667602539</v>
+        <v>102.0904312133789</v>
       </c>
       <c r="F48" t="n">
-        <v>23424200</v>
+        <v>15289400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>101.7235329175373</v>
+        <v>102.1201932202399</v>
       </c>
       <c r="C49" t="n">
-        <v>102.4573523337042</v>
+        <v>102.4771805146163</v>
       </c>
       <c r="D49" t="n">
-        <v>101.2475372418891</v>
+        <v>100.5335460351719</v>
       </c>
       <c r="E49" t="n">
-        <v>102.0904388427734</v>
+        <v>100.5434646606445</v>
       </c>
       <c r="F49" t="n">
-        <v>15289400</v>
+        <v>17604500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>102.1201932202399</v>
+        <v>100.7318761079755</v>
       </c>
       <c r="C50" t="n">
-        <v>102.4771805146163</v>
+        <v>100.8607879704448</v>
       </c>
       <c r="D50" t="n">
-        <v>100.5335460351719</v>
+        <v>98.84773833617163</v>
       </c>
       <c r="E50" t="n">
-        <v>100.5434646606445</v>
+        <v>99.76997375488281</v>
       </c>
       <c r="F50" t="n">
-        <v>17604500</v>
+        <v>22157000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>100.7318761079755</v>
+        <v>103.0721824077765</v>
       </c>
       <c r="C51" t="n">
-        <v>100.8607879704448</v>
+        <v>107.0090371351957</v>
       </c>
       <c r="D51" t="n">
-        <v>98.84773833617163</v>
+        <v>101.8227003318746</v>
       </c>
       <c r="E51" t="n">
-        <v>99.76997375488281</v>
+        <v>106.2157135009766</v>
       </c>
       <c r="F51" t="n">
-        <v>22157000</v>
+        <v>50375900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>103.0721824077765</v>
+        <v>107.0784532434011</v>
       </c>
       <c r="C52" t="n">
-        <v>107.0090371351957</v>
+        <v>107.247032058172</v>
       </c>
       <c r="D52" t="n">
-        <v>101.8227003318746</v>
+        <v>103.8456696217535</v>
       </c>
       <c r="E52" t="n">
-        <v>106.2157135009766</v>
+        <v>104.4406585693359</v>
       </c>
       <c r="F52" t="n">
-        <v>50375900</v>
+        <v>41420800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>107.0784532434011</v>
+        <v>104.4803264037246</v>
       </c>
       <c r="C53" t="n">
-        <v>107.247032058172</v>
+        <v>105.382724676061</v>
       </c>
       <c r="D53" t="n">
-        <v>103.8456696217535</v>
+        <v>102.8936866746697</v>
       </c>
       <c r="E53" t="n">
-        <v>104.4406585693359</v>
+        <v>103.1911773681641</v>
       </c>
       <c r="F53" t="n">
-        <v>41420800</v>
+        <v>42519200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>104.4803186790174</v>
+        <v>103.7365763126644</v>
       </c>
       <c r="C54" t="n">
-        <v>105.3827168846354</v>
+        <v>106.5231122506693</v>
       </c>
       <c r="D54" t="n">
-        <v>102.89367906727</v>
+        <v>103.3597517849156</v>
       </c>
       <c r="E54" t="n">
-        <v>103.1911697387695</v>
+        <v>106.1066207885742</v>
       </c>
       <c r="F54" t="n">
-        <v>42519200</v>
+        <v>20212900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>103.7365837716454</v>
+        <v>106.3049641152269</v>
       </c>
       <c r="C55" t="n">
-        <v>106.5231199100109</v>
+        <v>108.6750089527716</v>
       </c>
       <c r="D55" t="n">
-        <v>103.3597592168018</v>
+        <v>106.2752158013515</v>
       </c>
       <c r="E55" t="n">
-        <v>106.1066284179688</v>
+        <v>108.1891021728516</v>
       </c>
       <c r="F55" t="n">
-        <v>20212900</v>
+        <v>17783300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>106.3049641152269</v>
+        <v>108.3874371009857</v>
       </c>
       <c r="C56" t="n">
-        <v>108.6750089527716</v>
+        <v>109.7757421893681</v>
       </c>
       <c r="D56" t="n">
-        <v>106.2752158013515</v>
+        <v>108.0899388302207</v>
       </c>
       <c r="E56" t="n">
-        <v>108.1891021728516</v>
+        <v>109.5873336791992</v>
       </c>
       <c r="F56" t="n">
-        <v>17783300</v>
+        <v>9846500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>108.3874295551272</v>
+        <v>109.587327840119</v>
       </c>
       <c r="C57" t="n">
-        <v>109.7757345468567</v>
+        <v>110.8268912927673</v>
       </c>
       <c r="D57" t="n">
-        <v>108.0899313050738</v>
+        <v>109.4385787126623</v>
       </c>
       <c r="E57" t="n">
-        <v>109.5873260498047</v>
+        <v>110.5988082885742</v>
       </c>
       <c r="F57" t="n">
-        <v>9846500</v>
+        <v>17236800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>109.587327840119</v>
+        <v>110.5393119248386</v>
       </c>
       <c r="C58" t="n">
-        <v>110.8268912927673</v>
+        <v>111.7094601295289</v>
       </c>
       <c r="D58" t="n">
-        <v>109.4385787126623</v>
+        <v>109.8649891023782</v>
       </c>
       <c r="E58" t="n">
-        <v>110.5988082885742</v>
+        <v>111.4714660644531</v>
       </c>
       <c r="F58" t="n">
-        <v>17236800</v>
+        <v>18711800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>110.5393119248386</v>
+        <v>111.560708766128</v>
       </c>
       <c r="C59" t="n">
-        <v>111.7094601295289</v>
+        <v>113.9307534404373</v>
       </c>
       <c r="D59" t="n">
-        <v>109.8649891023782</v>
+        <v>111.2830477681546</v>
       </c>
       <c r="E59" t="n">
-        <v>111.4714660644531</v>
+        <v>113.4547653198242</v>
       </c>
       <c r="F59" t="n">
-        <v>18711800</v>
+        <v>24478300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>111.560708766128</v>
+        <v>112.6713570329028</v>
       </c>
       <c r="C60" t="n">
-        <v>113.9307534404373</v>
+        <v>113.9307501128403</v>
       </c>
       <c r="D60" t="n">
-        <v>111.2830477681546</v>
+        <v>112.2151986115989</v>
       </c>
       <c r="E60" t="n">
-        <v>113.4547653198242</v>
+        <v>113.8811645507812</v>
       </c>
       <c r="F60" t="n">
-        <v>24478300</v>
+        <v>25905100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>112.6713570329028</v>
+        <v>113.7720935914494</v>
       </c>
       <c r="C61" t="n">
-        <v>113.9307501128403</v>
+        <v>115.2992290848131</v>
       </c>
       <c r="D61" t="n">
-        <v>112.2151986115989</v>
+        <v>113.7225080277957</v>
       </c>
       <c r="E61" t="n">
-        <v>113.8811645507812</v>
+        <v>114.1489181518555</v>
       </c>
       <c r="F61" t="n">
-        <v>25905100</v>
+        <v>23956400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>113.7720859872408</v>
+        <v>113.6134239095882</v>
       </c>
       <c r="C62" t="n">
-        <v>115.299221378535</v>
+        <v>114.0299154007005</v>
       </c>
       <c r="D62" t="n">
-        <v>113.7225004269012</v>
+        <v>111.3623800798857</v>
       </c>
       <c r="E62" t="n">
-        <v>114.1489105224609</v>
+        <v>112.6118545532227</v>
       </c>
       <c r="F62" t="n">
-        <v>23956400</v>
+        <v>22700700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>113.6134239095882</v>
+        <v>112.9985942054707</v>
       </c>
       <c r="C63" t="n">
-        <v>114.0299154007005</v>
+        <v>114.7538201807431</v>
       </c>
       <c r="D63" t="n">
-        <v>111.3623800798857</v>
+        <v>112.0763587521143</v>
       </c>
       <c r="E63" t="n">
-        <v>112.6118545532227</v>
+        <v>114.0993270874023</v>
       </c>
       <c r="F63" t="n">
-        <v>22700700</v>
+        <v>24326700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>112.9986017612633</v>
+        <v>114.3869191950181</v>
       </c>
       <c r="C64" t="n">
-        <v>114.7538278539011</v>
+        <v>115.259576748144</v>
       </c>
       <c r="D64" t="n">
-        <v>112.0763662462405</v>
+        <v>112.0466226827729</v>
       </c>
       <c r="E64" t="n">
-        <v>114.0993347167969</v>
+        <v>112.2350387573242</v>
       </c>
       <c r="F64" t="n">
-        <v>24326700</v>
+        <v>22859600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>114.3869114193454</v>
+        <v>112.1953625812108</v>
       </c>
       <c r="C65" t="n">
-        <v>115.2595689131506</v>
+        <v>114.9025723932263</v>
       </c>
       <c r="D65" t="n">
-        <v>112.0466150661863</v>
+        <v>111.9077829626674</v>
       </c>
       <c r="E65" t="n">
-        <v>112.2350311279297</v>
+        <v>114.5554885864258</v>
       </c>
       <c r="F65" t="n">
-        <v>22859600</v>
+        <v>21586600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>112.1953625812108</v>
+        <v>114.5306574399956</v>
       </c>
       <c r="C66" t="n">
-        <v>114.9025723932263</v>
+        <v>116.2099582668437</v>
       </c>
       <c r="D66" t="n">
-        <v>111.9077829626674</v>
+        <v>114.2921706587026</v>
       </c>
       <c r="E66" t="n">
-        <v>114.5554885864258</v>
+        <v>115.961540222168</v>
       </c>
       <c r="F66" t="n">
-        <v>21586600</v>
+        <v>19092400</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>114.5306574399956</v>
+        <v>116.1900931187251</v>
       </c>
       <c r="C67" t="n">
-        <v>116.2099582668437</v>
+        <v>116.7067993380155</v>
       </c>
       <c r="D67" t="n">
-        <v>114.2921706587026</v>
+        <v>114.9082550437471</v>
       </c>
       <c r="E67" t="n">
-        <v>115.961540222168</v>
+        <v>116.0509796142578</v>
       </c>
       <c r="F67" t="n">
-        <v>19092400</v>
+        <v>18713700</v>
       </c>
       <c r="G67" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>116.190085480185</v>
+        <v>115.8423072543707</v>
       </c>
       <c r="C68" t="n">
-        <v>116.7067916655062</v>
+        <v>116.140404366624</v>
       </c>
       <c r="D68" t="n">
-        <v>114.9082474894773</v>
+        <v>114.2226167114376</v>
       </c>
       <c r="E68" t="n">
-        <v>116.0509719848633</v>
+        <v>114.6896438598633</v>
       </c>
       <c r="F68" t="n">
-        <v>18713700</v>
+        <v>19642300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>115.8423072543707</v>
+        <v>114.4710352169006</v>
       </c>
       <c r="C69" t="n">
-        <v>116.140404366624</v>
+        <v>115.6535075692186</v>
       </c>
       <c r="D69" t="n">
-        <v>114.2226167114376</v>
+        <v>114.3418605591895</v>
       </c>
       <c r="E69" t="n">
-        <v>114.6896438598633</v>
+        <v>114.9281311035156</v>
       </c>
       <c r="F69" t="n">
-        <v>19642300</v>
+        <v>16177800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>114.4710352169006</v>
+        <v>114.2822395916168</v>
       </c>
       <c r="C70" t="n">
-        <v>115.6535075692186</v>
+        <v>115.7429389097976</v>
       </c>
       <c r="D70" t="n">
-        <v>114.3418605591895</v>
+        <v>113.8847692032296</v>
       </c>
       <c r="E70" t="n">
-        <v>114.9281311035156</v>
+        <v>114.1033782958984</v>
       </c>
       <c r="F70" t="n">
-        <v>16177800</v>
+        <v>21476700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>114.2822472329707</v>
+        <v>114.4114079547907</v>
       </c>
       <c r="C71" t="n">
-        <v>115.7429466488196</v>
+        <v>114.5505214459093</v>
       </c>
       <c r="D71" t="n">
-        <v>113.8847768180071</v>
+        <v>112.81159522581</v>
       </c>
       <c r="E71" t="n">
-        <v>114.103385925293</v>
+        <v>113.636344909668</v>
       </c>
       <c r="F71" t="n">
-        <v>21476700</v>
+        <v>50043800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>114.411415636222</v>
+        <v>113.2885707737471</v>
       </c>
       <c r="C72" t="n">
-        <v>114.5505291366805</v>
+        <v>113.5966067328595</v>
       </c>
       <c r="D72" t="n">
-        <v>112.8116027998319</v>
+        <v>111.5098966082868</v>
       </c>
       <c r="E72" t="n">
-        <v>113.6363525390625</v>
+        <v>111.8874893188477</v>
       </c>
       <c r="F72" t="n">
-        <v>50043800</v>
+        <v>21473900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>113.2885707737471</v>
+        <v>111.2813411845575</v>
       </c>
       <c r="C73" t="n">
-        <v>113.5966067328595</v>
+        <v>111.6390637625677</v>
       </c>
       <c r="D73" t="n">
-        <v>111.5098966082868</v>
+        <v>109.9995032102072</v>
       </c>
       <c r="E73" t="n">
-        <v>111.8874893188477</v>
+        <v>110.1982421875</v>
       </c>
       <c r="F73" t="n">
-        <v>21473900</v>
+        <v>20319900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>111.2813411845575</v>
+        <v>110.1982488335626</v>
       </c>
       <c r="C74" t="n">
-        <v>111.6390637625677</v>
+        <v>111.003120892069</v>
       </c>
       <c r="D74" t="n">
-        <v>109.9995032102072</v>
+        <v>109.8504650787215</v>
       </c>
       <c r="E74" t="n">
-        <v>110.1982421875</v>
+        <v>110.9037551879883</v>
       </c>
       <c r="F74" t="n">
-        <v>20319900</v>
+        <v>9009600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>110.1982488335626</v>
+        <v>111.0130583586743</v>
       </c>
       <c r="C75" t="n">
-        <v>111.003120892069</v>
+        <v>111.2614764063509</v>
       </c>
       <c r="D75" t="n">
-        <v>109.8504650787215</v>
+        <v>110.6553357635307</v>
       </c>
       <c r="E75" t="n">
-        <v>110.9037551879883</v>
+        <v>111.0329284667969</v>
       </c>
       <c r="F75" t="n">
-        <v>9009600</v>
+        <v>9003800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>111.0130583586743</v>
+        <v>110.8838702636393</v>
       </c>
       <c r="C76" t="n">
-        <v>111.2614764063509</v>
+        <v>112.0663425340636</v>
       </c>
       <c r="D76" t="n">
-        <v>110.6553357635307</v>
+        <v>110.8640001565665</v>
       </c>
       <c r="E76" t="n">
-        <v>111.0329284667969</v>
+        <v>111.8179244995117</v>
       </c>
       <c r="F76" t="n">
-        <v>9003800</v>
+        <v>12979600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>110.8838702636393</v>
+        <v>111.1819830388479</v>
       </c>
       <c r="C77" t="n">
-        <v>112.0663425340636</v>
+        <v>111.9769238397842</v>
       </c>
       <c r="D77" t="n">
-        <v>110.8640001565665</v>
+        <v>111.1322963958704</v>
       </c>
       <c r="E77" t="n">
-        <v>111.8179244995117</v>
+        <v>111.2117919921875</v>
       </c>
       <c r="F77" t="n">
-        <v>12979600</v>
+        <v>11730600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>111.1819754114984</v>
+        <v>111.022991872357</v>
       </c>
       <c r="C78" t="n">
-        <v>111.9769161578998</v>
+        <v>111.5396980510222</v>
       </c>
       <c r="D78" t="n">
-        <v>111.1322887719295</v>
+        <v>110.6155826547936</v>
       </c>
       <c r="E78" t="n">
-        <v>111.211784362793</v>
+        <v>110.7050170898438</v>
       </c>
       <c r="F78" t="n">
-        <v>11730600</v>
+        <v>11487400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>111.022991872357</v>
+        <v>110.7248924392647</v>
       </c>
       <c r="C79" t="n">
-        <v>111.5396980510222</v>
+        <v>112.0762872242068</v>
       </c>
       <c r="D79" t="n">
-        <v>110.6155826547936</v>
+        <v>110.4168564863102</v>
       </c>
       <c r="E79" t="n">
-        <v>110.7050170898438</v>
+        <v>112.0464782714844</v>
       </c>
       <c r="F79" t="n">
-        <v>11487400</v>
+        <v>14306600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>110.7248924392647</v>
+        <v>112.106092568778</v>
       </c>
       <c r="C80" t="n">
-        <v>112.0762872242068</v>
+        <v>113.0103378715463</v>
       </c>
       <c r="D80" t="n">
-        <v>110.4168564863102</v>
+        <v>111.4403340423477</v>
       </c>
       <c r="E80" t="n">
-        <v>112.0464782714844</v>
+        <v>111.9967880249023</v>
       </c>
       <c r="F80" t="n">
-        <v>14306600</v>
+        <v>19557600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>112.106092568778</v>
+        <v>111.6887440152751</v>
       </c>
       <c r="C81" t="n">
-        <v>113.0103378715463</v>
+        <v>114.0636196950201</v>
       </c>
       <c r="D81" t="n">
-        <v>111.4403340423477</v>
+        <v>111.2813348209601</v>
       </c>
       <c r="E81" t="n">
-        <v>111.9967880249023</v>
+        <v>113.6164627075195</v>
       </c>
       <c r="F81" t="n">
-        <v>19557600</v>
+        <v>20120800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>111.6887590151699</v>
+        <v>113.4674284407305</v>
       </c>
       <c r="C82" t="n">
-        <v>114.0636350138627</v>
+        <v>114.0040123266269</v>
       </c>
       <c r="D82" t="n">
-        <v>111.2813497661395</v>
+        <v>111.3906496463658</v>
       </c>
       <c r="E82" t="n">
-        <v>113.6164779663086</v>
+        <v>112.0067291259766</v>
       </c>
       <c r="F82" t="n">
-        <v>20120800</v>
+        <v>23306000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>113.4674284407305</v>
+        <v>110.5857722677035</v>
       </c>
       <c r="C83" t="n">
-        <v>114.0040123266269</v>
+        <v>112.7519778145493</v>
       </c>
       <c r="D83" t="n">
-        <v>111.3906496463658</v>
+        <v>109.1151341794756</v>
       </c>
       <c r="E83" t="n">
-        <v>112.0067291259766</v>
+        <v>112.3545074462891</v>
       </c>
       <c r="F83" t="n">
-        <v>23306000</v>
+        <v>24058300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>110.5857797769927</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="C84" t="n">
-        <v>112.7519854709339</v>
+        <v>114.7293904053996</v>
       </c>
       <c r="D84" t="n">
-        <v>109.1151415889016</v>
+        <v>111.5496424227033</v>
       </c>
       <c r="E84" t="n">
-        <v>112.3545150756836</v>
+        <v>113.8052749633789</v>
       </c>
       <c r="F84" t="n">
-        <v>24058300</v>
+        <v>21902900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>111.5496424227033</v>
+        <v>116.7564835948294</v>
       </c>
       <c r="C85" t="n">
-        <v>114.7293904053996</v>
+        <v>118.0880007049746</v>
       </c>
       <c r="D85" t="n">
-        <v>111.5496424227033</v>
+        <v>115.673384534886</v>
       </c>
       <c r="E85" t="n">
-        <v>113.8052749633789</v>
+        <v>117.2235107421875</v>
       </c>
       <c r="F85" t="n">
-        <v>21902900</v>
+        <v>49182100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>116.756475995831</v>
+        <v>117.1440021366951</v>
       </c>
       <c r="C86" t="n">
-        <v>118.0879930193155</v>
+        <v>119.7474257428768</v>
       </c>
       <c r="D86" t="n">
-        <v>115.6733770063802</v>
+        <v>116.9850185444036</v>
       </c>
       <c r="E86" t="n">
-        <v>117.223503112793</v>
+        <v>119.5983734130859</v>
       </c>
       <c r="F86" t="n">
-        <v>49182100</v>
+        <v>31222100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>117.1440096095209</v>
+        <v>119.4294554726083</v>
       </c>
       <c r="C87" t="n">
-        <v>119.7474333817796</v>
+        <v>120.4728066581839</v>
       </c>
       <c r="D87" t="n">
-        <v>116.9850260070875</v>
+        <v>118.2767921653628</v>
       </c>
       <c r="E87" t="n">
-        <v>119.5983810424805</v>
+        <v>119.280403137207</v>
       </c>
       <c r="F87" t="n">
-        <v>31222100</v>
+        <v>32764000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>119.4294631115365</v>
+        <v>119.2207875004986</v>
       </c>
       <c r="C88" t="n">
-        <v>120.4728143638468</v>
+        <v>120.1051551046</v>
       </c>
       <c r="D88" t="n">
-        <v>118.2767997305645</v>
+        <v>117.9786973170847</v>
       </c>
       <c r="E88" t="n">
-        <v>119.2804107666016</v>
+        <v>118.4457168579102</v>
       </c>
       <c r="F88" t="n">
-        <v>32764000</v>
+        <v>34559400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>119.2207951798175</v>
+        <v>117.9190695805763</v>
       </c>
       <c r="C89" t="n">
-        <v>120.1051628408833</v>
+        <v>119.8368570903777</v>
       </c>
       <c r="D89" t="n">
-        <v>117.9787049163972</v>
+        <v>116.1602732501508</v>
       </c>
       <c r="E89" t="n">
-        <v>118.4457244873047</v>
+        <v>118.9425506591797</v>
       </c>
       <c r="F89" t="n">
-        <v>34559400</v>
+        <v>415144600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>117.9190771443211</v>
+        <v>120.1250298240042</v>
       </c>
       <c r="C90" t="n">
-        <v>119.8368647771362</v>
+        <v>120.8504138546603</v>
       </c>
       <c r="D90" t="n">
-        <v>116.1602807010803</v>
+        <v>116.8657862705671</v>
       </c>
       <c r="E90" t="n">
-        <v>118.9425582885742</v>
+        <v>117.9588241577148</v>
       </c>
       <c r="F90" t="n">
-        <v>415144600</v>
+        <v>45334000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>120.1250298240042</v>
+        <v>117.3328066996214</v>
       </c>
       <c r="C91" t="n">
-        <v>120.8504138546603</v>
+        <v>119.7275525860415</v>
       </c>
       <c r="D91" t="n">
-        <v>116.8657862705671</v>
+        <v>116.8061616847336</v>
       </c>
       <c r="E91" t="n">
-        <v>117.9588241577148</v>
+        <v>118.6047058105469</v>
       </c>
       <c r="F91" t="n">
-        <v>45334000</v>
+        <v>34811700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>117.3328142471995</v>
+        <v>118.5351491309384</v>
       </c>
       <c r="C92" t="n">
-        <v>119.7275602876645</v>
+        <v>118.763689475092</v>
       </c>
       <c r="D92" t="n">
-        <v>116.8061691984345</v>
+        <v>116.9055274465167</v>
       </c>
       <c r="E92" t="n">
-        <v>118.6047134399414</v>
+        <v>117.0843887329102</v>
       </c>
       <c r="F92" t="n">
-        <v>34811700</v>
+        <v>24547300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>118.5351568548667</v>
+        <v>117.4222340816893</v>
       </c>
       <c r="C93" t="n">
-        <v>118.7636972139123</v>
+        <v>117.8594522459602</v>
       </c>
       <c r="D93" t="n">
-        <v>116.9055350642564</v>
+        <v>116.3987529981613</v>
       </c>
       <c r="E93" t="n">
-        <v>117.0843963623047</v>
+        <v>116.9850234985352</v>
       </c>
       <c r="F93" t="n">
-        <v>24547300</v>
+        <v>20806900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>117.4222340816893</v>
+        <v>117.064521823182</v>
       </c>
       <c r="C94" t="n">
-        <v>117.8594522459602</v>
+        <v>118.0979418418126</v>
       </c>
       <c r="D94" t="n">
-        <v>116.3987529981613</v>
+        <v>116.6471813102112</v>
       </c>
       <c r="E94" t="n">
-        <v>116.9850234985352</v>
+        <v>116.8955993652344</v>
       </c>
       <c r="F94" t="n">
-        <v>20806900</v>
+        <v>19552200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>117.064521823182</v>
+        <v>116.7564814621505</v>
       </c>
       <c r="C95" t="n">
-        <v>118.0979418418126</v>
+        <v>116.8856561166937</v>
       </c>
       <c r="D95" t="n">
-        <v>116.6471813102112</v>
+        <v>114.7492669888757</v>
       </c>
       <c r="E95" t="n">
-        <v>116.8955993652344</v>
+        <v>116.2000274658203</v>
       </c>
       <c r="F95" t="n">
-        <v>19552200</v>
+        <v>22968600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>116.7564814621505</v>
+        <v>115.9019236934497</v>
       </c>
       <c r="C96" t="n">
-        <v>116.8856561166937</v>
+        <v>116.7167345864151</v>
       </c>
       <c r="D96" t="n">
-        <v>114.7492669888757</v>
+        <v>115.1367994424561</v>
       </c>
       <c r="E96" t="n">
-        <v>116.2000274658203</v>
+        <v>115.8323669433594</v>
       </c>
       <c r="F96" t="n">
-        <v>22968600</v>
+        <v>16342000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>115.9019236934497</v>
+        <v>115.7131212672227</v>
       </c>
       <c r="C97" t="n">
-        <v>116.7167345864151</v>
+        <v>116.9154712653777</v>
       </c>
       <c r="D97" t="n">
-        <v>115.1367994424561</v>
+        <v>115.3355285714882</v>
       </c>
       <c r="E97" t="n">
-        <v>115.8323669433594</v>
+        <v>116.6670532226562</v>
       </c>
       <c r="F97" t="n">
-        <v>16342000</v>
+        <v>16381100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>115.7131212672227</v>
+        <v>116.1702160933048</v>
       </c>
       <c r="C98" t="n">
-        <v>116.9154712653777</v>
+        <v>118.6543964981968</v>
       </c>
       <c r="D98" t="n">
-        <v>115.3355285714882</v>
+        <v>115.8621725679387</v>
       </c>
       <c r="E98" t="n">
-        <v>116.6670532226562</v>
+        <v>118.386100769043</v>
       </c>
       <c r="F98" t="n">
-        <v>16381100</v>
+        <v>22215400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>116.1702235798966</v>
+        <v>118.7438281911484</v>
       </c>
       <c r="C99" t="n">
-        <v>118.6544041448817</v>
+        <v>123.4140845101525</v>
       </c>
       <c r="D99" t="n">
-        <v>115.8621800346786</v>
+        <v>118.2966787324989</v>
       </c>
       <c r="E99" t="n">
-        <v>118.3861083984375</v>
+        <v>123.2749710083008</v>
       </c>
       <c r="F99" t="n">
-        <v>22215400</v>
+        <v>31210100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>118.7438208421828</v>
+        <v>122.8675641812365</v>
       </c>
       <c r="C100" t="n">
-        <v>123.4140768721483</v>
+        <v>127.3589590117064</v>
       </c>
       <c r="D100" t="n">
-        <v>118.2966714112071</v>
+        <v>122.8675641812365</v>
       </c>
       <c r="E100" t="n">
-        <v>123.2749633789062</v>
+        <v>126.9018707275391</v>
       </c>
       <c r="F100" t="n">
-        <v>31210100</v>
+        <v>32018700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>122.8675715680868</v>
+        <v>127.3192151881231</v>
       </c>
       <c r="C101" t="n">
-        <v>127.3589666685813</v>
+        <v>128.5911143047342</v>
       </c>
       <c r="D101" t="n">
-        <v>122.8675715680868</v>
+        <v>126.2857876794806</v>
       </c>
       <c r="E101" t="n">
-        <v>126.9018783569336</v>
+        <v>127.1900329589844</v>
       </c>
       <c r="F101" t="n">
-        <v>32018700</v>
+        <v>27531800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>127.3192151881231</v>
+        <v>127.7663710403251</v>
       </c>
       <c r="C102" t="n">
-        <v>128.5911143047342</v>
+        <v>128.779920911861</v>
       </c>
       <c r="D102" t="n">
-        <v>126.2857876794806</v>
+        <v>125.7591489863279</v>
       </c>
       <c r="E102" t="n">
-        <v>127.1900329589844</v>
+        <v>126.1367492675781</v>
       </c>
       <c r="F102" t="n">
-        <v>27531800</v>
+        <v>30517800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>127.7663710403251</v>
+        <v>126.4845378023196</v>
       </c>
       <c r="C103" t="n">
-        <v>128.779920911861</v>
+        <v>130.8666283506429</v>
       </c>
       <c r="D103" t="n">
-        <v>125.7591489863279</v>
+        <v>126.2460585922159</v>
       </c>
       <c r="E103" t="n">
-        <v>126.1367492675781</v>
+        <v>130.3499145507812</v>
       </c>
       <c r="F103" t="n">
-        <v>30517800</v>
+        <v>26593400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>126.4845378023196</v>
+        <v>130.5884053590928</v>
       </c>
       <c r="C104" t="n">
-        <v>130.8666283506429</v>
+        <v>130.9560592399128</v>
       </c>
       <c r="D104" t="n">
-        <v>126.2460585922159</v>
+        <v>127.2794749450073</v>
       </c>
       <c r="E104" t="n">
-        <v>130.3499145507812</v>
+        <v>128.2035980224609</v>
       </c>
       <c r="F104" t="n">
-        <v>26593400</v>
+        <v>27197300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>130.5884053590928</v>
+        <v>128.1241009271639</v>
       </c>
       <c r="C105" t="n">
-        <v>130.9560592399128</v>
+        <v>128.521563757884</v>
       </c>
       <c r="D105" t="n">
-        <v>127.2794749450073</v>
+        <v>125.590233685177</v>
       </c>
       <c r="E105" t="n">
-        <v>128.2035980224609</v>
+        <v>125.8982696533203</v>
       </c>
       <c r="F105" t="n">
-        <v>27197300</v>
+        <v>24662000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>128.1240931628847</v>
+        <v>125.8982534995816</v>
       </c>
       <c r="C106" t="n">
-        <v>128.5215559695187</v>
+        <v>128.9190252095116</v>
       </c>
       <c r="D106" t="n">
-        <v>125.5902260744493</v>
+        <v>125.8286967550185</v>
       </c>
       <c r="E106" t="n">
-        <v>125.8982620239258</v>
+        <v>127.9551620483398</v>
       </c>
       <c r="F106" t="n">
-        <v>24662000</v>
+        <v>19232100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>125.8982685130821</v>
+        <v>128.5613042513025</v>
       </c>
       <c r="C107" t="n">
-        <v>128.9190405832424</v>
+        <v>133.6389694112844</v>
       </c>
       <c r="D107" t="n">
-        <v>125.8287117602243</v>
+        <v>128.4917399247525</v>
       </c>
       <c r="E107" t="n">
-        <v>127.9551773071289</v>
+        <v>132.7943420410156</v>
       </c>
       <c r="F107" t="n">
-        <v>19232100</v>
+        <v>33382700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>128.5613042513025</v>
+        <v>131.8602829174213</v>
       </c>
       <c r="C108" t="n">
-        <v>133.6389694112844</v>
+        <v>133.7979404546978</v>
       </c>
       <c r="D108" t="n">
-        <v>128.4917399247525</v>
+        <v>130.9162974671823</v>
       </c>
       <c r="E108" t="n">
-        <v>132.7943420410156</v>
+        <v>133.0427551269531</v>
       </c>
       <c r="F108" t="n">
-        <v>33382700</v>
+        <v>24131200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>131.8602980405916</v>
+        <v>132.2676902838272</v>
       </c>
       <c r="C109" t="n">
-        <v>133.7979558000997</v>
+        <v>133.8376939791136</v>
       </c>
       <c r="D109" t="n">
-        <v>130.9163124820861</v>
+        <v>127.3490165534248</v>
       </c>
       <c r="E109" t="n">
-        <v>133.0427703857422</v>
+        <v>128.0346527099609</v>
       </c>
       <c r="F109" t="n">
-        <v>24131200</v>
+        <v>37995900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>132.2677060470971</v>
+        <v>127.3192261638227</v>
       </c>
       <c r="C110" t="n">
-        <v>133.8377099294918</v>
+        <v>128.0545339014254</v>
       </c>
       <c r="D110" t="n">
-        <v>127.3490317305018</v>
+        <v>124.9741515413755</v>
       </c>
       <c r="E110" t="n">
-        <v>128.03466796875</v>
+        <v>125.8187789916992</v>
       </c>
       <c r="F110" t="n">
-        <v>37995900</v>
+        <v>36485000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>127.3192184434441</v>
+        <v>127.6868687168009</v>
       </c>
       <c r="C111" t="n">
-        <v>128.0545261364593</v>
+        <v>129.2767501898412</v>
       </c>
       <c r="D111" t="n">
-        <v>124.9741439631975</v>
+        <v>123.6128144996477</v>
       </c>
       <c r="E111" t="n">
-        <v>125.8187713623047</v>
+        <v>124.0798416137695</v>
       </c>
       <c r="F111" t="n">
-        <v>36485000</v>
+        <v>42993300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>127.6868765679835</v>
+        <v>122.2216774308809</v>
       </c>
       <c r="C112" t="n">
-        <v>129.2767581387821</v>
+        <v>122.6986434102051</v>
       </c>
       <c r="D112" t="n">
-        <v>123.6128221003258</v>
+        <v>120.2840197235699</v>
       </c>
       <c r="E112" t="n">
-        <v>124.0798492431641</v>
+        <v>122.2117385864258</v>
       </c>
       <c r="F112" t="n">
-        <v>42993300</v>
+        <v>35151000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>122.2216774308809</v>
+        <v>122.738382951216</v>
       </c>
       <c r="C113" t="n">
-        <v>122.6986434102051</v>
+        <v>125.9976340329315</v>
       </c>
       <c r="D113" t="n">
-        <v>120.2840197235699</v>
+        <v>122.1819289626602</v>
       </c>
       <c r="E113" t="n">
-        <v>122.2117385864258</v>
+        <v>125.0138931274414</v>
       </c>
       <c r="F113" t="n">
-        <v>35151000</v>
+        <v>25662800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>122.7383904417398</v>
+        <v>125.1033248323272</v>
       </c>
       <c r="C114" t="n">
-        <v>125.9976417223621</v>
+        <v>127.2297750394507</v>
       </c>
       <c r="D114" t="n">
-        <v>122.1819364192246</v>
+        <v>124.1195915294407</v>
       </c>
       <c r="E114" t="n">
-        <v>125.0139007568359</v>
+        <v>125.9479446411133</v>
       </c>
       <c r="F114" t="n">
-        <v>25662800</v>
+        <v>20161200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>125.1033248323272</v>
+        <v>125.8088357226236</v>
       </c>
       <c r="C115" t="n">
-        <v>127.2297750394507</v>
+        <v>126.593837657093</v>
       </c>
       <c r="D115" t="n">
-        <v>124.1195915294407</v>
+        <v>124.626363398647</v>
       </c>
       <c r="E115" t="n">
-        <v>125.9479446411133</v>
+        <v>124.9542770385742</v>
       </c>
       <c r="F115" t="n">
-        <v>20161200</v>
+        <v>17345700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>125.8088357226236</v>
+        <v>125.1828241808018</v>
       </c>
       <c r="C116" t="n">
-        <v>126.593837657093</v>
+        <v>126.5242801033853</v>
       </c>
       <c r="D116" t="n">
-        <v>124.626363398647</v>
+        <v>123.1557320302039</v>
       </c>
       <c r="E116" t="n">
-        <v>124.9542770385742</v>
+        <v>123.6326904296875</v>
       </c>
       <c r="F116" t="n">
-        <v>17345700</v>
+        <v>18638300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>125.1828241808018</v>
+        <v>124.7257266802137</v>
       </c>
       <c r="C117" t="n">
-        <v>126.5242801033853</v>
+        <v>127.7862463456887</v>
       </c>
       <c r="D117" t="n">
-        <v>123.1557320302039</v>
+        <v>124.3580728314762</v>
       </c>
       <c r="E117" t="n">
-        <v>123.6326904296875</v>
+        <v>127.1403503417969</v>
       </c>
       <c r="F117" t="n">
-        <v>18638300</v>
+        <v>29205500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>124.7257341647123</v>
+        <v>126.6534608275313</v>
       </c>
       <c r="C118" t="n">
-        <v>127.7862540138419</v>
+        <v>127.9352989068956</v>
       </c>
       <c r="D118" t="n">
-        <v>124.3580802939128</v>
+        <v>126.2460591576593</v>
       </c>
       <c r="E118" t="n">
-        <v>127.1403579711914</v>
+        <v>126.2957382202148</v>
       </c>
       <c r="F118" t="n">
-        <v>29205500</v>
+        <v>17091500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>126.6534531765271</v>
+        <v>125.7193975573372</v>
       </c>
       <c r="C119" t="n">
-        <v>127.9352911784569</v>
+        <v>127.5576895255598</v>
       </c>
       <c r="D119" t="n">
-        <v>126.2460515312658</v>
+        <v>124.8747777428692</v>
       </c>
       <c r="E119" t="n">
-        <v>126.2957305908203</v>
+        <v>127.1006088256836</v>
       </c>
       <c r="F119" t="n">
-        <v>17091500</v>
+        <v>16480400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>125.7193975573372</v>
+        <v>126.3056608968421</v>
       </c>
       <c r="C120" t="n">
-        <v>127.5576895255598</v>
+        <v>127.3589508940441</v>
       </c>
       <c r="D120" t="n">
-        <v>124.8747777428692</v>
+        <v>125.4411634429717</v>
       </c>
       <c r="E120" t="n">
-        <v>127.1006088256836</v>
+        <v>127.0012283325195</v>
       </c>
       <c r="F120" t="n">
-        <v>16480400</v>
+        <v>16434100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>126.3056684844515</v>
+        <v>124.5866176413744</v>
       </c>
       <c r="C121" t="n">
-        <v>127.3589585449282</v>
+        <v>124.8847223336648</v>
       </c>
       <c r="D121" t="n">
-        <v>125.4411709786478</v>
+        <v>120.8802245827464</v>
       </c>
       <c r="E121" t="n">
-        <v>127.0012359619141</v>
+        <v>122.5297164916992</v>
       </c>
       <c r="F121" t="n">
-        <v>16434100</v>
+        <v>28604900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>124.5866098839056</v>
+        <v>121.7248475261227</v>
       </c>
       <c r="C122" t="n">
-        <v>124.8847145576342</v>
+        <v>123.4041560118284</v>
       </c>
       <c r="D122" t="n">
-        <v>120.8802170560586</v>
+        <v>120.8504186975863</v>
       </c>
       <c r="E122" t="n">
-        <v>122.5297088623047</v>
+        <v>123.0166244506836</v>
       </c>
       <c r="F122" t="n">
-        <v>28604900</v>
+        <v>21553000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>121.7248399768431</v>
+        <v>122.9073113026852</v>
       </c>
       <c r="C123" t="n">
-        <v>123.4041483583995</v>
+        <v>123.7221221667048</v>
       </c>
       <c r="D123" t="n">
-        <v>120.8504112025381</v>
+        <v>121.7248390120394</v>
       </c>
       <c r="E123" t="n">
-        <v>123.0166168212891</v>
+        <v>123.5531921386719</v>
       </c>
       <c r="F123" t="n">
-        <v>21553000</v>
+        <v>19375900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>122.9073188921967</v>
+        <v>123.4240170322698</v>
       </c>
       <c r="C124" t="n">
-        <v>123.7221298065307</v>
+        <v>125.3020567921792</v>
       </c>
       <c r="D124" t="n">
-        <v>121.7248465285333</v>
+        <v>122.5694583754614</v>
       </c>
       <c r="E124" t="n">
-        <v>123.5531997680664</v>
+        <v>124.3282623291016</v>
       </c>
       <c r="F124" t="n">
-        <v>19375900</v>
+        <v>18793600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>123.4240246061754</v>
+        <v>124.5170554078691</v>
       </c>
       <c r="C125" t="n">
-        <v>125.3020644813305</v>
+        <v>124.6959166991441</v>
       </c>
       <c r="D125" t="n">
-        <v>122.5694658969271</v>
+        <v>122.2713617943361</v>
       </c>
       <c r="E125" t="n">
-        <v>124.3282699584961</v>
+        <v>122.7085723876953</v>
       </c>
       <c r="F125" t="n">
-        <v>18793600</v>
+        <v>18176500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>124.5170631497059</v>
+        <v>121.5261159056028</v>
       </c>
       <c r="C126" t="n">
-        <v>124.6959244521016</v>
+        <v>124.5965594357429</v>
       </c>
       <c r="D126" t="n">
-        <v>122.2713693965471</v>
+        <v>121.506238215717</v>
       </c>
       <c r="E126" t="n">
-        <v>122.7085800170898</v>
+        <v>124.5369415283203</v>
       </c>
       <c r="F126" t="n">
-        <v>18176500</v>
+        <v>21751600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>121.5261084606577</v>
+        <v>124.5965592468419</v>
       </c>
       <c r="C127" t="n">
-        <v>124.596551802696</v>
+        <v>125.8883361672332</v>
       </c>
       <c r="D127" t="n">
-        <v>121.5062307719897</v>
+        <v>124.179218733282</v>
       </c>
       <c r="E127" t="n">
-        <v>124.5369338989258</v>
+        <v>125.7194061279297</v>
       </c>
       <c r="F127" t="n">
-        <v>21751600</v>
+        <v>15194100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>124.5965516855884</v>
+        <v>125.9578884818529</v>
       </c>
       <c r="C128" t="n">
-        <v>125.888328527587</v>
+        <v>126.1764975758589</v>
       </c>
       <c r="D128" t="n">
-        <v>124.1792111973551</v>
+        <v>124.0401008586876</v>
       </c>
       <c r="E128" t="n">
-        <v>125.7193984985352</v>
+        <v>125.192756652832</v>
       </c>
       <c r="F128" t="n">
-        <v>15194100</v>
+        <v>20463200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>125.9578884818529</v>
+        <v>125.8485858664739</v>
       </c>
       <c r="C129" t="n">
-        <v>126.1764975758589</v>
+        <v>126.3851697651471</v>
       </c>
       <c r="D129" t="n">
-        <v>124.0401008586876</v>
+        <v>124.0699117156269</v>
       </c>
       <c r="E129" t="n">
-        <v>125.192756652832</v>
+        <v>124.2885208129883</v>
       </c>
       <c r="F129" t="n">
-        <v>20463200</v>
+        <v>19895000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>125.8485858664739</v>
+        <v>123.5432578745883</v>
       </c>
       <c r="C130" t="n">
-        <v>126.3851697651471</v>
+        <v>123.8214848583074</v>
       </c>
       <c r="D130" t="n">
-        <v>124.0699117156269</v>
+        <v>121.0590775469296</v>
       </c>
       <c r="E130" t="n">
-        <v>124.2885208129883</v>
+        <v>121.2081298828125</v>
       </c>
       <c r="F130" t="n">
-        <v>19895000</v>
+        <v>19734900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>123.5432578745883</v>
+        <v>121.6254767010641</v>
       </c>
       <c r="C131" t="n">
-        <v>123.8214848583074</v>
+        <v>121.9732604488496</v>
       </c>
       <c r="D131" t="n">
-        <v>121.0590775469296</v>
+        <v>118.5152779167263</v>
       </c>
       <c r="E131" t="n">
-        <v>121.2081298828125</v>
+        <v>120.3237609863281</v>
       </c>
       <c r="F131" t="n">
-        <v>19734900</v>
+        <v>17927700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>121.6254689891314</v>
+        <v>120.1126709520348</v>
       </c>
       <c r="C132" t="n">
-        <v>121.9732527148649</v>
+        <v>120.7798034051914</v>
       </c>
       <c r="D132" t="n">
-        <v>118.5152704020027</v>
+        <v>117.513863427923</v>
       </c>
       <c r="E132" t="n">
-        <v>120.3237533569336</v>
+        <v>118.5095748901367</v>
       </c>
       <c r="F132" t="n">
-        <v>17927700</v>
+        <v>57545600</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>120.1126709520348</v>
+        <v>119.9633247632631</v>
       </c>
       <c r="C133" t="n">
-        <v>120.7798034051914</v>
+        <v>120.6105311603868</v>
       </c>
       <c r="D133" t="n">
-        <v>117.513863427923</v>
+        <v>118.5394570155744</v>
       </c>
       <c r="E133" t="n">
-        <v>118.5095748901367</v>
+        <v>120.2022933959961</v>
       </c>
       <c r="F133" t="n">
-        <v>57545600</v>
+        <v>22181500</v>
       </c>
       <c r="G133" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>119.9633247632631</v>
+        <v>120.1126723733929</v>
       </c>
       <c r="C134" t="n">
-        <v>120.6105311603868</v>
+        <v>123.577751645438</v>
       </c>
       <c r="D134" t="n">
-        <v>118.5394570155744</v>
+        <v>119.9732733747674</v>
       </c>
       <c r="E134" t="n">
-        <v>120.2022933959961</v>
+        <v>121.5265884399414</v>
       </c>
       <c r="F134" t="n">
-        <v>22181500</v>
+        <v>17269600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>120.1126723733929</v>
+        <v>122.2833215864677</v>
       </c>
       <c r="C135" t="n">
-        <v>123.577751645438</v>
+        <v>122.9604056810019</v>
       </c>
       <c r="D135" t="n">
-        <v>119.9732733747674</v>
+        <v>121.2577400013664</v>
       </c>
       <c r="E135" t="n">
-        <v>121.5265884399414</v>
+        <v>122.5322494506836</v>
       </c>
       <c r="F135" t="n">
-        <v>17269600</v>
+        <v>16597300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>122.2833215864677</v>
+        <v>123.0798964656872</v>
       </c>
       <c r="C136" t="n">
-        <v>122.9604056810019</v>
+        <v>123.2690840775393</v>
       </c>
       <c r="D136" t="n">
-        <v>121.2577400013664</v>
+        <v>121.2677018786759</v>
       </c>
       <c r="E136" t="n">
-        <v>122.5322494506836</v>
+        <v>121.6560287475586</v>
       </c>
       <c r="F136" t="n">
-        <v>16597300</v>
+        <v>16442500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>123.0798964656872</v>
+        <v>121.5066712193412</v>
       </c>
       <c r="C137" t="n">
-        <v>123.2690840775393</v>
+        <v>123.7370628172082</v>
       </c>
       <c r="D137" t="n">
-        <v>121.2677018786759</v>
+        <v>121.2975727192295</v>
       </c>
       <c r="E137" t="n">
-        <v>121.6560287475586</v>
+        <v>122.3629837036133</v>
       </c>
       <c r="F137" t="n">
-        <v>16442500</v>
+        <v>16543300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>121.5066712193412</v>
+        <v>123.1794582878797</v>
       </c>
       <c r="C138" t="n">
-        <v>123.7370628172082</v>
+        <v>124.7228140204241</v>
       </c>
       <c r="D138" t="n">
-        <v>121.2975727192295</v>
+        <v>122.6119030849671</v>
       </c>
       <c r="E138" t="n">
-        <v>122.3629837036133</v>
+        <v>122.9703598022461</v>
       </c>
       <c r="F138" t="n">
-        <v>16543300</v>
+        <v>20428900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>123.1794659302472</v>
+        <v>122.9006712768322</v>
       </c>
       <c r="C139" t="n">
-        <v>124.7228217585454</v>
+        <v>124.4639380346807</v>
       </c>
       <c r="D139" t="n">
-        <v>122.611910692122</v>
+        <v>122.313197539037</v>
       </c>
       <c r="E139" t="n">
-        <v>122.9703674316406</v>
+        <v>123.7470245361328</v>
       </c>
       <c r="F139" t="n">
-        <v>20428900</v>
+        <v>21330400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>122.9006712768322</v>
+        <v>123.2690839840767</v>
       </c>
       <c r="C140" t="n">
-        <v>124.4639380346807</v>
+        <v>124.6929517011257</v>
       </c>
       <c r="D140" t="n">
-        <v>122.313197539037</v>
+        <v>122.6019515205109</v>
       </c>
       <c r="E140" t="n">
-        <v>123.7470245361328</v>
+        <v>124.2050476074219</v>
       </c>
       <c r="F140" t="n">
-        <v>21330400</v>
+        <v>17039700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>123.2690839840767</v>
+        <v>124.613294570145</v>
       </c>
       <c r="C141" t="n">
-        <v>124.6929517011257</v>
+        <v>125.3600781881083</v>
       </c>
       <c r="D141" t="n">
-        <v>122.6019515205109</v>
+        <v>123.6175830795272</v>
       </c>
       <c r="E141" t="n">
-        <v>124.2050476074219</v>
+        <v>125.2505493164062</v>
       </c>
       <c r="F141" t="n">
-        <v>17039700</v>
+        <v>11898400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>124.613294570145</v>
+        <v>125.2704534168091</v>
       </c>
       <c r="C142" t="n">
-        <v>125.3600781881083</v>
+        <v>126.435441571189</v>
       </c>
       <c r="D142" t="n">
-        <v>123.6175830795272</v>
+        <v>124.8323455504126</v>
       </c>
       <c r="E142" t="n">
-        <v>125.2505493164062</v>
+        <v>126.2462539672852</v>
       </c>
       <c r="F142" t="n">
-        <v>11898400</v>
+        <v>10850400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>125.2704609872334</v>
+        <v>125.6488358778686</v>
       </c>
       <c r="C143" t="n">
-        <v>126.4354492120167</v>
+        <v>125.8181050086721</v>
       </c>
       <c r="D143" t="n">
-        <v>124.8323530943609</v>
+        <v>121.2677037842684</v>
       </c>
       <c r="E143" t="n">
-        <v>126.2462615966797</v>
+        <v>121.9646987915039</v>
       </c>
       <c r="F143" t="n">
-        <v>10850400</v>
+        <v>16076000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>125.6488358778686</v>
+        <v>121.7556020039852</v>
       </c>
       <c r="C144" t="n">
-        <v>125.8181050086721</v>
+        <v>126.7540780291546</v>
       </c>
       <c r="D144" t="n">
-        <v>121.2677037842684</v>
+        <v>120.8096791098908</v>
       </c>
       <c r="E144" t="n">
-        <v>121.9646987915039</v>
+        <v>126.7142486572266</v>
       </c>
       <c r="F144" t="n">
-        <v>16076000</v>
+        <v>20194300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>121.7556020039852</v>
+        <v>126.5449578917121</v>
       </c>
       <c r="C145" t="n">
-        <v>126.7540780291546</v>
+        <v>129.1338136031627</v>
       </c>
       <c r="D145" t="n">
-        <v>120.8096791098908</v>
+        <v>126.2761191568607</v>
       </c>
       <c r="E145" t="n">
-        <v>126.7142486572266</v>
+        <v>128.5762176513672</v>
       </c>
       <c r="F145" t="n">
-        <v>20194300</v>
+        <v>13853100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>126.5449729094413</v>
+        <v>128.1679831957248</v>
       </c>
       <c r="C146" t="n">
-        <v>129.1338289281244</v>
+        <v>128.3770740986961</v>
       </c>
       <c r="D146" t="n">
-        <v>126.2761341426855</v>
+        <v>125.6787044903905</v>
       </c>
       <c r="E146" t="n">
-        <v>128.5762329101562</v>
+        <v>126.2263412475586</v>
       </c>
       <c r="F146" t="n">
-        <v>13853100</v>
+        <v>13894000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>128.1679831957248</v>
+        <v>125.748399129494</v>
       </c>
       <c r="C147" t="n">
-        <v>128.3770740986961</v>
+        <v>125.7583583709996</v>
       </c>
       <c r="D147" t="n">
-        <v>125.6787044903905</v>
+        <v>123.4184304010941</v>
       </c>
       <c r="E147" t="n">
-        <v>126.2263412475586</v>
+        <v>124.035774230957</v>
       </c>
       <c r="F147" t="n">
-        <v>13894000</v>
+        <v>14510600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>125.7484068642315</v>
+        <v>122.6218719240817</v>
       </c>
       <c r="C148" t="n">
-        <v>125.7583661063497</v>
+        <v>124.663075927422</v>
       </c>
       <c r="D148" t="n">
-        <v>123.4184379925161</v>
+        <v>122.0244465474132</v>
       </c>
       <c r="E148" t="n">
-        <v>124.0357818603516</v>
+        <v>124.5137252807617</v>
       </c>
       <c r="F148" t="n">
-        <v>14510600</v>
+        <v>15320800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>122.6218644106077</v>
+        <v>124.0955206006192</v>
       </c>
       <c r="C149" t="n">
-        <v>124.6630682888762</v>
+        <v>124.5336360883443</v>
       </c>
       <c r="D149" t="n">
-        <v>122.0244390705456</v>
+        <v>122.651741974872</v>
       </c>
       <c r="E149" t="n">
-        <v>124.5137176513672</v>
+        <v>124.224967956543</v>
       </c>
       <c r="F149" t="n">
-        <v>15320800</v>
+        <v>17001400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>124.0955129791748</v>
+        <v>123.7968096196097</v>
       </c>
       <c r="C150" t="n">
-        <v>124.5336284399926</v>
+        <v>125.3999057035137</v>
       </c>
       <c r="D150" t="n">
-        <v>122.6517344420986</v>
+        <v>123.4383528805581</v>
       </c>
       <c r="E150" t="n">
-        <v>124.2249603271484</v>
+        <v>124.2847061157227</v>
       </c>
       <c r="F150" t="n">
-        <v>17001400</v>
+        <v>18324500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>123.7968020201654</v>
+        <v>124.0357815469104</v>
       </c>
       <c r="C151" t="n">
-        <v>125.3998980056611</v>
+        <v>127.0229160540335</v>
       </c>
       <c r="D151" t="n">
-        <v>123.4383453031182</v>
+        <v>122.8409307827315</v>
       </c>
       <c r="E151" t="n">
-        <v>124.2846984863281</v>
+        <v>126.9532165527344</v>
       </c>
       <c r="F151" t="n">
-        <v>18324500</v>
+        <v>24763700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>124.0357815469104</v>
+        <v>127.3216255408005</v>
       </c>
       <c r="C152" t="n">
-        <v>127.0229160540335</v>
+        <v>128.9147623376428</v>
       </c>
       <c r="D152" t="n">
-        <v>122.8409307827315</v>
+        <v>126.7739812059444</v>
       </c>
       <c r="E152" t="n">
-        <v>126.9532165527344</v>
+        <v>127.3714065551758</v>
       </c>
       <c r="F152" t="n">
-        <v>24763700</v>
+        <v>18933600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>127.3216255408005</v>
+        <v>127.2818063138542</v>
       </c>
       <c r="C153" t="n">
-        <v>128.9147623376428</v>
+        <v>129.2134891070832</v>
       </c>
       <c r="D153" t="n">
-        <v>126.7739812059444</v>
+        <v>126.9333087987552</v>
       </c>
       <c r="E153" t="n">
-        <v>127.3714065551758</v>
+        <v>129.0442199707031</v>
       </c>
       <c r="F153" t="n">
-        <v>18933600</v>
+        <v>17312400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>127.2817912634612</v>
+        <v>129.4424801273577</v>
       </c>
       <c r="C154" t="n">
-        <v>129.213473828279</v>
+        <v>129.8905472122055</v>
       </c>
       <c r="D154" t="n">
-        <v>126.9332937895701</v>
+        <v>128.2874512736634</v>
       </c>
       <c r="E154" t="n">
-        <v>129.0442047119141</v>
+        <v>129.4225616455078</v>
       </c>
       <c r="F154" t="n">
-        <v>17312400</v>
+        <v>17624500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>129.4424953884951</v>
+        <v>130.0100454912101</v>
       </c>
       <c r="C155" t="n">
-        <v>129.8905625261696</v>
+        <v>131.8919394396144</v>
       </c>
       <c r="D155" t="n">
-        <v>128.2874663986241</v>
+        <v>129.9303867555789</v>
       </c>
       <c r="E155" t="n">
-        <v>129.4225769042969</v>
+        <v>131.4637756347656</v>
       </c>
       <c r="F155" t="n">
-        <v>17624500</v>
+        <v>16376000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>130.010060581267</v>
+        <v>131.3741802679442</v>
       </c>
       <c r="C156" t="n">
-        <v>131.8919547480997</v>
+        <v>131.5534010485827</v>
       </c>
       <c r="D156" t="n">
-        <v>129.93040183639</v>
+        <v>128.7255839805935</v>
       </c>
       <c r="E156" t="n">
-        <v>131.4637908935547</v>
+        <v>129.3628387451172</v>
       </c>
       <c r="F156" t="n">
-        <v>16376000</v>
+        <v>16016300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>131.3741802679442</v>
+        <v>129.0641091249569</v>
       </c>
       <c r="C157" t="n">
-        <v>131.5534010485827</v>
+        <v>129.253296725292</v>
       </c>
       <c r="D157" t="n">
-        <v>128.7255839805935</v>
+        <v>126.8536361584495</v>
       </c>
       <c r="E157" t="n">
-        <v>129.3628387451172</v>
+        <v>127.0428161621094</v>
       </c>
       <c r="F157" t="n">
-        <v>16016300</v>
+        <v>17029500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>129.0641091249569</v>
+        <v>128.7853111434159</v>
       </c>
       <c r="C158" t="n">
-        <v>129.253296725292</v>
+        <v>129.2134749536506</v>
       </c>
       <c r="D158" t="n">
-        <v>126.8536361584495</v>
+        <v>126.236292344555</v>
       </c>
       <c r="E158" t="n">
         <v>127.0428161621094</v>
       </c>
       <c r="F158" t="n">
-        <v>17029500</v>
+        <v>16341800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>128.7853111434159</v>
+        <v>126.1367309249001</v>
       </c>
       <c r="C159" t="n">
-        <v>129.2134749536506</v>
+        <v>127.5307285199335</v>
       </c>
       <c r="D159" t="n">
-        <v>126.236292344555</v>
+        <v>125.3700364258034</v>
       </c>
       <c r="E159" t="n">
-        <v>127.0428161621094</v>
+        <v>127.4610214233398</v>
       </c>
       <c r="F159" t="n">
-        <v>16341800</v>
+        <v>16538800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>126.1367309249001</v>
+        <v>127.4709915844737</v>
       </c>
       <c r="C160" t="n">
-        <v>127.5307285199335</v>
+        <v>131.8620677904303</v>
       </c>
       <c r="D160" t="n">
-        <v>125.3700364258034</v>
+        <v>127.4012844860631</v>
       </c>
       <c r="E160" t="n">
-        <v>127.4610214233398</v>
+        <v>131.3642120361328</v>
       </c>
       <c r="F160" t="n">
-        <v>16538800</v>
+        <v>19867700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>127.470976777907</v>
+        <v>131.3542490271043</v>
       </c>
       <c r="C161" t="n">
-        <v>131.8620524738122</v>
+        <v>132.7980275509944</v>
       </c>
       <c r="D161" t="n">
-        <v>127.4012696875933</v>
+        <v>130.4182778590603</v>
       </c>
       <c r="E161" t="n">
-        <v>131.3641967773438</v>
+        <v>131.0356292724609</v>
       </c>
       <c r="F161" t="n">
-        <v>19867700</v>
+        <v>10480900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>131.3542490271043</v>
+        <v>129.850746393387</v>
       </c>
       <c r="C162" t="n">
-        <v>132.7980275509944</v>
+        <v>131.1849962189627</v>
       </c>
       <c r="D162" t="n">
-        <v>130.4182778590603</v>
+        <v>129.1238660254078</v>
       </c>
       <c r="E162" t="n">
-        <v>131.0356292724609</v>
+        <v>129.7710876464844</v>
       </c>
       <c r="F162" t="n">
-        <v>10480900</v>
+        <v>10340700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>129.8507311252314</v>
+        <v>129.9502974650302</v>
       </c>
       <c r="C163" t="n">
-        <v>131.184980793923</v>
+        <v>131.1650666644096</v>
       </c>
       <c r="D163" t="n">
-        <v>129.1238508427206</v>
+        <v>129.7412065662402</v>
       </c>
       <c r="E163" t="n">
-        <v>129.7710723876953</v>
+        <v>130.2290954589844</v>
       </c>
       <c r="F163" t="n">
-        <v>10340700</v>
+        <v>10637300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>129.9502974650302</v>
+        <v>130.2988095283542</v>
       </c>
       <c r="C164" t="n">
-        <v>131.1650666644096</v>
+        <v>130.5875591827794</v>
       </c>
       <c r="D164" t="n">
-        <v>129.7412065662402</v>
+        <v>128.9745113895137</v>
       </c>
       <c r="E164" t="n">
-        <v>130.2290954589844</v>
+        <v>129.5221557617188</v>
       </c>
       <c r="F164" t="n">
-        <v>10637300</v>
+        <v>16371500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>130.2988095283542</v>
+        <v>129.3429155964338</v>
       </c>
       <c r="C165" t="n">
-        <v>130.5875591827794</v>
+        <v>130.0399257893878</v>
       </c>
       <c r="D165" t="n">
-        <v>128.9745113895137</v>
+        <v>128.1181947261785</v>
       </c>
       <c r="E165" t="n">
-        <v>129.5221557617188</v>
+        <v>129.6416320800781</v>
       </c>
       <c r="F165" t="n">
-        <v>16371500</v>
+        <v>14935400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,25 +4733,25 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>129.3429155964338</v>
+        <v>130.0087618254011</v>
       </c>
       <c r="C166" t="n">
-        <v>130.0399257893878</v>
+        <v>131.0961549064253</v>
       </c>
       <c r="D166" t="n">
-        <v>128.1181947261785</v>
+        <v>129.9389217008702</v>
       </c>
       <c r="E166" t="n">
-        <v>129.6416320800781</v>
+        <v>130.1184844970703</v>
       </c>
       <c r="F166" t="n">
-        <v>14935400</v>
+        <v>15183700</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -4759,25 +4759,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>130.0087618254011</v>
+        <v>129.8690812906444</v>
       </c>
       <c r="C167" t="n">
-        <v>131.0961549064253</v>
+        <v>130.2880915922154</v>
       </c>
       <c r="D167" t="n">
-        <v>129.9389217008702</v>
+        <v>126.078161470576</v>
       </c>
       <c r="E167" t="n">
-        <v>130.1184844970703</v>
+        <v>127.285270690918</v>
       </c>
       <c r="F167" t="n">
-        <v>15183700</v>
+        <v>18699200</v>
       </c>
       <c r="G167" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>129.8690812906444</v>
+        <v>127.7741133789013</v>
       </c>
       <c r="C168" t="n">
-        <v>130.2880915922154</v>
+        <v>130.8068463681294</v>
       </c>
       <c r="D168" t="n">
-        <v>126.078161470576</v>
+        <v>127.4149725439082</v>
       </c>
       <c r="E168" t="n">
-        <v>127.285270690918</v>
+        <v>130.0386962890625</v>
       </c>
       <c r="F168" t="n">
-        <v>18699200</v>
+        <v>17935400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>127.7741133789013</v>
+        <v>128.8814524975413</v>
       </c>
       <c r="C169" t="n">
-        <v>130.8068463681294</v>
+        <v>132.2134717809921</v>
       </c>
       <c r="D169" t="n">
-        <v>127.4149725439082</v>
+        <v>128.4624574279768</v>
       </c>
       <c r="E169" t="n">
-        <v>130.0386962890625</v>
+        <v>131.156005859375</v>
       </c>
       <c r="F169" t="n">
-        <v>17935400</v>
+        <v>13786600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>128.8814524975413</v>
+        <v>131.0462673331121</v>
       </c>
       <c r="C170" t="n">
-        <v>132.2134717809921</v>
+        <v>132.4628740535408</v>
       </c>
       <c r="D170" t="n">
-        <v>128.4624574279768</v>
+        <v>130.5474615066649</v>
       </c>
       <c r="E170" t="n">
-        <v>131.156005859375</v>
+        <v>132.1436462402344</v>
       </c>
       <c r="F170" t="n">
-        <v>13786600</v>
+        <v>14200400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>131.0462673331121</v>
+        <v>133.370718441355</v>
       </c>
       <c r="C171" t="n">
-        <v>132.4628740535408</v>
+        <v>133.6300920185431</v>
       </c>
       <c r="D171" t="n">
-        <v>130.5474615066649</v>
+        <v>130.4776352080381</v>
       </c>
       <c r="E171" t="n">
-        <v>132.1436462402344</v>
+        <v>131.1360626220703</v>
       </c>
       <c r="F171" t="n">
-        <v>14200400</v>
+        <v>25323000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>133.370718441355</v>
+        <v>131.2058999637278</v>
       </c>
       <c r="C172" t="n">
-        <v>133.6300920185431</v>
+        <v>133.1512398071679</v>
       </c>
       <c r="D172" t="n">
-        <v>130.4776352080381</v>
+        <v>130.8168319950398</v>
       </c>
       <c r="E172" t="n">
-        <v>131.1360626220703</v>
+        <v>133.0215454101562</v>
       </c>
       <c r="F172" t="n">
-        <v>25323000</v>
+        <v>17183200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>131.2058999637278</v>
+        <v>132.6225008315265</v>
       </c>
       <c r="C173" t="n">
-        <v>133.1512398071679</v>
+        <v>134.8372000065807</v>
       </c>
       <c r="D173" t="n">
-        <v>130.8168319950398</v>
+        <v>131.7445976710087</v>
       </c>
       <c r="E173" t="n">
-        <v>133.0215454101562</v>
+        <v>133.8794860839844</v>
       </c>
       <c r="F173" t="n">
-        <v>17183200</v>
+        <v>16957100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>132.6225008315265</v>
+        <v>132.5925684137131</v>
       </c>
       <c r="C174" t="n">
-        <v>134.8372000065807</v>
+        <v>133.3307912944098</v>
       </c>
       <c r="D174" t="n">
-        <v>131.7445976710087</v>
+        <v>130.0187285230658</v>
       </c>
       <c r="E174" t="n">
-        <v>133.8794860839844</v>
+        <v>130.5374908447266</v>
       </c>
       <c r="F174" t="n">
-        <v>16957100</v>
+        <v>28471600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>132.5925684137131</v>
+        <v>124.112876676945</v>
       </c>
       <c r="C175" t="n">
-        <v>133.3307912944098</v>
+        <v>125.49955634699</v>
       </c>
       <c r="D175" t="n">
-        <v>130.0187285230658</v>
+        <v>120.1024733345915</v>
       </c>
       <c r="E175" t="n">
-        <v>130.5374908447266</v>
+        <v>121.0502014160156</v>
       </c>
       <c r="F175" t="n">
-        <v>28471600</v>
+        <v>53006600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>124.112876676945</v>
+        <v>121.0502017985552</v>
       </c>
       <c r="C176" t="n">
-        <v>125.49955634699</v>
+        <v>121.6587455533669</v>
       </c>
       <c r="D176" t="n">
-        <v>120.1024733345915</v>
+        <v>118.6260126387565</v>
       </c>
       <c r="E176" t="n">
-        <v>121.0502014160156</v>
+        <v>119.9827575683594</v>
       </c>
       <c r="F176" t="n">
-        <v>53006600</v>
+        <v>30330600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>121.0502017985552</v>
+        <v>120.401759010853</v>
       </c>
       <c r="C177" t="n">
-        <v>121.6587455533669</v>
+        <v>120.7608998332451</v>
       </c>
       <c r="D177" t="n">
-        <v>118.6260126387565</v>
+        <v>117.638370328068</v>
       </c>
       <c r="E177" t="n">
-        <v>119.9827575683594</v>
+        <v>118.2868194580078</v>
       </c>
       <c r="F177" t="n">
-        <v>30330600</v>
+        <v>28796600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>120.401759010853</v>
+        <v>118.0473918040102</v>
       </c>
       <c r="C178" t="n">
-        <v>120.7608998332451</v>
+        <v>119.1447631286873</v>
       </c>
       <c r="D178" t="n">
-        <v>117.638370328068</v>
+        <v>117.7580835037564</v>
       </c>
       <c r="E178" t="n">
-        <v>118.2868194580078</v>
+        <v>118.2568893432617</v>
       </c>
       <c r="F178" t="n">
-        <v>28796600</v>
+        <v>22062200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>118.0473918040102</v>
+        <v>118.6758897292679</v>
       </c>
       <c r="C179" t="n">
-        <v>119.1447631286873</v>
+        <v>118.8853872778886</v>
       </c>
       <c r="D179" t="n">
-        <v>117.7580835037564</v>
+        <v>117.0497853597791</v>
       </c>
       <c r="E179" t="n">
-        <v>118.2568893432617</v>
+        <v>118.6160354614258</v>
       </c>
       <c r="F179" t="n">
-        <v>22062200</v>
+        <v>21613100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>118.6758897292679</v>
+        <v>117.8279207851919</v>
       </c>
       <c r="C180" t="n">
-        <v>118.8853872778886</v>
+        <v>118.7956053707809</v>
       </c>
       <c r="D180" t="n">
-        <v>117.0497853597791</v>
+        <v>114.4360394170558</v>
       </c>
       <c r="E180" t="n">
-        <v>118.6160354614258</v>
+        <v>115.4735565185547</v>
       </c>
       <c r="F180" t="n">
-        <v>21613100</v>
+        <v>42191000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>117.8279207851919</v>
+        <v>114.4559959694409</v>
       </c>
       <c r="C181" t="n">
-        <v>118.7956053707809</v>
+        <v>115.7030106192767</v>
       </c>
       <c r="D181" t="n">
-        <v>114.4360394170558</v>
+        <v>113.2887844727029</v>
       </c>
       <c r="E181" t="n">
-        <v>115.4735565185547</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F181" t="n">
-        <v>42191000</v>
+        <v>26176200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>114.4559959694409</v>
+        <v>113.598048691841</v>
       </c>
       <c r="C182" t="n">
-        <v>115.7030106192767</v>
+        <v>114.2963738476551</v>
       </c>
       <c r="D182" t="n">
-        <v>113.2887844727029</v>
+        <v>112.4607719459876</v>
       </c>
       <c r="E182" t="n">
-        <v>114.326301574707</v>
+        <v>112.7899780273438</v>
       </c>
       <c r="F182" t="n">
-        <v>26176200</v>
+        <v>27366400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>113.598048691841</v>
+        <v>112.829882918774</v>
       </c>
       <c r="C183" t="n">
-        <v>114.2963738476551</v>
+        <v>117.0098784207316</v>
       </c>
       <c r="D183" t="n">
-        <v>112.4607719459876</v>
+        <v>112.6902178882183</v>
       </c>
       <c r="E183" t="n">
-        <v>112.7899780273438</v>
+        <v>116.6108322143555</v>
       </c>
       <c r="F183" t="n">
-        <v>27366400</v>
+        <v>32880600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>112.829882918774</v>
+        <v>119.613646228699</v>
       </c>
       <c r="C184" t="n">
-        <v>117.0098784207316</v>
+        <v>119.6535516106658</v>
       </c>
       <c r="D184" t="n">
-        <v>112.6902178882183</v>
+        <v>117.009879041958</v>
       </c>
       <c r="E184" t="n">
-        <v>116.6108322143555</v>
+        <v>117.4588012695312</v>
       </c>
       <c r="F184" t="n">
-        <v>32880600</v>
+        <v>22870400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>119.613646228699</v>
+        <v>118.0673439785114</v>
       </c>
       <c r="C185" t="n">
-        <v>119.6535516106658</v>
+        <v>120.601278627145</v>
       </c>
       <c r="D185" t="n">
-        <v>117.009879041958</v>
+        <v>117.8179410518094</v>
       </c>
       <c r="E185" t="n">
-        <v>117.4588012695312</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F185" t="n">
-        <v>22870400</v>
+        <v>36638100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>118.0673439785114</v>
+        <v>117.9675872503352</v>
       </c>
       <c r="C186" t="n">
-        <v>120.601278627145</v>
+        <v>119.8929781965846</v>
       </c>
       <c r="D186" t="n">
-        <v>117.8179410518094</v>
+        <v>117.8678275994195</v>
       </c>
       <c r="E186" t="n">
-        <v>118.596076965332</v>
+        <v>119.543815612793</v>
       </c>
       <c r="F186" t="n">
-        <v>36638100</v>
+        <v>19514100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>117.9675872503352</v>
+        <v>120.0924945255443</v>
       </c>
       <c r="C187" t="n">
-        <v>119.8929781965846</v>
+        <v>120.2122106703836</v>
       </c>
       <c r="D187" t="n">
-        <v>117.8678275994195</v>
+        <v>117.7181814033632</v>
       </c>
       <c r="E187" t="n">
-        <v>119.543815612793</v>
+        <v>118.596076965332</v>
       </c>
       <c r="F187" t="n">
-        <v>19514100</v>
+        <v>23959000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>120.0924945255443</v>
+        <v>119.4240987453198</v>
       </c>
       <c r="C188" t="n">
-        <v>120.2122106703836</v>
+        <v>120.53144836951</v>
       </c>
       <c r="D188" t="n">
-        <v>117.7181814033632</v>
+        <v>117.2493048793001</v>
       </c>
       <c r="E188" t="n">
-        <v>118.596076965332</v>
+        <v>120.3019943237305</v>
       </c>
       <c r="F188" t="n">
-        <v>23959000</v>
+        <v>22414900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>119.4240987453198</v>
+        <v>120.2820441244615</v>
       </c>
       <c r="C189" t="n">
-        <v>120.53144836951</v>
+        <v>121.5689641496319</v>
       </c>
       <c r="D189" t="n">
-        <v>117.2493048793001</v>
+        <v>119.1746945123655</v>
       </c>
       <c r="E189" t="n">
-        <v>120.3019943237305</v>
+        <v>120.2122116088867</v>
       </c>
       <c r="F189" t="n">
-        <v>22414900</v>
+        <v>22438000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>120.2820441244615</v>
+        <v>120.3019933173184</v>
       </c>
       <c r="C190" t="n">
-        <v>121.5689641496319</v>
+        <v>121.3195615310648</v>
       </c>
       <c r="D190" t="n">
-        <v>119.1746945123655</v>
+        <v>119.2445273327187</v>
       </c>
       <c r="E190" t="n">
-        <v>120.2122116088867</v>
+        <v>120.7509231567383</v>
       </c>
       <c r="F190" t="n">
-        <v>22438000</v>
+        <v>14753500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>120.3019933173184</v>
+        <v>119.4540258740917</v>
       </c>
       <c r="C191" t="n">
-        <v>121.3195615310648</v>
+        <v>121.1998463936268</v>
       </c>
       <c r="D191" t="n">
-        <v>119.2445273327187</v>
+        <v>118.2968002303814</v>
       </c>
       <c r="E191" t="n">
-        <v>120.7509231567383</v>
+        <v>120.5314483642578</v>
       </c>
       <c r="F191" t="n">
-        <v>14753500</v>
+        <v>20722500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>119.4540258740917</v>
+        <v>120.8506818055627</v>
       </c>
       <c r="C192" t="n">
-        <v>121.1998463936268</v>
+        <v>122.646385926027</v>
       </c>
       <c r="D192" t="n">
-        <v>118.2968002303814</v>
+        <v>119.5936889212378</v>
       </c>
       <c r="E192" t="n">
-        <v>120.5314483642578</v>
+        <v>120.7409439086914</v>
       </c>
       <c r="F192" t="n">
-        <v>20722500</v>
+        <v>23060700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>120.8506818055627</v>
+        <v>119.2944114353401</v>
       </c>
       <c r="C193" t="n">
-        <v>122.646385926027</v>
+        <v>120.7209965009543</v>
       </c>
       <c r="D193" t="n">
-        <v>119.5936889212378</v>
+        <v>117.1694935982547</v>
       </c>
       <c r="E193" t="n">
-        <v>120.7409439086914</v>
+        <v>117.8478698730469</v>
       </c>
       <c r="F193" t="n">
-        <v>23060700</v>
+        <v>21711100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>119.2944114353401</v>
+        <v>117.9176994360996</v>
       </c>
       <c r="C194" t="n">
-        <v>120.7209965009543</v>
+        <v>118.1970371043968</v>
       </c>
       <c r="D194" t="n">
-        <v>117.1694935982547</v>
+        <v>116.5210491504798</v>
       </c>
       <c r="E194" t="n">
-        <v>117.8478698730469</v>
+        <v>116.9001388549805</v>
       </c>
       <c r="F194" t="n">
-        <v>21711100</v>
+        <v>36526800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>117.9176994360996</v>
+        <v>116.6806630640479</v>
       </c>
       <c r="C195" t="n">
-        <v>118.1970371043968</v>
+        <v>118.1172263420262</v>
       </c>
       <c r="D195" t="n">
-        <v>116.5210491504798</v>
+        <v>116.6706848159582</v>
       </c>
       <c r="E195" t="n">
         <v>116.9001388549805</v>
       </c>
       <c r="F195" t="n">
-        <v>36526800</v>
+        <v>17053900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>116.6806630640479</v>
+        <v>119.4240968222584</v>
       </c>
       <c r="C196" t="n">
-        <v>118.1172263420262</v>
+        <v>119.9628080586903</v>
       </c>
       <c r="D196" t="n">
-        <v>116.6706848159582</v>
+        <v>116.0621426214644</v>
       </c>
       <c r="E196" t="n">
-        <v>116.9001388549805</v>
+        <v>119.1347885131836</v>
       </c>
       <c r="F196" t="n">
-        <v>17053900</v>
+        <v>23411400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>119.4240968222584</v>
+        <v>119.2744498995579</v>
       </c>
       <c r="C197" t="n">
-        <v>119.9628080586903</v>
+        <v>120.112447667685</v>
       </c>
       <c r="D197" t="n">
-        <v>116.0621426214644</v>
+        <v>118.6459572818424</v>
       </c>
       <c r="E197" t="n">
-        <v>119.1347885131836</v>
+        <v>118.7157897949219</v>
       </c>
       <c r="F197" t="n">
-        <v>23411400</v>
+        <v>20600100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>119.2744498995579</v>
+        <v>117.1894451773868</v>
       </c>
       <c r="C198" t="n">
-        <v>120.112447667685</v>
+        <v>118.2967947502302</v>
       </c>
       <c r="D198" t="n">
-        <v>118.6459572818424</v>
+        <v>115.1044328099781</v>
       </c>
       <c r="E198" t="n">
-        <v>118.7157897949219</v>
+        <v>115.5034790039062</v>
       </c>
       <c r="F198" t="n">
-        <v>20600100</v>
+        <v>20384700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>117.1894451773868</v>
+        <v>117.0098811702962</v>
       </c>
       <c r="C199" t="n">
-        <v>118.2967947502302</v>
+        <v>117.5984684398727</v>
       </c>
       <c r="D199" t="n">
-        <v>115.1044328099781</v>
+        <v>114.8151307892405</v>
       </c>
       <c r="E199" t="n">
-        <v>115.5034790039062</v>
+        <v>115.413703918457</v>
       </c>
       <c r="F199" t="n">
-        <v>20384700</v>
+        <v>36636000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>117.0098811702962</v>
+        <v>116.1918382308837</v>
       </c>
       <c r="C200" t="n">
-        <v>117.5984684398727</v>
+        <v>116.521051925122</v>
       </c>
       <c r="D200" t="n">
-        <v>114.8151307892405</v>
+        <v>113.9272553645249</v>
       </c>
       <c r="E200" t="n">
-        <v>115.413703918457</v>
+        <v>114.326301574707</v>
       </c>
       <c r="F200" t="n">
-        <v>36636000</v>
+        <v>20367000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>116.1918382308837</v>
+        <v>113.6978053385094</v>
       </c>
       <c r="C201" t="n">
-        <v>116.521051925122</v>
+        <v>114.3362762101566</v>
       </c>
       <c r="D201" t="n">
-        <v>113.9272553645249</v>
+        <v>112.6602882692895</v>
       </c>
       <c r="E201" t="n">
-        <v>114.326301574707</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F201" t="n">
-        <v>20367000</v>
+        <v>23034000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>113.6978053385094</v>
+        <v>109.8669732552887</v>
       </c>
       <c r="C202" t="n">
-        <v>114.3362762101566</v>
+        <v>110.4455898652017</v>
       </c>
       <c r="D202" t="n">
-        <v>112.6602882692895</v>
+        <v>106.9938543130583</v>
       </c>
       <c r="E202" t="n">
-        <v>112.989501953125</v>
+        <v>108.5601043701172</v>
       </c>
       <c r="F202" t="n">
-        <v>23034000</v>
+        <v>40391400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>109.8669732552887</v>
+        <v>109.0688912954154</v>
       </c>
       <c r="C203" t="n">
-        <v>110.4455898652017</v>
+        <v>112.1814349941213</v>
       </c>
       <c r="D203" t="n">
-        <v>106.9938543130583</v>
+        <v>108.8992991295087</v>
       </c>
       <c r="E203" t="n">
-        <v>108.5601043701172</v>
+        <v>111.5728912353516</v>
       </c>
       <c r="F203" t="n">
-        <v>40391400</v>
+        <v>29512200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>109.0688912954154</v>
+        <v>111.1339433224697</v>
       </c>
       <c r="C204" t="n">
-        <v>112.1814349941213</v>
+        <v>112.1016278755018</v>
       </c>
       <c r="D204" t="n">
-        <v>108.8992991295087</v>
+        <v>109.1087928180449</v>
       </c>
       <c r="E204" t="n">
-        <v>111.5728912353516</v>
+        <v>110.3857345581055</v>
       </c>
       <c r="F204" t="n">
-        <v>29512200</v>
+        <v>29523300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>111.1339433224697</v>
+        <v>112.7001980505562</v>
       </c>
       <c r="C205" t="n">
-        <v>112.1016278755018</v>
+        <v>113.228931048236</v>
       </c>
       <c r="D205" t="n">
-        <v>109.1087928180449</v>
+        <v>111.0341882926515</v>
       </c>
       <c r="E205" t="n">
-        <v>110.3857345581055</v>
+        <v>111.2736129760742</v>
       </c>
       <c r="F205" t="n">
-        <v>29523300</v>
+        <v>19941400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>112.7001980505562</v>
+        <v>112.879763389333</v>
       </c>
       <c r="C206" t="n">
-        <v>113.228931048236</v>
+        <v>113.5880667705184</v>
       </c>
       <c r="D206" t="n">
-        <v>111.0341882926515</v>
+        <v>111.5429597770651</v>
       </c>
       <c r="E206" t="n">
-        <v>111.2736129760742</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F206" t="n">
-        <v>19941400</v>
+        <v>19892000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>112.879763389333</v>
+        <v>110.9743243964893</v>
       </c>
       <c r="C207" t="n">
-        <v>113.5880667705184</v>
+        <v>112.4906984566786</v>
       </c>
       <c r="D207" t="n">
-        <v>111.5429597770651</v>
+        <v>110.7748050991254</v>
       </c>
       <c r="E207" t="n">
-        <v>112.8298797607422</v>
+        <v>111.942008972168</v>
       </c>
       <c r="F207" t="n">
-        <v>19892000</v>
+        <v>20464500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>110.9743243964893</v>
+        <v>111.6826280597077</v>
       </c>
       <c r="C208" t="n">
-        <v>112.4906984566786</v>
+        <v>113.8873566399898</v>
       </c>
       <c r="D208" t="n">
-        <v>110.7748050991254</v>
+        <v>111.6626791743936</v>
       </c>
       <c r="E208" t="n">
-        <v>111.942008972168</v>
+        <v>113.6279754638672</v>
       </c>
       <c r="F208" t="n">
-        <v>20464500</v>
+        <v>12461700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>111.6826280597077</v>
+        <v>114.4559909872762</v>
       </c>
       <c r="C209" t="n">
-        <v>113.8873566399898</v>
+        <v>115.26405400962</v>
       </c>
       <c r="D209" t="n">
-        <v>111.6626791743936</v>
+        <v>113.7377093624492</v>
       </c>
       <c r="E209" t="n">
-        <v>113.6279754638672</v>
+        <v>114.5058670043945</v>
       </c>
       <c r="F209" t="n">
-        <v>12461700</v>
+        <v>17043400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>114.4559909872762</v>
+        <v>114.8051528853423</v>
       </c>
       <c r="C210" t="n">
-        <v>115.26405400962</v>
+        <v>115.6032376551602</v>
       </c>
       <c r="D210" t="n">
-        <v>113.7377093624492</v>
+        <v>113.2289246190302</v>
       </c>
       <c r="E210" t="n">
-        <v>114.5058670043945</v>
+        <v>113.4284439086914</v>
       </c>
       <c r="F210" t="n">
-        <v>17043400</v>
+        <v>14682000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>114.8051528853423</v>
+        <v>112.9795273843265</v>
       </c>
       <c r="C211" t="n">
-        <v>115.6032376551602</v>
+        <v>114.4559960800755</v>
       </c>
       <c r="D211" t="n">
-        <v>113.2289246190302</v>
+        <v>111.8023452492967</v>
       </c>
       <c r="E211" t="n">
-        <v>113.4284439086914</v>
+        <v>112.2612457275391</v>
       </c>
       <c r="F211" t="n">
-        <v>14682000</v>
+        <v>16467900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>112.9795273843265</v>
+        <v>113.4883080789502</v>
       </c>
       <c r="C212" t="n">
-        <v>114.4559960800755</v>
+        <v>115.3139316886614</v>
       </c>
       <c r="D212" t="n">
-        <v>111.8023452492967</v>
+        <v>113.288781174082</v>
       </c>
       <c r="E212" t="n">
-        <v>112.2612457275391</v>
+        <v>114.6754608154297</v>
       </c>
       <c r="F212" t="n">
-        <v>16467900</v>
+        <v>20777600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>113.4883080789502</v>
+        <v>116.6806604264181</v>
       </c>
       <c r="C213" t="n">
-        <v>115.3139316886614</v>
+        <v>117.8079588775203</v>
       </c>
       <c r="D213" t="n">
-        <v>113.288781174082</v>
+        <v>113.3286845943574</v>
       </c>
       <c r="E213" t="n">
-        <v>114.6754608154297</v>
+        <v>113.967155456543</v>
       </c>
       <c r="F213" t="n">
-        <v>20777600</v>
+        <v>28289800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>116.6806604264181</v>
+        <v>113.6878284476981</v>
       </c>
       <c r="C214" t="n">
-        <v>117.8079588775203</v>
+        <v>114.1267800313856</v>
       </c>
       <c r="D214" t="n">
-        <v>113.3286845943574</v>
+        <v>111.8721754576813</v>
       </c>
       <c r="E214" t="n">
-        <v>113.967155456543</v>
+        <v>111.9320297241211</v>
       </c>
       <c r="F214" t="n">
-        <v>28289800</v>
+        <v>17738900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>113.6878284476981</v>
+        <v>111.2436859074791</v>
       </c>
       <c r="C215" t="n">
-        <v>114.1267800313856</v>
+        <v>111.5329942219063</v>
       </c>
       <c r="D215" t="n">
-        <v>111.8721754576813</v>
+        <v>109.6275521682845</v>
       </c>
       <c r="E215" t="n">
-        <v>111.9320297241211</v>
+        <v>110.1263580322266</v>
       </c>
       <c r="F215" t="n">
-        <v>17738900</v>
+        <v>22717000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>111.2436859074791</v>
+        <v>109.268405092928</v>
       </c>
       <c r="C216" t="n">
-        <v>111.5329942219063</v>
+        <v>109.737283796026</v>
       </c>
       <c r="D216" t="n">
-        <v>109.6275521682845</v>
+        <v>108.4603420750963</v>
       </c>
       <c r="E216" t="n">
-        <v>110.1263580322266</v>
+        <v>109.0688858032227</v>
       </c>
       <c r="F216" t="n">
-        <v>22717000</v>
+        <v>23494800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>109.268405092928</v>
+        <v>107.25323944858</v>
       </c>
       <c r="C217" t="n">
-        <v>109.737283796026</v>
+        <v>108.3007272005749</v>
       </c>
       <c r="D217" t="n">
-        <v>108.4603420750963</v>
+        <v>106.5349577836844</v>
       </c>
       <c r="E217" t="n">
-        <v>109.0688858032227</v>
+        <v>108.14111328125</v>
       </c>
       <c r="F217" t="n">
-        <v>23494800</v>
+        <v>21516800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>107.25323944858</v>
+        <v>107.8617828177618</v>
       </c>
       <c r="C218" t="n">
-        <v>108.3007272005749</v>
+        <v>109.3382439135796</v>
       </c>
       <c r="D218" t="n">
-        <v>106.5349577836844</v>
+        <v>107.7520449187408</v>
       </c>
       <c r="E218" t="n">
-        <v>108.14111328125</v>
+        <v>109.2085571289062</v>
       </c>
       <c r="F218" t="n">
-        <v>21516800</v>
+        <v>18405900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>107.8617828177618</v>
+        <v>109.6574762821653</v>
       </c>
       <c r="C219" t="n">
-        <v>109.3382439135796</v>
+        <v>112.2412945440321</v>
       </c>
       <c r="D219" t="n">
-        <v>107.7520449187408</v>
+        <v>109.6275491489408</v>
       </c>
       <c r="E219" t="n">
-        <v>109.2085571289062</v>
+        <v>111.4731292724609</v>
       </c>
       <c r="F219" t="n">
-        <v>18405900</v>
+        <v>19008700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>109.6574762821653</v>
+        <v>113.6878264165269</v>
       </c>
       <c r="C220" t="n">
-        <v>112.2412945440321</v>
+        <v>115.7528822947127</v>
       </c>
       <c r="D220" t="n">
-        <v>109.6275491489408</v>
+        <v>112.5704985921816</v>
       </c>
       <c r="E220" t="n">
-        <v>111.4731292724609</v>
+        <v>112.8298797607422</v>
       </c>
       <c r="F220" t="n">
-        <v>19008700</v>
+        <v>24867900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>113.6878264165269</v>
+        <v>112.9595787445935</v>
       </c>
       <c r="C221" t="n">
-        <v>115.7528822947127</v>
+        <v>114.4160909468376</v>
       </c>
       <c r="D221" t="n">
-        <v>112.5704985921816</v>
+        <v>112.1814352072651</v>
       </c>
       <c r="E221" t="n">
-        <v>112.8298797607422</v>
+        <v>113.9472122192383</v>
       </c>
       <c r="F221" t="n">
-        <v>24867900</v>
+        <v>23480000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>112.9595787445935</v>
+        <v>111.3434398479761</v>
       </c>
       <c r="C222" t="n">
-        <v>114.4160909468376</v>
+        <v>112.7600466022415</v>
       </c>
       <c r="D222" t="n">
-        <v>112.1814352072651</v>
+        <v>110.1762360128914</v>
       </c>
       <c r="E222" t="n">
-        <v>113.9472122192383</v>
+        <v>110.8346557617188</v>
       </c>
       <c r="F222" t="n">
-        <v>23480000</v>
+        <v>28747000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>111.3434398479761</v>
+        <v>110.2560414658192</v>
       </c>
       <c r="C223" t="n">
-        <v>112.7600466022415</v>
+        <v>111.642728727712</v>
       </c>
       <c r="D223" t="n">
-        <v>110.1762360128914</v>
+        <v>109.6275488363764</v>
       </c>
       <c r="E223" t="n">
-        <v>110.8346557617188</v>
+        <v>110.9344177246094</v>
       </c>
       <c r="F223" t="n">
-        <v>28747000</v>
+        <v>22799100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>110.2560414658192</v>
+        <v>112.8298784424625</v>
       </c>
       <c r="C224" t="n">
-        <v>111.642728727712</v>
+        <v>113.0194270954852</v>
       </c>
       <c r="D224" t="n">
-        <v>109.6275488363764</v>
+        <v>109.8969053059805</v>
       </c>
       <c r="E224" t="n">
-        <v>110.9344177246094</v>
+        <v>110.4455871582031</v>
       </c>
       <c r="F224" t="n">
-        <v>22799100</v>
+        <v>23942500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>112.8298784424625</v>
+        <v>108.7496500450106</v>
       </c>
       <c r="C225" t="n">
-        <v>113.0194270954852</v>
+        <v>111.4132713715266</v>
       </c>
       <c r="D225" t="n">
-        <v>109.8969053059805</v>
+        <v>108.3007202277679</v>
       </c>
       <c r="E225" t="n">
-        <v>110.4455871582031</v>
+        <v>111.2835845947266</v>
       </c>
       <c r="F225" t="n">
-        <v>23942500</v>
+        <v>29620000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>108.7496500450106</v>
+        <v>112.181431315027</v>
       </c>
       <c r="C226" t="n">
-        <v>111.4132713715266</v>
+        <v>112.8897423116165</v>
       </c>
       <c r="D226" t="n">
-        <v>108.3007202277679</v>
+        <v>111.0940382280446</v>
       </c>
       <c r="E226" t="n">
-        <v>111.2835845947266</v>
+        <v>112.0716934204102</v>
       </c>
       <c r="F226" t="n">
-        <v>29620000</v>
+        <v>21446300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>112.181431315027</v>
+        <v>113.7975687180191</v>
       </c>
       <c r="C227" t="n">
-        <v>112.8897423116165</v>
+        <v>114.2863963302149</v>
       </c>
       <c r="D227" t="n">
-        <v>111.0940382280446</v>
+        <v>110.7748064209645</v>
       </c>
       <c r="E227" t="n">
-        <v>112.0716934204102</v>
+        <v>111.8023452758789</v>
       </c>
       <c r="F227" t="n">
-        <v>21446300</v>
+        <v>23203100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>113.7975687180191</v>
+        <v>110.3458340692701</v>
       </c>
       <c r="C228" t="n">
-        <v>114.2863963302149</v>
+        <v>112.0218220801941</v>
       </c>
       <c r="D228" t="n">
-        <v>110.7748064209645</v>
+        <v>110.2360961700712</v>
       </c>
       <c r="E228" t="n">
-        <v>111.8023452758789</v>
+        <v>111.5828704833984</v>
       </c>
       <c r="F228" t="n">
-        <v>23203100</v>
+        <v>18819300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>110.3458340692701</v>
+        <v>110.8147094920761</v>
       </c>
       <c r="C229" t="n">
-        <v>112.0218220801941</v>
+        <v>112.4308355753539</v>
       </c>
       <c r="D229" t="n">
-        <v>110.2360961700712</v>
+        <v>110.4954740524384</v>
       </c>
       <c r="E229" t="n">
-        <v>111.5828704833984</v>
+        <v>112.3909378051758</v>
       </c>
       <c r="F229" t="n">
-        <v>18819300</v>
+        <v>19144000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>110.8147094920761</v>
+        <v>112.1714606731287</v>
       </c>
       <c r="C230" t="n">
-        <v>112.4308355753539</v>
+        <v>113.069305103701</v>
       </c>
       <c r="D230" t="n">
-        <v>110.4954740524384</v>
+        <v>111.9220577510424</v>
       </c>
       <c r="E230" t="n">
-        <v>112.3909378051758</v>
+        <v>112.989501953125</v>
       </c>
       <c r="F230" t="n">
-        <v>19144000</v>
+        <v>17005800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>112.1714606731287</v>
+        <v>112.1016271407472</v>
       </c>
       <c r="C231" t="n">
-        <v>113.069305103701</v>
+        <v>115.7728384249456</v>
       </c>
       <c r="D231" t="n">
-        <v>111.9220577510424</v>
+        <v>112.011838131802</v>
       </c>
       <c r="E231" t="n">
-        <v>112.989501953125</v>
+        <v>115.7329330444336</v>
       </c>
       <c r="F231" t="n">
-        <v>17005800</v>
+        <v>22054700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>112.1016271407472</v>
+        <v>115.8925486214695</v>
       </c>
       <c r="C232" t="n">
-        <v>115.7728384249456</v>
+        <v>116.0421918977476</v>
       </c>
       <c r="D232" t="n">
-        <v>112.011838131802</v>
+        <v>114.5357961092488</v>
       </c>
       <c r="E232" t="n">
-        <v>115.7329330444336</v>
+        <v>115.4436264038086</v>
       </c>
       <c r="F232" t="n">
-        <v>22054700</v>
+        <v>16822200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>115.8925486214695</v>
+        <v>115.3837731369623</v>
       </c>
       <c r="C233" t="n">
-        <v>116.0421918977476</v>
+        <v>116.1718796839166</v>
       </c>
       <c r="D233" t="n">
-        <v>114.5357961092488</v>
+        <v>114.3662049383982</v>
       </c>
       <c r="E233" t="n">
-        <v>115.4436264038086</v>
+        <v>114.9946975708008</v>
       </c>
       <c r="F233" t="n">
-        <v>16822200</v>
+        <v>14520000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>115.3837731369623</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="C234" t="n">
-        <v>116.1718796839166</v>
+        <v>114.9049142110052</v>
       </c>
       <c r="D234" t="n">
-        <v>114.3662049383982</v>
+        <v>113.6479213564676</v>
       </c>
       <c r="E234" t="n">
-        <v>114.9946975708008</v>
+        <v>114.0569458007812</v>
       </c>
       <c r="F234" t="n">
-        <v>14520000</v>
+        <v>18131100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>114.0569458007812</v>
+        <v>116.0222446904477</v>
       </c>
       <c r="C235" t="n">
-        <v>114.9049142110052</v>
+        <v>116.0322153274834</v>
       </c>
       <c r="D235" t="n">
-        <v>113.6479213564676</v>
+        <v>114.2065916862473</v>
       </c>
       <c r="E235" t="n">
-        <v>114.0569458007812</v>
+        <v>114.9248657226562</v>
       </c>
       <c r="F235" t="n">
-        <v>18131100</v>
+        <v>20675000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>116.0222446904477</v>
+        <v>114.9148971425914</v>
       </c>
       <c r="C236" t="n">
-        <v>116.0322153274834</v>
+        <v>116.590885146559</v>
       </c>
       <c r="D236" t="n">
-        <v>114.2065916862473</v>
+        <v>113.7177585048011</v>
       </c>
       <c r="E236" t="n">
-        <v>114.9248657226562</v>
+        <v>114.0270233154297</v>
       </c>
       <c r="F236" t="n">
-        <v>20675000</v>
+        <v>34286600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>114.9148971425914</v>
+        <v>106.1259298697332</v>
       </c>
       <c r="C237" t="n">
-        <v>116.590885146559</v>
+        <v>106.7444518635443</v>
       </c>
       <c r="D237" t="n">
-        <v>113.7177585048011</v>
+        <v>102.6043617877236</v>
       </c>
       <c r="E237" t="n">
-        <v>114.0270233154297</v>
+        <v>103.5919952392578</v>
       </c>
       <c r="F237" t="n">
-        <v>34286600</v>
+        <v>83633100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>106.1259298697332</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C238" t="n">
-        <v>106.7444518635443</v>
+        <v>104.2799987792969</v>
       </c>
       <c r="D238" t="n">
-        <v>102.6043617877236</v>
+        <v>102.1500015258789</v>
       </c>
       <c r="E238" t="n">
-        <v>103.5919952392578</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="F238" t="n">
-        <v>83633100</v>
+        <v>44454200</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>103.6900024414062</v>
+        <v>104.1399993896484</v>
       </c>
       <c r="C239" t="n">
-        <v>104.2799987792969</v>
+        <v>106.5999984741211</v>
       </c>
       <c r="D239" t="n">
-        <v>102.1500015258789</v>
+        <v>104</v>
       </c>
       <c r="E239" t="n">
-        <v>103.6999969482422</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="F239" t="n">
-        <v>44454200</v>
+        <v>35616300</v>
       </c>
       <c r="G239" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>104.1399993896484</v>
+        <v>105.5800018310547</v>
       </c>
       <c r="C240" t="n">
-        <v>106.5999984741211</v>
+        <v>106.0699996948242</v>
       </c>
       <c r="D240" t="n">
-        <v>104</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="E240" t="n">
-        <v>106.4899978637695</v>
+        <v>105.379997253418</v>
       </c>
       <c r="F240" t="n">
-        <v>35616300</v>
+        <v>27032500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>105.5800018310547</v>
+        <v>105.5100021362305</v>
       </c>
       <c r="C241" t="n">
-        <v>106.0699996948242</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="D241" t="n">
-        <v>104.4000015258789</v>
+        <v>104.0800018310547</v>
       </c>
       <c r="E241" t="n">
-        <v>105.379997253418</v>
+        <v>104.3399963378906</v>
       </c>
       <c r="F241" t="n">
-        <v>27032500</v>
+        <v>28409400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>105.5100021362305</v>
+        <v>103.6100006103516</v>
       </c>
       <c r="C242" t="n">
-        <v>106.0899963378906</v>
+        <v>103.75</v>
       </c>
       <c r="D242" t="n">
-        <v>104.0800018310547</v>
+        <v>102.2699966430664</v>
       </c>
       <c r="E242" t="n">
-        <v>104.3399963378906</v>
+        <v>102.629997253418</v>
       </c>
       <c r="F242" t="n">
-        <v>28409400</v>
+        <v>29816600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>103.6100006103516</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="C243" t="n">
-        <v>103.75</v>
+        <v>103.4000015258789</v>
       </c>
       <c r="D243" t="n">
-        <v>102.2699966430664</v>
+        <v>102.5</v>
       </c>
       <c r="E243" t="n">
-        <v>102.629997253418</v>
+        <v>103.0899963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>29816600</v>
+        <v>19420800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>103.0899963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="C244" t="n">
-        <v>103.4000015258789</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="D244" t="n">
-        <v>102.5</v>
+        <v>102.8399963378906</v>
       </c>
       <c r="E244" t="n">
-        <v>103.0899963378906</v>
+        <v>104.870002746582</v>
       </c>
       <c r="F244" t="n">
-        <v>19420800</v>
+        <v>34188700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>103.0800018310547</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="C245" t="n">
-        <v>104.9899978637695</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D245" t="n">
-        <v>102.8399963378906</v>
+        <v>104.6600036621094</v>
       </c>
       <c r="E245" t="n">
-        <v>104.870002746582</v>
+        <v>105.9199981689453</v>
       </c>
       <c r="F245" t="n">
-        <v>34188700</v>
+        <v>22074600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>105.1100006103516</v>
+        <v>105.9700012207031</v>
       </c>
       <c r="C246" t="n">
-        <v>106.6399993896484</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="D246" t="n">
-        <v>104.6600036621094</v>
+        <v>105.4599990844727</v>
       </c>
       <c r="E246" t="n">
-        <v>105.9199981689453</v>
+        <v>106.0899963378906</v>
       </c>
       <c r="F246" t="n">
-        <v>22074600</v>
+        <v>25181800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>105.9700012207031</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="C247" t="n">
-        <v>106.7799987792969</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="D247" t="n">
-        <v>105.4599990844727</v>
+        <v>106.0199966430664</v>
       </c>
       <c r="E247" t="n">
-        <v>106.0899963378906</v>
+        <v>108.4199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>25181800</v>
+        <v>25541200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>106.4199981689453</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="C248" t="n">
-        <v>109.3499984741211</v>
+        <v>109.2300033569336</v>
       </c>
       <c r="D248" t="n">
-        <v>106.0199966430664</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="E248" t="n">
-        <v>108.4199981689453</v>
+        <v>107.1399993896484</v>
       </c>
       <c r="F248" t="n">
-        <v>25541200</v>
+        <v>20540500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>108.1999969482422</v>
+        <v>106.7799987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>109.2300033569336</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="D249" t="n">
-        <v>106.9300003051758</v>
+        <v>105.6600036621094</v>
       </c>
       <c r="E249" t="n">
-        <v>107.1399993896484</v>
+        <v>106.0500030517578</v>
       </c>
       <c r="F249" t="n">
-        <v>20540500</v>
+        <v>22664800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>106.7799987792969</v>
+        <v>105.6900024414062</v>
       </c>
       <c r="C250" t="n">
-        <v>106.9000015258789</v>
+        <v>106.1500015258789</v>
       </c>
       <c r="D250" t="n">
-        <v>105.6600036621094</v>
+        <v>105.1600036621094</v>
       </c>
       <c r="E250" t="n">
-        <v>106.0500030517578</v>
+        <v>105.8300018310547</v>
       </c>
       <c r="F250" t="n">
-        <v>22664800</v>
+        <v>15460800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>105.6900024414062</v>
+        <v>106.1699981689453</v>
       </c>
       <c r="C251" t="n">
-        <v>106.1500015258789</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="D251" t="n">
-        <v>105.1600036621094</v>
+        <v>105.5899963378906</v>
       </c>
       <c r="E251" t="n">
-        <v>105.8300018310547</v>
+        <v>105.7300033569336</v>
       </c>
       <c r="F251" t="n">
-        <v>15460800</v>
+        <v>17174900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>106.1699981689453</v>
+        <v>106.1999969482422</v>
       </c>
       <c r="C252" t="n">
-        <v>107.1600036621094</v>
+        <v>107.2099990844727</v>
       </c>
       <c r="D252" t="n">
-        <v>105.5899963378906</v>
+        <v>105.7200012207031</v>
       </c>
       <c r="E252" t="n">
-        <v>105.7300033569336</v>
+        <v>107.1500015258789</v>
       </c>
       <c r="F252" t="n">
-        <v>17164500</v>
+        <v>17058300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10636,37 +10636,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D2" t="n">
         <v>105.73</v>
       </c>
-      <c r="D2" t="n">
-        <v>105.83</v>
-      </c>
       <c r="E2" t="n">
-        <v>106.17</v>
+        <v>106.49</v>
       </c>
       <c r="F2" t="n">
-        <v>107.155</v>
+        <v>107.21</v>
       </c>
       <c r="G2" t="n">
-        <v>105.59</v>
+        <v>105.715</v>
       </c>
       <c r="H2" t="n">
-        <v>16410703</v>
+        <v>17027931</v>
       </c>
       <c r="I2" t="n">
-        <v>24330998</v>
+        <v>24252751</v>
       </c>
       <c r="J2" t="n">
-        <v>841407725568</v>
+        <v>852708163584</v>
       </c>
       <c r="K2" t="n">
-        <v>38.307972</v>
+        <v>38.822464</v>
       </c>
       <c r="L2" t="n">
-        <v>32.728886</v>
+        <v>33.168446</v>
       </c>
       <c r="M2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
         <v>135.16</v>
@@ -10678,7 +10678,7 @@
         <v>0.595</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="R2" t="n">
         <v>0.03</v>
@@ -10702,7 +10702,7 @@
         <v>11.848</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.923870000000001</v>
+        <v>9.043721</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.091</v>
@@ -10714,7 +10714,7 @@
         <v>735839977472</v>
       </c>
       <c r="AC2" t="n">
-        <v>908958957568</v>
+        <v>920224923648</v>
       </c>
       <c r="AD2" t="n">
         <v>44073000960</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:14</t>
+          <t>2026-09-12 21:47:18</t>
         </is>
       </c>
     </row>
